--- a/Noticias_Calcario_20260803.xlsx
+++ b/Noticias_Calcario_20260803.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D505"/>
+  <dimension ref="A1:D504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,7 +578,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alta dos fertilizantes acende alerta para os custos da safra 2026/27 - agrolink.com.br</t>
+          <t>Alta dos fertilizantes acende alerta para os custos da safra 2026/27 - Agrolink</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Enxofre dispara para US$ 1.200 e pressiona custo dos fertilizantes no campo - CompreRural</t>
+          <t>Enxofre dispara para US$ 1.200 e pressiona custo dos fertilizantes no campo - comprerural.com</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Valuation de Mosaic Co (MOS): P/L, P/VP e Valor Justo - TradingKey</t>
+          <t>Avaliação de Riscos: Mosaic Co (MOS) — Volatilidade, Risco Financeiro e Risco de Investimento - TradingKey</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -742,447 +742,447 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9CZWxhMU84NjkzY3l1eWlUUUpxdkF5T1lfajk4bjNpWnZUZDNkMDYzVmZ4ZVlFOE9Dd21WNjc5cG9EOTdnSk5fTlA4dlJrbnB1dGs1WU5SUkMtVllBRldCMFgzTFdJU2dBbmlncFR6Vkk2a19B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE84T3J0UmZJcXFpMGNKaGVqd0NDZU9aZzB6X2ZHNzN2ejJial9Hb3VobGJJa1lJa1VaVnYzLWZ5dE4tdHZnM0x3dFAzaWFXRjdISHFQMUVQZXp5Z2RqcEg3c2JDUkc0Z1R4NmZSd0xRWVo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Queda da ureia melhora relação de troca e reduz custo dos fertilizantes para a safra 2026/27 - Portal do Agronegócio</t>
+          <t>Valuation de Mosaic Co (MOS): P/L, P/VP e Valor Justo - TradingKey</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>30/07/2026 19:40</t>
+          <t>31/07/2026 04:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNYUk4UHRPY3dvNlVVTUVTTWhwdnhhLTFnM2FuY3ZidUxVN29Lc05uM2FVcnJTcFF4SVJOVGZ0QW1mLVNoOXgwMGg0WlBYRzkwRXpkaVVDd1VEMDlwMGZLR3plTjY1LWF6ZkNPNnJ6MU1jT3h3S19vUXdyc2hYS1VQQ2I4VENnc0M1VlV0c1NTb0pyM3Z1RHZISjhTTDdxOTJoX25ZNXdtVnhlM0xlNl96YmRjTm5NSjdjQXJLWW1TMFJvbGlQSXdDZWg1MVFFZWh2QWlxYlNZMUo3UG1BemRGTHNtVlEtcmVuMmgzaUNtWnRRLXV6YTFSQUJyWnUyR0VLdEh2a1Q3QUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9CZWxhMU84NjkzY3l1eWlUUUpxdkF5T1lfajk4bjNpWnZUZDNkMDYzVmZ4ZVlFOE9Dd21WNjc5cG9EOTdnSk5fTlA4dlJrbnB1dGs1WU5SUkMtVllBRldCMFgzTFdJU2dBbmlncFR6Vkk2a19B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EuroChem pode paralisar e implementar layoff em Serra do Salitre devido à crise do enxofre - diariodocomercio.com.br</t>
+          <t>Queda da ureia melhora relação de troca e reduz custo dos fertilizantes para a safra 2026/27 - portaldoagronegocio.com.br</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>30/07/2026 18:46</t>
+          <t>30/07/2026 19:40</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1FUmpCMjBWeG01TDVyOEZqbWI3Tk83SjVvdjA4ajBzVWtZTTFTZjA2Qi1HU2RMOUtab3dWelVzbjE4dTUtS3NGSEZ6Rms0SDd3T1I0eUpXVmNGaFJHdlFkdW1SZHM2MDZQM2wtZ0xKcnI3a0lCZ01FNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNYUk4UHRPY3dvNlVVTUVTTWhwdnhhLTFnM2FuY3ZidUxVN29Lc05uM2FVcnJTcFF4SVJOVGZ0QW1mLVNoOXgwMGg0WlBYRzkwRXpkaVVDd1VEMDlwMGZLR3plTjY1LWF6ZkNPNnJ6MU1jT3h3S19vUXdyc2hYS1VQQ2I4VENnc0M1VlV0c1NTb0pyM3Z1RHZISjhTTDdxOTJoX25ZNXdtVnhlM0xlNl96YmRjTm5NSjdjQXJLWW1TMFJvbGlQSXdDZWg1MVFFZWh2QWlxYlNZMUo3UG1BemRGTHNtVlEtcmVuMmgzaUNtWnRRLXV6YTFSQUJyWnUyR0VLdEh2a1Q3QUk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Galeria de Flooring and Wall Tiles - Dietfurt Limestone - 19 - ArchDaily</t>
+          <t>EuroChem pode paralisar e implementar layoff em Serra do Salitre devido à crise do enxofre - Diário do Comércio</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>30/07/2026 18:20</t>
+          <t>30/07/2026 18:46</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxNbnN0dXQ1TkdzWFNGNzRubXJJUlgzNDRaZHp4OTZ3NVRvNnZzcEpwWlktMzhBR0VFZlVxTFpSeUFCZ3hVYW9JTVVTbExLeXpIalFyTUZldXlJaDNNYy1WbzhKd00zeWUwSGVxS3hrM1lkRVQ2YzdUckJ0MU1mLW5GaURXYXhRUWhfcFdvaDg1QzhVTVloRW9rbV9tRmtYNm1sb3hrR0NfUm5uY0loVll4VmlUelI2N2h3d2gtWnM4dll2WnBBWUJ6Rm92SndwZWc4cHE3RHJ0dGtsUzhQMFFST2Y1UWw3TnRlSkVFQ0p1eTlUNWJlT1V4MWhiR3IxR2NIYUV5TzdSVllZdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1FUmpCMjBWeG01TDVyOEZqbWI3Tk83SjVvdjA4ajBzVWtZTTFTZjA2Qi1HU2RMOUtab3dWelVzbjE4dTUtS3NGSEZ6Rms0SDd3T1I0eUpXVmNGaFJHdlFkdW1SZHM2MDZQM2wtZ0xKcnI3a0lCZ01FNg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mosaic transforma inovação agronômica em campanha para aproximar tecnologia do produtor rural - Gazeta da Semana</t>
+          <t>Galeria de Flooring and Wall Tiles - Dietfurt Limestone - 19 - ArchDaily</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>30/07/2026 11:09</t>
+          <t>30/07/2026 18:20</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxONkRONXYzRFllZmpxU0ZTYnAzc2trWHBXNE9UX2tfRDJETHFZN28tbHRBV3JHZWV6emlqQ0plUWNWNWNTTDRfQWVjX2dScFpjdV9VTU0xb0JxN3RreV9GaVpYdzc1Uk56Z1E5TzRJQlh3cFpWcjF3T2VTdl9Cb1hHX1RXWjEyOGxKR0NsS3JzTTBEbkdJYlRYRlF2SHhoLW5lU1FVRG1hNDJQMG5RaDVDQVBtcHd0V0hQVXhZcWppU0VRYk84aVhZVnVLMFJ0V1B5SUFNWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxNbnN0dXQ1TkdzWFNGNzRubXJJUlgzNDRaZHp4OTZ3NVRvNnZzcEpwWlktMzhBR0VFZlVxTFpSeUFCZ3hVYW9JTVVTbExLeXpIalFyTUZldXlJaDNNYy1WbzhKd00zeWUwSGVxS3hrM1lkRVQ2YzdUckJ0MU1mLW5GaURXYXhRUWhfcFdvaDg1QzhVTVloRW9rbV9tRmtYNm1sb3hrR0NfUm5uY0loVll4VmlUelI2N2h3d2gtWnM4dll2WnBBWUJ6Rm92SndwZWc4cHE3RHJ0dGtsUzhQMFFST2Y1UWw3TnRlSkVFQ0p1eTlUNWJlT1V4MWhiR3IxR2NIYUV5TzdSVllZdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Calcário de Escolinhas começa neste sábado em Macuco - jornaldaregiao.com</t>
+          <t>Mosaic transforma inovação agronômica em campanha para aproximar tecnologia do produtor rural - Gazeta da Semana</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>30/07/2026 10:37</t>
+          <t>30/07/2026 11:09</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNQ3NVZFk0TlBMVlpMSHNUdFEwR1lOT1MzTHhIZUFiSi1mUnRUc1hmVjdXajhneEg0Zjk5V1gwaDRJVHdadjNNejdfdEpDTnBLX3JhcE9pVHdNaGpNQjcybG9CemRiaFNWeW0wR2FjSHBzU3ZYYmgyN2dSSkwxMW9KbmVnaGlNY3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxONkRONXYzRFllZmpxU0ZTYnAzc2trWHBXNE9UX2tfRDJETHFZN28tbHRBV3JHZWV6emlqQ0plUWNWNWNTTDRfQWVjX2dScFpjdV9VTU0xb0JxN3RreV9GaVpYdzc1Uk56Z1E5TzRJQlh3cFpWcjF3T2VTdl9Cb1hHX1RXWjEyOGxKR0NsS3JzTTBEbkdJYlRYRlF2SHhoLW5lU1FVRG1hNDJQMG5RaDVDQVBtcHd0V0hQVXhZcWppU0VRYk84aVhZVnVLMFJ0V1B5SUFNWQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Preço da ureia sobe 14% em um mês e preocupa produtores às vésperas da próxima safra - Portal Tri Notícias</t>
+          <t>Calcário de Escolinhas começa neste sábado em Macuco - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>30/07/2026 09:13</t>
+          <t>30/07/2026 10:37</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOeFJwUWdQbGZjc3NoNk9raW0xNHZSME9uN2lfM2kzZU9WWE53RjBIN1FCdXVvY3VSZ1FRaDJ0NGZHSUVpMXRxcTBVRHdka3lMZ01ZX3JGWmZPZC1vLTZtX1B1TTdvazlBYnl6V1NqOVdZSlJMd2ZKTE5nSkZjaEZKcWs1d2VfZ3BuU3EyaWNiV0J5UEtwUjh3cUFlamZDcDllLTRWZkJoTXZnUmYyVlhzN2JjOHJOQXBYbHdzODRBak9taUo4RkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNQ3NVZFk0TlBMVlpMSHNUdFEwR1lOT1MzTHhIZUFiSi1mUnRUc1hmVjdXajhneEg0Zjk5V1gwaDRJVHdadjNNejdfdEpDTnBLX3JhcE9pVHdNaGpNQjcybG9CemRiaFNWeW0wR2FjSHBzU3ZYYmgyN2dSSkwxMW9KbmVnaGlNY3M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Galeria de Mosaic Tiles - Starlight - 3 - ArchDaily</t>
+          <t>Preço da ureia sobe 14% em um mês e preocupa produtores às vésperas da próxima safra - Portal Tri Notícias</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>30/07/2026 07:48</t>
+          <t>30/07/2026 09:13</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOTmIzdWtDTnlJekRGSF9FOEFsVW1uXzdLOVBIQU5sWUhTVV81LWl6Tzc4SjgxcnNKRTlqZHU0WlM0RGZBNUhuV2phaG9HUExBdDQtNDRPZ1BibXp1Qm1BMGxTZExZX1paT29BVWFic3FKajRXM1d0VElDWGozSTRybTQ3VHY3VVVaQ2c0R2VUWGFkQVE0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOeFJwUWdQbGZjc3NoNk9raW0xNHZSME9uN2lfM2kzZU9WWE53RjBIN1FCdXVvY3VSZ1FRaDJ0NGZHSUVpMXRxcTBVRHdka3lMZ01ZX3JGWmZPZC1vLTZtX1B1TTdvazlBYnl6V1NqOVdZSlJMd2ZKTE5nSkZjaEZKcWs1d2VfZ3BuU3EyaWNiV0J5UEtwUjh3cUFlamZDcDllLTRWZkJoTXZnUmYyVlhzN2JjOHJOQXBYbHdzODRBak9taUo4RkE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Clusters ferro-enxofre abrem novas frentes no controle de insetos - Revista Cultivar</t>
+          <t>Galeria de Mosaic Tiles - Starlight - 3 - ArchDaily</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>30/07/2026 06:43</t>
+          <t>30/07/2026 07:48</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNzF2ZFlUZ2ZYSVRweUxrUFRBbkxnYU1weG5MZnduVy1KR25MazlueWRpTndXaFJQTUY2elBUX2JlU0hhTTZuWVE5LUFlWDFFc2JOYkNleUxnb09nM2ZKd0Fqc1E3Wmd4YUI2cFlKamFIaUFoRWFOMnFkdG1IMHNjU0NVRWdRTWYteXpfUzVlZFFHOHFzQzB0U1VHM3VzcUFDaXNXY2hNb28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOTmIzdWtDTnlJekRGSF9FOEFsVW1uXzdLOVBIQU5sWUhTVV81LWl6Tzc4SjgxcnNKRTlqZHU0WlM0RGZBNUhuV2phaG9HUExBdDQtNDRPZ1BibXp1Qm1BMGxTZExZX1paT29BVWFic3FKajRXM1d0VElDWGozSTRybTQ3VHY3VVVaQ2c0R2VUWGFkQVE0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MOS|Mosaic Co|Preço:22.615|Var. %:-0.465 - TradingKey</t>
+          <t>Clusters ferro-enxofre abrem novas frentes no controle de insetos - revistacultivar.com.br</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>30/07/2026 01:44</t>
+          <t>30/07/2026 06:43</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE5iQndjWTVfY245N0x6UUFkSkdUQ2NWaEljRS1yVDNlMkhQQk5MMnVUUzJlQThyekNfX3o5cEtLQnZCS05ydTZ3cnZRSTQxY2NFN3pCSWlBQmRZMGVadDA1VVJxNFBHTmtGV1JJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNzF2ZFlUZ2ZYSVRweUxrUFRBbkxnYU1weG5MZnduVy1KR25MazlueWRpTndXaFJQTUY2elBUX2JlU0hhTTZuWVE5LUFlWDFFc2JOYkNleUxnb09nM2ZKd0Fqc1E3Wmd4YUI2cFlKamFIaUFoRWFOMnFkdG1IMHNjU0NVRWdRTWYteXpfUzVlZFFHOHFzQzB0U1VHM3VzcUFDaXNXY2hNb28?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nova fábrica de ureia na índia terá capacidade de 1,27 milhão de toneladas por ano - GlobalFert</t>
+          <t>MOS|Mosaic Co|Preço:22.615|Var. %:-0.465 - TradingKey</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>29/07/2026 22:32</t>
+          <t>30/07/2026 01:44</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNdWlvSWxaY3E2VEpHZUtQM1dMRUlBUlhzaTZQVTEwY29wa0lKZldWMXBiaW5BVlBjZkh3WmdNVVMxRlRSRmotRzFDbHRCVVZQMldyMVJ0WWljVE0wb19sM3d1NmRObzBzWW03THF5ZG4zTE5obU9lTVFQZ0lkemVoOG1sLTdTaEpURjZTd2hlODN5NW5hTzVnaGYteExpSlFmd0lsVGhuMEVHbFd1TE81RFdLZEpzSjFTX2hKdzgtbjFoNDNP?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE5iQndjWTVfY245N0x6UUFkSkdUQ2NWaEljRS1yVDNlMkhQQk5MMnVUUzJlQThyekNfX3o5cEtLQnZCS05ydTZ3cnZRSTQxY2NFN3pCSWlBQmRZMGVadDA1VVJxNFBHTmtGV1JJ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Selada por 5,5 milhões de anos, caverna na Romênia abriga vida sem luz solar em água rica em enxofre e ar quase irrespirável - Revista Oeste</t>
+          <t>Nova fábrica de ureia na índia terá capacidade de 1,27 milhão de toneladas por ano - GlobalFert</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>29/07/2026 19:10</t>
+          <t>29/07/2026 22:32</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxNcFJCZGs0N0xZVWhFMDJiSGwyV2NnYVN5dEtLbExqTGJQbldTdmt0Sy1aRHdDSjVkc2lwSC1laTdPUHFjT2tYcERaR1JCNDVWcXpLTHVvRV9ISlZ4dElUQTlwTnNEQzNjUG1oQ1BwSUFpMDBKczluNzI1LTJpZU9SR3RvR203S3RkVEtZRmR6TDJzSG1YVW1vSFZTQ2xKNl9mYndDS2pzNkR1RjB1MXhtZ0o0eWZmbnloZHZuSzRybUFTelZWajBRREszN3BCdGYxNnZLRDJwM1BTMTZERXZod0JKTGpXSFFHak1JOEZ3YnVoVTFMaXFDMmpZeGppXzA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNdWlvSWxaY3E2VEpHZUtQM1dMRUlBUlhzaTZQVTEwY29wa0lKZldWMXBiaW5BVlBjZkh3WmdNVVMxRlRSRmotRzFDbHRCVVZQMldyMVJ0WWljVE0wb19sM3d1NmRObzBzWW03THF5ZG4zTE5obU9lTVFQZ0lkemVoOG1sLTdTaEpURjZTd2hlODN5NW5hTzVnaGYteExpSlFmd0lsVGhuMEVHbFd1TE81RFdLZEpzSjFTX2hKdzgtbjFoNDNP?oc=5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Galeria de Mosaic Tiles in Impact Hub Co-working Space - 5 - ArchDaily</t>
+          <t>Selada por 5,5 milhões de anos, caverna na Romênia abriga vida sem luz solar em água rica em enxofre e ar quase irrespirável - revistaoeste.com</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>29/07/2026 18:36</t>
+          <t>29/07/2026 19:10</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOajZEWWMtTU54T1Z6ZVktZ0JKVzBDTjRrNlItNUpqcUw4eGRsOGEwUGpNMWFlTkhJNTVWV3cwTDYxWFgtcjRyMUJjeW04MEM1Q0N4OVhhVFdzUkR0QnI4ZHo0YXA3MkZJTEhxUGVMOWVDZjZWd1NjbFVtRFJ6Z1B3ekdxOXE0ZWRncl9rVU5jNGlZTk0wOGk3QjY3SHVLdWpIMV9hazdtbkEyd1dIcUE0MA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxNcFJCZGs0N0xZVWhFMDJiSGwyV2NnYVN5dEtLbExqTGJQbldTdmt0Sy1aRHdDSjVkc2lwSC1laTdPUHFjT2tYcERaR1JCNDVWcXpLTHVvRV9ISlZ4dElUQTlwTnNEQzNjUG1oQ1BwSUFpMDBKczluNzI1LTJpZU9SR3RvR203S3RkVEtZRmR6TDJzSG1YVW1vSFZTQ2xKNl9mYndDS2pzNkR1RjB1MXhtZ0o0eWZmbnloZHZuSzRybUFTelZWajBRREszN3BCdGYxNnZLRDJwM1BTMTZERXZod0JKTGpXSFFHak1JOEZ3YnVoVTFMaXFDMmpZeGppXzA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha acordo para comprar minério de ferro da brasileira Itaminas - InvestNews</t>
+          <t>Galeria de Mosaic Tiles in Impact Hub Co-working Space - 5 - ArchDaily</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>29/07/2026 15:19</t>
+          <t>29/07/2026 18:36</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5DT2VnclhuTHNCOFlEd05PUHRSdU9BU3gwVUhDaHpmVzBQSHEwV3Fub2hBbkREMEl5N2E2TzNDbVplZ3dudkptZHU4WXFNdEdmWENvT19zeFVSYTlhUWdLc2Q3V2tDdXBqTkZVVjk1aUxzQdIBd0FVX3lxTE9EMUJSRjJpOWxNRGhVVnFDS0F5NW9wNlFPSGNGcnp2RmxTOS1PRXBzbzY3N2wzVHpRU2d0aEJuSkhQNmJMMGRzcGxuc3lYOE1vUEtEeTVjLUhtMkNveFZrOHQtQlNsZWh3NGUxTERKYkg1eE9ZaFVz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOajZEWWMtTU54T1Z6ZVktZ0JKVzBDTjRrNlItNUpqcUw4eGRsOGEwUGpNMWFlTkhJNTVWV3cwTDYxWFgtcjRyMUJjeW04MEM1Q0N4OVhhVFdzUkR0QnI4ZHo0YXA3MkZJTEhxUGVMOWVDZjZWd1NjbFVtRFJ6Z1B3ekdxOXE0ZWRncl9rVU5jNGlZTk0wOGk3QjY3SHVLdWpIMV9hazdtbkEyd1dIcUE0MA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ormuz pressiona fertilizantes: enxofre sobe 322% em um ano, fosfatados perdem demanda e ureia volta a avançar - Money Times</t>
+          <t>Chinesa CMOC fecha acordo para comprar minério de ferro da brasileira Itaminas - InvestNews</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>29/07/2026 10:44</t>
+          <t>29/07/2026 15:19</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPX1FwemdXWEhUWnBFTkt4NkRMQ1p2aU1zVHB6aVJlbkh5WWJrWURlbkVZa0w3ZG9mLWl2VHZjY3gtekJsSWVrellJX29fRGJvMy1YZlotM3VVR3J5a05pc01UcEx1MjNSUkNVUDdieUx3eTR4RU5PdEEzMlYwVnQ5Yzdja0R1QlRnY1A2T0ZlNUFGTzdiRTY4ek50U0RKRDJtZXoyMlJWQTNGeTdwYlBHQVdYclRhVnFSUHIxRl9QXzBrazB2UGVoWGRaZkJ6SXdaaXBkSUJoeFVDUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5DT2VnclhuTHNCOFlEd05PUHRSdU9BU3gwVUhDaHpmVzBQSHEwV3Fub2hBbkREMEl5N2E2TzNDbVplZ3dudkptZHU4WXFNdEdmWENvT19zeFVSYTlhUWdLc2Q3V2tDdXBqTkZVVjk1aUxzQdIBd0FVX3lxTE9EMUJSRjJpOWxNRGhVVnFDS0F5NW9wNlFPSGNGcnp2RmxTOS1PRXBzbzY3N2wzVHpRU2d0aEJuSkhQNmJMMGRzcGxuc3lYOE1vUEtEeTVjLUhtMkNveFZrOHQtQlNsZWh3NGUxTERKYkg1eE9ZaFVz?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Casa dos Ventos e Mosaic fecham novo contrato de autoprodução eólica - MegaWhat</t>
+          <t>Ormuz pressiona fertilizantes: enxofre sobe 322% em um ano, fosfatados perdem demanda e ureia volta a avançar - Money Times</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>29/07/2026 09:04</t>
+          <t>29/07/2026 10:44</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQdk82clp1MVZjWnJWSE9rcGFlMGJFbDQ0WE9FSllpWGUtYTdWRWRHbFR0MGpZZzhrMW5uQVZpTkE2RUVrcVlhN1E5V2U2bjN4a3V4ZXRYLWVQV2JnZ3ZVck8xeFNTY09UakxkUVFNaEJSOFVkWlQxczE3dkVLYzVnWTFoNkxONF9pYW11UzlRdDRaTEV5QlJ0OFI0ck12bFBhNlJJU0FUdUFmaTVMcllZZzlpTEtYWk1YTnN5d0xRbmtsOFFM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPX1FwemdXWEhUWnBFTkt4NkRMQ1p2aU1zVHB6aVJlbkh5WWJrWURlbkVZa0w3ZG9mLWl2VHZjY3gtekJsSWVrellJX29fRGJvMy1YZlotM3VVR3J5a05pc01UcEx1MjNSUkNVUDdieUx3eTR4RU5PdEEzMlYwVnQ5Yzdja0R1QlRnY1A2T0ZlNUFGTzdiRTY4ek50U0RKRDJtZXoyMlJWQTNGeTdwYlBHQVdYclRhVnFSUHIxRl9QXzBrazB2UGVoWGRaZkJ6SXdaaXBkSUJoeFVDUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EXCLUSIVO | O que está acontecendo na cadeia de valor do enxofre? - Brasil Mineral</t>
+          <t>Casa dos Ventos e Mosaic fecham novo contrato de autoprodução eólica - MegaWhat</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>29/07/2026 08:38</t>
+          <t>29/07/2026 09:04</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPLWxUWFlOWFBnTG5hcDBndHo0SVNlaWRSWVhnRjl0S0pQTmpsVHZ2NkszYWxMNld3dUdZZmlnX0xCVl9RMDZEeWRUT1FVYk5vRHpzUUZnRVMyVlRlcVRoY2FZbEh2eE9GQndkeHNLWTRYbTlXcUUzbkpVaWxZa1FCcWpzZ290WDY2ZmFpcXlCWW1QUl8zUkV5eTlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQdk82clp1MVZjWnJWSE9rcGFlMGJFbDQ0WE9FSllpWGUtYTdWRWRHbFR0MGpZZzhrMW5uQVZpTkE2RUVrcVlhN1E5V2U2bjN4a3V4ZXRYLWVQV2JnZ3ZVck8xeFNTY09UakxkUVFNaEJSOFVkWlQxczE3dkVLYzVnWTFoNkxONF9pYW11UzlRdDRaTEV5QlJ0OFI0ck12bFBhNlJJU0FUdUFmaTVMcllZZzlpTEtYWk1YTnN5d0xRbmtsOFFM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Galeria de Porcelanato - serie New Limestone - 1 - ArchDaily</t>
+          <t>EXCLUSIVO | O que está acontecendo na cadeia de valor do enxofre? - Brasil Mineral</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>29/07/2026 08:35</t>
+          <t>29/07/2026 08:38</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxNTlpBLXlublBBZDV3d2lOMW5xQnFYMEVRVGMtYzhQTlQ1Z2NmMzFjTmVGVWtrR3RpNUhackpiRUhtRHRMTk9iQTRhdE1GQ2ZzMGlsTFo4OFdYU3RFS3RQN1Q2T2p2d1k0ODF4bWZwaHFwamY1RldCSXEwUVVQLU8zSDZubld0ZzI2TFpDY1MyS2VjY3dPdWw0b2Z0VVloLTRCRXdqRE5TT1owY1ZkLVdBeUUwVkFiODRFQVl6MnpHcUI0blNTVzhQOXBraVJhTE42RnQ2a3RrMGFSeEpndFprWVZabXNzUTQ2ck1uRFoxLXlGeWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPLWxUWFlOWFBnTG5hcDBndHo0SVNlaWRSWVhnRjl0S0pQTmpsVHZ2NkszYWxMNld3dUdZZmlnX0xCVl9RMDZEeWRUT1FVYk5vRHpzUUZnRVMyVlRlcVRoY2FZbEh2eE9GQndkeHNLWTRYbTlXcUUzbkpVaWxZa1FCcWpzZ290WDY2ZmFpcXlCWW1QUl8zUkV5eTlB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ureia cai forte e muda a conta para a próxima safra - agrolink.com.br</t>
+          <t>Galeria de Porcelanato - serie New Limestone - 1 - ArchDaily</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>29/07/2026 08:03</t>
+          <t>29/07/2026 08:35</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPLUtOVnNuaHlwVThqUERlWVNWNWYzOE9sSk96YnkxSndhelBJQXBremtlVjRldTdMTTNYTjJSb3FGb04tLURZdjlBZk1QZ1BMaWVXN1B3ZVBJREctc21HMnRxZkJtSjUyS205c2hYeUJ2dE9kOUpla2t3TXdNOTRuYXRzMGY1MWxwcUpYWVVZeXpDR3VER2lZNUJvdmg4RVYxdmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxNTlpBLXlublBBZDV3d2lOMW5xQnFYMEVRVGMtYzhQTlQ1Z2NmMzFjTmVGVWtrR3RpNUhackpiRUhtRHRMTk9iQTRhdE1GQ2ZzMGlsTFo4OFdYU3RFS3RQN1Q2T2p2d1k0ODF4bWZwaHFwamY1RldCSXEwUVVQLU8zSDZubld0ZzI2TFpDY1MyS2VjY3dPdWw0b2Z0VVloLTRCRXdqRE5TT1owY1ZkLVdBeUUwVkFiODRFQVl6MnpHcUI0blNTVzhQOXBraVJhTE42RnQ2a3RrMGFSeEpndFprWVZabXNzUTQ2ck1uRFoxLXlGeWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Crise do enxofre ameaça produção agrícola no Pará e no Brasil - bacananews.com.br</t>
+          <t>Ureia cai forte e muda a conta para a próxima safra - Agrolink</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>29/07/2026 07:18</t>
+          <t>29/07/2026 08:03</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQZG1UZUhyT1JFSW1zcC1ySjNRRlpwRVhKbEVrS3RHYTBWdGUtV0NxOWUwTG41Q1FVcF9MbVZMYXBXRkpSN2dvbjdGVU1NdDlEa245amJDTWNRNFlyRnpudEI3ck5SSVl6cjQ4cm5sdzVxVUZBTE81ckFxLUFzblZlRlJIOFBjR3dINEVPN2ZmM3hhQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPLUtOVnNuaHlwVThqUERlWVNWNWYzOE9sSk96YnkxSndhelBJQXBremtlVjRldTdMTTNYTjJSb3FGb04tLURZdjlBZk1QZ1BMaWVXN1B3ZVBJREctc21HMnRxZkJtSjUyS205c2hYeUJ2dE9kOUpla2t3TXdNOTRuYXRzMGY1MWxwcUpYWVVZeXpDR3VER2lZNUJvdmg4RVYxdmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Aumento da tensão no Oriente Médio faz ureia subir quase 14% em um mês - brasilagro.com.br</t>
+          <t>Crise do enxofre ameaça produção agrícola no Pará e no Brasil - Bacana News</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>29/07/2026 06:24</t>
+          <t>29/07/2026 07:18</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPV0ttektrOWVWbUNQcndLWHlINjhWUUIzek1DQ18tNWJST1RBMGFCandldlJhNmdUeUdOUkx6VkhNSjdvNkhLVjJRQndkNlQwalVfQVRkd1ZpQUdDcmcta3RobEtoOXIxUzVvekJTc2l0ZHlhbEl2dGdlUWlEckRrWWFoX2xLUloyVDQ3VUV2dUoza2d2VFJZTWVEYkNGRzNhVHdMNUF4TFdVdkstX1F4NGhaaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQZG1UZUhyT1JFSW1zcC1ySjNRRlpwRVhKbEVrS3RHYTBWdGUtV0NxOWUwTG41Q1FVcF9MbVZMYXBXRkpSN2dvbjdGVU1NdDlEa245amJDTWNRNFlyRnpudEI3ck5SSVl6cjQ4cm5sdzVxVUZBTE81ckFxLUFzblZlRlJIOFBjR3dINEVPN2ZmM3hhQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -1194,127 +1194,127 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>A Índia anunciou novo leilão para compra de ureia de 1,7 milhão de toneladas - GlobalFert</t>
+          <t>Aumento da tensão no Oriente Médio faz ureia subir quase 14% em um mês - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>29/07/2026 04:00</t>
+          <t>29/07/2026 06:24</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPMHhKTkQwVHotLXUzYXBVUmpkVnJBQnhtM1B3UnpQQmcxODBpZzhmSkVNa0E3ZHFNRUE3TDVpZ25JLUU5U1VUVzNzaXk1ZnRPdEd0eE51STh2T0EzM3Z1ZXcweC02cmQzQzdXZ1luZk9ZWHVtUy03TFJteW9jRzZVQnNnZl9PeHB1NHVuMEhZazl6a3ZPN3dHTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPV0ttektrOWVWbUNQcndLWHlINjhWUUIzek1DQ18tNWJST1RBMGFCandldlJhNmdUeUdOUkx6VkhNSjdvNkhLVjJRQndkNlQwalVfQVRkd1ZpQUdDcmcta3RobEtoOXIxUzVvekJTc2l0ZHlhbEl2dGdlUWlEckRrWWFoX2xLUloyVDQ3VUV2dUoza2d2VFJZTWVEYkNGRzNhVHdMNUF4TFdVdkstX1F4NGhaaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pesquisa aponta que calcário ultrafino melhora microbiologia do solo - Estadão MT</t>
+          <t>A Índia anunciou novo leilão para compra de ureia de 1,7 milhão de toneladas - GlobalFert</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>28/07/2026 21:26</t>
+          <t>29/07/2026 04:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNMkhNdkktcm9mVHc3Vk5vSVl3LW5kTjN6REdMZ0lPZ3N4ZDZfejJQRUpIcmZEX1NORWpFNUV5VWFjVC16S0t2RnBxTnhVSVRuZkFvMy1zRkVyUWZvQ3NxV0tncmU2YUVYWjd2V29sbElsWE9rTHlhajgtNnZFNE9KanRIaGRaelRQMlRJbXRnZW5MUWpLWS1zbDFEMWo3bTdmaEZKMlNOckYxSGxnaTBjZUJxU3BYRzJpUXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPMHhKTkQwVHotLXUzYXBVUmpkVnJBQnhtM1B3UnpQQmcxODBpZzhmSkVNa0E3ZHFNRUE3TDVpZ25JLUU5U1VUVzNzaXk1ZnRPdEd0eE51STh2T0EzM3Z1ZXcweC02cmQzQzdXZ1luZk9ZWHVtUy03TFJteW9jRzZVQnNnZl9PeHB1NHVuMEhZazl6a3ZPN3dHTg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Composição da Receita: Mosaic Co (MOS) — Segmentos, Regiões e Contribuição para os Lucros - TradingKey</t>
+          <t>Pesquisa aponta que calcário ultrafino melhora microbiologia do solo - Estadão MT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>28/07/2026 20:30</t>
+          <t>28/07/2026 21:26</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE5qazVweHhXUFRWQUZnSGJKNFpLaDNIdHVqX0lBcGRLeTQwYlR2OEZDUllNb0hlSTdHT2xabWZWUlZrM3VSenRuZXRQdm16T3o5cW45Sk5iZ0hlUUgtMzczcDYxeHMyMDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNMkhNdkktcm9mVHc3Vk5vSVl3LW5kTjN6REdMZ0lPZ3N4ZDZfejJQRUpIcmZEX1NORWpFNUV5VWFjVC16S0t2RnBxTnhVSVRuZkFvMy1zRkVyUWZvQ3NxV0tncmU2YUVYWjd2V29sbElsWE9rTHlhajgtNnZFNE9KanRIaGRaelRQMlRJbXRnZW5MUWpLWS1zbDFEMWo3bTdmaEZKMlNOckYxSGxnaTBjZUJxU3BYRzJpUXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Galeria de Facade System - LINEA Dietfurt Limestone - 11 - ArchDaily</t>
+          <t>Composição da Receita: Mosaic Co (MOS) — Segmentos, Regiões e Contribuição para os Lucros - TradingKey</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>28/07/2026 20:12</t>
+          <t>28/07/2026 20:30</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxNWW5sNjRCYS1obTRpa2xReWVNMTNLME9tVGxhVFF3ME5wUWtidlV3aVdCNF9kcjdNR0wwOUhoZ3VTV09qZWtuUnhlMF9sUG1xX0N5WnRucTFiME9vaHdIMDdFTnRnZ2dfQXlsenBIdkRRcE9hWHlXMWJ2eHYxbVJMa001R1RVSWt3RDhubmc3VFVBcl9ac2dqMnRkSWdoTk1vdldneEhNMXJxOUNCTmRWWTdFU3pHRFJHd3lHbE4yUGJndXRRRTBQWEYzRDBObkhYQlhXZGc2RzRuMDE5c0o3SjJyNGVwVW5BZ1Zv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE5qazVweHhXUFRWQUZnSGJKNFpLaDNIdHVqX0lBcGRLeTQwYlR2OEZDUllNb0hlSTdHT2xabWZWUlZrM3VSenRuZXRQdm16T3o5cW45Sk5iZ0hlUUgtMzczcDYxeHMyMDA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Megaprojeto de US$ 2,7 bilhões criará uma das maiores fábricas de ureia do mundo com 3,5 mil empregos para abastecer o Brasil - NSC Total</t>
+          <t>Galeria de Facade System - LINEA Dietfurt Limestone - 11 - ArchDaily</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>28/07/2026 17:51</t>
+          <t>28/07/2026 20:12</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxPV3FXdXFKMUZPa2s4LXJleENocHY4QmM2RUJGbE4tRmk0TDRpTnRwbzVmbUZITWxwTDhhQWVSUVRQMk9nNDBTam8wSm51Sml4X182ZG8ybE5oNUlWenN1bzBwVndpSldJdTQ0TlRTQkZUSFhrZ2M0cXRqZjY5cDJUYWxIVVBmdWZkUF9jeGU0b1RNM2t1T1Fhd2FrUko0MksyWGpiVnB3clhMV2ZHUlJRcUVMWUFpYTdEOXZKSlZWTXpkUVAzMmJfQlhzRUNIWWV2MFc2QmJEeS1IY1RfbnJkQTVFaGtnMHBzVVc5c1RTQW4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxNWW5sNjRCYS1obTRpa2xReWVNMTNLME9tVGxhVFF3ME5wUWtidlV3aVdCNF9kcjdNR0wwOUhoZ3VTV09qZWtuUnhlMF9sUG1xX0N5WnRucTFiME9vaHdIMDdFTnRnZ2dfQXlsenBIdkRRcE9hWHlXMWJ2eHYxbVJMa001R1RVSWt3RDhubmc3VFVBcl9ac2dqMnRkSWdoTk1vdldneEhNMXJxOUNCTmRWWTdFU3pHRFJHd3lHbE4yUGJndXRRRTBQWEYzRDBObkhYQlhXZGc2RzRuMDE5c0o3SjJyNGVwVW5BZ1Zv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Escassez mundial de enxofre ameaça agronegócio do Pará e pode elevar custo da produção - gazetacarajas.com</t>
+          <t>Megaprojeto de US$ 2,7 bilhões criará uma das maiores fábricas de ureia do mundo com 3,5 mil empregos para abastecer o Brasil - NSC Total</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>28/07/2026 17:46</t>
+          <t>28/07/2026 17:51</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOcW1Zd1BZUVpmZmZXT2hJVkwxSTczQ3ZCZGQxbkVDZ1BZNnczeGhEV1ZvMWJTSU15TGp5QVBkcS16aWRBMWxxRllCblRuQ2hSZmk2VjQ2cVNJSDFHRXhMX0poSXEyWV93ZlRRa25mS0JaN3k1M2pXMVNUV2d3aWlsX2E0ZkJHYng5elNRVGRTVXlBcDBNVUxkM0xYMTZ4ZDRmbGc4T21HeVVkc2k5cENOV25EWVB5Vzk5azQ3aHgtSFpNZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxPV3FXdXFKMUZPa2s4LXJleENocHY4QmM2RUJGbE4tRmk0TDRpTnRwbzVmbUZITWxwTDhhQWVSUVRQMk9nNDBTam8wSm51Sml4X182ZG8ybE5oNUlWenN1bzBwVndpSldJdTQ0TlRTQkZUSFhrZ2M0cXRqZjY5cDJUYWxIVVBmdWZkUF9jeGU0b1RNM2t1T1Fhd2FrUko0MksyWGpiVnB3clhMV2ZHUlJRcUVMWUFpYTdEOXZKSlZWTXpkUVAzMmJfQlhzRUNIWWV2MFc2QmJEeS1IY1RfbnJkQTVFaGtnMHBzVVc5c1RTQW4?oc=5</t>
         </is>
       </c>
     </row>
@@ -1326,83 +1326,83 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Enxofre caro ameaça fertilizantes da safra do Paraná - Blog do Esmael</t>
+          <t>Escassez mundial de enxofre ameaça agronegócio do Pará e pode elevar custo da produção - Gazeta Carajás</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>28/07/2026 17:41</t>
+          <t>28/07/2026 17:46</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE5Yb2lTdDUxanVKZE1qVWxFb0twbzAtTlJ6Z0g4TkJucEJsOWpvS1hZQVQtbGJYal9TN2ZJNXVGWFNiR0NURFIyQ1RyTnMwUnVLQ1kydXJKZ2JVM3R3Tl9aOHRLQzFtUHItYjNmYWdBNU1PMVBTMWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOcW1Zd1BZUVpmZmZXT2hJVkwxSTczQ3ZCZGQxbkVDZ1BZNnczeGhEV1ZvMWJTSU15TGp5QVBkcS16aWRBMWxxRllCblRuQ2hSZmk2VjQ2cVNJSDFHRXhMX0poSXEyWV93ZlRRa25mS0JaN3k1M2pXMVNUV2d3aWlsX2E0ZkJHYng5elNRVGRTVXlBcDBNVUxkM0xYMTZ4ZDRmbGc4T21HeVVkc2k5cENOV25EWVB5Vzk5azQ3aHgtSFpNZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mosaic transforma inovação agronômica em campanha - Grandes Nomes da Propaganda</t>
+          <t>Enxofre caro ameaça fertilizantes da safra do Paraná - Blog do Esmael</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>28/07/2026 17:10</t>
+          <t>28/07/2026 17:41</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNVzZGOGtSTEFHU3BnVnl2ZmpCRHUwbVpHSTlZWkJWeTZ5YXo3QTJmaEQ3NXREaWd4dWNzdHVWemNoUjFkZzNOVDNYTkJfMFQxRW9fNjRZMFRQMGNRTnVhTVhMNFBNaDNsOTdvaHhXZVNvSTZmaHVFNXV5bUNQUUlrcllqZ1JCMU44V0wybHVwRGJiUGk4U0lWVDJoZENwVlh2ZThSSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE5Yb2lTdDUxanVKZE1qVWxFb0twbzAtTlJ6Z0g4TkJucEJsOWpvS1hZQVQtbGJYal9TN2ZJNXVGWFNiR0NURFIyQ1RyTnMwUnVLQ1kydXJKZ2JVM3R3Tl9aOHRLQzFtUHItYjNmYWdBNU1PMVBTMWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Com guerra no Irã, estoque brasileiro de enxofre pode não alcançar setembro, afirma Ibram - Valor Econômico</t>
+          <t>Mosaic transforma inovação agronômica em campanha - Grandes Nomes da Propaganda</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>28/07/2026 15:39</t>
+          <t>28/07/2026 17:10</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWHRWcEVlMmJVOEtOTFhYSUFrbkxvNVcxcTBXNXkwb3VFaXJ1NE5yMXNSZ3cxR0RPT1RhbGRLeTZvc3NFUGJHRDh1LTR5TU5YdXN3U0dtdVJTMElMUGlzUHJQeEVMVWhYbGVSa1BzQ2twNkxpZHZ0dUNVSjBBU1VYOTI1Vk9RUThBZ2xtbWJ4UGRBOHhNMk5Sc1M1QkR3Yk1MbHlSNGhvUU1CcjY2ZENpTTY2OW5yaGJra3pqXzc3ajE0SDZ2Vlczdk5weE54bjlsWml6ZWJwYl96QdIB6AFBVV95cUxQVENsWFVQaUIwTTNGaFItb2sxd1BoX2hLZ1cwTlpUYXJFUHVSd1RoUFFnMTFxR0sxTUJ5aHJVcXJyZXZ0NFpOcUEyTVRNOXlkWFA4ZVlyaW9TZ2JELTJpZ3owZ2k2QjE0SFIxS2wwVUxDWHRPb2s1cGNmTWhzWGxsUUxMbGlfcXlYWlFXakVxNWxkMzdGRkg1YUVfa3lnel9WQjFCUktvM1FoaUxBblVod013Y2dsX1ZPNk1Edkdpb3dkZDFmYlBQYmZza3pOQ3ZZRDVRQWlYR2tfSTFaNTJFd19IMGNlUWV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNVzZGOGtSTEFHU3BnVnl2ZmpCRHUwbVpHSTlZWkJWeTZ5YXo3QTJmaEQ3NXREaWd4dWNzdHVWemNoUjFkZzNOVDNYTkJfMFQxRW9fNjRZMFRQMGNRTnVhTVhMNFBNaDNsOTdvaHhXZVNvSTZmaHVFNXV5bUNQUUlrcllqZ1JCMU44V0wybHVwRGJiUGk4U0lWVDJoZENwVlh2ZThSSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Galeria de Facade Panels - Dietfurt Limestone - 21 - ArchDaily</t>
+          <t>Com guerra no Irã, estoque brasileiro de enxofre pode não alcançar setembro, afirma Ibram - Valor Econômico</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>28/07/2026 15:09</t>
+          <t>28/07/2026 15:39</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxNYjFYcXVEc3A3bDJsVk14QURFUW1TbWNUQ3J2T2Myd2NHTFdyWmE3ODRJX0RFamFGODB3ZHYxdTd2S0dCS3ZpSFNyNzJENGxFeDllclcyYnVsN3hkZmZkeFdqZU9pVGFFdEV1aG9FdlZkcVRyLUU2R09ZSmtxRDVuS1dtdWtNWWFKR3k2OTRhVmEwcFh4RGJVM0EtRkdWcjRQY3pRb1VxdkIwOC04TXBmbmdCVE5SaFJHcGh1VWYwY1dDSGdsS2hTS2dwa3RIS2NMS3NHUVZHSDFINU5vY1E3WmZXWWdxSklvZ1BxNFkySHRmcmZHUkFTaXBmVjE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWHRWcEVlMmJVOEtOTFhYSUFrbkxvNVcxcTBXNXkwb3VFaXJ1NE5yMXNSZ3cxR0RPT1RhbGRLeTZvc3NFUGJHRDh1LTR5TU5YdXN3U0dtdVJTMElMUGlzUHJQeEVMVWhYbGVSa1BzQ2twNkxpZHZ0dUNVSjBBU1VYOTI1Vk9RUThBZ2xtbWJ4UGRBOHhNMk5Sc1M1QkR3Yk1MbHlSNGhvUU1CcjY2ZENpTTY2OW5yaGJra3pqXzc3ajE0SDZ2Vlczdk5weE54bjlsWml6ZWJwYl96QdIB6AFBVV95cUxQVENsWFVQaUIwTTNGaFItb2sxd1BoX2hLZ1cwTlpUYXJFUHVSd1RoUFFnMTFxR0sxTUJ5aHJVcXJyZXZ0NFpOcUEyTVRNOXlkWFA4ZVlyaW9TZ2JELTJpZ3owZ2k2QjE0SFIxS2wwVUxDWHRPb2s1cGNmTWhzWGxsUUxMbGlfcXlYWlFXakVxNWxkMzdGRkg1YUVfa3lnel9WQjFCUktvM1FoaUxBblVod013Y2dsX1ZPNk1Edkdpb3dkZDFmYlBQYmZza3pOQ3ZZRDVRQWlYR2tfSTFaNTJFd19IMGNlUWV3?oc=5</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Crise do enxofre põe em risco setor de fertilizantes e preocupa o Brasil - Associação Comercial e Industrial de Araçatuba</t>
+          <t>Crise do enxofre põe em risco setor de fertilizantes e preocupa o Brasil - aciara.com.br</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fertilizantes: ureia acumula alta de 14% nos portos brasileiros e tensão no Oriente Médio acende alerta para a próxima safra - Portal do Agronegócio</t>
+          <t>Fertilizantes: ureia acumula alta de 14% nos portos brasileiros e tensão no Oriente Médio acende alerta para a próxima safra - portaldoagronegocio.com.br</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ureia sobe 14% nos portos brasileiros em quatro semanas - Revista Cultivar</t>
+          <t>Ureia sobe 14% nos portos brasileiros em quatro semanas - revistacultivar.com.br</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1739,88 +1739,88 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Escalada Geopolítica e Restrições de Oferta Impulsionam o Preço da Ureia nos Portos Brasileiros - Cliquef5</t>
+          <t>Velomar busca investimentos e discute situação da Mosaic durante agenda em São Paulo e na capital do Paraná - Badiinho</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>27/07/2026 15:34</t>
+          <t>27/07/2026 15:10</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNUk5VZm5aLTd4RGdrbk5hZi1nRUpON1JMMHlkM0hzS0dTV0t2bEJPRDJZbG9WalJNZGJWRlZLNUhwR3ZNS01zbVFYZDFlTFF6blZ4THE4ZFg0RHNSNkxiX25OT19kQ096V1VpZjVKaE9nSG42d1FqYlZmUklOVUJ2ZVA3Y0Y0aWZSX1FYcjFpY256RHlhLUk5WEZpZWlVbkdwNVo5T3B5NmNkM3N1ZjFWWmZvNUZsTVdPWUx0VGdlcFZXbG5HUXd3eTJsNGt5RW5zbWV0VEtqLS1GSWFuZ1U4Wg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5MbjYzZ1BoSXdBa1FWMWZHcVBEaXJka1oxbGVqdU1iMmZvb2JPRk5Edlp4azk1QU9LYmsxUld0YWszRXJMZlZFaEM4d0g4YTJhd0hCRGdOZ3JmVkV2SHhtVDVfcV9LcEJYbFJYT9IBckFVX3lxTE1NWXp6X2dXdV9GclBfbWo2Y05tQXR0R3VMNFI4b1NXRHJJY0d4S3BhT1JxTjlPZEV1anEyZTFBcF93aUd4VUg2WHVWckhGZ3A4azJVbG1pVUJZaFpSWHFUeVZGTmtIcnQ3TzQ1ajdlaGhjZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Velomar busca investimentos e discute situação da Mosaic durante agenda em São Paulo e na capital do Paraná - Badiinho</t>
+          <t>Calcário ultrafino melhora microbiologia do solo, diz estudo - revistacultivar.com.br</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>27/07/2026 15:10</t>
+          <t>27/07/2026 14:59</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5MbjYzZ1BoSXdBa1FWMWZHcVBEaXJka1oxbGVqdU1iMmZvb2JPRk5Edlp4azk1QU9LYmsxUld0YWszRXJMZlZFaEM4d0g4YTJhd0hCRGdOZ3JmVkV2SHhtVDVfcV9LcEJYbFJYT9IBckFVX3lxTE1NWXp6X2dXdV9GclBfbWo2Y05tQXR0R3VMNFI4b1NXRHJJY0d4S3BhT1JxTjlPZEV1anEyZTFBcF93aUd4VUg2WHVWckhGZ3A4azJVbG1pVUJZaFpSWHFUeVZGTmtIcnQ3TzQ1ajdlaGhjZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQNXhhYnc0VGZFOEdldDFmUm1iNWRKVENuVGIzRmN3VTl4NG1NajlYRDhBUFY4Y2pQbjNzTDJYdWFEU29tYUs0SnJqekprbTNfTU9DRjR0YmkzT0gwQzROZzJhaDQ0U0pKRWxOQ1lESnNaMU12ZUNIbXBWZ1JxV1llVTlDSFlqM0toX1d3bVYzNHpYZmVMUEswUVJGc3VIRFhu?oc=5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Calcário ultrafino melhora microbiologia do solo, diz estudo - Revista Cultivar</t>
+          <t>Petróleo e ureia aliviam custos no campo gaúcho - Agrolink</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>27/07/2026 14:59</t>
+          <t>27/07/2026 10:32</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQNXhhYnc0VGZFOEdldDFmUm1iNWRKVENuVGIzRmN3VTl4NG1NajlYRDhBUFY4Y2pQbjNzTDJYdWFEU29tYUs0SnJqekprbTNfTU9DRjR0YmkzT0gwQzROZzJhaDQ0U0pKRWxOQ1lESnNaMU12ZUNIbXBWZ1JxV1llVTlDSFlqM0toX1d3bVYzNHpYZmVMUEswUVJGc3VIRFhu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNNUl4M1J3UVd2UTNSUHMxQWVhWEJLMXFsQjZydk9BZ1RaOGxkUVNHdnlydVpYYUkyX25zcnZpcnoyQVlJQnBIdzE3VlFVdS1lNmh4Z3pRNEpsOTJNRzhkYjFiXzBPTXh0cmFyNWM3X0MzTXdSZGVKbkJIRDk0ZzlDM0RMaVdTLTlIellKWGV5RkhuNXRPRHFzamNCcE0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Petróleo e ureia aliviam custos no campo gaúcho - agrolink.com.br</t>
+          <t>Mosaic e Elicit Plant desenvolvem solução para canola na América do Norte - CNN Brasil</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>27/07/2026 10:32</t>
+          <t>25/07/2026 12:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNNUl4M1J3UVd2UTNSUHMxQWVhWEJLMXFsQjZydk9BZ1RaOGxkUVNHdnlydVpYYUkyX25zcnZpcnoyQVlJQnBIdzE3VlFVdS1lNmh4Z3pRNEpsOTJNRzhkYjFiXzBPTXh0cmFyNWM3X0MzTXdSZGVKbkJIRDk0ZzlDM0RMaVdTLTlIellKWGV5RkhuNXRPRHFzamNCcE0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOVDJpQWxoSVUzaEhaVTBvY3ZVelozNHgzSUdiR19SWFZUamFLZG1USl9RZUd2aFJBM2lOZnBsa3QxY2VrTkdrU2JCUDhLNTdJZkhpNUtTbFZobWRJdVVEYVY3LUM4OXpMZ1NlTnZfelduVFBoaU5kT1RKQ2lUWEhTUzRGTFRBNVVVdDVnd3lpYmlNNXJmNFdDT0stOWZBTV96Y1FoM0JNeEJFQUVp?oc=5</t>
         </is>
       </c>
     </row>
@@ -1832,61 +1832,61 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mosaic e Elicit Plant desenvolvem solução para canola na América do Norte - CNN Brasil</t>
+          <t>MOS|Mosaic Co|Preço:22.635|Var. %:+0.015 - TradingKey</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>25/07/2026 12:00</t>
+          <t>25/07/2026 11:35</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOVDJpQWxoSVUzaEhaVTBvY3ZVelozNHgzSUdiR19SWFZUamFLZG1USl9RZUd2aFJBM2lOZnBsa3QxY2VrTkdrU2JCUDhLNTdJZkhpNUtTbFZobWRJdVVEYVY3LUM4OXpMZ1NlTnZfelduVFBoaU5kT1RKQ2lUWEhTUzRGTFRBNVVVdDVnd3lpYmlNNXJmNFdDT0stOWZBTV96Y1FoM0JNeEJFQUVp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9aUmdIb1pWRkdQQ1RoNjZpV2dyYncxdjYwZFhpMkVfMXdCZnZXRnFxY3BoS2M0N1hlcnk2Y0ZnX3ZyY21HTXcyMENpSlBIckFRYnRxTUJEVXh6M2RLblJyb0FEQTJLTlU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MOS|Mosaic Co|Preço:22.635|Var. %:+0.015 - TradingKey</t>
+          <t>ureia e creatina alta - Prefeitura de Russas</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>25/07/2026 11:35</t>
+          <t>25/07/2026 10:26</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9aUmdIb1pWRkdQQ1RoNjZpV2dyYncxdjYwZFhpMkVfMXdCZnZXRnFxY3BoS2M0N1hlcnk2Y0ZnX3ZyY21HTXcyMENpSlBIckFRYnRxTUJEVXh6M2RLblJyb0FEQTJLTlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFAwMzFCdm50SU1ESkl6Z0VFSHI0ejl4MlJ5MVpWeUtKTklYUmJiQWJld1dpcVlzT2JrRHoyMGVmdjd5MzNVeHJJbXE2VVVBM0ZubjBiLW1SS3haLUdPVDdsbXdEYWs5dw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ureia e creatina alta - Prefeitura de Russas</t>
+          <t>Metabase garante manutenção de empregos e direitos de trabalhadores da Mosaic durante período de crise - Diante do Fato Catalão</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>25/07/2026 10:26</t>
+          <t>25/07/2026 08:52</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFAwMzFCdm50SU1ESkl6Z0VFSHI0ejl4MlJ5MVpWeUtKTklYUmJiQWJld1dpcVlzT2JrRHoyMGVmdjd5MzNVeHJJbXE2VVVBM0ZubjBiLW1SS3haLUdPVDdsbXdEYWs5dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQODRKRjdiYUNzWWFHa1FsQnFwZUc1M3k0b1Y0LXZSY3FnQTV5UVl2WFF2YktlcWNjMGtCMUFIczVidkxTSlJlYjZmNE10YkNleEllZFF2NXZJLVNzYzlTNHpRaHdOTzF3RTA2QktTTHJRX1p6cExSaGVLNzZRWUswYnlFMUx4WXMwZWNSZzNxeTdGbU9hV2hnZnQyeWtvdThkWFdNWFJCSTNsQmdrVzlhSnM0ZHkwRmZTMUhoVmhJS3cxekh1YXpCdzJITlhxLU5BMlBSclA3VHhLdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -1898,17 +1898,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Metabase garante manutenção de empregos e direitos de trabalhadores da Mosaic durante período de crise - Diante do Fato Catalão</t>
+          <t>Metabase negocia acordo e garante empregos e direitos de trabalhadores da Mosaic - Badiinho</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>25/07/2026 08:52</t>
+          <t>24/07/2026 16:51</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQODRKRjdiYUNzWWFHa1FsQnFwZUc1M3k0b1Y0LXZSY3FnQTV5UVl2WFF2YktlcWNjMGtCMUFIczVidkxTSlJlYjZmNE10YkNleEllZFF2NXZJLVNzYzlTNHpRaHdOTzF3RTA2QktTTHJRX1p6cExSaGVLNzZRWUswYnlFMUx4WXMwZWNSZzNxeTdGbU9hV2hnZnQyeWtvdThkWFdNWFJCSTNsQmdrVzlhSnM0ZHkwRmZTMUhoVmhJS3cxekh1YXpCdzJITlhxLU5BMlBSclA3VHhLdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBlLTMyelJZNXl0N0Rrb3h2cFFUYWV2NllzZl9rLVd2MFYtbUNNUTRYeldSNmpBeWJMUEhHR0ZaT21aQThfMFNJenhFU1htc016Z3JjcW9aQXU4WUhaVG1QbVJyUHIta2xhVGh1QW1oYndyM2fSAXhBVV95cUxOMW5kZGZ5ejB5TzlyTDVYdVZZZXVvSE4xb0tpSnZVYWU4TVEzN3JPa0hwVndtTG9EUTE1MVdTRldkeEhGQ3daRDlKVlQ3dlVTTFVsTHBuYnRGamtZSTRVQ2Ftb2Z4X1hmZmdPUXBjbVdiWTl1VmJpYy0?oc=5</t>
         </is>
       </c>
     </row>
@@ -1920,83 +1920,83 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Metabase negocia acordo e garante empregos e direitos de trabalhadores da Mosaic - Badiinho</t>
+          <t>Mosaic e Elicit Plant anunciam parceria de soluções para a canola na América do Norte - alcir61.net</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>24/07/2026 16:51</t>
+          <t>24/07/2026 15:54</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBlLTMyelJZNXl0N0Rrb3h2cFFUYWV2NllzZl9rLVd2MFYtbUNNUTRYeldSNmpBeWJMUEhHR0ZaT21aQThfMFNJenhFU1htc016Z3JjcW9aQXU4WUhaVG1QbVJyUHIta2xhVGh1QW1oYndyM2fSAXhBVV95cUxOMW5kZGZ5ejB5TzlyTDVYdVZZZXVvSE4xb0tpSnZVYWU4TVEzN3JPa0hwVndtTG9EUTE1MVdTRldkeEhGQ3daRDlKVlQ3dlVTTFVsTHBuYnRGamtZSTRVQ2Ftb2Z4X1hmZmdPUXBjbVdiWTl1VmJpYy0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQVFZObmFMaFBLTDQ3WjMzSC11OWtQbkxwV2s3SWVjb0hyTWFTMXlTbnNzWUtsME85bTRWMHozQjh5Tlk3aEJxRGgtYU1PeF96NW9OakNrbU5pRmdJMHFXVkRYRC05NmhmWFh1RjB0MmJrVE9DRXlvQWMyLUZ1UzRPTU1pazI1cS1SeXdHejd6Q1QycUhZcnhQbmJqNFdleFVOSkVkNzRxa0RVdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mosaic e Elicit Plant anunciam parceria de soluções para a canola na América do Norte - Alcir 61</t>
+          <t>Galeria de Casa de Calcário / Archer + Braun - 33 - ArchDaily</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>24/07/2026 15:54</t>
+          <t>24/07/2026 15:34</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQVFZObmFMaFBLTDQ3WjMzSC11OWtQbkxwV2s3SWVjb0hyTWFTMXlTbnNzWUtsME85bTRWMHozQjh5Tlk3aEJxRGgtYU1PeF96NW9OakNrbU5pRmdJMHFXVkRYRC05NmhmWFh1RjB0MmJrVE9DRXlvQWMyLUZ1UzRPTU1pazI1cS1SeXdHejd6Q1QycUhZcnhQbmJqNFdleFVOSkVkNzRxa0RVdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPdGYwUF9mdU9NckpzajctXzFneG9SbnVDQVIxQVE5U29NMDMwVFdSR3JSMTBUVDlkWEJBLXltdG1COVRuZkV2SGFGcEtMUXdzZEUxYklJYVFuUjY2b2lIVnJ2TlMxVDBiWnQ2dmV2UTY2eHhJYWd6dmRZT3NnZGV5Ui1rdEV0TVlCekMxS2YyaXRJLUU4N2N0VmE0X1J1ZkllYmZuLWRoYl9ad1pyTTExTUliSkxhblJLOFN1LWFaZmVIdnZLd0lCcVJwSHRBWFgzaXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Galeria de Casa de Calcário / Archer + Braun - 33 - ArchDaily</t>
+          <t>FEQUIMFAR debate medidas para preservar empregos na Mosaic - Rádio Peão Brasil</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>24/07/2026 15:34</t>
+          <t>24/07/2026 04:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPdGYwUF9mdU9NckpzajctXzFneG9SbnVDQVIxQVE5U29NMDMwVFdSR3JSMTBUVDlkWEJBLXltdG1COVRuZkV2SGFGcEtMUXdzZEUxYklJYVFuUjY2b2lIVnJ2TlMxVDBiWnQ2dmV2UTY2eHhJYWd6dmRZT3NnZGV5Ui1rdEV0TVlCekMxS2YyaXRJLUU4N2N0VmE0X1J1ZkllYmZuLWRoYl9ad1pyTTExTUliSkxhblJLOFN1LWFaZmVIdnZLd0lCcVJwSHRBWFgzaXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNWWUxOGhRc1o4ZzNBczk4Zk1oZFVmNVdfTTN6WEdsQXZRTjZkODdrUGdmM2M1WE14UkFIOWFENkhkYVkzYVBxcThkcjJVNDI0TWtfTkxaVWRTcW9qLTg1eGhDeUVIMDF5NmRhVEQ3Yk93UF9TZGJqX2dQenNMVlgzTVBDVGRsTUpHSFJLV0xCZFFDYy1t?oc=5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FEQUIMFAR debate medidas para preservar empregos na Mosaic - Rádio Peão Brasil</t>
+          <t>SEADERMA fortalece agricultura familiar com projetos de piscicultura, distribuição de calcário e novos investimentos em Livramento - nossasenhoradolivramento.mt.gov.br</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>24/07/2026 04:00</t>
+          <t>23/07/2026 13:15</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNWWUxOGhRc1o4ZzNBczk4Zk1oZFVmNVdfTTN6WEdsQXZRTjZkODdrUGdmM2M1WE14UkFIOWFENkhkYVkzYVBxcThkcjJVNDI0TWtfTkxaVWRTcW9qLTg1eGhDeUVIMDF5NmRhVEQ3Yk93UF9TZGJqX2dQenNMVlgzTVBDVGRsTUpHSFJLV0xCZFFDYy1t?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxNUDh6cS1zSTl3a3JGRTRnT05DYklpQjBwYnVtOERvakhweEtIU3V0NzJQeExpRkxuc3Jjai1zeUdmem1hbFRaM0l0MUlSTG1mTFhvbDYwTEVuZ2dFYUo1TU42X0pBQWxBRVZEU2FwWVU1cVFabkJ3YUttOFRhMGlEN2FKYVdBM0wxNk9yRlJPZGU0VEEwQXBJOFpzVzVNTVJSTUgzd0JhQm9MTW9kd0Q4MzI3SjdGbXhSVjdwcGRfQmNlS0czTlVDQmx4d3JoNVBOc1JIM0Z6czJEM1loY2pnYTVubmNoMFpkdTJkWGZxNVNwMnFXaVg4VEVXV3pIeHBpN05lcUVGTGI0eS1HeW9qOWJtZWVmMmNwbXFnT1ZvOFJ5MC1zWjRjTm1sWXZfZnFrNmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -2008,61 +2008,61 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Para sustentar duas torres de 452 metros sobre solo com calcário cárstico e cavidades subterrâneas, engenheiros removeram mais de 500 caminhões de terra por noite, cravaram 104 elementos de fundação por torre e despejaram 13,2 mil metros cúbicos d - CPG Click Petróleo e Gás</t>
+          <t>Justiça dá 3 dias para "baronesa do calcário" pagar R$ 41 milhões a advogados em MT - FOLHAMAX</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>24/07/2026 00:40</t>
+          <t>23/07/2026 04:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxOSmV1TTk3M19kWlhaTVNtU1NFVmhzOFM0aXl4ekc5RVBjc2h5ak9LMXFPNnFsQzl3UktlbkQyanpMWmxHQTVfUnhLUHYtZTV2eVhteDdsSVFsN3pkNmNyZkVsd1JOVEZKWXhDRTJkWVFJSmNtUnl6Ukc5OUlxYl9ma3RhNGpLSEFiT0FENlMzTWR0N01ETzhaZG85d3lWcEZBVjhHZUMtQllzSkdHZ25lMjVQaU5oLWNIbW54QXRvOXhkVEdROWhYbEpXeU10a3NLSjFhUkI3X0NvdkdETHFZTGpOMy1YYlFDc3NlbDZXRGNfRy1sMExDSTlfWE9VdTc4OHR4MG9DZDFXWDE4bVlzX2VkR2xoVHVFMHFzSVlSZ3V2bDVYZE5JaklSTUpxbTEtcU5lY0N0TlkyLXpJdjBYUWkzRV9LYmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNdmUtWUVyak1ITk92eG04bmpRaEJndjJaMWJ2LVdKVXlnbHE4bXJJQXRCYWh3ck03ZDAxUElfNWxRSkI4cEZYVEJtdW10dzY0MG43cnZ2VUQwb3VLTW9aMXNFMjdOaGpwNVQ3NFl0NGp3ZEI4bWxEckhKOFFhc3h4Y1ItMEdUTHVEOXVFM1d4YXJQSEpodXd4VC1KWFZlQUp1NWo4MTlQdXhrSXhtR3ptb1Y0c1QySmM3TFRlcDdn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SEADERMA fortalece agricultura familiar com projetos de piscicultura, distribuição de calcário e novos investimentos em Livramento - Prefeitura de Nossa Senhora do Livramento - MT</t>
+          <t>A nova joia da Mosaic custa mais de 20.000 € e apenas alguns poucos poderão comprá-la - brujulabike.com</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>23/07/2026 13:15</t>
+          <t>22/07/2026 04:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxNUDh6cS1zSTl3a3JGRTRnT05DYklpQjBwYnVtOERvakhweEtIU3V0NzJQeExpRkxuc3Jjai1zeUdmem1hbFRaM0l0MUlSTG1mTFhvbDYwTEVuZ2dFYUo1TU42X0pBQWxBRVZEU2FwWVU1cVFabkJ3YUttOFRhMGlEN2FKYVdBM0wxNk9yRlJPZGU0VEEwQXBJOFpzVzVNTVJSTUgzd0JhQm9MTW9kd0Q4MzI3SjdGbXhSVjdwcGRfQmNlS0czTlVDQmx4d3JoNVBOc1JIM0Z6czJEM1loY2pnYTVubmNoMFpkdTJkWGZxNVNwMnFXaVg4VEVXV3pIeHBpN05lcUVGTGI0eS1HeW9qOWJtZWVmMmNwbXFnT1ZvOFJ5MC1zWjRjTm1sWXZfZnFrNmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNdmpIOTJoRUgwbF9JNlpCYXhDTEo2ZGp4aVpSTDNSNkVTWXViMzl5X2xfWmlaUmdkUzNJZnBSU2xjbDJtcmQ4SnJFY2dwOFI1QjREalNCQVQ0YlBUUFNZOS1Gem5xeFhCcjNsNGNyeS1yRG1FeWU0dDZzTVZTWVFDbm5GTEJ1MTBpaEFTeGx0QXFWaWxsOHE3YTc0a2JqUWN4QmM0N0wxRmF0RkY3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Justiça dá 3 dias para "baronesa do calcário" pagar R$ 41 milhões a advogados em MT - FOLHAMAX</t>
+          <t>Costa do Marfim: Banco Africano de Desenvolvimento concede um financiamento de 200 milhões de euros para reforçar a produção de combustíveis com baixo teor de enxofre - African Development Bank Group</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>23/07/2026 04:00</t>
+          <t>22/07/2026 04:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNdmUtWUVyak1ITk92eG04bmpRaEJndjJaMWJ2LVdKVXlnbHE4bXJJQXRCYWh3ck03ZDAxUElfNWxRSkI4cEZYVEJtdW10dzY0MG43cnZ2VUQwb3VLTW9aMXNFMjdOaGpwNVQ3NFl0NGp3ZEI4bWxEckhKOFFhc3h4Y1ItMEdUTHVEOXVFM1d4YXJQSEpodXd4VC1KWFZlQUp1NWo4MTlQdXhrSXhtR3ptb1Y0c1QySmM3TFRlcDdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wJBVV95cUxPZ3ltamlDUFg4Z0E1LW9Kak9Ic05rdTN5QmIxczBiR2NPaGctMnpjTEd3NnpmbFNscEdjS2dyUEcxVUlmcnpJbnRJd1YyS1lSTldxUVNYalc2eFpjdXVmcDNhWEVpNzM0cTZYTVZJenhLTzFaOUVZZjB3RzBIamg1cW1ma3BkSUNKNFlsV0ozajloVk9QQ3BNTVhOWVI5NExRXzNWYmhnU2p0QUpNMk5YSHFRbEhvbTE5UEstdktEU1p6UG04R1pqMmxZRHlGYklCc0hKcW9KVDZSamlUWEIyeVhsSEZaWDF3cFpoTjE0aG93RmFlT0VqUFVUNE1TOWNjTGh2ZU5CcXA2dDJmY01abkw0SVg3b0YwUm9CNGJHS2tzbDNKT0lEQV9wZU1nMXotbF9xQnp5cGU2Z3NHb1ctTE5faTcwX2dCenVCSWtTaUUtaFM0SWdZ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2091,12 +2091,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Costa do Marfim: Banco Africano de Desenvolvimento concede um financiamento de 200 milhões de euros para reforçar a produção de combustíveis com baixo teor de enxofre - African Development Bank Group</t>
+          <t>Escassez global de enxofre paralisa indústria de fertilizantes em Goiás e ameaça mais de 600 empregos - G1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2106,29 +2106,29 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wJBVV95cUxPZ3ltamlDUFg4Z0E1LW9Kak9Ic05rdTN5QmIxczBiR2NPaGctMnpjTEd3NnpmbFNscEdjS2dyUEcxVUlmcnpJbnRJd1YyS1lSTldxUVNYalc2eFpjdXVmcDNhWEVpNzM0cTZYTVZJenhLTzFaOUVZZjB3RzBIamg1cW1ma3BkSUNKNFlsV0ozajloVk9QQ3BNTVhOWVI5NExRXzNWYmhnU2p0QUpNMk5YSHFRbEhvbTE5UEstdktEU1p6UG04R1pqMmxZRHlGYklCc0hKcW9KVDZSamlUWEIyeVhsSEZaWDF3cFpoTjE0aG93RmFlT0VqUFVUNE1TOWNjTGh2ZU5CcXA2dDJmY01abkw0SVg3b0YwUm9CNGJHS2tzbDNKT0lEQV9wZU1nMXotbF9xQnp5cGU2Z3NHb1ctTE5faTcwX2dCenVCSWtTaUUtaFM0SWdZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxQazVGaElwb0d2SFd0bjRwZE9yM2E3VEt3UzVZaV9TRUUtNGtsQ2tTS21jbVRNdXk0M3ZQd3Vhc3BtakpoN2JOZEh0UllpNFNNU1RBQVZLb0otVnN0cnRUMHNROTFVYWNzMDJ4bmNIbjhsaGhZZVFDcFllcV9oZ3dFa25HaWdtdDJWQ01jeEllTnRYYi0zMFhfMEJ3ekRuNl8xOTlUN2dWbGdkX1p3NnQ1N2FHbFRUWjJSUlNla3lTSFpFSlV6U2w3QVlrNW1OVm5HVjVtQllSaTN0d3ptWjdObnVSWUY2bDRWUGltadIB-wFBVV95cUxPallYVTZnVk1ndHB4SGlqWGVwUWxla2RjRlh3SWtrMy1hWFU4Zkk3czd0ejhral9ha3FKV3Y5Mk9YNDBmejdTVXc0eDZRdGdORDRENFRIZjdkQzhLTUl0Sl80Z1dRQm9HdGlRTGxDT19xTTV1OVZrbHlGWGV1ZUpEaEh6Z055NHZlTS1vblFhVWJuNm5VWGE2WE5KNElrdGJTbEdMSnJVWTVrMUNrNGE1NU9QaVAwRkwxYUtvMFh4Mm4wRzVPay1EdnVTUjZhV1J1Si1KSHYwYm9DcGVVdmZ1OHZNM3hicWttR21GV3BscHp6VlBpd2ljRTJZaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>A nova joia da Mosaic custa mais de 20.000 € e apenas alguns poucos poderão comprá-la - brujulabike.com</t>
+          <t>Pampa Energia anuncia investimentos de 2,7 Bilhões em fábrica de ureia na argentina - GlobalFert</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>22/07/2026 04:00</t>
+          <t>21/07/2026 20:18</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNdmpIOTJoRUgwbF9JNlpCYXhDTEo2ZGp4aVpSTDNSNkVTWXViMzl5X2xfWmlaUmdkUzNJZnBSU2xjbDJtcmQ4SnJFY2dwOFI1QjREalNCQVQ0YlBUUFNZOS1Gem5xeFhCcjNsNGNyeS1yRG1FeWU0dDZzTVZTWVFDbm5GTEJ1MTBpaEFTeGx0QXFWaWxsOHE3YTc0a2JqUWN4QmM0N0wxRmF0RkY3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOcVVHZE43T3MwdHc2RUc0dWl0T3ExNFNMcGFraTJkeXRJZElYUzZmOXkwSkt5d09oRm92Y1BzU1VzdmN4bFBjRFVTUnRVU1BRTks2emRvWXh1Qm9VaDdTSVFNV2p5TWNpaXZaZVlmRFZCYXF2c0YxZFU3blhrVVB5VUxHOVdkbkl0Q0lVak1MeHRjWjdDeVlCc0Fwd3IyakgwczdXczFLRmRDNUJPR2p3bHRjSlBPd1VTVHZWMGxaNWRTTktoWGc?oc=5</t>
         </is>
       </c>
     </row>
@@ -2140,83 +2140,83 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Escassez global de enxofre paralisa indústria de fertilizantes em Goiás e ameaça mais de 600 empregos - G1</t>
+          <t>Mosaic pode demitir mais 650 funcionários em Catalão por causa da falta de matéria-prima provocada pela guerra no Irã - O Popular</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>22/07/2026 04:00</t>
+          <t>21/07/2026 17:19</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxQazVGaElwb0d2SFd0bjRwZE9yM2E3VEt3UzVZaV9TRUUtNGtsQ2tTS21jbVRNdXk0M3ZQd3Vhc3BtakpoN2JOZEh0UllpNFNNU1RBQVZLb0otVnN0cnRUMHNROTFVYWNzMDJ4bmNIbjhsaGhZZVFDcFllcV9oZ3dFa25HaWdtdDJWQ01jeEllTnRYYi0zMFhfMEJ3ekRuNl8xOTlUN2dWbGdkX1p3NnQ1N2FHbFRUWjJSUlNla3lTSFpFSlV6U2w3QVlrNW1OVm5HVjVtQllSaTN0d3ptWjdObnVSWUY2bDRWUGltadIB-wFBVV95cUxPallYVTZnVk1ndHB4SGlqWGVwUWxla2RjRlh3SWtrMy1hWFU4Zkk3czd0ejhral9ha3FKV3Y5Mk9YNDBmejdTVXc0eDZRdGdORDRENFRIZjdkQzhLTUl0Sl80Z1dRQm9HdGlRTGxDT19xTTV1OVZrbHlGWGV1ZUpEaEh6Z055NHZlTS1vblFhVWJuNm5VWGE2WE5KNElrdGJTbEdMSnJVWTVrMUNrNGE1NU9QaVAwRkwxYUtvMFh4Mm4wRzVPay1EdnVTUjZhV1J1Si1KSHYwYm9DcGVVdmZ1OHZNM3hicWttR21GV3BscHp6VlBpd2ljRTJZaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxOUHB5NHZZVzBfMXAxUUMxNUF2U2QxdVVJYnlXdzE4alNEbU5nRmxoRnhvSzR2WWs4RmF1ZXZOd1pTRmVTeU1iQ1A0QzZ6RjZSZnZlMUNxV0xaOGkycEM5clZrSVNYU2VDMWVYeU1IX0Fid0t5c2xjYnlkM1ZtR2pQOFhLcWV6dkhLckhYcmFQSFByZzlabmV3aWcwVWpEYTQ1Vm04VFRpQjlBMXRYb2hxUkRmSEdfd2poNXhHaUFZbGZfdVoyVEVQWktLRkh6RzhUcFotN0ZGVEcxRi1lQ01meEN6WHZxY0N3Qzd0UFBra00?oc=5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pampa Energia anuncia investimentos de 2,7 Bilhões em fábrica de ureia na argentina - GlobalFert</t>
+          <t>Parceria entre Sindicato de Produtores Rurais de Bragança (PA) e Prefeitura fortalece a agricultura com entrega de calcário e acesso a políticas públicas - Portal CNA Brasil</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>21/07/2026 20:18</t>
+          <t>21/07/2026 10:31</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOcVVHZE43T3MwdHc2RUc0dWl0T3ExNFNMcGFraTJkeXRJZElYUzZmOXkwSkt5d09oRm92Y1BzU1VzdmN4bFBjRFVTUnRVU1BRTks2emRvWXh1Qm9VaDdTSVFNV2p5TWNpaXZaZVlmRFZCYXF2c0YxZFU3blhrVVB5VUxHOVdkbkl0Q0lVak1MeHRjWjdDeVlCc0Fwd3IyakgwczdXczFLRmRDNUJPR2p3bHRjSlBPd1VTVHZWMGxaNWRTTktoWGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxQQllOWWdoRGR5V2xNN2tPakpEcHRwY3BLVFhiUS1nM0h2TFlhUDBqYVk2a0NqYnd4VlpaSktsYzBGV0tQTS1wTE9wam93clY0c0hQUjNIdFgyS3djYnlHMzI0YlRFRGs3MWkxYTg0cGJYZGdWcG02X1BaS1Z0QUlJdGMzY2RjcXRxTk1idS1rcUNzRGh6VmpyMFJvYlBUbDJSVGFROEZUQmt3ZXdTdWFTZ3hUTUxuUkx3TGpOSkFPRHhRYkFQdHNRWldHaWc0OXZwSlhtUnUtcXRTdzNyc0Utd0RyUEVsVDlHU3R4NnBROFFtUk02dW9RUFl0SWJxS1VuaHctT2lmUTdzdmZQVWtNZm5Eaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Mosaic pode demitir mais 650 funcionários em Catalão por causa da falta de matéria-prima provocada pela guerra no Irã - O Popular</t>
+          <t>Ureia valoriza mais de 18% em um mês puxada por demanda e geopolítica - CNN Brasil</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>21/07/2026 17:19</t>
+          <t>21/07/2026 04:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxOUHB5NHZZVzBfMXAxUUMxNUF2U2QxdVVJYnlXdzE4alNEbU5nRmxoRnhvSzR2WWs4RmF1ZXZOd1pTRmVTeU1iQ1A0QzZ6RjZSZnZlMUNxV0xaOGkycEM5clZrSVNYU2VDMWVYeU1IX0Fid0t5c2xjYnlkM1ZtR2pQOFhLcWV6dkhLckhYcmFQSFByZzlabmV3aWcwVWpEYTQ1Vm04VFRpQjlBMXRYb2hxUkRmSEdfd2poNXhHaUFZbGZfdVoyVEVQWktLRkh6RzhUcFotN0ZGVEcxRi1lQ01meEN6WHZxY0N3Qzd0UFBra00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQMGtJYlMwLWUzVkNubGpBZjAzUTNhY1lUWjN0aHd2ZGxVLUxRS0NmbDZIRXJzRFk2VnFCaUVrVFlodHdYSmJzVWZjelV1WFJhVGZOdXVzN083N2xVb24wakFhTjRWUWw5ZGRTeG5PNkt1MVo3T0VNbGxxVUliVUtvRDBaYU1zZU1Rc2VnbHFudUJMaFk4eExyNUhqV0stdXkxRFE3WC1B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Parceria entre Sindicato de Produtores Rurais de Bragança (PA) e Prefeitura fortalece a agricultura com entrega de calcário e acesso a políticas públicas - Portal CNA Brasil</t>
+          <t>Galeria de Patios and Terraces - Dietfurt Limestone Gala - 6 - ArchDaily</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>21/07/2026 10:31</t>
+          <t>20/07/2026 14:37</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxQQllOWWdoRGR5V2xNN2tPakpEcHRwY3BLVFhiUS1nM0h2TFlhUDBqYVk2a0NqYnd4VlpaSktsYzBGV0tQTS1wTE9wam93clY0c0hQUjNIdFgyS3djYnlHMzI0YlRFRGs3MWkxYTg0cGJYZGdWcG02X1BaS1Z0QUlJdGMzY2RjcXRxTk1idS1rcUNzRGh6VmpyMFJvYlBUbDJSVGFROEZUQmt3ZXdTdWFTZ3hUTUxuUkx3TGpOSkFPRHhRYkFQdHNRWldHaWc0OXZwSlhtUnUtcXRTdzNyc0Utd0RyUEVsVDlHU3R4NnBROFFtUk02dW9RUFl0SWJxS1VuaHctT2lmUTdzdmZQVWtNZm5Eaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPa2pndzB2emI5ZFVCRkhWMk9BS3VYeXVsQ2s1U3pZOTJSeHh6ZndXNmpBOUpCbTBqMFRnTWtVMmxENDdoWGtiV0J3cDl4bU02WG5MVHAwMFZGODNtd1NNbWVPcVBsVWs4X0ZXdmYwa2NYNmZfOHNEY3NRalBYalllLUVINnFLelZ6cFIwc3FwTFFJeUFjSk4tX1NUQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2228,17 +2228,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ureia valoriza mais de 18% em um mês puxada por demanda e geopolítica - CNN Brasil</t>
+          <t>Cotações da ureia voltam a ganhar força e acumulam três semanas de alta - Globo Rural</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>21/07/2026 04:00</t>
+          <t>20/07/2026 04:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQMGtJYlMwLWUzVkNubGpBZjAzUTNhY1lUWjN0aHd2ZGxVLUxRS0NmbDZIRXJzRFk2VnFCaUVrVFlodHdYSmJzVWZjelV1WFJhVGZOdXVzN083N2xVb24wakFhTjRWUWw5ZGRTeG5PNkt1MVo3T0VNbGxxVUliVUtvRDBaYU1zZU1Rc2VnbHFudUJMaFk4eExyNUhqV0stdXkxRFE3WC1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPNE43X3FKaDhjVWxiYmRWTGNFb2kyU0hka3lSbzVjQllEVXBmRVh6N3UxdVREQlREYS1fb2wzNTNjcF9BRnI1QU1ZX0VBSDBKRWp1SXo4dkU5ZFdreHJJNVZ4bTNOM1V3ZjJieTFxQnpQSm9wWTJjUmlpU3Y0YXhlamItUmx4MnZuckNBTF8xbWtvQ25VWGo4dVdST1JhS2tWR0MtNHY2XzQ4d1ByUHo1ak5BS0xrZFRRaUlpbWFERnNXV29PS1VLMzNR0gHYAUFVX3lxTE5FeHdzOEpTZzVPeWhxeEhIbGlQMVJiejdsMGlxRnlDcU1vSDhhcXJTcGVDWmtqc0NsTXUwWGhtVzNhLXNZbFhncWc3cWhJZWxaUFpJZ21DTkNZT3p3eVR2aUEzcEFVUkZ4S0QwbEwydmJ6R2tVX2tVUWtXVm1VbVgwX2Y0TkQ5cFB0WWduTWZxcVJwOHc5SzJXSi1PWnV5QUt0LWI4X1ZpVlh2UUo0Zm5udWhzYTl1MXRxOWtwZ1cwVmJUUVRTZFpGc0dmQ0VHZUtKeVFsUjFBNQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Da guerra no Oriente Médio à Mosaic: entenda por que empregos estão em risco em Uberaba - JM Online</t>
+          <t>Com “brisa de otimismo”, mercado de fertilizantes reage, mas ainda corre contra o tempo - AgFeed</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNbHZvTzRTZHlrTHpsQmFFV0k2Qi0wWTh1SXhHN0pvcDgwUzVHRGFVVzc4bXNSeHJLRGlwQzkzRWxtYVJERFBReVlRaC1paTNIRHN0YWVhc0QxQnJyaXBrdzhqeWdtSzZ6Vk1jaU9SZ0VNMkc3UHg0YlRVdmtFNVZWT0tybTdRUm9STWt4SlBKM0ktLXZ2SVRtb3ZYaC1ZV2VSQ0NqMWoyVmROQUVBNDNyazNmLTFvc3l3M2JzWDlKUHlaUmdM0gHMAUFVX3lxTE1qQkF4YVY1VXNFRjdHSllUaTJOM0c2V3V4Y1dYYWJyWmFDOXlJWXZVaEd1MWxhS185REZyc3owaHA5NjlrSzNSdC0wc3hzOXBkQ2xrMnRPcFZ6ZUFHYXlxcDQ4eUxBSU12Z2luVVNFRVMyRGx6SnJxeXVwQmhKT0FSODNWZVVPekNqVlM4aUVWSE5iTHRiRHl6RklWMkRGTXQzVW5YN1VBS0YtUERfeWlLX3hsNk1nZGJUc3diRTBqZ3ZLWmNjMWpKNWkxQw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPVVh2bHF6bEVibGowdkxud1piX1FVWEpHWTVpLXNWUW80eU92UXVUdElvOFlJMEVRaDcwckhLZmtQcmJnOElrU1RlSEhKeEZzRjRzRmJHZW1Cb3BqOG9KR2FoeTZQNVM1b1l4aUZvVmhCeTBfQ2Q1ZndnbEFOLUkwQ1YwYXd3ZGw0cExzR2w5bVNsNG9zODh1bkVad2pZdFpodmdEbFVIcGtYSnlHLTU2S1hQem92QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Com “brisa de otimismo”, mercado de fertilizantes reage, mas ainda corre contra o tempo - AgFeed</t>
+          <t>Da guerra no Oriente Médio à Mosaic: entenda por que empregos estão em risco em Uberaba - JM Online</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2304,161 +2304,161 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPVVh2bHF6bEVibGowdkxud1piX1FVWEpHWTVpLXNWUW80eU92UXVUdElvOFlJMEVRaDcwckhLZmtQcmJnOElrU1RlSEhKeEZzRjRzRmJHZW1Cb3BqOG9KR2FoeTZQNVM1b1l4aUZvVmhCeTBfQ2Q1ZndnbEFOLUkwQ1YwYXd3ZGw0cExzR2w5bVNsNG9zODh1bkVad2pZdFpodmdEbFVIcGtYSnlHLTU2S1hQem92QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNbHZvTzRTZHlrTHpsQmFFV0k2Qi0wWTh1SXhHN0pvcDgwUzVHRGFVVzc4bXNSeHJLRGlwQzkzRWxtYVJERFBReVlRaC1paTNIRHN0YWVhc0QxQnJyaXBrdzhqeWdtSzZ6Vk1jaU9SZ0VNMkc3UHg0YlRVdmtFNVZWT0tybTdRUm9STWt4SlBKM0ktLXZ2SVRtb3ZYaC1ZV2VSQ0NqMWoyVmROQUVBNDNyazNmLTFvc3l3M2JzWDlKUHlaUmdM0gHMAUFVX3lxTE1qQkF4YVY1VXNFRjdHSllUaTJOM0c2V3V4Y1dYYWJyWmFDOXlJWXZVaEd1MWxhS185REZyc3owaHA5NjlrSzNSdC0wc3hzOXBkQ2xrMnRPcFZ6ZUFHYXlxcDQ4eUxBSU12Z2luVVNFRVMyRGx6SnJxeXVwQmhKT0FSODNWZVVPekNqVlM4aUVWSE5iTHRiRHl6RklWMkRGTXQzVW5YN1VBS0YtUERfeWlLX3hsNk1nZGJUc3diRTBqZ3ZLWmNjMWpKNWkxQw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cotações da ureia voltam a ganhar força e acumulam três semanas de alta - Globo Rural</t>
+          <t>Mosaic pode demitir mais 650 trabalhadores em Catalão - O Popular</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>20/07/2026 04:00</t>
+          <t>19/07/2026 22:37</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPNE43X3FKaDhjVWxiYmRWTGNFb2kyU0hka3lSbzVjQllEVXBmRVh6N3UxdVREQlREYS1fb2wzNTNjcF9BRnI1QU1ZX0VBSDBKRWp1SXo4dkU5ZFdreHJJNVZ4bTNOM1V3ZjJieTFxQnpQSm9wWTJjUmlpU3Y0YXhlamItUmx4MnZuckNBTF8xbWtvQ25VWGo4dVdST1JhS2tWR0MtNHY2XzQ4d1ByUHo1ak5BS0xrZFRRaUlpbWFERnNXV29PS1VLMzNR0gHYAUFVX3lxTE5FeHdzOEpTZzVPeWhxeEhIbGlQMVJiejdsMGlxRnlDcU1vSDhhcXJTcGVDWmtqc0NsTXUwWGhtVzNhLXNZbFhncWc3cWhJZWxaUFpJZ21DTkNZT3p3eVR2aUEzcEFVUkZ4S0QwbEwydmJ6R2tVX2tVUWtXVm1VbVgwX2Y0TkQ5cFB0WWduTWZxcVJwOHc5SzJXSi1PWnV5QUt0LWI4X1ZpVlh2UUo0Zm5udWhzYTl1MXRxOWtwZ1cwVmJUUVRTZFpGc0dmQ0VHZUtKeVFsUjFBNQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOWC0wUm16Y1hGUHdCR2JRdnhOT0JyM3UxQ2tlVndJQVhDVWw5cU1WdlNIWnpFdzVpNDlrb294TFB5MERjbnZrZVpOOVMyOUtwRXZVNWJoakRQYlc2Z1lwYV9RaFhBbTZ2WFFnc2E0LTZ4UXg0NlFvVHB4c0JPQ0czam5YdTEwRmlqVnEtUi0tOC1MOFRtaWh1MW9zTHA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Mosaic pode demitir mais 650 trabalhadores em Catalão - O Popular</t>
+          <t>Ergueram pilares de calcário de até 5,5 metros há 11.500 anos, quando a agricultura ainda começava a transformar a vida humana - revistaoeste.com</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>19/07/2026 22:37</t>
+          <t>19/07/2026 04:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOWC0wUm16Y1hGUHdCR2JRdnhOT0JyM3UxQ2tlVndJQVhDVWw5cU1WdlNIWnpFdzVpNDlrb294TFB5MERjbnZrZVpOOVMyOUtwRXZVNWJoakRQYlc2Z1lwYV9RaFhBbTZ2WFFnc2E0LTZ4UXg0NlFvVHB4c0JPQ0czam5YdTEwRmlqVnEtUi0tOC1MOFRtaWh1MW9zTHA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQMHFxcXZoN2VHVEtqVWMtMXR0Tm5RX2dqZnJsT21XZUJnRW1qX0h2dUxoNzcyUUZGQ2ZvY1Fzd0lsTlk3MDdVMnBTSk5jbGJfY2VRSGFScnoyS0dybGlpME1odk9ZdGJSV3lNUkN5VUItTHZUdGVObFV2R01UbzZGUXRMUl9iMVB1LUh4X2JTZU9fSjA5aW04bHI5YldvT1Q1NFpsZFkyRGRQQTgzVko4elVBODRsbWhTeXdpVFRjX195WTE5NVFOclNBV0VOSmVLRG5IZlk2NWtuMEFkVTMzYVB2aHBwb2NpTkw1dGxWbkdLa2loekxXS0J4NjBMemhSUkE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Murang'a county distributes lime to coffee farmers to boost production</t>
+          <t>Na China, um sumidouro de 192 metros esconde árvores de 40 metros e três cavernas sob uma paisagem de calcário - revistaoeste.com</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>19/07/2026 13:59</t>
+          <t>18/07/2026 04:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a708df9e25249dbab0f0f4f5ec02cba&amp;url=https%3a%2f%2fwww.standardmedia.co.ke%2fsmart-harvest%2farticle%2f2001553298%2fmuranga-county-distributes-lime-to-coffee-farmers-to-boost-production&amp;c=8181289782834766550&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOaXc5OTRzUXRXT1o0cFpOZE9jbnoyVUpVTzZ6QzBaaFZVNVZfbDJ0YnA5RHNTdmFrMmlTUWNGbHNqQ1ZoY0hpZE53U3EyVEJQU2RDMUtzYUs0c0Q3aG9FTl9RaWlFVUY0cjA5RlFPZGM4anVmeDRYdlhQQ05WRnZNNXFsQ2x1eGxfcU1sS0F6X0RCRjVHOWhwYWZQdUdGN2tQQWF0QU9xZnAxM3JqQjFYUUtILVRaSW8yQlMwQVBRa3VCWWFBdWVrc0dURTY0OUhydGt2WUs5Y3NkRjhjUWVidzVKVGVsaTRlY0VyVS1R?oc=5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ergueram pilares de calcário de até 5,5 metros há 11.500 anos, quando a agricultura ainda começava a transformar a vida humana - Revista Oeste</t>
+          <t>Galeria de Flooring and Wall Tiles - Dietfurt Limestone - 7 - ArchDaily</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>19/07/2026 04:00</t>
+          <t>18/07/2026 01:44</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQMHFxcXZoN2VHVEtqVWMtMXR0Tm5RX2dqZnJsT21XZUJnRW1qX0h2dUxoNzcyUUZGQ2ZvY1Fzd0lsTlk3MDdVMnBTSk5jbGJfY2VRSGFScnoyS0dybGlpME1odk9ZdGJSV3lNUkN5VUItTHZUdGVObFV2R01UbzZGUXRMUl9iMVB1LUh4X2JTZU9fSjA5aW04bHI5YldvT1Q1NFpsZFkyRGRQQTgzVko4elVBODRsbWhTeXdpVFRjX195WTE5NVFOclNBV0VOSmVLRG5IZlk2NWtuMEFkVTMzYVB2aHBwb2NpTkw1dGxWbkdLa2loekxXS0J4NjBMemhSUkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxPZVRlQ1V1aUlpcmFSQ0ZIOWU3S1JSM2xNWDhwazQ3cmx1MHQ4aWt2dFc4a1pNbmNDNWJCUkR4RXZ1T1NEYkRpVVpkN3pyRnVXdmNZejhyRmtJcTFROTYtQjRqYnBkSkZ3ODBFSlNFVngtOXNqTDJBYmt5Si10YmVUT01pdWtNSFkwR3RYZVJ1TTk0X2ljeXRMRW1nVGgwTjNNYUUzeFdXR3p5NEc3Sk9pbHBMREl3eV8yZVlDc0dIdXBRVjRTQUtyZ2tsa3FXZDdsZW45NDFOOVBMOXdkakFKYklRdDlUWmtRUTNVMnY3R3NQNTZkRFE1N1VDRWRrRWNoQ1Q2T2ln?oc=5</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Na China, um sumidouro de 192 metros esconde árvores de 40 metros e três cavernas sob uma paisagem de calcário - Revista Oeste</t>
+          <t>Melhora no poder de compra de fertilizantes - GlobalFert</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>18/07/2026 04:00</t>
+          <t>17/07/2026 20:47</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOaXc5OTRzUXRXT1o0cFpOZE9jbnoyVUpVTzZ6QzBaaFZVNVZfbDJ0YnA5RHNTdmFrMmlTUWNGbHNqQ1ZoY0hpZE53U3EyVEJQU2RDMUtzYUs0c0Q3aG9FTl9RaWlFVUY0cjA5RlFPZGM4anVmeDRYdlhQQ05WRnZNNXFsQ2x1eGxfcU1sS0F6X0RCRjVHOWhwYWZQdUdGN2tQQWF0QU9xZnAxM3JqQjFYUUtILVRaSW8yQlMwQVBRa3VCWWFBdWVrc0dURTY0OUhydGt2WUs5Y3NkRjhjUWVidzVKVGVsaTRlY0VyVS1R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNY0VhZGVublZBbnlpeHVObmRmeXV0dzlUT0FwXzZBSzNqUWh5U3FqMThXOXY0UW81X09wanNPWk9FVk4tU2lhcmFwQWdtR1FYTjk4eG1SdE9XM3NFWkxTRGRjcGJ2RVdpcm9NMTRXTUlGazdWbkJydWVsUXgwWTZOcGNFQUhBQ0haTzRFOEJTSml2U1U?oc=5</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Galeria de Flooring and Wall Tiles - Dietfurt Limestone - 7 - ArchDaily</t>
+          <t>Bolsa de qualificação pode evitar demissões na Mosaic - JM Online</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>18/07/2026 01:44</t>
+          <t>17/07/2026 20:39</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxPZVRlQ1V1aUlpcmFSQ0ZIOWU3S1JSM2xNWDhwazQ3cmx1MHQ4aWt2dFc4a1pNbmNDNWJCUkR4RXZ1T1NEYkRpVVpkN3pyRnVXdmNZejhyRmtJcTFROTYtQjRqYnBkSkZ3ODBFSlNFVngtOXNqTDJBYmt5Si10YmVUT01pdWtNSFkwR3RYZVJ1TTk0X2ljeXRMRW1nVGgwTjNNYUUzeFdXR3p5NEc3Sk9pbHBMREl3eV8yZVlDc0dIdXBRVjRTQUtyZ2tsa3FXZDdsZW45NDFOOVBMOXdkakFKYklRdDlUWmtRUTNVMnY3R3NQNTZkRFE1N1VDRWRrRWNoQ1Q2T2ln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdDRaT2xrcWlGbVdCNTZYcVNOVEt0Sm9vSHNGOVdReWFsOUhrV0pYdjZ4MkRFSWQ3LUFkVmUxelQ1eTA1Z3Rqel9SLUxRYkQ5dng1V2pxSEhsbTJwWE9aMnI4dC1ueE8yWlZRbVVJRUluY21wQlk2azN6bUU3eEpTeFUwNXhZMTkzOHk3aGJjQkxsbkdGaFJZNUl2QdIBowFBVV95cUxNQkhuT3ZUMy1Qemh6NVRtazBZUmJ4SXg4WDZiaFhXMFY5WkJkc1ZiVUlLUWpteGdpVDc5YjhjdW1RejlyVUlrX0JacGFtLTctSWc2M09ta21ISlJTeVl2WGh5bFUtTTlfM004LTNwZ0M5UV9SRXBmb1NXVExmc3ZsYmJoclN5SzFMUEpfcGhaLXRJbGllQkZrdXcxSjVfVTNoRVdR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Melhora no poder de compra de fertilizantes - GlobalFert</t>
+          <t>Transporte de calcário ficará temporariamente suspenso a partir de agosto - Prefeitura de Sidrolândia</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>17/07/2026 20:47</t>
+          <t>17/07/2026 10:55</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNY0VhZGVublZBbnlpeHVObmRmeXV0dzlUT0FwXzZBSzNqUWh5U3FqMThXOXY0UW81X09wanNPWk9FVk4tU2lhcmFwQWdtR1FYTjk4eG1SdE9XM3NFWkxTRGRjcGJ2RVdpcm9NMTRXTUlGazdWbkJydWVsUXgwWTZOcGNFQUhBQ0haTzRFOEJTSml2U1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQckh6Yk1FVUpxQ2w3LTd3RENtblNmNFZ0ekd0TFNYUlI4blJwampSZ0FINEdOSlVMd1hYT1N2aW8tS1BGSGFFV25qWHpCZEt4VzV2bWJYMC04eVRXWDlXZDlYS3N4b3VndDhYZVhHQW9fMGQtdUxBUVBVQmQ2RklETUlRaFVHbFMza0lsaU80SFUyV1IwOElvdGNWbXk3TXFVVEszUjVnQ0hacmhoTk9aOTVPV3ZYUkl2M1IzazEzQ05WQ2FaWFBLNWhDdW5FbEJqM1RLSC1MZ185ZlFacFJsRmNjVllUc2l0N3c?oc=5</t>
         </is>
       </c>
     </row>
@@ -2470,17 +2470,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bolsa de qualificação pode evitar demissões na Mosaic - JM Online</t>
+          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 12 - ArchDaily</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>17/07/2026 20:39</t>
+          <t>17/07/2026 10:47</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdDRaT2xrcWlGbVdCNTZYcVNOVEt0Sm9vSHNGOVdReWFsOUhrV0pYdjZ4MkRFSWQ3LUFkVmUxelQ1eTA1Z3Rqel9SLUxRYkQ5dng1V2pxSEhsbTJwWE9aMnI4dC1ueE8yWlZRbVVJRUluY21wQlk2azN6bUU3eEpTeFUwNXhZMTkzOHk3aGJjQkxsbkdGaFJZNUl2QdIBowFBVV95cUxNQkhuT3ZUMy1Qemh6NVRtazBZUmJ4SXg4WDZiaFhXMFY5WkJkc1ZiVUlLUWpteGdpVDc5YjhjdW1RejlyVUlrX0JacGFtLTctSWc2M09ta21ISlJTeVl2WGh5bFUtTTlfM004LTNwZ0M5UV9SRXBmb1NXVExmc3ZsYmJoclN5SzFMUEpfcGhaLXRJbGllQkZrdXcxSjVfVTNoRVdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOVG5QeHc1MVllRXpLZGR1REtSVWZxMi12LUdudEh5My1CN3lKc1dCd0U4SFdjWTE1RWF1cUJYbk5ZTEppUkkycm45U3VSRldONnFLV3RONGFTZG5XS2ZWdkIwNjJVeEFLRGdleGU5ZWFoeWpyTzNZN0tCQ2NCM3BJWl9laF9kVG5BcmVVVWp1RnFjOEhXYTNqSFJCN0NJMkxSa09lZldnUHhma052SDAzNlJLSFQ0bkUyUWJGYU1kZHhyemJpd2N4ZlZwcDE?oc=5</t>
         </is>
       </c>
     </row>
@@ -2492,171 +2492,171 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Transporte de calcário ficará temporariamente suspenso a partir de agosto - Prefeitura de Sidrolândia</t>
+          <t>Galeria de Casa de Calcário / Archer + Braun - 47 - ArchDaily</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>17/07/2026 10:55</t>
+          <t>17/07/2026 08:01</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQckh6Yk1FVUpxQ2w3LTd3RENtblNmNFZ0ekd0TFNYUlI4blJwampSZ0FINEdOSlVMd1hYT1N2aW8tS1BGSGFFV25qWHpCZEt4VzV2bWJYMC04eVRXWDlXZDlYS3N4b3VndDhYZVhHQW9fMGQtdUxBUVBVQmQ2RklETUlRaFVHbFMza0lsaU80SFUyV1IwOElvdGNWbXk3TXFVVEszUjVnQ0hacmhoTk9aOTVPV3ZYUkl2M1IzazEzQ05WQ2FaWFBLNWhDdW5FbEJqM1RLSC1MZ185ZlFacFJsRmNjVllUc2l0N3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPV2xkLU53eUItRGo4bkM0Wmxnb1Z4Vkt1bWgxVjcwLVlYaTVWSXFsVDBHOVU0QTJnOUNVLXNvNUtuRkt6QkFDcmY1dWZnSGJvRXpUMXBhNDhnVmd5QW1oU3hKZUZDWVZJell5Y2pOODhLNi1FNk5LWktQTEdEcEhCZjlVX2ZJTldaNW10dTlrS1hDX3pmQUZFMEpOQ1ZHUmZlbEQ2X0I4SjhQRThJR3piNnRYNXBudUI2SHUzb2F5bmFfc25WaHFOQ1lXZmJ5dmQ1d1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 12 - ArchDaily</t>
+          <t>Ibram alerta Fazenda sobre ‘escassez crítica’ de enxofre frente à guerra no Irã - Agência iNFRA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>17/07/2026 10:47</t>
+          <t>17/07/2026 04:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOVG5QeHc1MVllRXpLZGR1REtSVWZxMi12LUdudEh5My1CN3lKc1dCd0U4SFdjWTE1RWF1cUJYbk5ZTEppUkkycm45U3VSRldONnFLV3RONGFTZG5XS2ZWdkIwNjJVeEFLRGdleGU5ZWFoeWpyTzNZN0tCQ2NCM3BJWl9laF9kVG5BcmVVVWp1RnFjOEhXYTNqSFJCN0NJMkxSa09lZldnUHhma052SDAzNlJLSFQ0bkUyUWJGYU1kZHhyemJpd2N4ZlZwcDE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQWVlDSXJhUjhBLXJpZ0pnVFJEYm1FbjNpeVkxX3RnR20tZXNLOUZFWHVWVWdBekVYOXh2cGpJVEtodmtjSnRKR2VKWWpkeHpEbDQ4S0dXS19WNHdPWkdJMDNodkVTUllxLVhEV1lMVkxMUmZFWWlETm5uQlZaRVZFRXRva0sxOUFGVzB4Mnl4a1RuM3djY01YX0hYSDYzaWpIaVhzRjdyZ09ERE8z?oc=5</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Galeria de Casa de Calcário / Archer + Braun - 47 - ArchDaily</t>
+          <t>Índia aprova nova política de investimentos em ureia - GlobalFert</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>17/07/2026 08:01</t>
+          <t>16/07/2026 20:53</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPV2xkLU53eUItRGo4bkM0Wmxnb1Z4Vkt1bWgxVjcwLVlYaTVWSXFsVDBHOVU0QTJnOUNVLXNvNUtuRkt6QkFDcmY1dWZnSGJvRXpUMXBhNDhnVmd5QW1oU3hKZUZDWVZJell5Y2pOODhLNi1FNk5LWktQTEdEcEhCZjlVX2ZJTldaNW10dTlrS1hDX3pmQUZFMEpOQ1ZHUmZlbEQ2X0I4SjhQRThJR3piNnRYNXBudUI2SHUzb2F5bmFfc25WaHFOQ1lXZmJ5dmQ1d1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOeUZvQlZWVTlrTnNwbkkwZnVGT3hZYlNEWjhCeEVxR21OOU5aV2YwdmoxUHV4X0Yycm1LSGlHYkp3S1F5NkRaZFUyTEpBdmNaemJhSFB0WXFYNmU1c194SFZtaXBlQlF5d2Z3a0ltOThHbXVNSGxvLXdXT2JfT2hkZUs3ZHF0MUFodzJPdW5WSzVlQk1rZzlyNGZuNmY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ibram alerta Fazenda sobre ‘escassez crítica’ de enxofre frente à guerra no Irã - Agência iNFRA</t>
+          <t>Esqueça o asfalto comum: asfalto com caroços de azeitona captura carbono em Barcelona, substitui calcário por biochar e promete reduzir 76% da pegada climática sem perder resistência ao calor, à umidade, às fissuras e ao tráfego urbano, abrindo caminh - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>17/07/2026 04:00</t>
+          <t>16/07/2026 04:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQWVlDSXJhUjhBLXJpZ0pnVFJEYm1FbjNpeVkxX3RnR20tZXNLOUZFWHVWVWdBekVYOXh2cGpJVEtodmtjSnRKR2VKWWpkeHpEbDQ4S0dXS19WNHdPWkdJMDNodkVTUllxLVhEV1lMVkxMUmZFWWlETm5uQlZaRVZFRXRva0sxOUFGVzB4Mnl4a1RuM3djY01YX0hYSDYzaWpIaVhzRjdyZ09ERE8z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxOVkZzaEljMWxZcmVQc1hIWGVDY095R1ZNbk9aQUswNENKME5IQnc4d21nNm1KUWxGYk80Y1dLSUJLd1lONERoc21RNFRHTGRUN0huRXYzQXFfMjJvTzlYcmIxRWxLY3BZemxZaVZHRl9sVDJUZlVYdGxmS0dnQXpfRFhPR1R4RTRVcERfbWhZdVE3T0ZtREJpUU9uR2pjbjRVQzM2TGZjX3B0ZDVHZWd4YzZ1Vm5nZV9vT2ZsbmZPZ3ZiNm5VVmMwQUtwb3REcVktalFMc011LXhTT1p3dng3Q0NfNmRhcG5MVFFEcmNjeVB6VG0yWTJhQ3haTlFjVEI3NGdnWVBDaG93OTBKamR3SXU0akx1UFJxQnJOMFRncE5vSHVNOGRDc2tEbERBNkEtd09HbVVnNXBXdS1qWEJaaWQwZ1NLZjg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Índia aprova nova política de investimentos em ureia - GlobalFert</t>
+          <t>Preço do enxofre importado pelo Brasil entre 2020 e junho de 2026 - Farmnews</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>16/07/2026 20:53</t>
+          <t>16/07/2026 04:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOeUZvQlZWVTlrTnNwbkkwZnVGT3hZYlNEWjhCeEVxR21OOU5aV2YwdmoxUHV4X0Yycm1LSGlHYkp3S1F5NkRaZFUyTEpBdmNaemJhSFB0WXFYNmU1c194SFZtaXBlQlF5d2Z3a0ltOThHbXVNSGxvLXdXT2JfT2hkZUs3ZHF0MUFodzJPdW5WSzVlQk1rZzlyNGZuNmY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQNXZMb055LVlJVzBzMmRkX2xrNUNpZHREU0NjUGUxR2wtNmU1a3RNaEZNdzVMd2lzaDUwMDNjanpZbjVLck9wX2RmdFk0UnNvWGJtdjFLcEtrUVdjNm14MXR1N1U0RWdyUTNjNWsySm5DUjBnWHFXUWJxNGloMmlmbkpRQWlCbW9RLTRzSkdxcGxUZjJCVTBfVldOV0xOQllmTGVrMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Preço do enxofre importado pelo Brasil entre 2020 e junho de 2026 - Farmnews</t>
+          <t>Galeria de Revestimiento porcelánico estilo piedra - Limestone - 1 - ArchDaily</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>16/07/2026 04:00</t>
+          <t>16/07/2026 02:55</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQNXZMb055LVlJVzBzMmRkX2xrNUNpZHREU0NjUGUxR2wtNmU1a3RNaEZNdzVMd2lzaDUwMDNjanpZbjVLck9wX2RmdFk0UnNvWGJtdjFLcEtrUVdjNm14MXR1N1U0RWdyUTNjNWsySm5DUjBnWHFXUWJxNGloMmlmbkpRQWlCbW9RLTRzSkdxcGxUZjJCVTBfVldOV0xOQllmTGVrMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQOWo3UnlLclN0X1FmSmlMSHFyR01tdERWeFhhcUZyTUZYTFhqaUFUZUszQkNLbVdlUC1nMF9IYy1PMkk5cmRlaFFoVDFPVTdrWUItekFIbkc1dnNMejdJZjdxckRtVGlPajJ0bGRuY09xZWNUZzZISXk0cG5GS2NPaUU4c201VlZGWGIzRm16ZHRzLU1vOXNfNFMyczVNMF93aWh4UGs4c2VtMElWYV9qU0JXcUpsdVhNdkctWQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Galeria de Revestimiento porcelánico estilo piedra - Limestone - 1 - ArchDaily</t>
+          <t>Inscrições abertas para programa de transporte de calcário - Prefeitura de São José dos Campos</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>16/07/2026 02:55</t>
+          <t>15/07/2026 16:02</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQOWo3UnlLclN0X1FmSmlMSHFyR01tdERWeFhhcUZyTUZYTFhqaUFUZUszQkNLbVdlUC1nMF9IYy1PMkk5cmRlaFFoVDFPVTdrWUItekFIbkc1dnNMejdJZjdxckRtVGlPajJ0bGRuY09xZWNUZzZISXk0cG5GS2NPaUU4c201VlZGWGIzRm16ZHRzLU1vOXNfNFMyczVNMF93aWh4UGs4c2VtMElWYV9qU0JXcUpsdVhNdkctWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQTUp6cUdvLVg1dzUwM09XdVNwdjBXZjZsQ19EWk9iWlFPWHNyclc2SDJXbW4teFRqcGFQN2tRVXBuOFZjMDYwUE9wRldmdzlVclozN1cydWdnTjJQQnRTaEJielBIa3ZJNFZrWERtRHpoR25JWnliSXRmeUZ1YnN1WlpHemhhWENnZVVlYlc5RkhaV0JLSVhGZ29UR0FjRVdWRUx4bUQ4ZE43NFRr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Inscrições abertas para programa de transporte de calcário - Prefeitura de São José dos Campos</t>
+          <t>Coco ralado com excesso de enxofre: quais os riscos? Em quais sintomas prestar atenção? - Estadão</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>15/07/2026 16:02</t>
+          <t>14/07/2026 19:16</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQTUp6cUdvLVg1dzUwM09XdVNwdjBXZjZsQ19EWk9iWlFPWHNyclc2SDJXbW4teFRqcGFQN2tRVXBuOFZjMDYwUE9wRldmdzlVclozN1cydWdnTjJQQnRTaEJielBIa3ZJNFZrWERtRHpoR25JWnliSXRmeUZ1YnN1WlpHemhhWENnZVVlYlc5RkhaV0JLSVhGZ29UR0FjRVdWRUx4bUQ4ZE43NFRr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQQ203UGF1QlY0cDdHcXY1bFpSazZmZG1VbXR1ZkRHcTFqX0UtYUdLLTRDR2Q3anBfYlpBZ1lBUnhjM2x0TFkzWTdnRm5QZDQtbzlRcHRpR0d6TWliQ1dTSkZBSUxYMmhoZldSZ2RZZDZLWUZ4NmxLUlRITlNObUxOLTc2UzdqTVRTdE1DSVY0d0xxeHlVSEdFbXNiNnBQcmhSYTVmbkFBc19FMzBJQ2g0SXY5VDBDclBxYVZFZUxtanlHaGtGS2FJVG9wUTdBTVduVUJqSzd4ZHNHcUcyVUJHaUx6bzc?oc=5</t>
         </is>
       </c>
     </row>
@@ -2668,61 +2668,61 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Coco ralado com excesso de enxofre: quais os riscos? Em quais sintomas prestar atenção? - Estadão</t>
+          <t>Anvisa manda recolher lote de coco ralado ‘Casa de Mãe’, da marca Qualicoco, por excesso de enxofre - Estadão</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>14/07/2026 19:16</t>
+          <t>14/07/2026 15:20</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQQ203UGF1QlY0cDdHcXY1bFpSazZmZG1VbXR1ZkRHcTFqX0UtYUdLLTRDR2Q3anBfYlpBZ1lBUnhjM2x0TFkzWTdnRm5QZDQtbzlRcHRpR0d6TWliQ1dTSkZBSUxYMmhoZldSZ2RZZDZLWUZ4NmxLUlRITlNObUxOLTc2UzdqTVRTdE1DSVY0d0xxeHlVSEdFbXNiNnBQcmhSYTVmbkFBc19FMzBJQ2g0SXY5VDBDclBxYVZFZUxtanlHaGtGS2FJVG9wUTdBTVduVUJqSzd4ZHNHcUcyVUJHaUx6bzc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPYlAteXhKQmc0VXRFcE5jcWZGbkxlZzVJRXd2V3FiWHN3VkJfU2J3cFVZZVFRQ1dvSXZ4VE1VY0FjbS1EanN1c1ZXa1lMLU84RGx6cG1TTHdJNHR1UDEwYnZoV2pMREFmd3V5V0UyY3BuLVBQMnVNUEtqb0tFTGpKT0Z1S0RJeU5RZ1VFdF8tbXdPNTdMVFlQQzBVMldOZ3FOa3RRa053QXc4ZXNWWlcyWFk1YmI1a3lsVkFrZ1JDSFZKU1hMOHpENjltVUZrWUFYT1dEWGl6S2JKQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado ‘Casa de Mãe’, da marca Qualicoco, por excesso de enxofre - Estadão</t>
+          <t>Mosaic reduz produção de fertilizantes em sete unidades no Brasil e pressiona custos do agro - Economic News Brasil</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>14/07/2026 15:20</t>
+          <t>14/07/2026 07:17</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPYlAteXhKQmc0VXRFcE5jcWZGbkxlZzVJRXd2V3FiWHN3VkJfU2J3cFVZZVFRQ1dvSXZ4VE1VY0FjbS1EanN1c1ZXa1lMLU84RGx6cG1TTHdJNHR1UDEwYnZoV2pMREFmd3V5V0UyY3BuLVBQMnVNUEtqb0tFTGpKT0Z1S0RJeU5RZ1VFdF8tbXdPNTdMVFlQQzBVMldOZ3FOa3RRa053QXc4ZXNWWlcyWFk1YmI1a3lsVkFrZ1JDSFZKU1hMOHpENjltVUZrWUFYT1dEWGl6S2JKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQdWlnLW42MkVwbEVHUUc2LXRpQUhhYjJCbzM5VzE4S0xxcDdrRlptQ1h1YkZDVFJ0SkxzOFN5WS05eVdiZ3FMR2VJdEIyeFpzckJvb1pHZnJRZV9fbEZwakdLTWdGS2Q1NVN3bWIwTmN3MUxJNXNvaWVjTHl1VGdqUWxYaVdpWFU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Mosaic reduz produção de fertilizantes em sete unidades no Brasil e pressiona custos do agro - Economic News Brasil</t>
+          <t>Caminhão sai com fertilizante e chega com calcário; caso é investigado pela Polícia Civil - JM Online</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>14/07/2026 07:17</t>
+          <t>14/07/2026 07:13</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQdWlnLW42MkVwbEVHUUc2LXRpQUhhYjJCbzM5VzE4S0xxcDdrRlptQ1h1YkZDVFJ0SkxzOFN5WS05eVdiZ3FMR2VJdEIyeFpzckJvb1pHZnJRZV9fbEZwakdLTWdGS2Q1NVN3bWIwTmN3MUxJNXNvaWVjTHl1VGdqUWxYaVdpWFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQdWY0Z2sxNlFFZ1pzd1pBSDJPLTRyWVR4ZGJiSy1vLS1fRUY4azdOOEJTdlJzYkkwaFBmX0dtWk10TEdkVlRKdmQxYTgxMDhRc3lxeTR1R2J1NVNub1FuRFZwMDRZcnBkRzJVTWpCTGtOYWNKVGw4SFhXQW56NS1peUdhbHZOMU81QjBsNUt3WWlJUnc0QXVadlk2eUdFUVREdzc2ZWNVdm1ReTZVRzZMZDl3MzhiS2RuZFIzV2k3RTBQZTFhaW9JRNIB0AFBVV95cUxPdzREdE1BVFdYdHRvbk5kOG05ams1aHR5R1hEX0xkckRCMVJyNm5ucG9ZcjRwS2prTllwdzdLcnU2WmFFQU05QmgyS09Fbzh1VFptZFgzcjBHOFBOemNfR3doUDBmTHJtaFdydzJISHpHM0NueTNjRDRwcDhRNEliX0M4QVBKaDlyaDZaYnRJOERXelpLRzdVTklQWVgwaVlZODFPcmFlRnJpdjRBWk9NRkhSZmZudHI3eGpqS0ZxS3o2cjl6Z1FER2FLLW9FcThM?oc=5</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Guerra no Irã: empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - G1</t>
+          <t>Mosaic prorroga paralisação da unidade de Catalão por falta de enxofre - Badiinho</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2744,19 +2744,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTUZhRXRNY2trQVZ1YkFrZTVzNEdyX0xBSkZOdGduN080THhRLWNrRzNRV2piY1hPSkNOaDZxcWh0a2NnNzZOR2hGeHR4Rkh2QjdVNDlDdXhlcFhlRVB5R0JEUHp4c1lhRFh6bmdJdWlRU1h1WEhkQ2VONEhrUWZBVnRJRl81SE1sN0Z3dGx6dGxTd2NDUzYxM01oVHdKTVRVMDlXZXMxZmF0SnFrTjNPUjZtZlRtamVwTmZxaG1SLWtMYWxaa1E3OEVFTlBkQkRQb2ZIQ1AtSkdPVXRwQUN4aHBtdmZXVnNQYUtydUxzeXTSAf8BQVVfeXFMUEtWemJJN0VvVFA5R2c0WE43dWdwQW1qaXZBMGZzdUlzVWc3NXI1LWE1cE9ZT05Fb2JRbVAxdUdVSHZhWVpwa2VDU0NVbFBSNHVZZnNFZVdQN0loOVlUeUtKMll4d2xLclh3dXhTYVZSM3dHNXBSWXNMUGhydEcwYU1Lc1B5RHU4cEpQclFNNEZMZXZjeUp6QjVCc3l2anp4Ymw0M0VmNU9kQ2hlaUMtZ1c4VTg5eWF2eXhoMXh0UERTSUdORlcwQ0hCUDZTd21GUEdVYVM4aEFVTi1mWUxzbVZyUnhQdGhfcF9wdmxzSUtDYmh1dGVqX0pFa1g2QnFV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBodUloejIyYmJxUW80NXhoTVUzaXZFMklTTjc1NnRHMzZDZGJOUkVtWUFXT25IWVFwd3o3RGdEeVItVi13ZDdLRk85ZEZHS0t2MFFFMk8xdDQ0VEJRZUc1elhPcHNJcjBzQlBtdUhvLVoxQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Caminhão sai com fertilizante e chega com calcário; caso é investigado pela Polícia Civil - JM Online</t>
+          <t>Parceria investirá R$ 320 mil para pesquisa de solo na UEMS de Cassilândia - Midiamax</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2766,19 +2766,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQdWY0Z2sxNlFFZ1pzd1pBSDJPLTRyWVR4ZGJiSy1vLS1fRUY4azdOOEJTdlJzYkkwaFBmX0dtWk10TEdkVlRKdmQxYTgxMDhRc3lxeTR1R2J1NVNub1FuRFZwMDRZcnBkRzJVTWpCTGtOYWNKVGw4SFhXQW56NS1peUdhbHZOMU81QjBsNUt3WWlJUnc0QXVadlk2eUdFUVREdzc2ZWNVdm1ReTZVRzZMZDl3MzhiS2RuZFIzV2k3RTBQZTFhaW9JRNIB0AFBVV95cUxPdzREdE1BVFdYdHRvbk5kOG05ams1aHR5R1hEX0xkckRCMVJyNm5ucG9ZcjRwS2prTllwdzdLcnU2WmFFQU05QmgyS09Fbzh1VFptZFgzcjBHOFBOemNfR3doUDBmTHJtaFdydzJISHpHM0NueTNjRDRwcDhRNEliX0M4QVBKaDlyaDZaYnRJOERXelpLRzdVTklQWVgwaVlZODFPcmFlRnJpdjRBWk9NRkhSZmZudHI3eGpqS0ZxS3o2cjl6Z1FER2FLLW9FcThM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYml3VUVFMndVQl83VnhfUWVEaEtQYU8yajNNN2syUWxpMXktamtzRjlaalVNTGhlQkVwT0xZWU1wVmx1b2twRGdRSzNFRGNNOGc3VDhCRXh4VThheXRXNVUzeEVvU24xVkF2Qk9KbmpvVml0U3ZyQTJ6dTRZamtYSHNOUW9YVUNTUmtfSFVPbi1HM3FsTFRfOFIweF9ORU5F?oc=5</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Tensão em Ormuz afeta produção de fertilizantes no Brasil - CNN Brasil</t>
+          <t>Guerra no Irã: empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - G1</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2788,19 +2788,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOaU1rV2NIc09fUTUwZVc4TEI3NEhSZ19UcHVqdEJKaDJ5dDNqSDdUaGo2VXlpWUp6OEpoRnU4ZEpCb2MxQ1RURXV3S3dreU1Lc24tVk8wazB0OTBsN2RIMmVER0ROd2hxUE1QOEdPMFZkc01MQVlHcWdDNDN1dVNETzFQQV94cDFwV0VzeGozdldYbXBBMkQ0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTUZhRXRNY2trQVZ1YkFrZTVzNEdyX0xBSkZOdGduN080THhRLWNrRzNRV2piY1hPSkNOaDZxcWh0a2NnNzZOR2hGeHR4Rkh2QjdVNDlDdXhlcFhlRVB5R0JEUHp4c1lhRFh6bmdJdWlRU1h1WEhkQ2VONEhrUWZBVnRJRl81SE1sN0Z3dGx6dGxTd2NDUzYxM01oVHdKTVRVMDlXZXMxZmF0SnFrTjNPUjZtZlRtamVwTmZxaG1SLWtMYWxaa1E3OEVFTlBkQkRQb2ZIQ1AtSkdPVXRwQUN4aHBtdmZXVnNQYUtydUxzeXTSAf8BQVVfeXFMUEtWemJJN0VvVFA5R2c0WE43dWdwQW1qaXZBMGZzdUlzVWc3NXI1LWE1cE9ZT05Fb2JRbVAxdUdVSHZhWVpwa2VDU0NVbFBSNHVZZnNFZVdQN0loOVlUeUtKMll4d2xLclh3dXhTYVZSM3dHNXBSWXNMUGhydEcwYU1Lc1B5RHU4cEpQclFNNEZMZXZjeUp6QjVCc3l2anp4Ymw0M0VmNU9kQ2hlaUMtZ1c4VTg5eWF2eXhoMXh0UERTSUdORlcwQ0hCUDZTd21GUEdVYVM4aEFVTi1mWUxzbVZyUnhQdGhfcF9wdmxzSUtDYmh1dGVqX0pFa1g2QnFV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Mosaic prorroga paralisação da unidade de Catalão por falta de enxofre - Badiinho</t>
+          <t>Tensão em Ormuz afeta produção de fertilizantes no Brasil - CNN Brasil</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2810,85 +2810,85 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBodUloejIyYmJxUW80NXhoTVUzaXZFMklTTjc1NnRHMzZDZGJOUkVtWUFXT25IWVFwd3o3RGdEeVItVi13ZDdLRk85ZEZHS0t2MFFFMk8xdDQ0VEJRZUc1elhPcHNJcjBzQlBtdUhvLVoxQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOaU1rV2NIc09fUTUwZVc4TEI3NEhSZ19UcHVqdEJKaDJ5dDNqSDdUaGo2VXlpWUp6OEpoRnU4ZEpCb2MxQ1RURXV3S3dreU1Lc24tVk8wazB0OTBsN2RIMmVER0ROd2hxUE1QOEdPMFZkc01MQVlHcWdDNDN1dVNETzFQQV94cDFwV0VzeGozdldYbXBBMkQ0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Parceria investirá R$ 320 mil para pesquisa de solo na UEMS de Cassilândia - Midiamax</t>
+          <t>Uberaba propõe reduzir ISS para tentar preservar empregos após hibernação da Mosaic - Regionalzão</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>14/07/2026 04:00</t>
+          <t>13/07/2026 17:54</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYml3VUVFMndVQl83VnhfUWVEaEtQYU8yajNNN2syUWxpMXktamtzRjlaalVNTGhlQkVwT0xZWU1wVmx1b2twRGdRSzNFRGNNOGc3VDhCRXh4VThheXRXNVUzeEVvU24xVkF2Qk9KbmpvVml0U3ZyQTJ6dTRZamtYSHNOUW9YVUNTUmtfSFVPbi1HM3FsTFRfOFIweF9ORU5F?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE4xbkloamZJdlJQX1V6US13ZkFvei1CRk9vVDBVSElYMm1qUVZiMWY4Ynk1UlhEVlQ3bm5Ha1RmNXNrMjl5NEdwQ3pwMFBXNk9GUGppSm13aTdja1U1TzlaR1JQNEtSQzVXNFlXZ1FNbTZJWlRDbHhvRjQzb1BRNDA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Uberaba propõe reduzir ISS para tentar preservar empregos após hibernação da Mosaic - Regionalzão</t>
+          <t>Livro A Rota do Calcário traz fatos curiosos sobre a história econômica de Arcos - Jornal Correio Centro Oeste Arcos</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>13/07/2026 17:54</t>
+          <t>13/07/2026 16:03</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE4xbkloamZJdlJQX1V6US13ZkFvei1CRk9vVDBVSElYMm1qUVZiMWY4Ynk1UlhEVlQ3bm5Ha1RmNXNrMjl5NEdwQ3pwMFBXNk9GUGppSm13aTdja1U1TzlaR1JQNEtSQzVXNFlXZ1FNbTZJWlRDbHhvRjQzb1BRNDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPazk4R0l0bkdTOGVENHBvc195X3hZMmFrTVBlNXlSMl9SWENKRllNV2Q3THJ5R3k0RW9Qc3lXOXdzeld4WkFZVlN1cWpPZXhNQlRPUXo0ODhnRXlkdEUySEtUNXRucGE5cjJKR1QzTklOdjdocUdvVmszcElRcVh2QlZYVzVLSTkwZThVMWJ1WTBKR3BtMTBSSGhEa0xFUzI4OXdRREdMamhsN19GdWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Livro A Rota do Calcário traz fatos curiosos sobre a história econômica de Arcos - Jornal Correio Centro Oeste Arcos</t>
+          <t>Mosaic Fertilizantes inicia hibernação em Uberaba devido a falta de enxofre - canalrural.com.br</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>13/07/2026 16:03</t>
+          <t>13/07/2026 04:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPazk4R0l0bkdTOGVENHBvc195X3hZMmFrTVBlNXlSMl9SWENKRllNV2Q3THJ5R3k0RW9Qc3lXOXdzeld4WkFZVlN1cWpPZXhNQlRPUXo0ODhnRXlkdEUySEtUNXRucGE5cjJKR1QzTklOdjdocUdvVmszcElRcVh2QlZYVzVLSTkwZThVMWJ1WTBKR3BtMTBSSGhEa0xFUzI4OXdRREdMamhsN19GdWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOV3NNYmk3Z2wtOE5EbW1waDVvbU1Wem1BWU1RcVc1SDNFN1FsZkZXcFFmMkxVYzh0Uml6dlJBcVBmdk9wbDI0cTVEU0lEbWNRc0hnYkZvRFdaYS1rXzFVWDBYRkZmLTA0bldYdERnQ3BRazJFNzdOYUVFZ3M3RFlHbE00YkNydXFaN1ljSEVlelNxMlFzQ0c5N3dqVGxBb095a1pLSGkwa1NZX2trQUJuZFJjMA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Por que a transição energética ameaça o enxofre para fertilizantes - CNN Brasil</t>
+          <t>Mosaic prorroga paralisação temporária da unidade de Catalão por escassez global de enxofre - Portal Serra Dourada News</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNYXc2bkZWdVRXcm9FUmpYWEx4eVRLdHRLdWZsMV9qRDdPWmlVMHBGekhCaC1fd0xDOXV0RXB5TFl2Rlk5QkJ5UUNrM3FEQ1ZWdFhFVkdaZ3FGVXVPSFpMalQ1a3ZFa2V4MUt4Zms4MkNoTGttcktMVFVVSGVSejNUQkZqWUVwSC1UdXlsYWNqY092b1l0bkVSdmlmT2RDMTdFOHNHYUtiT3lRZjIwR1pBSDJqaHVxWU9kbGZ6ekJFeGNCZzNyN1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQTWV4dkpSb09jVG43Rk5yY3oybVJnNXowZjFORV9XWUdMMVl1X3ZvYkVkYnk5d3dtNVIxb05IcC1aeXQzWFJjYVFCbUdjdlFHZHlWS2Naa0ttY0dNaVJodGtNNGRaaWVwYUFja3ctQlluZTZVUVdYNWF6V1MwVE00MlVOOGhDNkJvSFU1VFlqd2wwa3hnczdVNTFyVmpxWTFnTnl3RlU1QjRyUHdBYWI4Z0UxQ09QdHBkQUVrZXExc18tUkptWHNsekp1YnI?oc=5</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Mosaic prorroga paralisação temporária da unidade de Catalão por escassez global de enxofre - Portal Serra Dourada News</t>
+          <t>Fabricante de fertilizantes Mosaic reduz produção no Brasil por impactos da guerra no Irã - folha.uol.com.br</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2920,19 +2920,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQTWV4dkpSb09jVG43Rk5yY3oybVJnNXowZjFORV9XWUdMMVl1X3ZvYkVkYnk5d3dtNVIxb05IcC1aeXQzWFJjYVFCbUdjdlFHZHlWS2Naa0ttY0dNaVJodGtNNGRaaWVwYUFja3ctQlluZTZVUVdYNWF6V1MwVE00MlVOOGhDNkJvSFU1VFlqd2wwa3hnczdVNTFyVmpxWTFnTnl3RlU1QjRyUHdBYWI4Z0UxQ09QdHBkQUVrZXExc18tUkptWHNsekp1YnI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNdG53eFV5WG9kaWlMRjlEZ0d2OUM5Mm5EMDZ3UVFNX0IwNFktOVdfN1NiYmpvZHU2WEF3UjJ6RmdNcExjSkJQQm1iYmRuNHllMTVzSnNKeG5SeUhhY01uVG5EMk9yREs1WjQyNS1tSDkwQVZOUF9acWlsc3dkVG5SMGtxV1JfWGp0SWRjdG5yMklKN2lCVWhJQ3ZRWjBYRlZjaVd6MVZfYzFPbG5nR2NQaFhZWXFuZmN2QnRfRkY1MWNBR1FyZGJyS0lkY1VNU1RFUzJEbXBCcWY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Fabricante de fertilizantes Mosaic reduz produção no Brasil por impactos da guerra no Irã - folha.uol.com.br</t>
+          <t>Por que a transição energética ameaça o enxofre para fertilizantes - CNN Brasil</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNdG53eFV5WG9kaWlMRjlEZ0d2OUM5Mm5EMDZ3UVFNX0IwNFktOVdfN1NiYmpvZHU2WEF3UjJ6RmdNcExjSkJQQm1iYmRuNHllMTVzSnNKeG5SeUhhY01uVG5EMk9yREs1WjQyNS1tSDkwQVZOUF9acWlsc3dkVG5SMGtxV1JfWGp0SWRjdG5yMklKN2lCVWhJQ3ZRWjBYRlZjaVd6MVZfYzFPbG5nR2NQaFhZWXFuZmN2QnRfRkY1MWNBR1FyZGJyS0lkY1VNU1RFUzJEbXBCcWY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNYXc2bkZWdVRXcm9FUmpYWEx4eVRLdHRLdWZsMV9qRDdPWmlVMHBGekhCaC1fd0xDOXV0RXB5TFl2Rlk5QkJ5UUNrM3FEQ1ZWdFhFVkdaZ3FGVXVPSFpMalQ1a3ZFa2V4MUt4Zms4MkNoTGttcktMVFVVSGVSejNUQkZqWUVwSC1UdXlsYWNqY092b1l0bkVSdmlmT2RDMTdFOHNHYUtiT3lRZjIwR1pBSDJqaHVxWU9kbGZ6ekJFeGNCZzNyN1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -2954,17 +2954,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Mosaic Fertilizantes inicia hibernação em Uberaba devido a falta de enxofre - Canal Rural</t>
+          <t>Mosaic anuncia paralisação temporária das atividades em Goiás - O Popular</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>13/07/2026 04:00</t>
+          <t>12/07/2026 06:03</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOV3NNYmk3Z2wtOE5EbW1waDVvbU1Wem1BWU1RcVc1SDNFN1FsZkZXcFFmMkxVYzh0Uml6dlJBcVBmdk9wbDI0cTVEU0lEbWNRc0hnYkZvRFdaYS1rXzFVWDBYRkZmLTA0bldYdERnQ3BRazJFNzdOYUVFZ3M3RFlHbE00YkNydXFaN1ljSEVlelNxMlFzQ0c5N3dqVGxBb095a1pLSGkwa1NZX2trQUJuZFJjMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNd1hMbnIzRXEzWC13ZTRoRXcxbDhCeUhEbkRYY1ZObjhPczh6RlpSZVEwck9FelpCT0pzcGhST2xDMHNTV1dRdDIyYWQ0T00wRXFnaHd5VDc2SDJqbmlvTzg0Rk95R3VaUktfaUp4VFZBT2FWaXJEbFBoMEloOElESjVtUkNRQnJ6a3A4SGhTZTVWQXdpb3RpZUt0X2EyVmFGSGs2cXBoVQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2976,17 +2976,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Mosaic anuncia paralisação temporária das atividades em Goiás - O Popular</t>
+          <t>Anderson Adauto articula ação com sindicatos e promete levar crise da Mosaic ao governo federal - Folha de Uberaba</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>12/07/2026 06:03</t>
+          <t>10/07/2026 20:16</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNd1hMbnIzRXEzWC13ZTRoRXcxbDhCeUhEbkRYY1ZObjhPczh6RlpSZVEwck9FelpCT0pzcGhST2xDMHNTV1dRdDIyYWQ0T00wRXFnaHd5VDc2SDJqbmlvTzg0Rk95R3VaUktfaUp4VFZBT2FWaXJEbFBoMEloOElESjVtUkNRQnJ6a3A4SGhTZTVWQXdpb3RpZUt0X2EyVmFGSGs2cXBoVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQbjRwcEFiRTF6ZlBDOE9FYmt1ZnJQVjZXN3FmSTJwaENRUDNYWm5rR25PY0dWb1lUdGhxeENUNFMzdS1ubnI4SEZUa3NQbVo0d0t1RVJoT2tuRUM0MFpCMy1yMnc5LVcwZHd2YmgzVDFZc0V3YUZ3ZmhkWnE2VXJNZE5FV3B2eW41ZGhHMDNPS25aNDhxeTloZ1BwU0VQclJfVEs3M3U1a2FYalBqMmcwMFg1MUE2aVVCaXhYNGRLRHhGUXZjYXNF?oc=5</t>
         </is>
       </c>
     </row>
@@ -2998,61 +2998,61 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Anderson Adauto articula ação com sindicatos e promete levar crise da Mosaic ao governo federal - Folha de Uberaba</t>
+          <t>Crise global no fornecimento de enxofre afeta operações da Mosaic em Minas. Unidade de Uberaba entrará em hibernação. Entenda… – Jornal Araxá - Jornal Araxá</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>10/07/2026 20:16</t>
+          <t>10/07/2026 08:50</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQbjRwcEFiRTF6ZlBDOE9FYmt1ZnJQVjZXN3FmSTJwaENRUDNYWm5rR25PY0dWb1lUdGhxeENUNFMzdS1ubnI4SEZUa3NQbVo0d0t1RVJoT2tuRUM0MFpCMy1yMnc5LVcwZHd2YmgzVDFZc0V3YUZ3ZmhkWnE2VXJNZE5FV3B2eW41ZGhHMDNPS25aNDhxeTloZ1BwU0VQclJfVEs3M3U1a2FYalBqMmcwMFg1MUE2aVVCaXhYNGRLRHhGUXZjYXNF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPbjdHT0tYWjY2TzhYZVNDT2JfVDZHYUdYMnQ0d3BWTlB0S3p2NGJzQXRwWlIxVVZJSHdFUkNJQ3FoMWZTcl8xZTBkdnM5QWRFaUo4REI0Szc5S1psZ0VVYXhSYUNOM1ZrZmpuWkV1NHVkVjJXRHU2SHJ1aTFlVFpXeW1felpCQTJzNkE2bzlJcG1iNmtwUC03TDh4UWNCTnM5cmp6VERkbEJZdmhQcU9kc2N3X1c3Y1Z1dGtZMjdYdmhhS1RGdzgweEQ5endrbkNGUnUwUzVya1RWQmJnWktZcUIwRXd2dw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Crise global no fornecimento de enxofre afeta operações da Mosaic em Minas. Unidade de Uberaba entrará em hibernação. Entenda… – Jornal Araxá - Jornal Araxá</t>
+          <t>"Calcário convencional: herança do passado, desafios do futuro" - Revista Attalea Agronegócios</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>10/07/2026 08:50</t>
+          <t>10/07/2026 08:32</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPbjdHT0tYWjY2TzhYZVNDT2JfVDZHYUdYMnQ0d3BWTlB0S3p2NGJzQXRwWlIxVVZJSHdFUkNJQ3FoMWZTcl8xZTBkdnM5QWRFaUo4REI0Szc5S1psZ0VVYXhSYUNOM1ZrZmpuWkV1NHVkVjJXRHU2SHJ1aTFlVFpXeW1felpCQTJzNkE2bzlJcG1iNmtwUC03TDh4UWNCTnM5cmp6VERkbEJZdmhQcU9kc2N3X1c3Y1Z1dGtZMjdYdmhhS1RGdzgweEQ5endrbkNGUnUwUzVya1RWQmJnWktZcUIwRXd2dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQRXBKODRUMjRqNVVvbmlITmlfVVNET045UHpPY0FoeldGMU5QZXRDdE9YTDU1WExQcXBOUHRTUlVoek1xUjc2NGxwVVhCcjNTV2t4RDlZZFBkY3l3OGZfZDZYNnFCczJ1b25MTmpmMGQ1MkwwVnBISmNOX25jd3BNRnI0NEJMU2ZZVlEtZTVCejlOSFlDdXBDc3dxaEtycEFaSUdwSE00MHhHQWZZQWZGdk5kTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>"Calcário convencional: herança do passado, desafios do futuro" - Revista Attalea Agronegócios</t>
+          <t>Fertilizantes: Mosaic avalia alternativas contra restrições na oferta de enxofre - Money Times</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>10/07/2026 08:32</t>
+          <t>10/07/2026 04:00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQRXBKODRUMjRqNVVvbmlITmlfVVNET045UHpPY0FoeldGMU5QZXRDdE9YTDU1WExQcXBOUHRTUlVoek1xUjc2NGxwVVhCcjNTV2t4RDlZZFBkY3l3OGZfZDZYNnFCczJ1b25MTmpmMGQ1MkwwVnBISmNOX25jd3BNRnI0NEJMU2ZZVlEtZTVCejlOSFlDdXBDc3dxaEtycEFaSUdwSE00MHhHQWZZQWZGdk5kTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPQ1FzejVNV0p1cUcyYmFqaDdjYUVULVh5Unhta29iWVhpRXFXUU9XX2VHU29NYkloeXpwR2pMb1FaalBfWWhmVGhHNUxfSHRQZ3NFaU1TRlh5Sl9zcHI0TUxjUlZOc0VwOVZhWXRpdFFhLWFoa3Jhek81M2U0VEZYMk5Hc0xLMTVkNy1wc1NMRjRfeXBWUWtVaW43bWwtZUROUTBwTE9OMGhQUXlza0FJN1BmOHluUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Fertilizantes: Mosaic avalia alternativas contra restrições na oferta de enxofre - Money Times</t>
+          <t>Crise da Mosaic mobiliza autoridades e acende alerta sobre empregos e economia de Uberaba - JM Online</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPQ1FzejVNV0p1cUcyYmFqaDdjYUVULVh5Unhta29iWVhpRXFXUU9XX2VHU29NYkloeXpwR2pMb1FaalBfWWhmVGhHNUxfSHRQZ3NFaU1TRlh5Sl9zcHI0TUxjUlZOc0VwOVZhWXRpdFFhLWFoa3Jhek81M2U0VEZYMk5Hc0xLMTVkNy1wc1NMRjRfeXBWUWtVaW43bWwtZUROUTBwTE9OMGhQUXlza0FJN1BmOHluUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxObTBDYTQzZm1LS01jMnNkVzAwUnN1UFowRXlROEQ5SlNxcm5hQjRRemNhWXhOTTVoT0N4NG8zN1BiYjF2QXdDUkcwdGVwby1CcEJxTTI5R2VfWlZCX2ZEMmlQUkdHZVNOZk9Lb3pHb193M1pMZ3ZsdW5OTExiQ3k3bC1mN1U0X3lQOXFnMDJwWU5zTEJFTFpyTE1Nb0xvWnNMNklNa1hvRkNvUlZpYzhURGlYTWpBMTJCRnNYc3QzYWFPNV9GWFZuUEwwa2RtbGwwVWg4MjZwb1BQUdIB4gFBVV95cUxPM3Bnd3VXQnlxUzJVNXY1U0VKdVFrT3N1Z0ZUQVdPWEQtODM1TjJ3UnY0UzBMUHJhc050SWFQQlNvU2pRX0kxUEpOWndKWE4zN0d4TWxyTHhsbV9YdkFyWGV1anJrTzRoM1BwSS00eDgwWTVqNE8wNjA2UWh1NmFidUt5V3hFOVNFZkZ2LTV4Z0pKWE5ZMEJLcHZWVEU2YTJ3eDJMSDNwMzhEelhTWURKSUNxdUhaNTdfNDR3cEg2d1hWNjA5VVV6bUcwOEtpbU9uTmZEVGFHRnZUcl9RcWZzZlhB?oc=5</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Crise da Mosaic mobiliza autoridades e acende alerta sobre empregos e economia de Uberaba - JM Online</t>
+          <t>Alta do enxofre impacta produção de fertilizantes e Mosaic anuncia hibernação da unidade em Uberaba - G1</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3118,51 +3118,51 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxObTBDYTQzZm1LS01jMnNkVzAwUnN1UFowRXlROEQ5SlNxcm5hQjRRemNhWXhOTTVoT0N4NG8zN1BiYjF2QXdDUkcwdGVwby1CcEJxTTI5R2VfWlZCX2ZEMmlQUkdHZVNOZk9Lb3pHb193M1pMZ3ZsdW5OTExiQ3k3bC1mN1U0X3lQOXFnMDJwWU5zTEJFTFpyTE1Nb0xvWnNMNklNa1hvRkNvUlZpYzhURGlYTWpBMTJCRnNYc3QzYWFPNV9GWFZuUEwwa2RtbGwwVWg4MjZwb1BQUdIB4gFBVV95cUxPM3Bnd3VXQnlxUzJVNXY1U0VKdVFrT3N1Z0ZUQVdPWEQtODM1TjJ3UnY0UzBMUHJhc050SWFQQlNvU2pRX0kxUEpOWndKWE4zN0d4TWxyTHhsbV9YdkFyWGV1anJrTzRoM1BwSS00eDgwWTVqNE8wNjA2UWh1NmFidUt5V3hFOVNFZkZ2LTV4Z0pKWE5ZMEJLcHZWVEU2YTJ3eDJMSDNwMzhEelhTWURKSUNxdUhaNTdfNDR3cEg2d1hWNjA5VVV6bUcwOEtpbU9uTmZEVGFHRnZUcl9RcWZzZlhB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNdjlTZE83dWZYdURPNTFzRWhqdVpEUmdWQ1ZuZHlQakpNWno4RllBdm5nZWVWSkdONE0tRjF1WVVTdmV3aTFheFlTUWZlQVpjZnFNZnFycjRLRGxjdEFaS2I1YzBHYnJVQlQ2bUVlOFB1a1Q0aERCbUlTZ1kwU0hOdFZlb0R0NVJ6R2ZfczlCUl8tWW0wcVZEdldjYTBQZ3h6ZVdSeWZJMzBkZnZ6cUNEOU9EX0pJV1ZDcFd6SUw5eTNmTnNoWG56dnFTeUJUSHNCZXlyVnVULWs2RF9LeWJUblk0QlkxcDA5dERwMGlfQUZLNW1mNTUtTWN30gGIAkFVX3lxTE1KSHdXV3lzVzM3YXlzaGJYM3p3c2lCMW5zVDd4YTVjU0x0d3pJakNiUVQzQ1FpUmx4MXM2YkFaSXowZ0Z4UlBHV0dMTklQb2s0MHFuMEVQRGZLN0JLa0lZS3hVTnRwUXloQ2RSQjlQZl9GM21xd2ZfTDRUQXh2VS1nLUNaMWJ0QnFfVHl4UUxzdWVZVjBBNThNeVR1Z29ycjhKTF9Vakx0aWxKWEVGaE5uWUZvNnlzNDkwdXBkNmxSbXU0eGd3Q0ktY1ZjdTBUTXlMUkdUYlRob19aREJvd2dfQ25VMVRWNXF1c2ZscjEwQ1RzQ196dEZGZUxOUWlMbi1LdTJkUU8ybw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Alta do enxofre impacta produção de fertilizantes e Mosaic anuncia hibernação da unidade em Uberaba - G1</t>
+          <t>Prefeitura inicia distribuição de calcário para fortalecer a produção da agricultura familiar em Palmas - luizarmandocosta.com.br</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>10/07/2026 04:00</t>
+          <t>09/07/2026 06:50</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNdjlTZE83dWZYdURPNTFzRWhqdVpEUmdWQ1ZuZHlQakpNWno4RllBdm5nZWVWSkdONE0tRjF1WVVTdmV3aTFheFlTUWZlQVpjZnFNZnFycjRLRGxjdEFaS2I1YzBHYnJVQlQ2bUVlOFB1a1Q0aERCbUlTZ1kwU0hOdFZlb0R0NVJ6R2ZfczlCUl8tWW0wcVZEdldjYTBQZ3h6ZVdSeWZJMzBkZnZ6cUNEOU9EX0pJV1ZDcFd6SUw5eTNmTnNoWG56dnFTeUJUSHNCZXlyVnVULWs2RF9LeWJUblk0QlkxcDA5dERwMGlfQUZLNW1mNTUtTWN30gGIAkFVX3lxTE1KSHdXV3lzVzM3YXlzaGJYM3p3c2lCMW5zVDd4YTVjU0x0d3pJakNiUVQzQ1FpUmx4MXM2YkFaSXowZ0Z4UlBHV0dMTklQb2s0MHFuMEVQRGZLN0JLa0lZS3hVTnRwUXloQ2RSQjlQZl9GM21xd2ZfTDRUQXh2VS1nLUNaMWJ0QnFfVHl4UUxzdWVZVjBBNThNeVR1Z29ycjhKTF9Vakx0aWxKWEVGaE5uWUZvNnlzNDkwdXBkNmxSbXU0eGd3Q0ktY1ZjdTBUTXlMUkdUYlRob19aREJvd2dfQ25VMVRWNXF1c2ZscjEwQ1RzQ196dEZGZUxOUWlMbi1LdTJkUU8ybw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQMWpueTF3aVVYMWVnUU5aWHduSWUyZy1jNzBCWXlLZl9qQ3pTMnY0MmFhY2twNXk4V0ZaNy1oU0c3SHlrZi1KTV9pVUhvdW5EVnl1MnJEaHB0UF9rVTcwTnhCLWcwM0N6cTFSUEhfUHBscDF6WTRZcDFFUFk5R2ZxaDJmQ3FGUHgyQUF2RDJnWURZRm5EdWYzTDI4aGphekttRjY1Zm5POTFqc2lhWTdoTWxDYUo4QnpLbkpZN3lGLVY4dFVIRVVIYXRwaEp4YUhuT1BWOWw4WDJTTVc0X1Jvc1NfVjlST0NR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Prefeitura inicia distribuição de calcário para fortalecer a produção da agricultura familiar em Palmas - Luiz Armando Costa</t>
+          <t>Sem enxofre por Ormuz, Mosaic fecha fábrica de fertilizantes na Bahia e demite 30 - Movimento Econômico</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>09/07/2026 06:50</t>
+          <t>09/07/2026 04:00</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQMWpueTF3aVVYMWVnUU5aWHduSWUyZy1jNzBCWXlLZl9qQ3pTMnY0MmFhY2twNXk4V0ZaNy1oU0c3SHlrZi1KTV9pVUhvdW5EVnl1MnJEaHB0UF9rVTcwTnhCLWcwM0N6cTFSUEhfUHBscDF6WTRZcDFFUFk5R2ZxaDJmQ3FGUHgyQUF2RDJnWURZRm5EdWYzTDI4aGphekttRjY1Zm5POTFqc2lhWTdoTWxDYUo4QnpLbkpZN3lGLVY4dFVIRVVIYXRwaEp4YUhuT1BWOWw4WDJTTVc0X1Jvc1NfVjlST0NR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRnJPcG92M29uVXBLdEU4dHBWUHU5TE5wMlI5Q2xGNkd0Y01HR0ptejQ0MjJteEFXUERMWlEwTTRUbnZJaE1OYU1USVVMeVVobXFkNk13WGVlRzNoZVQ1WG13LXFJVjBQODdrTDJuNWdROEJIOTF3Ykp5SXBjTFBiUEJqdTFrX2htRzBTa1JaMnY5LUU2WkstS0RMblk3OFVaSmJqVmVDOGVJaUJWSDJyQ3VySXdNSFNKUVkxZGwzTXM5b2hHV0hUM0wxV3hWOEE4eTJiVQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Sem enxofre por Ormuz, Mosaic fecha fábrica de fertilizantes na Bahia e demite 30 - Movimento Econômico</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - comprerural.com</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRnJPcG92M29uVXBLdEU4dHBWUHU5TE5wMlI5Q2xGNkd0Y01HR0ptejQ0MjJteEFXUERMWlEwTTRUbnZJaE1OYU1USVVMeVVobXFkNk13WGVlRzNoZVQ1WG13LXFJVjBQODdrTDJuNWdROEJIOTF3Ykp5SXBjTFBiUEJqdTFrX2htRzBTa1JaMnY5LUU2WkstS0RMblk3OFVaSmJqVmVDOGVJaUJWSDJyQ3VySXdNSFNKUVkxZGwzTXM5b2hHV0hUM0wxV3hWOEE4eTJiVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNYmd5aEw0ajhQRGtrcXUxdG1JN2gxeWZVYTZsS1VVTGk4cnBEbThDNzY4WndKQVhONjk5WmhGUi1YNmtxek1fM1dRNmluc0VxOUtJc2xYQ2tCYjhuSnVCLTBnZXc0b3YwUUhpcWp5MkpLTWVTa2lwVjZ4eENrbWdrYXZFakpBYVVvaFRybDNXcXRTbkVJRVpxbUJMRUJXU0JTYzV3RzZsc050WlNOeXhGc0xaYnVaUHV3b3k0Mw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Mosaic Reduz Temporariamente Produção de Fosfato e Mistura no Brasil - Forbes Brasil</t>
+          <t>Mosaic reduz produção de fertilizantes no Brasil por escassez global de enxofre - canalrural.com.br</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOaTJvRzFTQnJIaEpOUk1PMDBoQmlUa09zVDRoM2p1bl9tZUdRM1BDYmVRS1Z3ZnVUYmZZQ3oxVkFERzhQUjBPTFBSNzhCM1FoeE00dXVfNDV3QkxGdEtzVVY3UXM4VFV4aXR3VC1QNklKeFZ3bjN5NC02a2tCZjJjUW1mLWFNVTJYYm5iZkFkM3ZtMEJuVkI0akROT054eUQzOC1ieDZZSGtBb1U4M3o5dA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQSWJRLTNNNlZ6Y2hKcDlTblhmZFY5WUZhWUlYTUlsY2l3TXpMTW80bjRYeE9GdTNCYm5UVzVvMzZZVnR6TkxlbTQ2YjAyc1YzcFNqbHF5Qlh3MkhSdVgyRmROODdoR1ZIbjEySkdPZ3N3am5uMUFRTDQ4NDVTVEZYbWJfQldRMmpFaDBTLXRGU244czdfMEk2Z3JGbUNrMmNCMDV0WWZtb0tKN0xGM0dCVXB4d0I4M2FFZlZZ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - CompreRural</t>
+          <t>Mosaic Reduz Temporariamente Produção de Fosfato e Mistura no Brasil - Forbes Brasil</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNYmd5aEw0ajhQRGtrcXUxdG1JN2gxeWZVYTZsS1VVTGk4cnBEbThDNzY4WndKQVhONjk5WmhGUi1YNmtxek1fM1dRNmluc0VxOUtJc2xYQ2tCYjhuSnVCLTBnZXc0b3YwUUhpcWp5MkpLTWVTa2lwVjZ4eENrbWdrYXZFakpBYVVvaFRybDNXcXRTbkVJRVpxbUJMRUJXU0JTYzV3RzZsc050WlNOeXhGc0xaYnVaUHV3b3k0Mw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOaTJvRzFTQnJIaEpOUk1PMDBoQmlUa09zVDRoM2p1bl9tZUdRM1BDYmVRS1Z3ZnVUYmZZQ3oxVkFERzhQUjBPTFBSNzhCM1FoeE00dXVfNDV3QkxGdEtzVVY3UXM4VFV4aXR3VC1QNklKeFZ3bjN5NC02a2tCZjJjUW1mLWFNVTJYYm5iZkFkM3ZtMEJuVkI0akROT054eUQzOC1ieDZZSGtBb1U4M3o5dA?oc=5</t>
         </is>
       </c>
     </row>
@@ -3240,61 +3240,61 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Mosaic reduz produção de fertilizantes no Brasil por escassez global de enxofre - Canal Rural</t>
+          <t>Mosaic reduz operações no Brasil por escassez de enxofre</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>09/07/2026 04:00</t>
+          <t>08/07/2026 11:07</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQSWJRLTNNNlZ6Y2hKcDlTblhmZFY5WUZhWUlYTUlsY2l3TXpMTW80bjRYeE9GdTNCYm5UVzVvMzZZVnR6TkxlbTQ2YjAyc1YzcFNqbHF5Qlh3MkhSdVgyRmROODdoR1ZIbjEySkdPZ3N3am5uMUFRTDQ4NDVTVEZYbWJfQldRMmpFaDBTLXRGU244czdfMEk2Z3JGbUNrMmNCMDV0WWZtb0tKN0xGM0dCVXB4d0I4M2FFZlZZ?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a70b559c20b4f1d8d5f10f011fa6db5&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f07%2fmosaic-reduz-operacoes-no-brasil-por-escassez-de-enxofre.ghtml&amp;c=17049096324127703512&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Mosaic reduz operações no Brasil por escassez de enxofre</t>
+          <t>Sorriso começa a receber mais de 1,2 mil toneladas de calcári... - PREFEITURA MUNICIPAL DE Sorriso MT</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>08/07/2026 11:07</t>
+          <t>08/07/2026 09:54</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a708dfeb1c047e6bc0032a232694450&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f07%2fmosaic-reduz-operacoes-no-brasil-por-escassez-de-enxofre.ghtml&amp;c=17049096324127703512&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOX3JwQnFZQXByS2VBOVNuWG5vRjhyZ19OUE1DNml6MXlhZjdLUEZOX0d5VHpVOHRxRURNYVNYVU1ITFZXMDhfMzZuWmFKX3MyckNNYUxReVdHU0t6OVAzdFgxZjBNQnJ2T0tNSkJ6bFU4NmlDSjZHRmtyQmZScXhPaUlMZGZSZVh6V3d0OTJ4QmlXVmotN01xSFFzWGZqWklWcVA3UEs0ZHZEV2x0bE1CSG00YVZTUVg4cG1xV0NkYmJidjlvMkdTemU1TTNxdnBkcWlpOUdqY1FXVGNG?oc=5</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Sorriso começa a receber mais de 1,2 mil toneladas de calcári... - PREFEITURA MUNICIPAL DE Sorriso MT</t>
+          <t>Gaúcha LW mira R$ 600 milhões em contratos erguendo estruturas para empresas como Yara e Mosaic - AgFeed</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>08/07/2026 09:54</t>
+          <t>08/07/2026 04:00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOX3JwQnFZQXByS2VBOVNuWG5vRjhyZ19OUE1DNml6MXlhZjdLUEZOX0d5VHpVOHRxRURNYVNYVU1ITFZXMDhfMzZuWmFKX3MyckNNYUxReVdHU0t6OVAzdFgxZjBNQnJ2T0tNSkJ6bFU4NmlDSjZHRmtyQmZScXhPaUlMZGZSZVh6V3d0OTJ4QmlXVmotN01xSFFzWGZqWklWcVA3UEs0ZHZEV2x0bE1CSG00YVZTUVg4cG1xV0NkYmJidjlvMkdTemU1TTNxdnBkcWlpOUdqY1FXVGNG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOcFlMVVRvZTZBbXpHWUJZeDFMYmRLeVU2TV8xT3VySk5DWTlwNk01R0hpRVVTdmI4SU1fQlY2RC16WVFnb1VmZUI1dTBlenFLVGc2VnlYQ3JuZ0xLTnhrQlZuNXdSWXpNS2dERnI2SjBZNW0zTnhoRkxuWXpZM2hMTE5CaVlwcU5FNDlTVloybWVPWTAyTUN1Q0ZyLVgxSkl0ZWZNeFMxVm1aWWhNRlQ5QWFWdWt6eWFWUUdTdXg3NThLUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MPGO celebra acordos com mineradora que garantem R$ 11 milhões para reparação ambiental em Catalão - mpgo.mp.br</t>
+          <t>MPGO celebra acordos com mineradora que garantem R$ 11 milhões para reparação ambiental em Catalão - Portal MPGO</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3345,12 +3345,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Gaúcha LW mira R$ 600 milhões em contratos erguendo estruturas para empresas como Yara e Mosaic - AgFeed</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOcFlMVVRvZTZBbXpHWUJZeDFMYmRLeVU2TV8xT3VySk5DWTlwNk01R0hpRVVTdmI4SU1fQlY2RC16WVFnb1VmZUI1dTBlenFLVGc2VnlYQ3JuZ0xLTnhrQlZuNXdSWXpNS2dERnI2SjBZNW0zTnhoRkxuWXpZM2hMTE5CaVlwcU5FNDlTVloybWVPWTAyTUN1Q0ZyLVgxSkl0ZWZNeFMxVm1aWWhNRlQ5QWFWdWt6eWFWUUdTdXg3NThLUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQeC1fdHVhNWRCd2I4T05LeVlMV1ZRU193US0zTDRXMVl0QVpfa2VFQXktajRWUGprTUlYM0hwZWxyaFJlZTBtV2ZDdlJTVmh6QnJnMzZWUXBTWWN6azZfaTVianNDRUpzMDFoSXRnd0p5UUhTcW0xclVKcnppdFJydGlaZnViNWhqYXAyYkhTSUh3b0FNZ0QwWjZSV0I3OEJLdUhzdW1aVEZUd2lmdnFHRXJfb21oZ0g4RUR2N0xVNjM1N0NxbC1MMzlMRVoxRHluZ19HZ2NFcDR4b1p0eFM5U3pqR1dYZno1QVRkT1RaZGtiOWvSAfgBQVVfeXFMTjBtbzUxT0tUb1A4NGxyamM1THlMZGw4V2NaSjZ0TnQxZUtvbk51ZHdsYWk0WWNoald1M0lrM19HdG8wS2dBNFJLaXlLNnRybUhsVGsxOW1nWmNycWgxQldaeWZ0YWpBcEd2Qk1BRTVYNFR0SEpJWjdkRnFXRlNMdFNlT01nVDBGdnNTeVNRNFdlNjBhVkZIQVJ0dWhhaTIxVjlkOWo4RXVVMjdqQlc2bVh4S3p0dWNkQTE2a0NDMTE1Z0puOFoxZDhqOHE2eW9yOWxoLWV0eVV5MGFyVlJHWjZzcXh3MXd3Y0Y5SEFxX25GRW80cWN6VTI?oc=5</t>
         </is>
       </c>
     </row>
@@ -3372,17 +3372,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - Notícias Agrícolas</t>
+          <t>Enxofre ganha espaço no manejo das lavouras - Agrolink</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>08/07/2026 04:00</t>
+          <t>06/07/2026 10:47</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQeC1fdHVhNWRCd2I4T05LeVlMV1ZRU193US0zTDRXMVl0QVpfa2VFQXktajRWUGprTUlYM0hwZWxyaFJlZTBtV2ZDdlJTVmh6QnJnMzZWUXBTWWN6azZfaTVianNDRUpzMDFoSXRnd0p5UUhTcW0xclVKcnppdFJydGlaZnViNWhqYXAyYkhTSUh3b0FNZ0QwWjZSV0I3OEJLdUhzdW1aVEZUd2lmdnFHRXJfb21oZ0g4RUR2N0xVNjM1N0NxbC1MMzlMRVoxRHluZ19HZ2NFcDR4b1p0eFM5U3pqR1dYZno1QVRkT1RaZGtiOWvSAfgBQVVfeXFMTjBtbzUxT0tUb1A4NGxyamM1THlMZGw4V2NaSjZ0TnQxZUtvbk51ZHdsYWk0WWNoald1M0lrM19HdG8wS2dBNFJLaXlLNnRybUhsVGsxOW1nWmNycWgxQldaeWZ0YWpBcEd2Qk1BRTVYNFR0SEpJWjdkRnFXRlNMdFNlT01nVDBGdnNTeVNRNFdlNjBhVkZIQVJ0dWhhaTIxVjlkOWo4RXVVMjdqQlc2bVh4S3p0dWNkQTE2a0NDMTE1Z0puOFoxZDhqOHE2eW9yOWxoLWV0eVV5MGFyVlJHWjZzcXh3MXd3Y0Y5SEFxX25GRW80cWN6VTI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNRVJxOGlMRVRqcWk4R0VXOUtaSHJ2VHN5T1VpVHp6UDBQdlV2Y2ZMWnFCX0Roa2NlSjUtWThaVEJ3WkVsUERlNlNZS0FmeHYwSXRKRVhqMEh5MGxnYWVBVnNIZTdjNFE3SlBzWVdzcTMyTnNnS3pfc1ZMb1BWbmk2QTFFdHFnUkYyTXZjUDZsMjNPOFZjaFhR?oc=5</t>
         </is>
       </c>
     </row>
@@ -3394,61 +3394,61 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Enxofre ganha espaço no manejo das lavouras - agrolink.com.br</t>
+          <t>Adolescentes de Enxofre - Minecraft</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>06/07/2026 10:47</t>
+          <t>06/07/2026 06:03</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNRVJxOGlMRVRqcWk4R0VXOUtaSHJ2VHN5T1VpVHp6UDBQdlV2Y2ZMWnFCX0Roa2NlSjUtWThaVEJ3WkVsUERlNlNZS0FmeHYwSXRKRVhqMEh5MGxnYWVBVnNIZTdjNFE3SlBzWVdzcTMyTnNnS3pfc1ZMb1BWbmk2QTFFdHFnUkYyTXZjUDZsMjNPOFZjaFhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQMlh1NlJuV2FMN3hicE42dEJqc01iSTM1endySVlqQ0kzaW1VVkhIN1l5UnNJXzlaenZhQW1WZFFnYVV5WlZTR2VjX2x2WGVUTzB6V1lUd1dXT1ZnYnYzQ056UmdjZUZCYm04bS1GXzgyQThXWUd6Nlk3VUFvazhsODhYQkU0UGNmT1pCM3NtcWVvakJCZ2ZsVzlJVFlERjhtQUd3NkZnZVNYVDhWc1F1Q3BOZjN4TzJZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Adolescentes de Enxofre - Minecraft</t>
+          <t>Fertilizantes subiram mais que a inflação desde 2016; ureia ainda custa 149% a mais em termos reais - Agrolink</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>06/07/2026 06:03</t>
+          <t>04/07/2026 04:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQMlh1NlJuV2FMN3hicE42dEJqc01iSTM1endySVlqQ0kzaW1VVkhIN1l5UnNJXzlaenZhQW1WZFFnYVV5WlZTR2VjX2x2WGVUTzB6V1lUd1dXT1ZnYnYzQ056UmdjZUZCYm04bS1GXzgyQThXWUd6Nlk3VUFvazhsODhYQkU0UGNmT1pCM3NtcWVvakJCZ2ZsVzlJVFlERjhtQUd3NkZnZVNYVDhWc1F1Q3BOZjN4TzJZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOTEZVZTZETDBfN3VETnZRZ1lwamFoV1dlYzJCS3NSQlZaaHdMbXZyM0xUT2JKRWZId3Z3ZDc4VlJjc0s0VDJ5M1hTMnJYclpYZDlEZmxrQVhPXzR3UDBUSkxLc0xGU1lPcWQ2UDROZllLMzdlNHhGTG5RNGtDVGJTbVRPR3BWcGw1YlpvdXVTYnVrSXMzaGE1d1Z1a0dGcWJUSWZqTFUxRERITWVSQUU1eWhTTFBCaFlLa0NFWHFvUDROVnJQbjRyVU1wS25KNmdyX0psZ3lGeW92TTBYYlYzUlVB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Fertilizantes subiram mais que a inflação desde 2016; ureia ainda custa 149% a mais em termos reais - agrolink.com.br</t>
+          <t>Alta do enxofre afeta produção e gera demissões em Araxá - G1</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>04/07/2026 04:00</t>
+          <t>03/07/2026 04:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOTEZVZTZETDBfN3VETnZRZ1lwamFoV1dlYzJCS3NSQlZaaHdMbXZyM0xUT2JKRWZId3Z3ZDc4VlJjc0s0VDJ5M1hTMnJYclpYZDlEZmxrQVhPXzR3UDBUSkxLc0xGU1lPcWQ2UDROZllLMzdlNHhGTG5RNGtDVGJTbVRPR3BWcGw1YlpvdXVTYnVrSXMzaGE1d1Z1a0dGcWJUSWZqTFUxRERITWVSQUU1eWhTTFBCaFlLa0NFWHFvUDROVnJQbjRyVU1wS25KNmdyX0psZ3lGeW92TTBYYlYzUlVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPdDlyUTJPY3lkTzRodWhvRVhRTjB1RHlEX2lGcWJxcHFQQlRjamRIY0VIYnhjWlVXVjFWQmtYOTQtSGhsU0NYbGZmSjVYX0Z0NVJXdEVfNzM2OHQwQl9uRG5oUElfbUtjblNEMl9VWWJQUTdoTEVFYkhnZWxNTFpHR1NOVm9TTU12eE1xR3pjak95YkFzWHpNN3ZKUmFvdjZEaFk3MkwxNXhMb1NLSTFaUDdJUlk5MWlpdW1OYnNuMkhZYzQ1cDQtRkd6cnMza0xNbHRQRHg3ZW5NbmVENjNaeUpQN1JOVUnSAfYBQVVfeXFMT1B5bkdkT0s0YXRtRzF5RS1pNDFXQTlLZHhrQnVZbU5RM3V2R2J2UW81a3NQOE8zd1VBcmtFbUNiRnlPaDA3LTlIT25DZ3dhOE9wRksxRXE5eEJaV2xLSVZ4OFowMFN5SzF3OU4tajdDdjFfVEFvZTFXVDl2dmdQZHVHd1drUjdOOVc4TlhDZmhhT0h6RmlWQ1M2ckxJMGxPWXZFVUl5WnJudzJIM2NoWkhUa3ptb1pGVUszN0RjRGN2TjN4aExoV202enh1OEdYOWJRdmhhTldhcFAxeHFydnFPU2VFXzdCblVIYmJnSWoxOXRCaEpB?oc=5</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Retomada da obras da UFN-III deve suprir 15% da ureia nacional - Notícias Agrícolas</t>
+          <t>Ureia, MAP e potássio registram queda no Brasil - Agrolink</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3558,19 +3558,19 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQaG9vWDljNUdZd3NycVNvUGpFQVdvLUc5UUE3RV9BSTlOTF9SX29XRkR5VEprWF9XejVyUjVlQVNpT0ZuWHFCa3lRYmp4Z1Rxb3d6ZjRjU0stWThQU2FadEtzSjhlSFoxMVpiSEhEYzROOEo4WTBqSmtCeG1paGItSzEyalB3QjJXRXNnVlFiOTZRN3hnaGNzbjZYUmFCaUpLb1BBTWxpRzNnUkU3M1ZrWDBWaG1wUDlxUkFReVhmSEY1a25TMTFZR2hJa05Ncnd1ZnBR0gHYAUFVX3lxTFA3SXZoYkJzV1h5SjRvMmE3bGlVQW51cW1Kd3AzS3Y0ay1QRzhWZ095Ylg5dnBGM1pHMGE5OWdOQzhUaGN3RDNYNUhXZzAzeE5VSFhfTkotUEpaWXk1UEplNkNlVmdzenZMZWVBTVFnUFJSNWtsQmczUGhnc2lqOVNPbUYzYkxqaWxKOGp3TUhZMTRBeXdQS2hIN1RQaXhUeTNhSkNnN1NDLXQ2YTFTNGhza3A5TGMyZ3VuNHFPenR5ZVE3S1drbVZua09VNWVLbVZuamM5Z2hNaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQckZkR0twcU1KM1hzRlBoYnlKaEVXbERoOEJfSk5zLVJHSlFXc2pVS0hqRlQ0djV0b2o5NDY0azg3REJLbnBlaVJ2VWZ6Y2lzaVF4STlrWlh4TDcteXBGN29xWDdTc0hmU1pROF9UZ2d4UlR0bGFtNjd6UzZqakxCeGlHTEZRTUVReHllcG5NOFV4OFRXZ05YZTIySlg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ureia, MAP e potássio registram queda no Brasil - agrolink.com.br</t>
+          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi - Valor Econômico</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3580,19 +3580,19 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQckZkR0twcU1KM1hzRlBoYnlKaEVXbERoOEJfSk5zLVJHSlFXc2pVS0hqRlQ0djV0b2o5NDY0azg3REJLbnBlaVJ2VWZ6Y2lzaVF4STlrWlh4TDcteXBGN29xWDdTc0hmU1pROF9UZ2d4UlR0bGFtNjd6UzZqakxCeGlHTEZRTUVReHllcG5NOFV4OFRXZ05YZTIySlg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOQmNERDdXd2o0VlYxZXE2aDRFUV90bEdkWTd6ZUwyNjhJMDZBV20xbWxWZ2V6VGVtZG83VHFjSnVDU3ppbUZpTm1tY3NSWUNmRFhxeW5VaEp2SHp3c1BjVkxQZXBNZEhrd2RUdHVKZUNFTHlHZFliODlHMHp4c3lMbXhVUkhqWjltOFRzUVlJMU9Da0RIZnk2Y3B6bUVTelRSZ2tUT0c1aFVZamlSTERiX2ZIa1puUnVrUlQ1aDhtRW1uLVBZZ0NSSU91RGpPY243OWVLOXp3TGNjU0pKR015dFQ2RGI1dDdO0gH3AUFVX3lxTE1jZVlGVWNwdWlxX2lGVGpRTnRPUXJJNTJWbXJTcXRjb3lQQVFNT3A5TVhPM2xpSmRNOVZKZmFFR3Y5eEJnRlRNX0taNmppMTdVT1dBeDRKVjQ2TzNPZHR0OEhBRWlmM3VBaWcwQjVzSDZmM1hVNmJTcVVRR1VGYzkxY2trZ3FXMjNpNzlnUkRxLXB6UG0xbVBFZmU5MVVIa3FVZkdSMFFwaGhBeGZna01zOVNwUGFKMXpQdkstaWhud1RxVEJXUXVFdmt1bXdjNHF3azh6Vi0zSG1tbzE0aHQwaUFUNjNwdXVRNUdOaWlJeFVXTmZTSXM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Programa Terra Boa 2026 garante distribuição gratuita de calcário para fortalecer a agricultura em Navegantes - Prefeitura de Navegantes -</t>
+          <t>Martin Marietta confirma acordo de US$ 13,5 bilhões pela Lhoist North America - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3602,19 +3602,19 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQYlpYdmcxN2o2cDRhamVVcW5PQjNBTDdLd05XZDIzUDJrd0ZuOTVwUHg1SUlqb2pXamZGMXZmODZjRTlSOU11YnpINUk1bnhkUjhrWjFZX1RlQWUxVDV2UEIzbU83N09lWTBadmlEdnJVcm1uZ2d3a1pGeFFLcGlGYndtLUJHWVJjSS1Bc0UwRHdpNlJMbzJJTjREVm5ocDhHay16VTdrbVZ1NWhzb0dPOHFkWTAza25ENVZSSDFDdk94dnFYZGZMcVFNNDktekVwMjhvQVN2Zk9UVHppem5vcFl2SEM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNYUJCZDhUVml3MGVqMUw2QllsRmVrTF90WjJCYjhGUEtuVlVpc2hRNzJ6UzhJaDd3a1lnU0MtYnFGUGU4SmxNb1Jwc0hpZnJubUpVQ1U3UjhGYkk2a2VtRFg0Vl9mYWt4aXIxYV9xZF9SM29OcFhPdUJaVWVMQlcxcERTay1YODdGaVNMT2owWWdYeWNEWW5KbHk1Q19sTllKMng2T1lNNTBTZFAxRW5nV1pid2tZNnRzejJCc3M3SURsdGFXQnJGazhZRQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi - Valor Econômico</t>
+          <t>Programa Terra Boa 2026 garante distribuição gratuita de calcário para fortalecer a agricultura em Navegantes - Prefeitura de Navegantes -</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOQmNERDdXd2o0VlYxZXE2aDRFUV90bEdkWTd6ZUwyNjhJMDZBV20xbWxWZ2V6VGVtZG83VHFjSnVDU3ppbUZpTm1tY3NSWUNmRFhxeW5VaEp2SHp3c1BjVkxQZXBNZEhrd2RUdHVKZUNFTHlHZFliODlHMHp4c3lMbXhVUkhqWjltOFRzUVlJMU9Da0RIZnk2Y3B6bUVTelRSZ2tUT0c1aFVZamlSTERiX2ZIa1puUnVrUlQ1aDhtRW1uLVBZZ0NSSU91RGpPY243OWVLOXp3TGNjU0pKR015dFQ2RGI1dDdO0gH3AUFVX3lxTE1jZVlGVWNwdWlxX2lGVGpRTnRPUXJJNTJWbXJTcXRjb3lQQVFNT3A5TVhPM2xpSmRNOVZKZmFFR3Y5eEJnRlRNX0taNmppMTdVT1dBeDRKVjQ2TzNPZHR0OEhBRWlmM3VBaWcwQjVzSDZmM1hVNmJTcVVRR1VGYzkxY2trZ3FXMjNpNzlnUkRxLXB6UG0xbVBFZmU5MVVIa3FVZkdSMFFwaGhBeGZna01zOVNwUGFKMXpQdkstaWhud1RxVEJXUXVFdmt1bXdjNHF3azh6Vi0zSG1tbzE0aHQwaUFUNjNwdXVRNUdOaWlJeFVXTmZTSXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQYlpYdmcxN2o2cDRhamVVcW5PQjNBTDdLd05XZDIzUDJrd0ZuOTVwUHg1SUlqb2pXamZGMXZmODZjRTlSOU11YnpINUk1bnhkUjhrWjFZX1RlQWUxVDV2UEIzbU83N09lWTBadmlEdnJVcm1uZ2d3a1pGeFFLcGlGYndtLUJHWVJjSS1Bc0UwRHdpNlJMbzJJTjREVm5ocDhHay16VTdrbVZ1NWhzb0dPOHFkWTAza25ENVZSSDFDdk94dnFYZGZMcVFNNDktekVwMjhvQVN2Zk9UVHppem5vcFl2SEM?oc=5</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Martin Marietta confirma acordo de US$ 13,5 bilhões pela Lhoist North America - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Martin Marietta anuncia aquisição da Lhoist North America por US$ 13,5 bilhões - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3646,29 +3646,29 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNYUJCZDhUVml3MGVqMUw2QllsRmVrTF90WjJCYjhGUEtuVlVpc2hRNzJ6UzhJaDd3a1lnU0MtYnFGUGU4SmxNb1Jwc0hpZnJubUpVQ1U3UjhGYkk2a2VtRFg0Vl9mYWt4aXIxYV9xZF9SM29OcFhPdUJaVWVMQlcxcERTay1YODdGaVNMT2owWWdYeWNEWW5KbHk1Q19sTllKMng2T1lNNTBTZFAxRW5nV1pid2tZNnRzejJCc3M3SURsdGFXQnJGazhZRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXg3YkM0VFFac3BVN0QwMmZqYm9rQW9XM1ppUzRJTl85Y3FkMEhHSFY1Q0NON2pxTE9uTUNob0N1bkw5bFA5Y002X1VVTzdLT1JmdDFGUk16cDBJaEc1eFdLdlZwNWYtZXFxVnVjUnA5QlhWaGhFZmJUalBLQXpJZFF2TmpmVjZfZFM4THVXQndEUUlZYnI4X3FLY1VoQ2tNY1NyNFVZVkpaSmdxanJwQTVxcGJCNmxtOTBOZklvY3JlbzQtM2NMX0NRZmY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Falta de enxofre acende alerta na indústria de fertilizantes no Brasil - Primeira Página</t>
+          <t>Retomada da obras da UFN-III deve suprir 15% da ureia nacional - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>28/06/2026 04:00</t>
+          <t>29/06/2026 04:00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNeEpidlVpTkg1WmVXMWlzMTQ3cGNIblRXMV9wX2xsOU1yZG9weml0QkdfVC0xdmNuektjM1N5eEc5Ulh0dUdmWlFfRW9kVGRSVUwwVzJOb3NiclRjeEdJY0pyd1hiVUl2aEZIZkJwbGRuSV9WeUE1NHVTQWhvNlBKcVZwa0NnRnN2V2JlYmpudHhkei1BQUVfMXRUZi1LUDJ2TFhwZC1RNXFydw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQaG9vWDljNUdZd3NycVNvUGpFQVdvLUc5UUE3RV9BSTlOTF9SX29XRkR5VEprWF9XejVyUjVlQVNpT0ZuWHFCa3lRYmp4Z1Rxb3d6ZjRjU0stWThQU2FadEtzSjhlSFoxMVpiSEhEYzROOEo4WTBqSmtCeG1paGItSzEyalB3QjJXRXNnVlFiOTZRN3hnaGNzbjZYUmFCaUpLb1BBTWxpRzNnUkU3M1ZrWDBWaG1wUDlxUkFReVhmSEY1a25TMTFZR2hJa05Ncnd1ZnBR0gHYAUFVX3lxTFA3SXZoYkJzV1h5SjRvMmE3bGlVQW51cW1Kd3AzS3Y0ay1QRzhWZ095Ylg5dnBGM1pHMGE5OWdOQzhUaGN3RDNYNUhXZzAzeE5VSFhfTkotUEpaWXk1UEplNkNlVmdzenZMZWVBTVFnUFJSNWtsQmczUGhnc2lqOVNPbUYzYkxqaWxKOGp3TUhZMTRBeXdQS2hIN1RQaXhUeTNhSkNnN1NDLXQ2YTFTNGhza3A5TGMyZ3VuNHFPenR5ZVE3S1drbVZua09VNWVLbVZuamM5Z2hNaQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3680,17 +3680,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - Globo Rural</t>
+          <t>Falta de enxofre acende alerta na indústria de fertilizantes no Brasil - Primeira Página</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>26/06/2026 04:00</t>
+          <t>28/06/2026 04:00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWDFOU0tpUTJqVVQxcEVDUmRCQXB2Sm95SXJwZlIyVkNxVmMxM3FpY0xVbnZxR3IyZkNFZE9NS3VOenZGYjVZcEUxN3hWOVJkNG51SGNhemc1TVQ4YWlLNEE1SFl6eVNjaWtZVnltMG4wU2VYTEZCMFI3Y21mZVBjNTBvSHE5eXlGR0dkQzFCVG5LTTBzOWdXRnJhM1dSV2hiQkJhNFFzajhwRTdlSXVzWV9MTDZiZ3RMSW9jbmxZYW_SAc8BQVVfeXFMT0l2YXdPMW5WTVN1OHFpQWNBekR5R0dKX1Y4WkY5dEtVbFdKVHJDMm9hV1lTY2FsQnFsVG92d2RuM0V1cGNCUmhYZHZjdzFzVlNkckxKaDhnVm9PUVNYRnJBaEt4WG5NVDloSWhLbEFZQmdXSWhqdFNzRU1ySDBHdmRYUlZZTDd0UzI3d3lzSm5ZRTM0Y2NCWnVMaU9WWElKa0pBZjlPUk5yS1ZhLV9Nd3FDRHVxMVF2bUVTWFprQTYwc2hpa3YtRzhKVi1hQUtr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNeEpidlVpTkg1WmVXMWlzMTQ3cGNIblRXMV9wX2xsOU1yZG9weml0QkdfVC0xdmNuektjM1N5eEc5Ulh0dUdmWlFfRW9kVGRSVUwwVzJOb3NiclRjeEdJY0pyd1hiVUl2aEZIZkJwbGRuSV9WeUE1NHVTQWhvNlBKcVZwa0NnRnN2V2JlYmpudHhkei1BQUVfMXRUZi1LUDJ2TFhwZC1RNXFydw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Crise dos fertilizantes: estoque baixo de enxofre ameaça a próxima safra - band.com.br</t>
+          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - Globo Rural</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3712,19 +3712,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQdGoxOXo2NXl5WnpUd3E1ZWQ5RldtTUR2M0F6YnljMXNxb2NVM0RrVDY3WTE5SExJYzdmbzZPYlFlOXhrUTRoZnJ2amFPR2wzNGlVd2JTNDhzYkplbHVET0pJeTh0U292YmtkT1NPb01lY1JyRDk5MG9TaTNEZHQ3ZjlJU0lXNXJJTkRWZUNFbUtUbmdPN3oxX3Z4cVJvWWdtRks4TV9VcXM3SjduOElxckFTSGpncTNJb01YUllNa0RNTmYtVm53T2lHYlJPTEV5ajVCQk1wQThIMnU5aWtHSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWDFOU0tpUTJqVVQxcEVDUmRCQXB2Sm95SXJwZlIyVkNxVmMxM3FpY0xVbnZxR3IyZkNFZE9NS3VOenZGYjVZcEUxN3hWOVJkNG51SGNhemc1TVQ4YWlLNEE1SFl6eVNjaWtZVnltMG4wU2VYTEZCMFI3Y21mZVBjNTBvSHE5eXlGR0dkQzFCVG5LTTBzOWdXRnJhM1dSV2hiQkJhNFFzajhwRTdlSXVzWV9MTDZiZ3RMSW9jbmxZYW_SAc8BQVVfeXFMT0l2YXdPMW5WTVN1OHFpQWNBekR5R0dKX1Y4WkY5dEtVbFdKVHJDMm9hV1lTY2FsQnFsVG92d2RuM0V1cGNCUmhYZHZjdzFzVlNkckxKaDhnVm9PUVNYRnJBaEt4WG5NVDloSWhLbEFZQmdXSWhqdFNzRU1ySDBHdmRYUlZZTDd0UzI3d3lzSm5ZRTM0Y2NCWnVMaU9WWElKa0pBZjlPUk5yS1ZhLV9Nd3FDRHVxMVF2bUVTWFprQTYwc2hpa3YtRzhKVi1hQUtr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Ureia despenca após trégua no Oriente Médio - agrolink.com.br</t>
+          <t>Crise dos fertilizantes: estoque baixo de enxofre ameaça a próxima safra - band.com.br</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3734,63 +3734,63 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPbnhnc1BFMXFtQ2VwTkVHaUtLWHlXSVAweGtSVE8xMXRBTGJyT0p5QzZzaWVrQU5PODJuMlp2elZib3Ftem1UaEotZ0FmZFZGclhtdzN5MTdyX0FIZ3dfNHk0dng3d1dLM0xlWlNkR1V5ZGoxcDlNNkNNMEZHcHJINmVnQ1R2X1luYkRxamdqTWFYSVBaVFdV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQdGoxOXo2NXl5WnpUd3E1ZWQ5RldtTUR2M0F6YnljMXNxb2NVM0RrVDY3WTE5SExJYzdmbzZPYlFlOXhrUTRoZnJ2amFPR2wzNGlVd2JTNDhzYkplbHVET0pJeTh0U292YmtkT1NPb01lY1JyRDk5MG9TaTNEZHQ3ZjlJU0lXNXJJTkRWZUNFbUtUbmdPN3oxX3Z4cVJvWWdtRks4TV9VcXM3SjduOElxckFTSGpncTNJb01YUllNa0RNTmYtVm53T2lHYlJPTEV5ajVCQk1wQThIMnU5aWtHSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CMOC: Produção de cobre, cobalto e nióbio aumenta em relação ao mesmo período do ano anterior no primeiro trimestre; planeja produzir 600.000-660.000 toneladas de cobre metal em 2025 - Shanghai Metals Market</t>
+          <t>Ureia despenca após trégua no Oriente Médio - Agrolink</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>25/06/2026 02:45</t>
+          <t>26/06/2026 04:00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxNeHdIR1BSb0xPU1ZwbXhzOFpLcm5VUlpxLXhIdU4xLXUxbjZKTlhIMFhGRnJuTFBYejVabTNBNUtyVDZPbVBaeXcySUhGN2YxTDBLdVpfUllHOGdkNjN1SWpWOXBfck54ZVRJVFQyYUh6Yy1QX0ZCN29nQzRhRWxON0d4bjJJU2JQbDAtakZKcGZ1enZzaEVlamgyUnR3WmVpamJwM1JSS0pZS1NiYUU2aXEyc0E2bzhQa0Z6S2ZlWHhMb1BMQVlVb1NMdjFCeHJyRlEwUWNJdTFUdWdMVXcyOWRSaXRmSW9rRldyaGtndkMxSTlPUHVQNS1JamF0X2tDTHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPbnhnc1BFMXFtQ2VwTkVHaUtLWHlXSVAweGtSVE8xMXRBTGJyT0p5QzZzaWVrQU5PODJuMlp2elZib3Ftem1UaEotZ0FmZFZGclhtdzN5MTdyX0FIZ3dfNHk0dng3d1dLM0xlWlNkR1V5ZGoxcDlNNkNNMEZHcHJINmVnQ1R2X1luYkRxamdqTWFYSVBaVFdV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - Globo Rural</t>
+          <t>CMOC: Produção de cobre, cobalto e nióbio aumenta em relação ao mesmo período do ano anterior no primeiro trimestre; planeja produzir 600.000-660.000 toneladas de cobre metal em 2025 - Shanghai Metals Market</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>24/06/2026 04:00</t>
+          <t>25/06/2026 02:45</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxNeHdIR1BSb0xPU1ZwbXhzOFpLcm5VUlpxLXhIdU4xLXUxbjZKTlhIMFhGRnJuTFBYejVabTNBNUtyVDZPbVBaeXcySUhGN2YxTDBLdVpfUllHOGdkNjN1SWpWOXBfck54ZVRJVFQyYUh6Yy1QX0ZCN29nQzRhRWxON0d4bjJJU2JQbDAtakZKcGZ1enZzaEVlamgyUnR3WmVpamJwM1JSS0pZS1NiYUU2aXEyc0E2bzhQa0Z6S2ZlWHhMb1BMQVlVb1NMdjFCeHJyRlEwUWNJdTFUdWdMVXcyOWRSaXRmSW9rRldyaGtndkMxSTlPUHVQNS1JamF0X2tDTHc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
+          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - Globo Rural</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3800,51 +3800,51 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank</t>
+          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>23/06/2026 20:20</t>
+          <t>24/06/2026 04:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a708dfe9d64428db7eaae7b5418b70f&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f06%2fimportacao-de-ureia-no-brasil-atinge-menor-nivel-em-dez-anos-diz-rabobank.ghtml&amp;c=12218677441374849487&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Produtores rurais podem se inscrever para receber calcário gratuito em Santa Cruz - gaz.com.br</t>
+          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>23/06/2026 04:00</t>
+          <t>23/06/2026 20:20</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOVG45N0p1WG9vdGlfX3Q1YUNZWkFmYmJ2cU1DUHFGbEZqcHJkYnhSNWxtQ01PT3N4S3AxVzFnVllQcmJfZUZoZG45a2JmM2Q2RFJGazZQeWJYTlJTcTdtUm5fcl9YRFg5ZEtySDR5QzFBX2dXUThWQVJ1bXdBME4wc2d1R1o1dFIzME5DVTFCQ0daUi1JbUwtZWFFTy1VTWNMQVNHeW04dlHSAa4BQVVfeXFMTWxhNlNVMXpuVllWUDl1LXlOVV93Q3E2RHpEbWJaZEF6T1NIbHFGRTBRdy1XT05EWDloR2ZNQjJSLXJNaHhfcUNZZUsySkp2UDZyaEZPT0hwMHdXWGRMQVpYdFA0U2tYcTFzYnJjOVV3bHAwQjBmR0hZUWxiN0IzODRlWGR4Rno1bWpveDFZNk1HeENPUXFSS0VQdGpZMmpkd0FJdlNFT3I4cWNGd2Fn?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a70b55a3a634a76ae17ecd7f5011589&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f06%2fimportacao-de-ureia-no-brasil-atinge-menor-nivel-em-dez-anos-diz-rabobank.ghtml&amp;c=12218677441374849487&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -3895,34 +3895,34 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ureia despenca e volta aos níveis pré-guerra - agrolink.com.br</t>
+          <t>Produtores rurais podem se inscrever para receber calcário gratuito em Santa Cruz - gaz.com.br</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>22/06/2026 04:00</t>
+          <t>23/06/2026 04:00</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOVG45N0p1WG9vdGlfX3Q1YUNZWkFmYmJ2cU1DUHFGbEZqcHJkYnhSNWxtQ01PT3N4S3AxVzFnVllQcmJfZUZoZG45a2JmM2Q2RFJGazZQeWJYTlJTcTdtUm5fcl9YRFg5ZEtySDR5QzFBX2dXUThWQVJ1bXdBME4wc2d1R1o1dFIzME5DVTFCQ0daUi1JbUwtZWFFTy1VTWNMQVNHeW04dlHSAa4BQVVfeXFMTWxhNlNVMXpuVllWUDl1LXlOVV93Q3E2RHpEbWJaZEF6T1NIbHFGRTBRdy1XT05EWDloR2ZNQjJSLXJNaHhfcUNZZUsySkp2UDZyaEZPT0hwMHdXWGRMQVpYdFA0U2tYcTFzYnJjOVV3bHAwQjBmR0hZUWxiN0IzODRlWGR4Rno1bWpveDFZNk1HeENPUXFSS0VQdGpZMmpkd0FJdlNFT3I4cWNGd2Fn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Visconde supera Monerá e é campeão da Copa do Calcário 2026 - Serra News</t>
+          <t>Preços dos fertilizantes despencam com fim de interrupções no Oriente Médio - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQdDBrMzFVejA0SWNzMERWbzFwVWNVSm5XZ2lWd1lTQzlqX3BBX09mRFcwZV9Qa2l1WUxNekNKSFZHNFJrekl6TnEzWE9IWW1hb2xVTS1XSzRwOU1rdEtFdzRzWk1SNEdOVTN6VzE1ZTN1Vk9aLWttaFBldUU1Qm1EUFhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOWVZYaXFVXzYxUkM4OVhCXzdzd1JicHdJQmF6cy1wOHhTX1p5NUNKS2RndEZWMEtVbUlCaURtQUhlVl93cF9NdzNLcTV4NEJJWTJaaW5tLTBHOUl3OVJFbXRJY1ZVTnlJUExfY2E4a2hwLVVUWExaakhSWFc3RHV2T0l0Y1dxYnh5aE12bklILU1ySzU3MmNRcHNWczBNUHVhYVRueUdsQUplSDVkcjNsck1GVF9uMXQzdWk4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Prefeitura de Peixoto garante 1.752 toneladas de calcário para fortalecer a agricultura familiar e aumentar a produtividade no campo - Nortão Agora</t>
+          <t>Ureia despenca e volta aos níveis pré-guerra - Agrolink</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3954,19 +3954,19 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxQTWhuakU3WXV0dkFOZXdxRjRiaDRjOHZUbWVWSjE2ZFFLVEVIcnhkb3BpM3Awd3NBdHBKMDAtRmlxTEt0MGpMUXU5OFNoSlRQQTlGUTJ2Tk5nM1RZb29GaG5abFJEaEJWb1owTHhrTU52REEydVpMVmpabVU0dS1pdllxV2gwRWNORkxwcE9xS1BGS0JWN2t6YzN4WWRWN1dSaTZucHN6M0d5MnBlZlNoVXk5MkVudVctQjljd3lsSUUyTFVkdHZaY2MyT1Z4Q3ZhSzY5bkF2bGREMjkteFJPZFhvY1BWUGhqa0VOT0QtUEp3c3ZGZ2tnM1NRdTVRMmJHTXBtZDlGQlJGOTdiREZ0QTNSUkthdmstOTdiTDBxRHVVNHJoTWZ4eklJZ0U2T2xmX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Preços dos fertilizantes despencam com fim de interrupções no Oriente Médio - brasilagro.com.br</t>
+          <t>Visconde supera Monerá e é campeão da Copa do Calcário 2026 - Serra News</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3976,29 +3976,29 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOWVZYaXFVXzYxUkM4OVhCXzdzd1JicHdJQmF6cy1wOHhTX1p5NUNKS2RndEZWMEtVbUlCaURtQUhlVl93cF9NdzNLcTV4NEJJWTJaaW5tLTBHOUl3OVJFbXRJY1ZVTnlJUExfY2E4a2hwLVVUWExaakhSWFc3RHV2T0l0Y1dxYnh5aE12bklILU1ySzU3MmNRcHNWczBNUHVhYVRueUdsQUplSDVkcjNsck1GVF9uMXQzdWk4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQdDBrMzFVejA0SWNzMERWbzFwVWNVSm5XZ2lWd1lTQzlqX3BBX09mRFcwZV9Qa2l1WUxNekNKSFZHNFJrekl6TnEzWE9IWW1hb2xVTS1XSzRwOU1rdEtFdzRzWk1SNEdOVTN6VzE1ZTN1Vk9aLWttaFBldUU1Qm1EUFhn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia: perspectiva após fim do conflito com Irã - Farmnews</t>
+          <t>Prefeitura de Peixoto garante 1.752 toneladas de calcário para fortalecer a agricultura familiar e aumentar a produtividade no campo - nortaoagora.com.br</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>21/06/2026 04:00</t>
+          <t>22/06/2026 04:00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNb1dTZU45Ulg5NzZPTUFZT0JnV2swWVJkTERUb1hDMy1faHZ6RHFsdzJXWHNCeERXdW1iNl9MYXV1WlhjVWtNWlJDV2xWWXJIelJjTHFETjgtbkZaWXBSVndiTXJpWW1SaXBnN242ZGlBX01jWGlvUVgyTUNXS0RsOFg1WU82c2U3T2FvOHZQMUZoRWRnZkhTbklsSi15TWtz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxQTWhuakU3WXV0dkFOZXdxRjRiaDRjOHZUbWVWSjE2ZFFLVEVIcnhkb3BpM3Awd3NBdHBKMDAtRmlxTEt0MGpMUXU5OFNoSlRQQTlGUTJ2Tk5nM1RZb29GaG5abFJEaEJWb1owTHhrTU52REEydVpMVmpabVU0dS1pdllxV2gwRWNORkxwcE9xS1BGS0JWN2t6YzN4WWRWN1dSaTZucHN6M0d5MnBlZlNoVXk5MkVudVctQjljd3lsSUUyTFVkdHZaY2MyT1Z4Q3ZhSzY5bkF2bGREMjkteFJPZFhvY1BWUGhqa0VOT0QtUEp3c3ZGZ2tnM1NRdTVRMmJHTXBtZDlGQlJGOTdiREZ0QTNSUkthdmstOTdiTDBxRHVVNHJoTWZ4eklJZ0U2T2xmX2c?oc=5</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Principais exportadores de ureia para o Brasil em 2026, até abril - Farmnews</t>
+          <t>Preço futuro da ureia: perspectiva após fim do conflito com Irã - Farmnews</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4020,41 +4020,41 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPQkZnLXNRb0ZVWkxHckFMZVE4c3paNXJDcnU2SlZYbDA3bkRDYzlVOFJMVUxuS1hwVW5GWjJEVzZVTTMtT3hPd1J3X2FBR1hsZ2lHZjU4TmRYUGxZVVRlcFp3djlHNkhUZUNWUGpUS2hsTFczTUlLLXN5Mjl6R0JId21Pb0p2V3FzTEVfQ1JhTm00b25fZzFJVGhfMHM1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNb1dTZU45Ulg5NzZPTUFZT0JnV2swWVJkTERUb1hDMy1faHZ6RHFsdzJXWHNCeERXdW1iNl9MYXV1WlhjVWtNWlJDV2xWWXJIelJjTHFETjgtbkZaWXBSVndiTXJpWW1SaXBnN242ZGlBX01jWGlvUVgyTUNXS0RsOFg1WU82c2U3T2FvOHZQMUZoRWRnZkhTbklsSi15TWtz?oc=5</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Alan Trindade vai apitar a grande final da Copa do Calcário - FERJ</t>
+          <t>Principais exportadores de ureia para o Brasil em 2026, até abril - Farmnews</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>20/06/2026 04:00</t>
+          <t>21/06/2026 04:00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMEpsNl94b085dkU2TXVTZTFRV0pDZ2FoZzJ3Y3d6ZU1fMk11TVJzWEIwNzRZQmpXbGFyNFBWOElBOFREcmRWZDZGNVkwVEVVaEFQZy11X09VVVBzdmJ5U09CNzdxQ2VuQjAxT1NRSkZzTGZPYkdpSlUxSTFET1lOLXVFbUNicTlVbzhMdmk4WnQ5clpnNjJsVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPQkZnLXNRb0ZVWkxHckFMZVE4c3paNXJDcnU2SlZYbDA3bkRDYzlVOFJMVUxuS1hwVW5GWjJEVzZVTTMtT3hPd1J3X2FBR1hsZ2lHZjU4TmRYUGxZVVRlcFp3djlHNkhUZUNWUGpUS2hsTFczTUlLLXN5Mjl6R0JId21Pb0p2V3FzTEVfQ1JhTm00b25fZzFJVGhfMHM1QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>O recuo estratégico da Mosaic no Brasil - VEJA</t>
+          <t>Alan Trindade vai apitar a grande final da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4064,95 +4064,95 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNcWNOZnE5TE9kN3JvVzA4eThSNEV3NFVQanBMcm1WdVd5YUhoa2N1UFlTMTNvUXQtNDhoX05LeGlGRlBLNzBfeGI1VnNJV3M0NklZLTBhNXJEY0FwV0YzMjg3Vm5iQzJ5OFV0UkRqbThiTjhmQ1ExX2V3MnFJbEM2c1RZUkd2QS13YWxwS0w4Z2stNms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMEpsNl94b085dkU2TXVTZTFRV0pDZ2FoZzJ3Y3d6ZU1fMk11TVJzWEIwNzRZQmpXbGFyNFBWOElBOFREcmRWZDZGNVkwVEVVaEFQZy11X09VVVBzdmJ5U09CNzdxQ2VuQjAxT1NRSkZzTGZPYkdpSlUxSTFET1lOLXVFbUNicTlVbzhMdmk4WnQ5clpnNjJsVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Viter, da Votorantim Cimentos, entra no mercado de foliares e investe R$ 300 milhões na “mistura” - AgFeed</t>
+          <t>O recuo estratégico da Mosaic no Brasil - VEJA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>19/06/2026 04:00</t>
+          <t>20/06/2026 04:00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPUWJ5VkZXQTJ4VjNNaWw2R2xKZ3BtLUYwazI4QzVZeGJzUnlESXFvcXFreEdDQVZnT0ZnMS1LMzhfWE1zTVoyRGp4ODlDdHppdFU2N3R4Y1RSM2k0WFN5OU51c2hHZzJfZldiWnlMaXJTM0w3dF8xTmZGM0FnSi10VXFTT3EtakJVR2dJUno5NzNiWHhpWHl2V0hBR0ZEQUtoaTlyWndNMjdMZEdVRHpIbF96aXVJZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNcWNOZnE5TE9kN3JvVzA4eThSNEV3NFVQanBMcm1WdVd5YUhoa2N1UFlTMTNvUXQtNDhoX05LeGlGRlBLNzBfeGI1VnNJV3M0NklZLTBhNXJEY0FwV0YzMjg3Vm5iQzJ5OFV0UkRqbThiTjhmQ1ExX2V3MnFJbEM2c1RZUkd2QS13YWxwS0w4Z2stNms?oc=5</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Acordo EUA-Irã derruba preço da ureia no mercado, diz StoneX - Revista Cultivar</t>
+          <t>Viter, da Votorantim Cimentos, entra no mercado de foliares e investe R$ 300 milhões na “mistura” - AgFeed</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>17/06/2026 04:00</t>
+          <t>19/06/2026 04:00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPeXVPMHdlb3dCNlk1NlBBNjFmcER0XzF0VVpVT2hmTDVqZDRpZThJOHFYdGlNN2pyMTFuZ3ZySjJTRWdLSWdCb2dkWVUtZW9WQkRtSGl2cEFxWFJBSFRvQUlKQnFYQTluTTFabWxvRFFPSHJ6eG5BYVBUS05WX085OFlCVEUzd0JKNEk0YmdMV2dqRlg1dnhtTFJORUlITjZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPUWJ5VkZXQTJ4VjNNaWw2R2xKZ3BtLUYwazI4QzVZeGJzUnlESXFvcXFreEdDQVZnT0ZnMS1LMzhfWE1zTVoyRGp4ODlDdHppdFU2N3R4Y1RSM2k0WFN5OU51c2hHZzJfZldiWnlMaXJTM0w3dF8xTmZGM0FnSi10VXFTT3EtakJVR2dJUno5NzNiWHhpWHl2V0hBR0ZEQUtoaTlyWndNMjdMZEdVRHpIbF96aXVJZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Atualização Chaos Cubed - Minecraft</t>
+          <t>Acordo EUA-Irã derruba preço da ureia no mercado, diz StoneX - revistacultivar.com.br</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>16/06/2026 14:20</t>
+          <t>17/06/2026 04:00</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9iNk5LM015QjM1VEdzU2F5cDlKZHNJVHZfLWtuR1FyVWtfUUdzN0cyOVdJYWNPXzVWejQtdkRXUDhPc0ljenhLaGFzcUJ3b25UMzluVjc5Rzlwb2pRbXFSTk1YTWJuMDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPeXVPMHdlb3dCNlk1NlBBNjFmcER0XzF0VVpVT2hmTDVqZDRpZThJOHFYdGlNN2pyMTFuZ3ZySjJTRWdLSWdCb2dkWVUtZW9WQkRtSGl2cEFxWFJBSFRvQUlKQnFYQTluTTFabWxvRFFPSHJ6eG5BYVBUS05WX085OFlCVEUzd0JKNEk0YmdMV2dqRlg1dnhtTFJORUlITjZn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil despenca em maio: dados de 2018 a 2026 - Farmnews</t>
+          <t>Atualização Chaos Cubed - Minecraft</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>16/06/2026 04:00</t>
+          <t>16/06/2026 14:20</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOc2dmVzJBa0tyZGQ3T3dCOFlFZjhkQXg0SmFjUmltT3RmbVlKSDlfYm1vOHNDMG5kdTdDalcyQ3dmTTlyY00taHRwTVhRSE54ZUdjdEZNWVEwYkRmRV9JS0FOY0xIQ01ISUF3VHA5ZmVZVS1XdlA2Mzk1UUNEbHFuT1VyUFhYSWZlU2lVay0wYUl1WmFzaEg5VmpKaGw1OTFHdWlHdDBGWlpqUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9iNk5LM015QjM1VEdzU2F5cDlKZHNJVHZfLWtuR1FyVWtfUUdzN0cyOVdJYWNPXzVWejQtdkRXUDhPc0ljenhLaGFzcUJ3b25UMzluVjc5Rzlwb2pRbXFSTk1YTWJuMDg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ureia cai mais de 40% e volta ao nível pré-crise com avanço de acordo entre EUA e Irã - Notícias Agrícolas</t>
+          <t>Importação de ureia pelo Brasil despenca em maio: dados de 2018 a 2026 - Farmnews</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOMGREaHlncEZNM3ZPbjY2Mkdjcmp3b0xIYnNyd0ZrQ0ZIU1VOd1Z1SzlZRXRWYnJVSW9YN25rTVI2dV9BbkpxQ3ExTnJET2laeDJxSEJhTlFmbVR1NjJLVGVXMlRwN1pONGprSFhTeHVfeHFhaTh3LU91dml3ZnBkU19QMDRWeTlvVmZVOFBzTkpYRWNXVzgtS3ljUXVRYkVRSFlnX2VrWHQyWl83RUxZaFBNZFNkTEJsMmdIVW5EaWJ1QzFsbEhTNG1Ia2ZaVWItOG5vMndxaVlZMElfM3NmZXUwX2U0bmRVdEHSAe8BQVVfeXFMUHU1T0d6VUZOVnNHME1ySkpyV2NsbmtiTHBjZjIwVHJjRHBXRUR2R1pleTZjT1FBZi1CbUhxNnFTUUJUZ0xBZTZ5NG1KWUUzcnVpMHZSNkYzWG9NcGI2OEpuOFdCSllRYTlVa2hXMEpnRjUwTTV5NTlmQ21FOVhEQTFVZm5wdEU0akc2V0hNdV9JbFNCSGxlWW1DN3lFa0xIRmxSdldQR1BwYmJ5RDRzMW5kek1NNllsZ0I1VDB5WEhTNktSNGdqb1RkV0xWZ1NadlBPbmx3dXh1aUNHcVRTWk1Sbmw0NnFJbmk5R3JlYmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOc2dmVzJBa0tyZGQ3T3dCOFlFZjhkQXg0SmFjUmltT3RmbVlKSDlfYm1vOHNDMG5kdTdDalcyQ3dmTTlyY00taHRwTVhRSE54ZUdjdEZNWVEwYkRmRV9JS0FOY0xIQ01ISUF3VHA5ZmVZVS1XdlA2Mzk1UUNEbHFuT1VyUFhYSWZlU2lVay0wYUl1WmFzaEg5VmpKaGw1OTFHdWlHdDBGWlpqUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4186,29 +4186,29 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Ureia volta ao preço pré-guerra, mas vendas ainda não reagem - CNN Brasil</t>
+          <t>Ureia cai mais de 40% e volta ao nível pré-crise com avanço de acordo entre EUA e Irã - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>15/06/2026 04:00</t>
+          <t>16/06/2026 04:00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOT2J4STBfU3p3enNZSHhWZjZxcVc2YUp3VDlhanpJMHI4dWVpREtfanF3dWFiV1hiSWN2NWxmMFJqQk1FY0w3Rm43OWVfSlpFS3J5SWM3ZzZnbXJQa25hWVMxYmNCd2QwalBGa2dQenc1NmZVZHJ3U0NxRUxqay1nTHdlMTFGNDR3RUxwRWs4cnAwWF9TVGNlWXc5ZDdiSldlUzFKdzhTRGQ4bTN3ckVpNFV5cHhmX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOMGREaHlncEZNM3ZPbjY2Mkdjcmp3b0xIYnNyd0ZrQ0ZIU1VOd1Z1SzlZRXRWYnJVSW9YN25rTVI2dV9BbkpxQ3ExTnJET2laeDJxSEJhTlFmbVR1NjJLVGVXMlRwN1pONGprSFhTeHVfeHFhaTh3LU91dml3ZnBkU19QMDRWeTlvVmZVOFBzTkpYRWNXVzgtS3ljUXVRYkVRSFlnX2VrWHQyWl83RUxZaFBNZFNkTEJsMmdIVW5EaWJ1QzFsbEhTNG1Ia2ZaVWItOG5vMndxaVlZMElfM3NmZXUwX2U0bmRVdEHSAe8BQVVfeXFMUHU1T0d6VUZOVnNHME1ySkpyV2NsbmtiTHBjZjIwVHJjRHBXRUR2R1pleTZjT1FBZi1CbUhxNnFTUUJUZ0xBZTZ5NG1KWUUzcnVpMHZSNkYzWG9NcGI2OEpuOFdCSllRYTlVa2hXMEpnRjUwTTV5NTlmQ21FOVhEQTFVZm5wdEU0akc2V0hNdV9JbFNCSGxlWW1DN3lFa0xIRmxSdldQR1BwYmJ5RDRzMW5kek1NNllsZ0I1VDB5WEhTNktSNGdqb1RkV0xWZ1NadlBPbmx3dXh1aUNHcVRTWk1Sbmw0NnFJbmk5R3JlYmM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Fertilizantes mais caros pela crise global elevam busca por calcário no Nordeste - Movimento Econômico</t>
+          <t>Ureia volta ao preço pré-guerra, mas vendas ainda não reagem - CNN Brasil</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPb2k2YlpLQ3ByYm54MXAzMk9FbFBXbTVYYTFkWkpvSi1hbEtBcERXSXI5QVVxd2RiVVdTTU5MWGM4U3k0Y3J1b3FwNnFRVTRlNC1uUGZFdHZ0eDNzME0tTHJ6RDJKd09wNW04SnVUUTV2TC14Vzh1c3J6RjVmUHIwN1J4dVloX2oxNjljT0pCRk9iMC0zZTJfWHFwdlljek5uQ0s4TjVVR3dLbHJzMGpYNzNpdjFUTFRXcjFzcHZ5M04zcGFxQ2JRQk9BdmZxQTY2SzlGVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOT2J4STBfU3p3enNZSHhWZjZxcVc2YUp3VDlhanpJMHI4dWVpREtfanF3dWFiV1hiSWN2NWxmMFJqQk1FY0w3Rm43OWVfSlpFS3J5SWM3ZzZnbXJQa25hWVMxYmNCd2QwalBGa2dQenc1NmZVZHJ3U0NxRUxqay1nTHdlMTFGNDR3RUxwRWs4cnAwWF9TVGNlWXc5ZDdiSldlUzFKdzhTRGQ4bTN3ckVpNFV5cHhmX2c?oc=5</t>
         </is>
       </c>
     </row>
@@ -4269,100 +4269,100 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Programa de Calcário entra na reta final e deve beneficiar mais de 600 produtores em Patrocínio - difusora95.com.br</t>
+          <t>Fertilizantes mais caros pela crise global elevam busca por calcário no Nordeste - Movimento Econômico</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>12/06/2026 04:00</t>
+          <t>15/06/2026 04:00</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNbXkwMlBGcUY3Tm1nUWpFZkp4X1Q5VmlEazBKQ1R3emRpVnVDZjJLNG8wOXVhMk05YTdVenF4akpxbjJXZ3J4c0QwR2pueHJyak5sWDFWOE1wWlRKZ3ZqRl8za1ZLdF95QUE3SjRyVzQ3ZTJVUnlueXIxMnJ6WklKSWU5U0x6MHFaVkRPU1ZqYXp0aUZsWmdhR1d3YlJET1lNV0JWQlBMaDJDTmlYTjQ2eGlTdUt4ckdMMlJEd05HWWRrZDRuSW4tMnpTaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPb2k2YlpLQ3ByYm54MXAzMk9FbFBXbTVYYTFkWkpvSi1hbEtBcERXSXI5QVVxd2RiVVdTTU5MWGM4U3k0Y3J1b3FwNnFRVTRlNC1uUGZFdHZ0eDNzME0tTHJ6RDJKd09wNW04SnVUUTV2TC14Vzh1c3J6RjVmUHIwN1J4dVloX2oxNjljT0pCRk9iMC0zZTJfWHFwdlljek5uQ0s4TjVVR3dLbHJzMGpYNzNpdjFUTFRXcjFzcHZ5M04zcGFxQ2JRQk9BdmZxQTY2SzlGVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>cal agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Usina Ipê contrata: veja os cargos que estão disponíveis em Nova Independência - Andravirtual</t>
+          <t>Programa de Calcário entra na reta final e deve beneficiar mais de 600 produtores em Patrocínio - difusora95.com.br</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>11/06/2026 04:00</t>
+          <t>12/06/2026 04:00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNLUdjdzBOczQwTk8wWlNCb2pMbXppNGhHR2hkWm8xTUxXWGhfZS0zVTR2RXJCYlRyaVZLZWpPZGROTkh1OTRkU1psb2F3WGFCeHl5Umt0Z3ZJX3owcGZIZ0ljSl9BdmY1cll3d3FYNWdWbkZGZWZRS2lLOGZBeG8zaWkxMXBFMWttckdkSEVYSVhOaVdMUm1aYnlCZmthRHBWTW8xMEdzMG5xakhmQW1LZzlDem1VRnZ6eFZ2R1ZQcnpSdU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNbXkwMlBGcUY3Tm1nUWpFZkp4X1Q5VmlEazBKQ1R3emRpVnVDZjJLNG8wOXVhMk05YTdVenF4akpxbjJXZ3J4c0QwR2pueHJyak5sWDFWOE1wWlRKZ3ZqRl8za1ZLdF95QUE3SjRyVzQ3ZTJVUnlueXIxMnJ6WklKSWU5U0x6MHFaVkRPU1ZqYXp0aUZsWmdhR1d3YlJET1lNV0JWQlBMaDJDTmlYTjQ2eGlTdUt4ckdMMlJEd05HWWRrZDRuSW4tMnpTaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>cal agricola</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Governo do Tocantins fortalece agricultura familiar com distribuição de 60 mil toneladas de calcário - Agência Tocantins</t>
+          <t>Usina Ipê contrata: veja os cargos que estão disponíveis em Nova Independência - Andravirtual</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>10/06/2026 04:00</t>
+          <t>11/06/2026 04:00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOdnJQWjZ6cnBCdGlCMjliVDZTeGxBN3JmdEUzT1VRM016MmM2UWFPVkx1WFo3UjFFRm96VF9GaVBnSGk4YkJPWHB3TGppemN1S3pGNDJ5VU9NbDUxbnVaanRMUm5vUTN3VzZ1MzhzYXAzT3lVVzU1Y3dJR1Z5LXRXZHdQRnhZNHRHdW1LR2c4NFk2RmxQYjFmV1d3anVDZ083R2RSSDZad0FmbGZhUEFweWhxbEU3SnA2ZGJwU3hac185SDJJelZYWGxXUlJodnJJVFA1TW5zNk45SFJoX0FsNHNtQ2JYZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNLUdjdzBOczQwTk8wWlNCb2pMbXppNGhHR2hkWm8xTUxXWGhfZS0zVTR2RXJCYlRyaVZLZWpPZGROTkh1OTRkU1psb2F3WGFCeHl5Umt0Z3ZJX3owcGZIZ0ljSl9BdmY1cll3d3FYNWdWbkZGZWZRS2lLOGZBeG8zaWkxMXBFMWttckdkSEVYSVhOaVdMUm1aYnlCZmthRHBWTW8xMEdzMG5xakhmQW1LZzlDem1VRnZ6eFZ2R1ZQcnpSdU0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
+          <t>Governo do Tocantins fortalece agricultura familiar com distribuição de 60 mil toneladas de calcário - Agência Tocantins</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>09/06/2026 04:00</t>
+          <t>10/06/2026 04:00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOdnJQWjZ6cnBCdGlCMjliVDZTeGxBN3JmdEUzT1VRM016MmM2UWFPVkx1WFo3UjFFRm96VF9GaVBnSGk4YkJPWHB3TGppemN1S3pGNDJ5VU9NbDUxbnVaanRMUm5vUTN3VzZ1MzhzYXAzT3lVVzU1Y3dJR1Z5LXRXZHdQRnhZNHRHdW1LR2c4NFk2RmxQYjFmV1d3anVDZ083R2RSSDZad0FmbGZhUEFweWhxbEU3SnA2ZGJwU3hac185SDJJelZYWGxXUlJodnJJVFA1TW5zNk45SFJoX0FsNHNtQ2JYZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Próximos jogos Copa do Mundo 2026: como colocar no seu calendário do celular - Exame</t>
+          <t>Preço da ureia cai mais de 30% e alivia pressão sobre alimentos após choque da guerra - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4372,19 +4372,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQR1dUblpzcG93RTlEeS1RQ2FDdERVVHgwVGF0YlFLdnZucnlCRi00TUxPQ0wwQkVqTU40QXJVNjJxUlVqOXdDQXhwV3Z6dWdjX2NLdXdlRHlyc3FpRUxQTTVtbzBTVzA2N2Z2dTk4dnJ0MDIyTnpCZXVZQ1R5VkJGQ3pjd1ZiYzZ0ejhhdmhpODFRRzF6LWxtRUVxcms4TFN5ZVAyeXoxM2J1Zi1LTWg0Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNXzFFRXVUUkQzY1F4TE5zTUtTMEtBM0M4UE1HTF9WazN5RXBYeVBnekxhV3RBVUM5bWhfdy1UUk1kWkRLYkR6YVV2VVIxZzVWdXMzYkpRNExqSlNGYWFaNWEtTU55RExMVlUzWkxVSHpsWFA5XzZjaU1uZ01hQkV6Um50dnZ1Y3BhZHV5SzFOX0dlTkM5azlqdHQxWWE2bmV5VEhMckY3NFJsVDVzVVAzVi04Um9XNFpBNzUtYWhpMFNhZ9IB1gFBVV95cUxOVXVKbXdHM3RhdzdIWXpFN21kRl9zQlZDU3RYMlhVMTVEU3FXWDBBd1hQa0NueVhsSmJPemlmQVlDT3NlbnJKa3hOTnhCajlmU2N5U2Z0NFljZ0dmeHljT2R1cGZQRmJESFZRLVNGcE04by14dkEtei1tQTBtX0lUZ2I5Q3BXNU85Z0V1RDV5eHZFM1FpRHkzbUdrS3kwQXo5WnFkY1dxRUpEMTZjOEdxNmE0aTZ6TGxvRnA3eXFQSjB6T2VuUWNPdmdGRDF6SGdRQlJ6WXJn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Queda do risco da guerra no Irã derruba preços da ureia - Globo Rural</t>
+          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Preço da ureia cai mais de 30% e alivia pressão sobre alimentos após choque da guerra - Bloomberg Línea Brasil</t>
+          <t>Queda do risco da guerra no Irã derruba preços da ureia - Globo Rural</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4416,63 +4416,63 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNXzFFRXVUUkQzY1F4TE5zTUtTMEtBM0M4UE1HTF9WazN5RXBYeVBnekxhV3RBVUM5bWhfdy1UUk1kWkRLYkR6YVV2VVIxZzVWdXMzYkpRNExqSlNGYWFaNWEtTU55RExMVlUzWkxVSHpsWFA5XzZjaU1uZ01hQkV6Um50dnZ1Y3BhZHV5SzFOX0dlTkM5azlqdHQxWWE2bmV5VEhMckY3NFJsVDVzVVAzVi04Um9XNFpBNzUtYWhpMFNhZ9IB1gFBVV95cUxOVXVKbXdHM3RhdzdIWXpFN21kRl9zQlZDU3RYMlhVMTVEU3FXWDBBd1hQa0NueVhsSmJPemlmQVlDT3NlbnJKa3hOTnhCajlmU2N5U2Z0NFljZ0dmeHljT2R1cGZQRmJESFZRLVNGcE04by14dkEtei1tQTBtX0lUZ2I5Q3BXNU85Z0V1RDV5eHZFM1FpRHkzbUdrS3kwQXo5WnFkY1dxRUpEMTZjOEdxNmE0aTZ6TGxvRnA3eXFQSjB6T2VuUWNPdmdGRDF6SGdRQlJ6WXJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Com conflitos se arrastando, oferta mundial de gás natural e enxofre segue restrita e preços, em alta - CEPEA-Esalq/USP</t>
+          <t>Próximos jogos Copa do Mundo 2026: como colocar no seu calendário do celular - Exame</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>08/06/2026 14:33</t>
+          <t>09/06/2026 04:00</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxORC1iTVJMYlpNR2J3LU1md0ZhOFZ3NF9kamV0YmRNTWZfYU9xU0d0R0NXWGo1TndlcXBOamRXWm1OUHVxSGFNUjFiaE14LWprNlBibHRfMDVCd1ZEQ3hmZS1RNkZycl9lb0djN3dwd2JWTEdGbGppSmk3b2JqbVY0c2p0R09pcFpHQVFiNGQzekxUZVFwd0JZMVRGRE85bC0temhncE1OWm5ZVTBkbFhzNEVYMGpfb2JjQkJXMEJZVzZ2T0h3aXBVQUdMOXJaRmlfMmpWOGtvVUx0QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQR1dUblpzcG93RTlEeS1RQ2FDdERVVHgwVGF0YlFLdnZucnlCRi00TUxPQ0wwQkVqTU40QXJVNjJxUlVqOXdDQXhwV3Z6dWdjX2NLdXdlRHlyc3FpRUxQTTVtbzBTVzA2N2Z2dTk4dnJ0MDIyTnpCZXVZQ1R5VkJGQ3pjd1ZiYzZ0ejhhdmhpODFRRzF6LWxtRUVxcms4TFN5ZVAyeXoxM2J1Zi1LTWg0Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Ureia cai 32%, mas compras seguem lentas - agrolink.com.br</t>
+          <t>Com conflitos se arrastando, oferta mundial de gás natural e enxofre segue restrita e preços, em alta - cepea.org.br</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>08/06/2026 04:00</t>
+          <t>08/06/2026 14:33</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxORC1iTVJMYlpNR2J3LU1md0ZhOFZ3NF9kamV0YmRNTWZfYU9xU0d0R0NXWGo1TndlcXBOamRXWm1OUHVxSGFNUjFiaE14LWprNlBibHRfMDVCd1ZEQ3hmZS1RNkZycl9lb0djN3dwd2JWTEdGbGppSmk3b2JqbVY0c2p0R09pcFpHQVFiNGQzekxUZVFwd0JZMVRGRE85bC0temhncE1OWm5ZVTBkbFhzNEVYMGpfb2JjQkJXMEJZVzZ2T0h3aXBVQUdMOXJaRmlfMmpWOGtvVUx0QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Empresas ampliam vagas e buscam talentos - Portal UAI</t>
+          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNNmJmTzczLUFGbU8tQ3dxY2RFTU1aeDY4ZVVQSXo2dlNUbzBHY3lmd2IyU2VzVk1nQTFYdTBxdDRLWkxQNTk1elR5ZkcyWUk4M1F1cDZUekYtcGhpZXl1SHZPel9vT19YT0xGLUIwdkVNZUVrZTczaTdXdU9kNUd5eFY4aU9oQ0JtVEc4dXFBNmNCdWpUa3V3YUg3M09PZ2xEYUlDd3VSS0dfSEhRXzlhUlducmpoSkx1WG5rZVFOLUhlVlNGRHpmNUFhdFVuRWNXR1V0X3hzRUoyc0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Visconde e Monerá estão na decisão da Copa do Calcário - FERJ</t>
+          <t>Monerá e Visconde são os grandes finalistas da Copa do Calcário - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4504,19 +4504,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdTE4ODV2amJMQVVTaUd3bXdPa1psaE91azdMNDIwTHJSd3NDdDRMZEstX3pzWHBmdXlhd2d0dXphTlNYelc2T19zVTRJVVJmWktXRDlac2Q0RVoxeWQ1TTl3R2NnVkRHNS1pWTljYm8xSjRzY1JrUV82SldFNEFsRkp5MjBDdjdSQnhNRF9ibmxDUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOb2tvdUhDbG0yZzRQc0dxa0l1eS14YzVtQjdEdV9CVUF3LUZXMUdreUdJcHUtWkhIcVNtU1E5NmNfcC05LXQ3aHBJaGNqOUxMZEhtQ1hYNWVKQmR3U3lzNm5fQ1ZiLXNvS2szVU1iTWVLN0hkazZhcS15NGdUX0YzZnFLcnlyeGVxSDRnbFNURndKR29IaWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Final da Copa do Calcário terá duelo entre Monnerat e Visconde de Imbé - Serra News</t>
+          <t>Empresas ampliam vagas e buscam talentos - Portal UAI</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1uYVlFb3dGSV9VTGxhQTVScHhYZkVBR3hhN3Qwem5hZU5UWmpOUTlkTFBVT2MtYmJOcEZEX3BGYzM3eHAxYTlORnFpdXA0Rk5LVzdPcHJ0Rm0yaFZXRTI0U2d3dnFLN3VmdFF4dUZJWS0zY19BVVNDMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNNmJmTzczLUFGbU8tQ3dxY2RFTU1aeDY4ZVVQSXo2dlNUbzBHY3lmd2IyU2VzVk1nQTFYdTBxdDRLWkxQNTk1elR5ZkcyWUk4M1F1cDZUekYtcGhpZXl1SHZPel9vT19YT0xGLUIwdkVNZUVrZTczaTdXdU9kNUd5eFY4aU9oQ0JtVEc4dXFBNmNCdWpUa3V3YUg3M09PZ2xEYUlDd3VSS0dfSEhRXzlhUlducmpoSkx1WG5rZVFOLUhlVlNGRHpmNUFhdFVuRWNXR1V0X3hzRUoyc0k?oc=5</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Monerá e Visconde são os grandes finalistas da Copa do Calcário - jornaldaregiao.com</t>
+          <t>Visconde e Monerá estão na decisão da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4548,29 +4548,29 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOb2tvdUhDbG0yZzRQc0dxa0l1eS14YzVtQjdEdV9CVUF3LUZXMUdreUdJcHUtWkhIcVNtU1E5NmNfcC05LXQ3aHBJaGNqOUxMZEhtQ1hYNWVKQmR3U3lzNm5fQ1ZiLXNvS2szVU1iTWVLN0hkazZhcS15NGdUX0YzZnFLcnlyeGVxSDRnbFNURndKR29IaWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdTE4ODV2amJMQVVTaUd3bXdPa1psaE91azdMNDIwTHJSd3NDdDRMZEstX3pzWHBmdXlhd2d0dXphTlNYelc2T19zVTRJVVJmWktXRDlac2Q0RVoxeWQ1TTl3R2NnVkRHNS1pWTljYm8xSjRzY1JrUV82SldFNEFsRkp5MjBDdjdSQnhNRF9ibmxDUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Fraqueza da demanda leva a sexta semana consecutiva de queda para cotações da ureia - Notícias Agrícolas</t>
+          <t>Final da Copa do Calcário terá duelo entre Monnerat e Visconde de Imbé - Serra News</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>04/06/2026 04:00</t>
+          <t>08/06/2026 04:00</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQNU13Y2pGel8wdnA0OXNQWWNNQWFTSDluTFpDUjFlaFFzNnZlTFc2S0RYS3BaT3NUZVhLR0R0VGc5VGxoRUFjVUxfSjVCRDZsLW5nTGlVWXBCaWUtczVFVlpPN0tTOEgwb2ZKT29MYWp6cUFUektYVmJyRWNTV3Y1b21BRUpMYklhZzdyMEhGbzZSbkREcS1MOEdEYnFxV0VOOE1yV1dseUh6bVJVR3VGNE5xSFF3RmVpNm5neDFmM29lNnZWLUIzSkFDS19hS0VqZWoxWWRNY2RHMFp3ZTVEVWFlbWpHZk1Q0gHuAUFVX3lxTE1nZFhKbkZGNkJUeDZoZWQ1NmUxVzAzTjRWVmhLTmZVaVNjM1BaYTYxdzdSUzZ3OWc3NlM4TjJJVzc0bmpTNjdlOHBmNWhpdmhrRE5RelhUYXdMajJRakU1RE5tZlJZeVZmX0hkNWw4c0xfRjFseUtmMXdzZVJoUWN6Q09BMTJheFZSMC16dUJYbUxUY3Z4blRtaVhTQzhxemFkYms4bTRRWW1OTThVZmRhQzBPVGZTN21zbVRUUnNCVXVFWjF0eTJ6QmJrN0gzaWZMZTVGaVdMVXZ1TVhET24ydDY0bWpkNHJ3aW5sa1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1uYVlFb3dGSV9VTGxhQTVScHhYZkVBR3hhN3Qwem5hZU5UWmpOUTlkTFBVT2MtYmJOcEZEX3BGYzM3eHAxYTlORnFpdXA0Rk5LVzdPcHJ0Rm0yaFZXRTI0U2d3dnFLN3VmdFF4dUZJWS0zY19BVVNDMg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4582,61 +4582,61 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Ureia recua e fosfatados seguem sustentados - agrolink.com.br</t>
+          <t>Fraqueza da demanda leva a sexta semana consecutiva de queda para cotações da ureia - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>03/06/2026 04:00</t>
+          <t>04/06/2026 04:00</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNM3A5LWx3T1lNOWVsYXFVUFBUd3hESks0cXV0bDNLUTlxaFlsZXNOeHRJaU9vSDY4d1did1ozNDQ1NEN4eWR3Y3JoU3pBZnlTMkxGQzV6QlJWYXl2QUZRRFFTdk5Dd1lpaWJnX29uMkxIS2phb05IaXJKeUh2YnNFT2hud0VjOHE1ZFlGVUtSWXBvT1JLcWVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQNU13Y2pGel8wdnA0OXNQWWNNQWFTSDluTFpDUjFlaFFzNnZlTFc2S0RYS3BaT3NUZVhLR0R0VGc5VGxoRUFjVUxfSjVCRDZsLW5nTGlVWXBCaWUtczVFVlpPN0tTOEgwb2ZKT29MYWp6cUFUektYVmJyRWNTV3Y1b21BRUpMYklhZzdyMEhGbzZSbkREcS1MOEdEYnFxV0VOOE1yV1dseUh6bVJVR3VGNE5xSFF3RmVpNm5neDFmM29lNnZWLUIzSkFDS19hS0VqZWoxWWRNY2RHMFp3ZTVEVWFlbWpHZk1Q0gHuAUFVX3lxTE1nZFhKbkZGNkJUeDZoZWQ1NmUxVzAzTjRWVmhLTmZVaVNjM1BaYTYxdzdSUzZ3OWc3NlM4TjJJVzc0bmpTNjdlOHBmNWhpdmhrRE5RelhUYXdMajJRakU1RE5tZlJZeVZmX0hkNWw4c0xfRjFseUtmMXdzZVJoUWN6Q09BMTJheFZSMC16dUJYbUxUY3Z4blRtaVhTQzhxemFkYms4bTRRWW1OTThVZmRhQzBPVGZTN21zbVRUUnNCVXVFWjF0eTJ6QmJrN0gzaWZMZTVGaVdMVXZ1TVhET24ydDY0bWpkNHJ3aW5sa1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações em Tapira, devido à falta de enxofre e custo da matéria-prima - Jornal Araxá</t>
+          <t>Ureia recua e fosfatados seguem sustentados - Agrolink</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>02/06/2026 12:15</t>
+          <t>03/06/2026 04:00</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPeGt1SzZTRTQ4QkxZbXVuRmlZQWJIWlg5RGZkX0VuVTk2ZkVzMERUUy1CZ0dyU21qZTZQclpTd0ZUaXdMb21VZGszMHVldE1oYWI3UlhmZjUwV1V4em9zblNSd2lRT3c3eGhIdjlnOWxnanl0Sk5keW5DZjQ2cUYyR0RSUGZaU1NhNkFEYUw1TDVpOFdjRnZZLWVvNUlxRjZRZlppSHhFVFJoUGxNc1pkb0ZuNUc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNM3A5LWx3T1lNOWVsYXFVUFBUd3hESks0cXV0bDNLUTlxaFlsZXNOeHRJaU9vSDY4d1did1ozNDQ1NEN4eWR3Y3JoU3pBZnlTMkxGQzV6QlJWYXl2QUZRRFFTdk5Dd1lpaWJnX29uMkxIS2phb05IaXJKeUh2YnNFT2hud0VjOHE1ZFlGVUtSWXBvT1JLcWVR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Ureia mais barata, mas não o suficiente - AgFeed</t>
+          <t>Mosaic suspende operações em Tapira, devido à falta de enxofre e custo da matéria-prima - Jornal Araxá</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>02/06/2026 04:00</t>
+          <t>02/06/2026 12:15</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQNERlNFpxYnhTaVVMdkhzcG9RWG1rN1M4T0VWR1lLbmRGSE1OR1E0UkhxMUw5ZGtJWjd2dmJabHZ6eWF3UFRBZ2JfWDhjS1gzaTJUSWVDd21BY2tuN3ZTcmNqMGNsZjhuUFA4RnNld0pPZmtwTGg5ajZsdllNeG5WaFlCbTlUREtUcmhudEx3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPeGt1SzZTRTQ4QkxZbXVuRmlZQWJIWlg5RGZkX0VuVTk2ZkVzMERUUy1CZ0dyU21qZTZQclpTd0ZUaXdMb21VZGszMHVldE1oYWI3UlhmZjUwV1V4em9zblNSd2lRT3c3eGhIdjlnOWxnanl0Sk5keW5DZjQ2cUYyR0RSUGZaU1NhNkFEYUw1TDVpOFdjRnZZLWVvNUlxRjZRZlppSHhFVFJoUGxNc1pkb0ZuNUc?oc=5</t>
         </is>
       </c>
     </row>
@@ -4670,29 +4670,29 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Preços da ureia acumulam 25% de queda; o que isso significa para a próxima safra? - Canal Rural</t>
+          <t>Ureia mais barata, mas não o suficiente - AgFeed</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>01/06/2026 04:00</t>
+          <t>02/06/2026 04:00</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZ1daY2E3S1J5SkVNUnpBSjd2N0kyWTBpY3o2MTNBRno4UFNoeVhQMzJiUFhVb3dZXzFmRnlES2dqcHpfRFQyS3Y2UTBUdXk2UUpNY1FubFA1eFMzcnlSblFvRVljSUNmYUN4SWdFeURZSm42YkEwWnBic1hYMy1VRDIydmNEWTlIWnI2SHJXMHlvdGRYcUdqSjFNdFU5LUd3V1A0a0lfT1pnUXlpMU5kZ0IyNXhFRi13ZnI3a2F3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQNERlNFpxYnhTaVVMdkhzcG9RWG1rN1M4T0VWR1lLbmRGSE1OR1E0UkhxMUw5ZGtJWjd2dmJabHZ6eWF3UFRBZ2JfWDhjS1gzaTJUSWVDd21BY2tuN3ZTcmNqMGNsZjhuUFA4RnNld0pPZmtwTGg5ajZsdllNeG5WaFlCbTlUREtUcmhudEx3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Ureia cai pela sexta semana seguida no Brasil - agrolink.com.br</t>
+          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - Clarim Araxá</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4702,19 +4702,19 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTGszenpHeUpYSkdXWW16LWIzWG54YVBRR1lvNElURnZURHlYUlJ5a3hvR3ROTVhiN1RXVDVJTzBPOHRrT2hVc1VsWWdYaHVUaW9nRWFCaDJFUHJaUk5XZUtrQ3BibGxqR3JRWklEbE0tRFM0cEYtcTUtNEtvaEV6eFQ3WmY1SjdCUURkcnhDMG1KRnFoT0x6WE1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Copa do Calcário: vagas para a grande final serão decididas no próximo domingo - Serra News</t>
+          <t>Mosaic suspende mineração em Tapira por 30 dias e acende alerta em Uberaba - JM Online</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNem9RT0xBWGhHc0dKc0t1NjBWaUdkVGxVcGhRbE1GYmU2WDV3WDdMQ2ZfQnBhZGQ2YlMxZFo4NmsxR1NLeWVJbkxHdFRmT3VIVnpNRlZrVjktNDZYR05fQnVPYzJoQkpJdlhQVTRuSDAtWTdfT3JWamRTUGhOQW9xV2JkSFllT1UzTnNMbk9vaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOMU1lSmhaSEJPbE5tbmdCU3ozeXVFcUdfX2dGZ2k3c3hGUzNaX2NCTUlfMlZiZjBLa2xXSHpFUURHbFBwLWRVZFdKOXJFVjBhb2t5SnZjVGJYcS1zRGlPNVN3dFRuVHF3WEtXeFkxelM2dUV4S0tLME41WVBFV1lZZWJSbFNZVzQwSEZNUk9teEtQM1M5eV90cnBpeWpCSW5kVDFNZl96aFd4TEd6aEV0OUMyMTLSAbwBQVVfeXFMTjl1UzR0Q2dTWHFEN0FqdktmQ0Nlc2p3YXBYLVpNTnlGVUFXOGNwUXNuMTZRdWZoQ2ttSHFzNEZsY2ltWjdqT05uUVpPSjdaUkR2YTFXYXV6RVZERU5rRk52ZGU1d2Vac2ptRDFTVXFVWGgzZTFCNzMyZ0VpZ1o4RWpLa044YUVEX2lMWEJYVDAta1RWRnhrV1BKYmZpSVpKSm56N2wzU3dCQldWV3R0VEJLNTJGbHdxY0VRdVo?oc=5</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Preços da ureia recuam 25% - mas nem isso anima o mercado - AgFeed</t>
+          <t>Preços da ureia acumulam 25% de queda; o que isso significa para a próxima safra? - canalrural.com.br</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPajBDOHUtVWZFN2QwalllTlN0eEhJOG03dE5Ia1JQNlpwRW52MVVjbG5Ya1ZYaGt0QU04dVB4b2ZSdU53blVHcHVVRThzVEs0bFpoY3ZOcjJUay1EVjZXZW00TTNJc19RV0gtdUxtNGVZRFNFM2FjaHk1NkRjR0dGWkVfS0NfZFJzWFNFUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZ1daY2E3S1J5SkVNUnpBSjd2N0kyWTBpY3o2MTNBRno4UFNoeVhQMzJiUFhVb3dZXzFmRnlES2dqcHpfRFQyS3Y2UTBUdXk2UUpNY1FubFA1eFMzcnlSblFvRVljSUNmYUN4SWdFeURZSm42YkEwWnBic1hYMy1VRDIydmNEWTlIWnI2SHJXMHlvdGRYcUdqSjFNdFU5LUd3V1A0a0lfT1pnUXlpMU5kZ0IyNXhFRi13ZnI3a2F3?oc=5</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Ureia acumula queda de 25% no Brasil e completa seis semanas de recuo - StoneX</t>
+          <t>Preços da ureia recuam 25% - mas nem isso anima o mercado - AgFeed</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4768,19 +4768,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYlZ0RlFXX1VzV2k0cnNvMkJWc09sU3ZfQ09uQWlUQ1oxb0wzcTB2QjZaWXlzZnd0bzcxNGJheGp4UmRrWTU1WlVIRTdYaS1Gc1NaaEZidWsyaFlBZE9FcFN6MmMyUDdoX256OEYxbGpVUnJsMXZlZ0d4TWg1UXlidHJha01tYy02WXVGVzR0X0hxWmoyV3RTbXhROUJuLXhMOFRpZm5ZMFNUOEFKalhMNjUyQno?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPajBDOHUtVWZFN2QwalllTlN0eEhJOG03dE5Ia1JQNlpwRW52MVVjbG5Ya1ZYaGt0QU04dVB4b2ZSdU53blVHcHVVRThzVEs0bFpoY3ZOcjJUay1EVjZXZW00TTNJc19RV0gtdUxtNGVZRFNFM2FjaHk1NkRjR0dGWkVfS0NfZFJzWFNFUw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - Clarim Araxá</t>
+          <t>Ureia cai pela sexta semana seguida no Brasil - Agrolink</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4790,29 +4790,29 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTGszenpHeUpYSkdXWW16LWIzWG54YVBRR1lvNElURnZURHlYUlJ5a3hvR3ROTVhiN1RXVDVJTzBPOHRrT2hVc1VsWWdYaHVUaW9nRWFCaDJFUHJaUk5XZUtrQ3BibGxqR3JRWklEbE0tRFM0cEYtcTUtNEtvaEV6eFQ3WmY1SjdCUURkcnhDMG1KRnFoT0x6WE1B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário mais nutritivo resistente à umidade e ao vento - Paraná Central</t>
+          <t>Ureia acumula queda de 25% no Brasil e completa seis semanas de recuo - StoneX</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>31/05/2026 04:00</t>
+          <t>01/06/2026 04:00</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOdk56ZUFYa2pGdWtqdzRMRjJNTmRzNExlY3pPSnpmZjVsQ2ZCT3pJeDl1UGk1dzR1bmRJYjB0akk5alp1YW83empGWHY2TVhzWXdfRHlrenRSRFNHUmx5dS1pLW83YXhWX3ZsSldMM3luSXNScEJRUUpNdTVBM3hTV2tFdDdnRkZvTkowU3IxbU1ZWTBiNVRKSXRhWi05QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYlZ0RlFXX1VzV2k0cnNvMkJWc09sU3ZfQ09uQWlUQ1oxb0wzcTB2QjZaWXlzZnd0bzcxNGJheGp4UmRrWTU1WlVIRTdYaS1Gc1NaaEZidWsyaFlBZE9FcFN6MmMyUDdoX256OEYxbGpVUnJsMXZlZ0d4TWg1UXlidHJha01tYy02WXVGVzR0X0hxWmoyV3RTbXhROUJuLXhMOFRpZm5ZMFNUOEFKalhMNjUyQno?oc=5</t>
         </is>
       </c>
     </row>
@@ -4824,17 +4824,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Embrapa desenvolve calcário granulado com função corretiva e nutritiva - Canal Rural</t>
+          <t>Copa do Calcário: vagas para a grande final serão decididas no próximo domingo - Serra News</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>31/05/2026 04:00</t>
+          <t>01/06/2026 04:00</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOck1oOHdwUmVRMjZleHc1UWEzV1B2REJFbXF5ZGQ0enIyaXpPbVZMY1NWcU1FWjUxMjd6MG9KbVVNanBjNDhZcTlmek1zRFczeE9jaFhUcEhzUGpXMkYwOEVjaHNTSURmMG81LUZhYW9FeWZONFMyMjJlb0EzeUlvSzNLYTUyQXYzWEJPdUgwLTR6d3JHdU5aNVRjQXdQZjJrVmozQ1U4NFYtRlZmLXQ4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNem9RT0xBWGhHc0dKc0t1NjBWaUdkVGxVcGhRbE1GYmU2WDV3WDdMQ2ZfQnBhZGQ2YlMxZFo4NmsxR1NLeWVJbkxHdFRmT3VIVnpNRlZrVjktNDZYR05fQnVPYzJoQkpJdlhQVTRuSDAtWTdfT3JWamRTUGhOQW9xV2JkSFllT1UzTnNMbk9vaw?oc=5</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário mais nutritivo e resistente à umidade - CompreRural</t>
+          <t>Embrapa cria calcário mais nutritivo resistente à umidade e ao vento - Paraná Central</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY3VDcDE0TVJIcGRwOVozMnozYk12NFEtRnhYcVVJSTd2ZlpCR0Y4WlpXdmI1QTJaMVAxSDJQc285M3NGSGZNYTNVd001WVVxbW1XdGFpTzJfdlg3Y0lQVHBBWEVqMXVFLVFBcFZaSTVqWmR3eFZvejVZa00zako5Tk5GYk9IS0xNMURFSGZ2clUyZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOdk56ZUFYa2pGdWtqdzRMRjJNTmRzNExlY3pPSnpmZjVsQ2ZCT3pJeDl1UGk1dzR1bmRJYjB0akk5alp1YW83empGWHY2TVhzWXdfRHlrenRSRFNHUmx5dS1pLW83YXhWX3ZsSldMM3luSXNScEJRUUpNdTVBM3hTV2tFdDdnRkZvTkowU3IxbU1ZWTBiNVRKSXRhWi05QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário mais nutritivo resistente à umidade e ao vento - Tua Rádio</t>
+          <t>Embrapa cria calcário que reduz perdas e aumenta produtividade no campo - Exame</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOTm55bWM5blVJYmljekhUT0xQRlZZMUh2OUdYUXNqRUVtNUFUaFdaQURiQ1FldWZrZmVmWXZ4XzJmRVRxTlNDckRRekdHM3pzc2h0YjJ1RGpIR0dLaFp6N2VPRTcza0hfMzlYSjlGUkE5azFKMXRBd3I1dU5QNk42U3h3QVA4bFRINldUc2M2YU0tYkdzZ0kxMFhKYkh4TlM4NmxONTVtRnFUQWRFVU4tUVpXVHZxWjFKRm1uc3ZocmdNVS0xdWJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbUFVRVpOaU54dHozMHJBc3EzSlE1c0JBXzZkci1IR09EVEcxejBEekdPYXE4THV0SUtIemQ3QjItVTRwYXpZTHVUV3ctU3M5WHBVbjNJaVhHVnlNVGI3elZmUWlLWFlwZzNETEE0TjRNY1NkYklMYlQwQ1BNN0Z1Y1JsQ3FDZVItSmFuYzFKRnFXLVdNM1BjRnJlRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário que reduz perdas e aumenta produtividade no campo - Exame</t>
+          <t>Embrapa cria calcário mais nutritivo e resistente à umidade - comprerural.com</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4900,73 +4900,73 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbUFVRVpOaU54dHozMHJBc3EzSlE1c0JBXzZkci1IR09EVEcxejBEekdPYXE4THV0SUtIemQ3QjItVTRwYXpZTHVUV3ctU3M5WHBVbjNJaVhHVnlNVGI3elZmUWlLWFlwZzNETEE0TjRNY1NkYklMYlQwQ1BNN0Z1Y1JsQ3FDZVItSmFuYzFKRnFXLVdNM1BjRnJlRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY3VDcDE0TVJIcGRwOVozMnozYk12NFEtRnhYcVVJSTd2ZlpCR0Y4WlpXdmI1QTJaMVAxSDJQc285M3NGSGZNYTNVd001WVVxbW1XdGFpTzJfdlg3Y0lQVHBBWEVqMXVFLVFBcFZaSTVqWmR3eFZvejVZa00zako5Tk5GYk9IS0xNMURFSGZ2clUyZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações em Tapira, no Alto Paranaíba, devido à falta de enxofre e custo da matéria-prima - diariodocomercio.com.br</t>
+          <t>Embrapa cria calcário mais nutritivo resistente à umidade e ao vento - Tua Rádio</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>30/05/2026 04:00</t>
+          <t>31/05/2026 04:00</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQQjJhMWdjMVBkN05lbEV2T1hBOGZqV2FEektlU2Nqd0cwZlEzLUY4Q0FIQ1dQUEtWYW05dFFza3B1QzJ0dVMxaUxCOEhEd0VxU2tidXhZMFVWMGsxeE1CeFliRkRONmZieWRSRDQ5RHVfNWFybmxTU2lJVHZYWENZRkZGZ25tbWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOTm55bWM5blVJYmljekhUT0xQRlZZMUh2OUdYUXNqRUVtNUFUaFdaQURiQ1FldWZrZmVmWXZ4XzJmRVRxTlNDckRRekdHM3pzc2h0YjJ1RGpIR0dLaFp6N2VPRTcza0hfMzlYSjlGUkE5azFKMXRBd3I1dU5QNk42U3h3QVA4bFRINldUc2M2YU0tYkdzZ0kxMFhKYkh4TlM4NmxONTVtRnFUQWRFVU4tUVpXVHZxWjFKRm1uc3ZocmdNVS0xdWJB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher coco ralado por excesso de enxofre - Pleno.News</t>
+          <t>Embrapa desenvolve calcário granulado com função corretiva e nutritiva - canalrural.com.br</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>28/05/2026 04:00</t>
+          <t>31/05/2026 04:00</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdHBVZWl1TWRoenctMVBqRFhvUkhUNVVkV3hGZ3Vkc2lNX2V3eTRXTVFqdmhZU2Y1OFdZUjJDMW9KV29MSWNfTi12SGhkb3lwZ2ViRnlsalhmY0JCVmJHTElIWGlpVi11Y2VMUnRleU5STUszZ1ZMeHRQMjB1Zk5uTEEtbjVMNUJrQXdNYnNUZ0pQakEwY0JrZk1nONIBowFBVV95cUxORFQ1MVBTQ1VsdTlOQ28xemxBLUNHaEtIUFctakRUckU5aEFKM1VhNU9vdVE3WDZ6NWtFaVZnd09NWk1IUDd5XzBKZTVFbVN1R0U3a1N2Yk5sczBIZDhERmQyZjNIMG51d3NjTFd1VFJaOWN0bmRPa1RCZWQwUjVjRnV1c29kZHpoa3R2c2VOangxc2VaTlItNUNTajJmQVhBNUlV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOck1oOHdwUmVRMjZleHc1UWEzV1B2REJFbXF5ZGQ0enIyaXpPbVZMY1NWcU1FWjUxMjd6MG9KbVVNanBjNDhZcTlmek1zRFczeE9jaFhUcEhzUGpXMkYwOEVjaHNTSURmMG81LUZhYW9FeWZONFMyMjJlb0EzeUlvSzNLYTUyQXYzWEJPdUgwLTR6d3JHdU5aNVRjQXdQZjJrVmozQ1U4NFYtRlZmLXQ4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado da Qualicoco por excesso de enxofre - UOL Notícias</t>
+          <t>Mosaic suspende operações em Tapira, no Alto Paranaíba, devido à falta de enxofre e custo da matéria-prima - Diário do Comércio</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>28/05/2026 04:00</t>
+          <t>30/05/2026 04:00</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQX3Vlc2VrZ2dNdkFzaFhqQzlTLV9acFE3LTRSempETklLa25tdDI1NkxtZXFpS3VyREFIVjBVN2VBSGhjR2EyWmhvZ19xV3IxdVpVbkkwdHdwVEx0b2RRUEJaTFlDdkJKOVN0MldteEViTVJocHJsMWxxUmRWM3dqbS1sc1pMUUJGU3ZqTm1EWlhuLXNkMEtjR3EzMVdmYnFnbktyRzVJcEdMZHVvdEFQM3FmeWpMRUFrSVczNHdwVjBVWmMwMUZhdDk1bVI5OHVKbWxfdl9YRHBTeHJIdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQQjJhMWdjMVBkN05lbEV2T1hBOGZqV2FEektlU2Nqd0cwZlEzLUY4Q0FIQ1dQUEtWYW05dFFza3B1QzJ0dVMxaUxCOEhEd0VxU2tidXhZMFVWMGsxeE1CeFliRkRONmZieWRSRDQ5RHVfNWFybmxTU2lJVHZYWENZRkZGZ25tbWs?oc=5</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
+          <t>Anvisa manda recolher coco ralado por excesso de enxofre - Pleno.News</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdHBVZWl1TWRoenctMVBqRFhvUkhUNVVkV3hGZ3Vkc2lNX2V3eTRXTVFqdmhZU2Y1OFdZUjJDMW9KV29MSWNfTi12SGhkb3lwZ2ViRnlsalhmY0JCVmJHTElIWGlpVi11Y2VMUnRleU5STUszZ1ZMeHRQMjB1Zk5uTEEtbjVMNUJrQXdNYnNUZ0pQakEwY0JrZk1nONIBowFBVV95cUxORFQ1MVBTQ1VsdTlOQ28xemxBLUNHaEtIUFctakRUckU5aEFKM1VhNU9vdVE3WDZ6NWtFaVZnd09NWk1IUDd5XzBKZTVFbVN1R0U3a1N2Yk5sczBIZDhERmQyZjNIMG51d3NjTFd1VFJaOWN0bmRPa1RCZWQwUjVjRnV1c29kZHpoa3R2c2VOangxc2VaTlItNUNTajJmQVhBNUlV?oc=5</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher coco ralado por excesso de enxofre; veja se você tem em casa - Exame</t>
+          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5010,19 +5010,19 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNZzd6c1RaVDEtMFk3TnFhekVMSDNOQnAyUkVxaHkyQklSbWMwYTQ4b0tFSVJtTGZ4R0pONmthWmFOWDRNRTQ4YnFjWkh2ZDFfdlA1VGFidmpTQTVQdUxMaWpmd2Y5QldZZkxlQ1U5SHdHa1hOMzVUQmV3bzRJeV9GUDE1b0FMRE5sOVByV3pJOHNOWTBxNGhWRkRRbFM3SEppcHNCR3RrNHQ3MUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbEhqa29HQTVER2pnczg0QVFJclpNcDZJMlFLdDVCb1pnLWdEbGE3clRBLVkzak1SVXBSWTcza19aSlVtZklGV01lM2JyMms1ZElzUlZVSTZDVFNraUxpZDBkd1NYZVFNeXBKTkpTbl9VTlBvTWh3V3ppUm1BSzVqc09xa2x3RHl0MEFtS19jYnp4RGJSMFZKRm01VThReXhLSmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por apresentar excesso de enxofre - Metrópoles</t>
+          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hblFncjhMbjEzXzJtaEdzYXQ0djFOYlpDLW8ybnAwVzVTLWh0WlVIa2RwM09UMld3ekVKd2VuZ2IzclNxcmlONjFmbjVJMVZFT0c1N1VxM0J2bjlLSmZMLTF2UTRILWl5NTN0VE1Jc0dkWk1WSG5vdXZaRWw2NW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Anvisa determina recolhimento de lote de coco ralado por excesso de enxofre; veja marca - GZH</t>
+          <t>Anvisa recolhe lote de coco ralado por apresentar excesso de enxofre - Metrópoles</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5054,19 +5054,19 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNZklVdWVqSnZBODhORUZwWlFOeXFpSHlEN01yMWd6YW1ZeE5lZXhRSFVHbFdlU3BmT05kTkdZYnY5dE5kelRsdXBDY29aWTAxWjV1ZENBdHhpQ1hqT1d4dHBKOTQxREMyTV94bXQ3MGk5RWRwTTBlQTJrNmF5cWMwcXI4VWZOYUllRElnVm11dW56N1NUZ1FjVkdmQzlsc0xaLW5lakRlVkM4X1JuMzFIYm1wbXBZOHpwZ0Mwb3NWaXhOMkU1UGt5a1NSb3hYZzRnN0FaVmhqZ242Vk9OYlhyd3BKTlgtN0JQWUhxZ2w0b01iSGNBRm5qa1BheFU2S1dV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hblFncjhMbjEzXzJtaEdzYXQ0djFOYlpDLW8ybnAwVzVTLWh0WlVIa2RwM09UMld3ekVKd2VuZ2IzclNxcmlONjFmbjVJMVZFT0c1N1VxM0J2bjlLSmZMLTF2UTRILWl5NTN0VE1Jc0dkWk1WSG5vdXZaRWw2NW8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
+          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5076,19 +5076,19 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUWpoTWRpSkZ2YlpjVWJkbmtHSTROcVdZYVJmcGpwd085QUdoc1dxelhudXJvVlR2X0xvZnRMbjBFRE1YdDRGOTFjVWNuNTJ4bmQ3UU9UYmRSYUMxSmxpWHlJSE9Hb190d3VGdkoxejI5Q1VrSVpfVHp1eFpkd0YzSUl1YjducElqUmhmM1hSNDJHaTZHWHRuVktXY2R2dHQyMU5hNklqcElfSFJjVGc2WFlaQ19ZZXIxVTJQODJwLTJqRjNhbnZjLUNEa1NhQXZOXzhhRlNxdGU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
+          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - CNN Brasil</t>
+          <t>Anvisa recolhe coco ralado por excesso de dióxido de enxofre; saiba quais são os riscos à saúde - folha.uol.com.br</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5120,19 +5120,19 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbEhqa29HQTVER2pnczg0QVFJclpNcDZJMlFLdDVCb1pnLWdEbGE3clRBLVkzak1SVXBSWTcza19aSlVtZklGV01lM2JyMms1ZElzUlZVSTZDVFNraUxpZDBkd1NYZVFNeXBKTkpTbl9VTlBvTWh3V3ppUm1BSzVqc09xa2x3RHl0MEFtS19jYnp4RGJSMFZKRm01VThReXhLSmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOaE0ySXkzcF9LdzVFZ25SRUNnT3JkRUZ0S2VkQ1MtbDdoaFZ6SE5UbVd3QnpFbmFHZkZGOExHUzJFVDJ2MHk1UkhrU2FGdmY0aHl5c2hwN0lHUm9mSkpsZDdWUmZwR3NfRTlVLVFHa1JTNkJtN2tIT0JQclFudHd5ZlRPY21uZGpQRnk2S3lNWWFMMjM3VnV5d2thcFhZNkVCTGpiMDNtVEJLLUpxZmhiTmUzQVNkZC1HcU1TaXJuTG9XaWZLSTJXTnBBZ2M2MjRPZWZncm5pa3Z3RHJubkxQanpNYXc5Mm8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
+          <t>Dá para substituir ureia por farelo de soja no proteico da seca? Especialista responde - girodoboi.canalrural.com.br</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -5142,19 +5142,19 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUWpoTWRpSkZ2YlpjVWJkbmtHSTROcVdZYVJmcGpwd085QUdoc1dxelhudXJvVlR2X0xvZnRMbjBFRE1YdDRGOTFjVWNuNTJ4bmQ3UU9UYmRSYUMxSmxpWHlJSE9Hb190d3VGdkoxejI5Q1VrSVpfVHp1eFpkd0YzSUl1YjducElqUmhmM1hSNDJHaTZHWHRuVktXY2R2dHQyMU5hNklqcElfSFJjVGc2WFlaQ19ZZXIxVTJQODJwLTJqRjNhbnZjLUNEa1NhQXZOXzhhRlNxdGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR082Wi1qR1lQM0swUUVtTUN1NkhLeXlVbDZJSGFRRjVVaWFEb1hSN3IwS2ZCOVZsLWdvMnFtNFo3aFlGcHlMeUd0LVA4ZzFTWEtyZm81Y1dhZkhCMDR4SHVyeW1tQlpjelVoT1VrbU5LMXRESkprTVN5Z2l4TnJYU0tFTGpiVHlUaFZadWJFeUp2b29qUDV3VXVNQmswcXkxUDdrX2FwV05USVRSdFVMWVBnQXBXMDBfbEVBT1RiVU5SM0ZIdk5VMU1hcw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
+          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5164,19 +5164,19 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Dá para substituir ureia por farelo de soja no proteico da seca? Especialista responde - Giro do Boi - Canal Rural</t>
+          <t>Anvisa manda recolher coco ralado por excesso de enxofre; veja se você tem em casa - Exame</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR082Wi1qR1lQM0swUUVtTUN1NkhLeXlVbDZJSGFRRjVVaWFEb1hSN3IwS2ZCOVZsLWdvMnFtNFo3aFlGcHlMeUd0LVA4ZzFTWEtyZm81Y1dhZkhCMDR4SHVyeW1tQlpjelVoT1VrbU5LMXRESkprTVN5Z2l4TnJYU0tFTGpiVHlUaFZadWJFeUp2b29qUDV3VXVNQmswcXkxUDdrX2FwV05USVRSdFVMWVBnQXBXMDBfbEVBT1RiVU5SM0ZIdk5VMU1hcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNZzd6c1RaVDEtMFk3TnFhekVMSDNOQnAyUkVxaHkyQklSbWMwYTQ4b0tFSVJtTGZ4R0pONmthWmFOWDRNRTQ4YnFjWkh2ZDFfdlA1VGFidmpTQTVQdUxMaWpmd2Y5QldZZkxlQ1U5SHdHa1hOMzVUQmV3bzRJeV9GUDE1b0FMRE5sOVByV3pJOHNOWTBxNGhWRkRRbFM3SEppcHNCR3RrNHQ3MUU?oc=5</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Anvisa recolhe coco ralado por excesso de dióxido de enxofre; saiba quais são os riscos à saúde - folha.uol.com.br</t>
+          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5208,51 +5208,51 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOaE0ySXkzcF9LdzVFZ25SRUNnT3JkRUZ0S2VkQ1MtbDdoaFZ6SE5UbVd3QnpFbmFHZkZGOExHUzJFVDJ2MHk1UkhrU2FGdmY0aHl5c2hwN0lHUm9mSkpsZDdWUmZwR3NfRTlVLVFHa1JTNkJtN2tIT0JQclFudHd5ZlRPY21uZGpQRnk2S3lNWWFMMjM3VnV5d2thcFhZNkVCTGpiMDNtVEJLLUpxZmhiTmUzQVNkZC1HcU1TaXJuTG9XaWZLSTJXTnBBZ2M2MjRPZWZncm5pa3Z3RHJubkxQanpNYXc5Mm8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>China libera cotas de exportação de ureia e alivia pressão global - CNN Brasil</t>
+          <t>Anvisa recolhe lote de coco ralado da Qualicoco por excesso de enxofre - UOL Notícias</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>27/05/2026 04:00</t>
+          <t>28/05/2026 04:00</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeWZUcGlPVTM1aW9Nak5sZXVITDhRV3FndUlKQUJqMElZUUhWbmoxdDk0Q2ZNVUVmbmlSdm5pZ1lxWHVYT3ZqMDdPSVZSSTBiWlJEN1drblFHc0dCOVFlMnBmclpTWGFZN3hxbVZwQk9TdkktQmVzN1VFWHhEQllTSi05UUpXSjZydVJOcFQ4VmxaSnM2eG1pQ2QzaFR6RkJNTlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQX3Vlc2VrZ2dNdkFzaFhqQzlTLV9acFE3LTRSempETklLa25tdDI1NkxtZXFpS3VyREFIVjBVN2VBSGhjR2EyWmhvZ19xV3IxdVpVbkkwdHdwVEx0b2RRUEJaTFlDdkJKOVN0MldteEViTVJocHJsMWxxUmRWM3dqbS1sc1pMUUJGU3ZqTm1EWlhuLXNkMEtjR3EzMVdmYnFnbktyRzVJcEdMZHVvdEFQM3FmeWpMRUFrSVczNHdwVjBVWmMwMUZhdDk1bVI5OHVKbWxfdl9YRHBTeHJIdnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>China libera cotas de exportação de Ureia - Notícias Agrícolas</t>
+          <t>Anvisa determina recolhimento de lote de coco ralado por excesso de enxofre; veja marca - gauchazh.clicrbs.com.br</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>27/05/2026 04:00</t>
+          <t>28/05/2026 04:00</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTENSOXc1NlM2MkJZRlRZeTRmTGZxeXREZ0NqS0JsRGVxSFFrLWNSWThaTUpnVC1EVENybkxYQkhEUHZOM1RlOXBMNnlOZ0ZpbFZHZWJMSnB4SDRtOEVOa2ktNzN5cEQ1SlhUa09fNWxBbWxhNnZMc3AxbWZvUzc5YVhDeC15YWwyTmxYZ20tMVZGTWloUE9NTGtwWlhYemVVRXl1d9IBqgFBVV95cUxORTJOMzJaT2lMNUNabklSUnNKVFdjZVMycmlOQ2xrdFFVN1p5QmtJall0ZWx0MU13bGVWRFZ0dTd6Y25memNYNEI5Q1A0dHBQNHRhb0J5MmVUVGFEd0xXOHcyelMzYkV4MHlKbXdOQW1SejNjSGZjUjUySG1Gd0N3dEszMURXbnQ0dVVqZzlBY3RmR2Jhc3JCWXpRQmpHUndiWlJXWjZTTUpKZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNZklVdWVqSnZBODhORUZwWlFOeXFpSHlEN01yMWd6YW1ZeE5lZXhRSFVHbFdlU3BmT05kTkdZYnY5dE5kelRsdXBDY29aWTAxWjV1ZENBdHhpQ1hqT1d4dHBKOTQxREMyTV94bXQ3MGk5RWRwTTBlQTJrNmF5cWMwcXI4VWZOYUllRElnVm11dW56N1NUZ1FjVkdmQzlsc0xaLW5lakRlVkM4X1JuMzFIYm1wbXBZOHpwZ0Mwb3NWaXhOMkU1UGt5a1NSb3hYZzRnN0FaVmhqZ242Vk9OYlhyd3BKTlgtN0JQWUhxZ2w0b01iSGNBRm5qa1BheFU2S1dV?oc=5</t>
         </is>
       </c>
     </row>
@@ -5286,73 +5286,73 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Pela 5ª semana consecutiva, cotações da ureia diminuíram nos portos - brasilagro.com.br</t>
+          <t>China libera cotas de exportação de ureia e alivia pressão global - CNN Brasil</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>26/05/2026 04:00</t>
+          <t>27/05/2026 04:00</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNcE11QW1BUkZZUDUyX1N0WWZzcExyX1ZyMVVOZmN1MHdpLUVTdWhGNWtYSnNFZ0lXLXo0SS1kTm11cGZnTGtOY1RsdTVPX2YxUjZsaVBxUTU3R1NaQTg1ZE1yRG9MVWJiMkh2eEx0T3ItWDJWQndSbEZFMURKX3FQd08xcno4aHhpSVgxMlpka1pzTUxlTUd2dkp4VGZaTF84VkluLXFrUEs1azFKY3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeWZUcGlPVTM1aW9Nak5sZXVITDhRV3FndUlKQUJqMElZUUhWbmoxdDk0Q2ZNVUVmbmlSdm5pZ1lxWHVYT3ZqMDdPSVZSSTBiWlJEN1drblFHc0dCOVFlMnBmclpTWGFZN3hxbVZwQk9TdkktQmVzN1VFWHhEQllTSi05UUpXSjZydVJOcFQ4VmxaSnM2eG1pQ2QzaFR6RkJNTlE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Definidos os semifinalistas da Copa do Calcário 2026 - jornaldaregiao.com</t>
+          <t>China libera cotas de exportação de Ureia - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>25/05/2026 04:00</t>
+          <t>27/05/2026 04:00</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPd3lVWExUMExpNnYzRHRkVWcxbS1lV1hMbE9mMHlZTkFTSkd1NFJ1Z3lxYXhtZzNpOVNJTjJOV2Z4UmhkMzkwNmlaRmtKOWlPQmE3ZVhoX2pCQ1N1d00wT09UY0YyTHJ4TFIwRTM3Y3M1bU9QeklBaDNvRWVGdmpoLU44OGpSNms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTENSOXc1NlM2MkJZRlRZeTRmTGZxeXREZ0NqS0JsRGVxSFFrLWNSWThaTUpnVC1EVENybkxYQkhEUHZOM1RlOXBMNnlOZ0ZpbFZHZWJMSnB4SDRtOEVOa2ktNzN5cEQ1SlhUa09fNWxBbWxhNnZMc3AxbWZvUzc5YVhDeC15YWwyTmxYZ20tMVZGTWloUE9NTGtwWlhYemVVRXl1d9IBqgFBVV95cUxORTJOMzJaT2lMNUNabklSUnNKVFdjZVMycmlOQ2xrdFFVN1p5QmtJall0ZWx0MU13bGVWRFZ0dTd6Y25memNYNEI5Q1A0dHBQNHRhb0J5MmVUVGFEd0xXOHcyelMzYkV4MHlKbXdOQW1SejNjSGZjUjUySG1Gd0N3dEszMURXbnQ0dVVqZzlBY3RmR2Jhc3JCWXpRQmpHUndiWlJXWjZTTUpKZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Copa do Calcário define os semifinalistas - FERJ</t>
+          <t>Pela 5ª semana consecutiva, cotações da ureia diminuíram nos portos - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>25/05/2026 04:00</t>
+          <t>26/05/2026 04:00</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY2hPQlpoTF8tRzlCb0JEUF8teWEyOWE2Ym1XcXVydmdSNFdqb2ZUNWwzR1lfb01XbmNTZlhGUDMxODJab1czSDRCcEcybEtLRmItdHh5Y2hvNG5SSXpqOTdjTU0teThRM0Q2OVZmYzR4dXJUVU9DLTE0MTBqNGZKNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNcE11QW1BUkZZUDUyX1N0WWZzcExyX1ZyMVVOZmN1MHdpLUVTdWhGNWtYSnNFZ0lXLXo0SS1kTm11cGZnTGtOY1RsdTVPX2YxUjZsaVBxUTU3R1NaQTg1ZE1yRG9MVWJiMkh2eEx0T3ItWDJWQndSbEZFMURKX3FQd08xcno4aHhpSVgxMlpka1pzTUxlTUd2dkp4VGZaTF84VkluLXFrUEs1azFKY3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Definidos os semifinalistas da Copa do Calcário 2026 após rodada decisiva - Serra News</t>
+          <t>Mosaic anuncia iniciativas selecionadas no Edital da Água 2026 - ibram.org.br</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -5362,19 +5362,19 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxORTlOcWI2YW9vOHdRRjJSbWtFZVhpZDFYTXZaTUowOW5XOFFBako2SkdwSlk3bEIzUzllUU9VOEFyMVVFNjB2RVRiYko3XzhVMmNXUVJqMk8xRDE1UzhFcGpYbUtyZVhyV0U0SG9JTEZ6QkFseVJZQ1hBdTZ5T1ZxQkVnT2J5cnZGZy1xMGxxd1RvZF85RS1pMXEtenI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdld0UllhbUlrZ0dxa3Z5TjRkSXI3VTNYcmxENU1CakwyWGs1a2R0ajFKNUtpZV9EZ1V0OWtDbXBVOWZrbUoxcWJOT2ZFWkwxNzhhNnRaYVBGdl85ay0xZUJHb19HNGxkVkczNUdPc2p0eHFBLTdRNlJmdTJJN1hHbFZEOTBGYzMtX3N4Q3BhcEc4N3pEWWVF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
+          <t>Definidos os semifinalistas da Copa do Calcário 2026 após rodada decisiva - Serra News</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5384,19 +5384,19 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxORTlOcWI2YW9vOHdRRjJSbWtFZVhpZDFYTXZaTUowOW5XOFFBako2SkdwSlk3bEIzUzllUU9VOEFyMVVFNjB2RVRiYko3XzhVMmNXUVJqMk8xRDE1UzhFcGpYbUtyZVhyV0U0SG9JTEZ6QkFseVJZQ1hBdTZ5T1ZxQkVnT2J5cnZGZy1xMGxxd1RvZF85RS1pMXEtenI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Mosaic anuncia iniciativas selecionadas no Edital da Água 2026 - ibram.org.br</t>
+          <t>Copa do Calcário define os semifinalistas - FERJ</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5406,19 +5406,19 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdld0UllhbUlrZ0dxa3Z5TjRkSXI3VTNYcmxENU1CakwyWGs1a2R0ajFKNUtpZV9EZ1V0OWtDbXBVOWZrbUoxcWJOT2ZFWkwxNzhhNnRaYVBGdl85ay0xZUJHb19HNGxkVkczNUdPc2p0eHFBLTdRNlJmdTJJN1hHbFZEOTBGYzMtX3N4Q3BhcEc4N3pEWWVF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY2hPQlpoTF8tRzlCb0JEUF8teWEyOWE2Ym1XcXVydmdSNFdqb2ZUNWwzR1lfb01XbmNTZlhGUDMxODJab1czSDRCcEcybEtLRmItdHh5Y2hvNG5SSXpqOTdjTU0teThRM0Q2OVZmYzR4dXJUVU9DLTE0MTBqNGZKNg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
+          <t>Cotações da ureia recuam pela 5ª semana seguida com demanda enfraquecida - canalrural.com.br</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNalY1bGttNXJOYUVBSVFzeVNDd2pBQXkwUUhvLVhFZFJYd0kyYl81UHNuMW1pR01sSElyVXJVbTNYVTU0QVV6M1ZTb2M3MV8wbFN6U2p3WkhWd1hlcXFJR2NFSW9DcXYtWC1JNF82UlJSUXRtYmt1VUgwVHhZcDNHWG1qZk5majdOWldPblpLYnloR0NTcWt5dFhXMkNiTzl2emszMG5CczJabUZaMFdCeWNCUlRKQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Cotações da ureia recuam pela 5ª semana seguida com demanda enfraquecida - Canal Rural</t>
+          <t>Ureia cai pela quinta semana nos portos - Agrolink</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNalY1bGttNXJOYUVBSVFzeVNDd2pBQXkwUUhvLVhFZFJYd0kyYl81UHNuMW1pR01sSElyVXJVbTNYVTU0QVV6M1ZTb2M3MV8wbFN6U2p3WkhWd1hlcXFJR2NFSW9DcXYtWC1JNF82UlJSUXRtYmt1VUgwVHhZcDNHWG1qZk5majdOWldPblpLYnloR0NTcWt5dFhXMkNiTzl2emszMG5CczJabUZaMFdCeWNCUlRKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOem1iVWpuSWx2Qk9PN0xvMVNEaGZEM1kzQWdmeWRFdTh4VjVJLTVNTDhRY1Z6ZnYyYVhkWUNYVm51U3ZNb0JiaExrb2RYcXBlX0NaZGNQUk5KZ1FremQ0NzZTWk5GQXZ6UXBxYm4yRUxTNTRwTDdiRnh1M042a1JCM3VZUXpoVlJRZU92ejA5QV9BZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Ureia cai pela 5ª semana no Brasil com demanda fraca - StoneX</t>
+          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5472,19 +5472,19 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOemd1bExnV1NEMlMwdGp2clZ0TjB2QlFkemdjNXhrUkJyaWxjd2N5MWpPMDlJV3MtX2FyRDctd1RVLW92bm5MT2c5UnJIUGh4UWpBancxVnJDd1c5WjVKVWktTDZoR3ZaU1FVekxXaDhkNTM1Rm80dkVuNEVNekZ3YllvWVRDLTR5STBvMElpRWxEV2dLREQ4djUwczR6bFFmbFY2dUt1UDhWb29WZC1hMDJDZng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Ureia cai pela quinta semana nos portos - agrolink.com.br</t>
+          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOem1iVWpuSWx2Qk9PN0xvMVNEaGZEM1kzQWdmeWRFdTh4VjVJLTVNTDhRY1Z6ZnYyYVhkWUNYVm51U3ZNb0JiaExrb2RYcXBlX0NaZGNQUk5KZ1FremQ0NzZTWk5GQXZ6UXBxYm4yRUxTNTRwTDdiRnh1M042a1JCM3VZUXpoVlJRZU92ejA5QV9BZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
         </is>
       </c>
     </row>
@@ -5506,73 +5506,73 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Insumo essencial no campo, calcário tem dia nacional neste domingo - Primeira Página</t>
+          <t>Definidos os semifinalistas da Copa do Calcário 2026 - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>23/05/2026 04:00</t>
+          <t>25/05/2026 04:00</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPb2RUbXdJZ0xldmZuYlRPRS1tdkM4SEtfd3hnVWpCaTJnVU4xUjZFcTJtR1pRM0h3enJGaVA1T3RueENpSEdyYmNMYV9NZnM5M2NzUjhOVXV2NXFnbDZLOTBBaG9iU2hQU1IzdEFEV1dRSFlfZzlKSW1MOF9BdHJRYmVMQVNfSHpfNUhFaGhYX285MnZRLXBmSEdQT2N6Z1ZvdWUwNUhQNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPd3lVWExUMExpNnYzRHRkVWcxbS1lV1hMbE9mMHlZTkFTSkd1NFJ1Z3lxYXhtZzNpOVNJTjJOV2Z4UmhkMzkwNmlaRmtKOWlPQmE3ZVhoX2pCQ1N1d00wT09UY0YyTHJ4TFIwRTM3Y3M1bU9QeklBaDNvRWVGdmpoLU44OGpSNms?oc=5</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Mosaic e Inpasa fecham acordo de barter para fornecimento de insumos agrícolas - GlobalFert</t>
+          <t>Ureia cai pela 5ª semana no Brasil com demanda fraca - StoneX</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>22/05/2026 04:00</t>
+          <t>25/05/2026 04:00</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNanViVXlRQTdDUHdhS2VpT3RscTREdVpDVjdSRG50cTVUR0YtVGFXWEwxTWVvVDlCeHBVNW9iQ2hkb2Nqb1hhZTdxR0VoWmhOb2VYSHFpWEszR183bDFQblVMcGFGbVZEMVE0WVNZclUwemJ0a1ZfVktDYTRBa1YzelI1ckNYNi1GTlNYRll0VW1FRFB2QUlnUzA0WWJmM3c3ZTNBNFdnU1NaUnZzZHE4UU91Wl9SSXMzVEt6b0hxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOemd1bExnV1NEMlMwdGp2clZ0TjB2QlFkemdjNXhrUkJyaWxjd2N5MWpPMDlJV3MtX2FyRDctd1RVLW92bm5MT2c5UnJIUGh4UWpBancxVnJDd1c5WjVKVWktTDZoR3ZaU1FVekxXaDhkNTM1Rm80dkVuNEVNekZ3YllvWVRDLTR5STBvMElpRWxEV2dLREQ4djUwczR6bFFmbFY2dUt1UDhWb29WZC1hMDJDZng?oc=5</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Casa Criativa CMOC seleciona projetos com impacto social - Terra</t>
+          <t>Insumo essencial no campo, calcário tem dia nacional neste domingo - Primeira Página</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>22/05/2026 04:00</t>
+          <t>23/05/2026 04:00</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQblBlQWhYdmdqY2MyeGdKeVd1SnZySzcwSWpoRDlKRVNhZ1JaZjBRUUI5cXE3S284eXVYZVRDTHl4RkxneEFIdE1mbVkzWlQtZ0gxcHJnclVQTEhSZkRMLXQ2d3RvaHBwb3hKd0VwMGtRcjNRcmJaUC1FTmF4Z0FkYjEwSXR6eWE0Rmo3cHpSbkh0T3VuRGZDMVFIVjFaWGd6Yl9kUy1hVGdSWXJQYlljV1lrUlNPZS1rN2RKZFNld3Z3VlNzaS1MY1AzLTE1MU9ON2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPb2RUbXdJZ0xldmZuYlRPRS1tdkM4SEtfd3hnVWpCaTJnVU4xUjZFcTJtR1pRM0h3enJGaVA1T3RueENpSEdyYmNMYV9NZnM5M2NzUjhOVXV2NXFnbDZLOTBBaG9iU2hQU1IzdEFEV1dRSFlfZzlKSW1MOF9BdHJRYmVMQVNfSHpfNUhFaGhYX285MnZRLXBmSEdQT2N6Z1ZvdWUwNUhQNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Crise internacional pode afetar produção de fertilizantes em Catalão, alerta Metabase - Badiinho</t>
+          <t>Severiano de Almeida adquire distribuidor de calcário para atender contrapartida do Programa Terra Forte - jornalbomdia.com.br</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5582,19 +5582,19 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9UOVFBd2FaZHdNSjBOeGVrdTZ3dnBwaWNxVEdCSEEydTROLWhfVXYzdHB5UTdPUzZsN2JqbFVfQVItV1htb1N3Z2s5Q0l6cVdBYjZlSlZ2bVZ3WFBUX0ZtaU5EOWJ6dTBWaHcxaGNwRXF6YWRvdmhV0gF8QVVfeXFMTnU4U1hjc0VldVhHQVBQMkNDNm5fdFNNN1FDN1hzNDdJWU1DazJiNGVzM05BYm1XamR5eWJQMEg0QXJRQUJOU01MeWdMNEVUTUhZdVduQnZDZGJGVUNHbFJsTWcwMDFTd0lYLUkwZnczTE1PZkZvcUhTUmsyLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNWTNLdW1XQmxUS3VCWUJicEhjN3p1SWRhS2dRRkV6VkVGZ2JTWHdhQjVlVjFGUTF0NjFTbU50QWlPY2hBdE5tcTlZYXgxLTR5Q1psTk5rdzUxNHNCZU95V0NwMWxJX2NUdXU0cnFLaFNvd3VnbGlSV3NVbWhBWWUwZ0FlQmZXNzBXMnRvRGlhbk0tRW1lbWhqd0FfTXRmTXJuOEZTN19XdkRTQ25oZl9zVWVBN1VPa2pnUGdkaEs2S1NWTGEyR2lsaXFyQ2Y4SS14bWM4NFZtazlSWHN1UDBwRDJUaEw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Severiano de Almeida adquire distribuidor de calcário para atender contrapartida do Programa Terra Forte - Jornal Bom Dia</t>
+          <t>Casa Criativa CMOC seleciona projetos com impacto social - Terra</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5604,19 +5604,19 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNWTNLdW1XQmxUS3VCWUJicEhjN3p1SWRhS2dRRkV6VkVGZ2JTWHdhQjVlVjFGUTF0NjFTbU50QWlPY2hBdE5tcTlZYXgxLTR5Q1psTk5rdzUxNHNCZU95V0NwMWxJX2NUdXU0cnFLaFNvd3VnbGlSV3NVbWhBWWUwZ0FlQmZXNzBXMnRvRGlhbk0tRW1lbWhqd0FfTXRmTXJuOEZTN19XdkRTQ25oZl9zVWVBN1VPa2pnUGdkaEs2S1NWTGEyR2lsaXFyQ2Y4SS14bWM4NFZtazlSWHN1UDBwRDJUaEw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQblBlQWhYdmdqY2MyeGdKeVd1SnZySzcwSWpoRDlKRVNhZ1JaZjBRUUI5cXE3S284eXVYZVRDTHl4RkxneEFIdE1mbVkzWlQtZ0gxcHJnclVQTEhSZkRMLXQ2d3RvaHBwb3hKd0VwMGtRcjNRcmJaUC1FTmF4Z0FkYjEwSXR6eWE0Rmo3cHpSbkh0T3VuRGZDMVFIVjFaWGd6Yl9kUy1hVGdSWXJQYlljV1lrUlNPZS1rN2RKZFNld3Z3VlNzaS1MY1AzLTE1MU9ON2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio traz oportunidades para o mercado de calcário agrícola no Brasil - Sistema FIEB</t>
+          <t>Crise internacional pode afetar produção de fertilizantes em Catalão, alerta Metabase - Badiinho</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5626,107 +5626,107 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQcktOOE9RSHdxNlg5anFPdkxFbno0R0s0UGc1UmVQTkVFTGVrVTcxY1F0b1Z0SFN3VGZiOUU2dUd6TGhGQXNXNUV6NmpJQVBBRW9Dc0tSSkVUeVRHNGhzQ1Rpb2p1eVNrd2dLdzNWTEI4aGwxVVYyNXdiUldLQV9wcHBYVl9RZHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9UOVFBd2FaZHdNSjBOeGVrdTZ3dnBwaWNxVEdCSEEydTROLWhfVXYzdHB5UTdPUzZsN2JqbFVfQVItV1htb1N3Z2s5Q0l6cVdBYjZlSlZ2bVZ3WFBUX0ZtaU5EOWJ6dTBWaHcxaGNwRXF6YWRvdmhV0gF8QVVfeXFMTnU4U1hjc0VldVhHQVBQMkNDNm5fdFNNN1FDN1hzNDdJWU1DazJiNGVzM05BYm1XamR5eWJQMEg0QXJRQUJOU01MeWdMNEVUTUhZdVduQnZDZGJGVUNHbFJsTWcwMDFTd0lYLUkwZnczTE1PZkZvcUhTUmsyLQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
+          <t>Conflito no Oriente Médio traz oportunidades para o mercado de calcário agrícola no Brasil - Sistema FIEB</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>21/05/2026 04:00</t>
+          <t>22/05/2026 04:00</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQcktOOE9RSHdxNlg5anFPdkxFbno0R0s0UGc1UmVQTkVFTGVrVTcxY1F0b1Z0SFN3VGZiOUU2dUd6TGhGQXNXNUV6NmpJQVBBRW9Dc0tSSkVUeVRHNGhzQ1Rpb2p1eVNrd2dLdzNWTEI4aGwxVVYyNXdiUldLQV9wcHBYVl9RZHM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>SENAI/SC conquista 4 pódios no Grand Prix SENAI, competição nacional de inovação - FIESC</t>
+          <t>Mosaic e Inpasa fecham acordo de barter para fornecimento de insumos agrícolas - GlobalFert</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>21/05/2026 04:00</t>
+          <t>22/05/2026 04:00</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd09RQ1FuMHBlZlRaOGpYbVhPTmFIOHVSOVdHMHRSVG8zSU5rN3dJb1Z0WXBzNER4eUstZ2pZM2lvTEpjdW5ibm41V1I5ZmFjUkhWLVBmNWJBMjM5azVHY0VYenpkR3dMWm8xaUFfSFdYX05LdzVfbmkyc21IRjM2ekdHbzdqVUtIZUl4VnBnTUROYmhCTUhwOGhmWmlQZEQzUVlfWGg2TmsxTlBTY2J2NFR6a1o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNanViVXlRQTdDUHdhS2VpT3RscTREdVpDVjdSRG50cTVUR0YtVGFXWEwxTWVvVDlCeHBVNW9iQ2hkb2Nqb1hhZTdxR0VoWmhOb2VYSHFpWEszR183bDFQblVMcGFGbVZEMVE0WVNZclUwemJ0a1ZfVktDYTRBa1YzelI1ckNYNi1GTlNYRll0VW1FRFB2QUlnUzA0WWJmM3c3ZTNBNFdnU1NaUnZzZHE4UU91Wl9SSXMzVEt6b0hxdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>AgriConnection e Mosaic lançam Fiagro de até R$ 100 milhões para o mercado de fertilizantes - AgFeed</t>
+          <t>SENAI/SC conquista 4 pódios no Grand Prix SENAI, competição nacional de inovação - FIESC</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>20/05/2026 04:00</t>
+          <t>21/05/2026 04:00</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUmlJREVBVDhtRldoNDVjX3RoRkNEYVB1QU13RjFmNmV4MHFNRnp1Qk0wdENJNU41Yk9aVTVNNURDU1V4VUpfczlXOFhUYmlfYUN3NnNnSncxY2RNYWFJQlBXdEZJRmNmSnVTeTRDcmhtU3FzNVdybzliOUJwTkFONTV4MGFydDlxakwtblZiTzNlOEx1cHJxd3BUTlhrYjRyR3RkSmFKc0EyTXRqRDhqV3ZoUGd0YXMxdWxkVjJjTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd09RQ1FuMHBlZlRaOGpYbVhPTmFIOHVSOVdHMHRSVG8zSU5rN3dJb1Z0WXBzNER4eUstZ2pZM2lvTEpjdW5ibm41V1I5ZmFjUkhWLVBmNWJBMjM5azVHY0VYenpkR3dMWm8xaUFfSFdYX05LdzVfbmkyc21IRjM2ekdHbzdqVUtIZUl4VnBnTUROYmhCTUhwOGhmWmlQZEQzUVlfWGg2TmsxTlBTY2J2NFR6a1o?oc=5</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Mosaic e Inpasa assinam novo acordo de barter focado em insumos - CNN Brasil</t>
+          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>20/05/2026 04:00</t>
+          <t>21/05/2026 04:00</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVm00RUZmWGVBMzJ5Vnc4aDB3ZktTenoyMmJXanVXWF9xYTlNT3VmalhFbk9lYlNiT3h5cFZMdk5qZ0xkUkpTMkM0bkxhNHZvRk51SDZENWliR3FmRUNxMEFJQ3d5U3FNb2hhRUdCWUs2X1UxeFgzQjhMbmItbmhaSzhyQkVFSHF2ZV81UWRVb2VDTF91cnVvVGNZSW0xU28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Dia do Calcário Agrícola: o insumo que transformou o solo vive dias de consumo estagnado - Jornal do Brás</t>
+          <t>Ureia cai 14% em quatro semanas, mas preço ainda está 43% acima do nível pré-conflito - Agrolink</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5736,19 +5736,19 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOMEhDZUNyR0d2RnkxOVdKcV95OGVVQUNFTFJtMllSeEtXOTZyd0Q3NG93eTlPU0pzNGhPMlZMUzhCaTI3bE9Ga3ZlejRQMmlmT2JnZkY1NzgtNG9NMjRCTzU3bHJXcjdENTlucnBWQUU2STQ5LXBFdzlWR2d5blR3YmtMTmhKa29QWVAxWEpMWjZxWFRUT1prX0RiOFZSR0Z3bnMwU2RMaHhQZndlc0JjcGJDb2RPeTJLX1hhTWdCSTBGUWRzSnhqYjd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNcDRET2JCb0V6aVhxVWROTHZEY1Vkcy1wSGFONnVQZGFqY1VmaU1hVFBFRmRIYzVod2tvNm42WlJXVXhxMXB1am5aMnlXYnlnY0V5QU5pWU52TUZaekpsUmJtaXB0NnJEaUpXSUtsMjBrT01KWmZqLVdrWTc4MDVxM3BfWU9KVHhRZHA1TFdGeWtMeXF5dmVDTXJfU05qYVdLSERnZll6WXVaa3ZDOFhWemRQck1YM3lkMkVoXzV3dWluc3c5MTBNdFJvOEFmZlU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
+          <t>Mosaic e Inpasa assinam novo acordo de barter focado em insumos - CNN Brasil</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVm00RUZmWGVBMzJ5Vnc4aDB3ZktTenoyMmJXanVXWF9xYTlNT3VmalhFbk9lYlNiT3h5cFZMdk5qZ0xkUkpTMkM0bkxhNHZvRk51SDZENWliR3FmRUNxMEFJQ3d5U3FNb2hhRUdCWUs2X1UxeFgzQjhMbmItbmhaSzhyQkVFSHF2ZV81UWRVb2VDTF91cnVvVGNZSW0xU28?oc=5</t>
         </is>
       </c>
     </row>
@@ -5787,12 +5787,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Ureia cai 14% em quatro semanas, mas preço ainda está 43% acima do nível pré-conflito - agrolink.com.br</t>
+          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -5802,63 +5802,63 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNcDRET2JCb0V6aVhxVWROTHZEY1Vkcy1wSGFONnVQZGFqY1VmaU1hVFBFRmRIYzVod2tvNm42WlJXVXhxMXB1am5aMnlXYnlnY0V5QU5pWU52TUZaekpsUmJtaXB0NnJEaUpXSUtsMjBrT01KWmZqLVdrWTc4MDVxM3BfWU9KVHhRZHA1TFdGeWtMeXF5dmVDTXJfU05qYVdLSERnZll6WXVaa3ZDOFhWemRQck1YM3lkMkVoXzV3dWluc3c5MTBNdFJvOEFmZlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>aumento dos preços do enxofre em meio a crise global de suprimentos - Sunsirs</t>
+          <t>AgriConnection e Mosaic lançam Fiagro de até R$ 100 milhões para o mercado de fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>19/05/2026 04:00</t>
+          <t>20/05/2026 04:00</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1rQ09LNEtPX1l6VWFRT1VRTG9ZWmFtM3pRUGExdXJXVlY5V2RsLURoNk5vT3N2b0p5MDZzQkZsLWtkM3dtTDZSd1VQeVJra0UxZ1QtRzJIdi1ndFBwdWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUmlJREVBVDhtRldoNDVjX3RoRkNEYVB1QU13RjFmNmV4MHFNRnp1Qk0wdENJNU41Yk9aVTVNNURDU1V4VUpfczlXOFhUYmlfYUN3NnNnSncxY2RNYWFJQlBXdEZJRmNmSnVTeTRDcmhtU3FzNVdybzliOUJwTkFONTV4MGFydDlxakwtblZiTzNlOEx1cHJxd3BUTlhrYjRyR3RkSmFKc0EyTXRqRDhqV3ZoUGd0YXMxdWxkVjJjTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Demanda enfraquecida derruba preço da ureia, mas relação de troca segue desfavorável - Canal Rural</t>
+          <t>Dia do Calcário Agrícola: o insumo que transformou o solo vive dias de consumo estagnado - Jornal do Brás</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>19/05/2026 04:00</t>
+          <t>20/05/2026 04:00</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWHFYa0tMRUlRN2NycUdya2FNQzRVaU92UFc4Wk5NcHNUOV9MVHlIUjJEWXhSQjZ2ZGFuQ0ctNU9ES2U1RndpeXRQMFRrYUlHazJkazJ1aUhfN2hCSm8tc2VZd0kyVGM5MmZqTWxMZThsNEQya3owZk9ZeWo4U0VrY1VfQ1g3YklGbVVRVklaLUdCdmEtRklQSXpsTnF5TWRDbklfVGpFTGp3VnlVc3p5Q2VaMlRYTThiUlB0cGNTbmM3Nkxs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOMEhDZUNyR0d2RnkxOVdKcV95OGVVQUNFTFJtMllSeEtXOTZyd0Q3NG93eTlPU0pzNGhPMlZMUzhCaTI3bE9Ga3ZlejRQMmlmT2JnZkY1NzgtNG9NMjRCTzU3bHJXcjdENTlucnBWQUU2STQ5LXBFdzlWR2d5blR3YmtMTmhKa29QWVAxWEpMWjZxWFRUT1prX0RiOFZSR0Z3bnMwU2RMaHhQZndlc0JjcGJDb2RPeTJLX1hhTWdCSTBGUWRzSnhqYjd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
+          <t>Demanda enfraquecida derruba preço da ureia, mas relação de troca segue desfavorável - canalrural.com.br</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5868,73 +5868,73 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWHFYa0tMRUlRN2NycUdya2FNQzRVaU92UFc4Wk5NcHNUOV9MVHlIUjJEWXhSQjZ2ZGFuQ0ctNU9ES2U1RndpeXRQMFRrYUlHazJkazJ1aUhfN2hCSm8tc2VZd0kyVGM5MmZqTWxMZThsNEQya3owZk9ZeWo4U0VrY1VfQ1g3YklGbVVRVklaLUdCdmEtRklQSXpsTnF5TWRDbklfVGpFTGp3VnlVc3p5Q2VaMlRYTThiUlB0cGNTbmM3Nkxs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Conexão Cultural – Jornada ESG chega a Minas Gerais, Bahia e Maranhão para conscientizar sobre sustentabilidade - O Maranhense</t>
+          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>18/05/2026 14:18</t>
+          <t>19/05/2026 04:00</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQUHhsWkkwMlFtdl9jNVN3cXd5YlRZc1kzQVZ1aW02X1pUZFFKUFUyNHZkNVlBZzFfTHo1VmFleU1pU2JNakxXZ083RXNvUzRXY29aS0IyeE45S3FmUlJ2MW1pYVhSRjlhSzRiOGxyNkItU3dtMVNYX3o1RnVQVUc5QUlYdnJhWWVhc0dRVDVCS1cxWllGNGR5R3hLeHZNODJhakRpWjFpNFRIRUxfdFUxMmJYTHdaY1piVHdWc25pb2VRSVR3emd3aG9MQUh1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Acidente com carreta de calcário deixa feridos na BR-282 em SC - ND Mais</t>
+          <t>aumento dos preços do enxofre em meio a crise global de suprimentos - Sunsirs</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>18/05/2026 04:00</t>
+          <t>19/05/2026 04:00</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxObnpROGFDVUpELUEyQjBhX20xS0pHR19uYzJmZkhrLTJtdjdIQktnSFpoWXFsc1BlRTIzU1kyS0dhZENFRXJWUDMxMmJacERxMVdaVUw0aGc4Z1VJdUdpbXhoNlA5b290RG1odlZERFFDcDBkZEFranZjbFQ3c0dJb0NKYnhtbmk0bDRnbWlMam9iekJra3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1rQ09LNEtPX1l6VWFRT1VRTG9ZWmFtM3pRUGExdXJXVlY5V2RsLURoNk5vT3N2b0p5MDZzQkZsLWtkM3dtTDZSd1VQeVJra0UxZ1QtRzJIdi1ndFBwdWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Copa do Calcário: Macuco, Monerá e Altense garantem vaga nas semifinais - FERJ</t>
+          <t>Conexão Cultural – Jornada ESG chega a Minas Gerais, Bahia e Maranhão para conscientizar sobre sustentabilidade - O Maranhense</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>18/05/2026 04:00</t>
+          <t>18/05/2026 14:18</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNHZMQkhrMlBjTmpobDAwc0lrUFNZd2NqZnlFRzhDU2VfdThPNF96dW5UckVacHdhVWZJTlhJQzFrZ215NTNZaXFTaU1oanN2bTVJR0RVZFpMWG0zUm51My1wckdVTWhJZmJVSV85WUhHNHJxakd1bW5iWTU4aXFWQmkzZnBfa0tad0Exdzl5eExNN2RLd0JpUnU3WUdRNi1vaDB3SEVOZHE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQUHhsWkkwMlFtdl9jNVN3cXd5YlRZc1kzQVZ1aW02X1pUZFFKUFUyNHZkNVlBZzFfTHo1VmFleU1pU2JNakxXZ083RXNvUzRXY29aS0IyeE45S3FmUlJ2MW1pYVhSRjlhSzRiOGxyNkItU3dtMVNYX3o1RnVQVUc5QUlYdnJhWWVhc0dRVDVCS1cxWllGNGR5R3hLeHZNODJhakRpWjFpNFRIRUxfdFUxMmJYTHdaY1piVHdWc25pb2VRSVR3emd3aG9MQUh1UQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5968,17 +5968,17 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Cidade do século 9, suspensa sobre falésias de calcário, atrai turistas no Mediterrâneo - Terra</t>
+          <t>Acidente com carreta de calcário deixa feridos na BR-282 em SC - ND Mais</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>17/05/2026 18:07</t>
+          <t>18/05/2026 04:00</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNR2ctaUFlZEp1YkFkMlpnTlZ0M3ZOUXF6T1FBZk9iaWpCM0plY0QyMkdZdlZzcXlXbDJpZjFfc3drZ0pTb1dWUEw3N2VrNG9WRmxhSWh1S3hMRnhpdms0TW5kak9udXA5aVcwZmNocWpmQi1yYXhZUlZZQmZmaWNLUnkyZ3FKVU44YzFBTk1lbEh0NS1VZWhiTjF6RndjTWhwYnhBZEE3TjEtWFRXWF96a05sMGhETDd5ZkVyZ0F1N3ljLUZWUWM3WTVwQksxR1E1ZmtKSTlLR3JqRWdUX0tMZGVoMk41SjZXRDc0QzZTeENuUkN1Yk5YSDRBYnU1QTJReHg4WG5n0gGGAkFVX3lxTE1HZy1pQWVkSnViQWQyWmdOVnQzdk5RcXpPUUFmT2JpakIzSmVjRDIyR1l2VnNxeVdsMmlmMV9zd2tnSlNvV1ZQTDc3ZWs0b1ZGbGFJaHVLeExGeGl2azRNbmRqT251cDlpVzBmY2hxamZCLXJheFlSVllCZmZpY0tSeTJncUpVTjhjMUFOTWVsSHQ1LVVlaGJOMXpGd2NNaHBieEFkQTdOMS1YVFdYX3prTmwwaERMN3lmRXJnQXU3eWMtRlZRYzdZNXBCSzFHUTVma0pJOUtHcmpFZ1RfS0xkZWgyTjVKNldENzRDNlN4Q25SQ3ViTlhINEFidTVBMlF4eDhYbmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxObnpROGFDVUpELUEyQjBhX20xS0pHR19uYzJmZkhrLTJtdjdIQktnSFpoWXFsc1BlRTIzU1kyS0dhZENFRXJWUDMxMmJacERxMVdaVUw0aGc4Z1VJdUdpbXhoNlA5b290RG1odlZERFFDcDBkZEFranZjbFQ3c0dJb0NKYnhtbmk0bDRnbWlMam9iekJra3c?oc=5</t>
         </is>
       </c>
     </row>
@@ -5990,127 +5990,127 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Copa do Calcário 2026 começa em abril - FERJ</t>
+          <t>Copa do Calcário: Macuco, Monerá e Altense garantem vaga nas semifinais - FERJ</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>17/05/2026 14:07</t>
+          <t>18/05/2026 04:00</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE11Y1dOay0tTWZ4bzdMS0dUbEFxam5TLTBoeXVtbzFfQ25oZm9FSzgzSW9nTmZ5MGdHdFl3OUM4RUR1M1JMN1Z4SzRGYzZiYS0xcWlYcU5pTE1mLVpFNi1DUmUyZXZ5SjJac1lyamZkWlI5Rlk0a3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNHZMQkhrMlBjTmpobDAwc0lrUFNZd2NqZnlFRzhDU2VfdThPNF96dW5UckVacHdhVWZJTlhJQzFrZ215NTNZaXFTaU1oanN2bTVJR0RVZFpMWG0zUm51My1wckdVTWhJZmJVSV85WUhHNHJxakd1bW5iWTU4aXFWQmkzZnBfa0tad0Exdzl5eExNN2RLd0JpUnU3WUdRNi1vaDB3SEVOZHE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>BARRAGENS | CMOC Brasil Unidade Ouro promove workshop de segurança - Brasil Mineral</t>
+          <t>Cidade do século 9, suspensa sobre falésias de calcário, atrai turistas no Mediterrâneo - Terra</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>15/05/2026 04:00</t>
+          <t>17/05/2026 18:07</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdDFyUHVYU1pJeTZZNzNxUlR2N0RyTlBIaldQT1BORENXVjZ5QmYzMDM5Z2NTUGg4Z0Q4aEtJWktlUS1Ed3c3WjJqOHNwZVhWLTN3c3d4OFVXUWJBNndDa1V5YUliYkNpSWpYN08xWld5MjJUVFVLRmRTVmNfQktGUVppWE9sRExYMTdjZUwxQkdoQmVpUFNsaWdCSjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNR2ctaUFlZEp1YkFkMlpnTlZ0M3ZOUXF6T1FBZk9iaWpCM0plY0QyMkdZdlZzcXlXbDJpZjFfc3drZ0pTb1dWUEw3N2VrNG9WRmxhSWh1S3hMRnhpdms0TW5kak9udXA5aVcwZmNocWpmQi1yYXhZUlZZQmZmaWNLUnkyZ3FKVU44YzFBTk1lbEh0NS1VZWhiTjF6RndjTWhwYnhBZEE3TjEtWFRXWF96a05sMGhETDd5ZkVyZ0F1N3ljLUZWUWM3WTVwQksxR1E1ZmtKSTlLR3JqRWdUX0tMZGVoMk41SjZXRDc0QzZTeENuUkN1Yk5YSDRBYnU1QTJReHg4WG5n0gGGAkFVX3lxTE1HZy1pQWVkSnViQWQyWmdOVnQzdk5RcXpPUUFmT2JpakIzSmVjRDIyR1l2VnNxeVdsMmlmMV9zd2tnSlNvV1ZQTDc3ZWs0b1ZGbGFJaHVLeExGeGl2azRNbmRqT251cDlpVzBmY2hxamZCLXJheFlSVllCZmZpY0tSeTJncUpVTjhjMUFOTWVsSHQ1LVVlaGJOMXpGd2NNaHBieEFkQTdOMS1YVFdYX3prTmwwaERMN3lmRXJnQXU3eWMtRlZRYzdZNXBCSzFHUTVma0pJOUtHcmpFZ1RfS0xkZWgyTjVKNldENzRDNlN4Q25SQ3ViTlhINEFidTVBMlF4eDhYbmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Reunião discute bônus e estabilidade de trabalhadores afetados pela Mosaic - Prefeitura de Araxá</t>
+          <t>Copa do Calcário 2026 começa em abril - FERJ</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>15/05/2026 04:00</t>
+          <t>17/05/2026 14:07</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOa0hzTkNxSFM2TDh6d24yeVVEb1RzU2dvOTJRRmR3OHRXMl9yNjk2TjNhcEQwLVF4TlBRME9OUVR6ZmFVOTdNZVF4MGZWNDU3dDl5bV9BWk9IcXlUMTZqYmYzUnhibHRQei1WeklNLU1yNkhwRmJqNjBOTi05QkJoUXJsZnJqUEtFZXlIREtZNVBic1N2RkJVMWVVb1BwZGRGZGNodXBDbUNUS2MydU9EUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE11Y1dOay0tTWZ4bzdMS0dUbEFxam5TLTBoeXVtbzFfQ25oZm9FSzgzSW9nTmZ5MGdHdFl3OUM4RUR1M1JMN1Z4SzRGYzZiYS0xcWlYcU5pTE1mLVpFNi1DUmUyZXZ5SjJac1lyamZkWlI5Rlk0a3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>O obstáculo virou o caminho - CNN Brasil</t>
+          <t>BARRAGENS | CMOC Brasil Unidade Ouro promove workshop de segurança - Brasil Mineral</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>14/05/2026 04:00</t>
+          <t>15/05/2026 04:00</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPY1JJbEVNOFRhMXg1R2FSNk43TVlIb0NUUGhlUlRERmxGYk5EZk01OVI5X0JxZEh0QU12OHJqUFhvRHJXNGZjaU4zcENiMVZnMDdjdk5HQmNpX2VvVFJ0OXVCRk1fUnNmTWdLdjFoc3RoYmQ0X0dVM25nWXJnWS1sazFhREZubTkyWVBldEdoMThKVjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdDFyUHVYU1pJeTZZNzNxUlR2N0RyTlBIaldQT1BORENXVjZ5QmYzMDM5Z2NTUGg4Z0Q4aEtJWktlUS1Ed3c3WjJqOHNwZVhWLTN3c3d4OFVXUWJBNndDa1V5YUliYkNpSWpYN08xWld5MjJUVFVLRmRTVmNfQktGUVppWE9sRExYMTdjZUwxQkdoQmVpUFNsaWdCSjA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil no menor valor para abril em 7 anos - Farmnews</t>
+          <t>Reunião discute bônus e estabilidade de trabalhadores afetados pela Mosaic - Prefeitura de Araxá</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>13/05/2026 04:00</t>
+          <t>15/05/2026 04:00</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNSFJIZGVZei1nU0tZTXdGeVdSekJlTkd5ajN1d3MwYk5LcmNTMlc1VWJXcjB3S2JGZmY4d2hTQnVBcGdBUjVYT3Z6Vnh0dVRrZFlXY1hEV25xWXBfVThpZkxFSGM4X3dvTjV6bWtMR2FHWTAwdElxNlpzV0RFNmxLMFhxbHRqUkxKNHdPODhMMEVBeHJfa1BpMGZ2a2FqbTQ5UVh1ZlJKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOa0hzTkNxSFM2TDh6d24yeVVEb1RzU2dvOTJRRmR3OHRXMl9yNjk2TjNhcEQwLVF4TlBRME9OUVR6ZmFVOTdNZVF4MGZWNDU3dDl5bV9BWk9IcXlUMTZqYmYzUnhibHRQei1WeklNLU1yNkhwRmJqNjBOTi05QkJoUXJsZnJqUEtFZXlIREtZNVBic1N2RkJVMWVVb1BwZGRGZGNodXBDbUNUS2MydU9EUg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Mosaic registra prejuízo no 1º trimestre e reduz produção diante da alta dos custos de matérias-primas - GlobalFert</t>
+          <t>O obstáculo virou o caminho - CNN Brasil</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>12/05/2026 04:00</t>
+          <t>14/05/2026 04:00</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPUFFYa0l4STNuY0phdjkxVi10MTN0WnVnTGp5bVVrWDRKajFzZm9nRU84MEtLNXdYc3dQZHE2LTNfV2poUGZHZ0xuWGlaS0pRUmRfTlBkeERWMmxYZ3FNd3VYZWQ3ZUdHc3A4eExHeU5ONTRJREpud3ZnZ0puMW81TXJlbFBmdGpWQnljWU5nMURSNDZ2T3psV2tYdjFrNjl4Y3Mya19id3NKUlU2ZEdJcFBQNE02OXRseU9HMmdmaVlBdFdwa3MyaklWX1JVRHBkbERaTWllZXhEZ2NHaFNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPY1JJbEVNOFRhMXg1R2FSNk43TVlIb0NUUGhlUlRERmxGYk5EZk01OVI5X0JxZEh0QU12OHJqUFhvRHJXNGZjaU4zcENiMVZnMDdjdk5HQmNpX2VvVFJ0OXVCRk1fUnNmTWdLdjFoc3RoYmQ0X0dVM25nWXJnWS1sazFhREZubTkyWVBldEdoMThKVjQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6122,29 +6122,29 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Ureia cai após meses de valorização - agrolink.com.br</t>
+          <t>Importação de ureia pelo Brasil no menor valor para abril em 7 anos - Farmnews</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>12/05/2026 04:00</t>
+          <t>13/05/2026 04:00</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOamEzNkdxNEZfcGNucldUQll1RjZYQzBwZE1sYlh4Ty1MaFdpSUZuckVHTk9uVXU1WTRPLTRLZ2Z1eEVVVU1Wa0haSXZURmhycm0tTEJubGJnZEE3ODRaQmt6bUVkUVlJTkVJWDlTUUVxSWZid3RzOHBhelAwZ082WGs3dkxnMXVwaU9PbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNSFJIZGVZei1nU0tZTXdGeVdSekJlTkd5ajN1d3MwYk5LcmNTMlc1VWJXcjB3S2JGZmY4d2hTQnVBcGdBUjVYT3Z6Vnh0dVRrZFlXY1hEV25xWXBfVThpZkxFSGM4X3dvTjV6bWtMR2FHWTAwdElxNlpzV0RFNmxLMFhxbHRqUkxKNHdPODhMMEVBeHJfa1BpMGZ2a2FqbTQ5UVh1ZlJKQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Novo revestimento de ureia controla liberação e reduz perdas - agrolink.com.br</t>
+          <t>Mosaic tem prejuízo milionário após encerrar operações em Araxá e Patrocínio - JM Online</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQZ01QdFBLLUUtYkI4VmRsYkpIMF9KZ0x4QV9fWGR1ak1YWTQ4enZhMkFCbkQ2dmJFbHgtVlRObml5X1Z3VWZVcnlrd2xSVFlJdzl3ZGdzTjNKUnM1b1pacXlZRjhxZ2RrNEZXWmVaZHBxdzZuMGFyNFJaVEhnVmtOYjJiMVV6enZUODk3bEgzdzRBME5rMkQ2a1NIbklNeGVmWlJ6YWZUamYwQTB4SThBLWxXMzhFcG1jLXFYR3Y5WFd2d3pFT2psV2ItaXRDelhYeURN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNQkZGXzhCdVRrM3pfOEFZWF9YemljbG94ZWM0TEt5MmVRZ1plcEpwVjNhZGl4S3BnMEhjMXp6T3RPVFlxNzZZQS1ZNTlGUXVEdktVdkZaT3N6dUFyNEJtM0FRQ2p5SVBoY1lxY05FODRTUlhpOWdUZTdqRURFODhVa1hoOXZRWkVva2R6X1E5LTRVT0trcl9DMnZuWGJSdG53RjNBVzg4UC1NVEZHTFVqamt1UUI1QdIBvgFBVV95cUxPM3BIRjRldGZwM3RMSXRuTmk4S0NodGdXRmFZcEJHaTgtYkNRTEl2VDFoYnNnZkxndHB2YVdNX3ZmRVEyWlNhM1hheWFuNDh1Qlg2b2IxMkJMNDlDQnVkaUdRWURfQ0ZtZENVRUt0cHhPZkY2UFlDcDdTTEFGeG5CQlZ2OUU1bnhyMjg3cFBNQVlMZTNLU0tOUVM0TzRrUlhmS3V6MjlLR0JLT0ZQZGhydkwxQ3RPS25LWkQ5UTBn?oc=5</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Mosaic Fertilizantes tem prejuízo de US$ 422 mi com paralisações em Minas - diariodocomercio.com.br</t>
+          <t>MOSAIC FERTILIZANTES TEM PREJUÍZO DE US$ 422 MILHÕES COM PARALISAÇÕES EM ARAXÁ E PATROCÍNIO - Jornal de Patrocínio</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -6176,19 +6176,19 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1OTzdvNnBuejJSeVRQaXZRQXBnTHVzNFoxNUp6dl9JcEVDUlVoUmpEcTNpUXRlSG1nNHVKSTd4d1E0eWFTemR2UzJyWnhYZXB2SFc5RWlILXJnaGpoQjh3N0hxV0R2MVQzbU9BU2EySHpIY0VjVUJ6YWZJM1gyUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNSmlUbVFybFZNbFluRHpHc1hhczRiN09pREhsMm5DMjRlSkV2blV2dUdReVI5bmo1RW1NZ1oxLWJBWHl4SnJEN29EV3lMU3A4enhVNjBmNUxfbmhVZVpmaTVsTzFJOXhMZWFJWUlCX0V5djVNQmktSHNJMzFiMkh2TVp3aHo4THF4VlJ0LU1tNmxmVkVDTHdfTEctNnpUdUtOc184ZjRfLTI4WVVkSlVVb3g5bXlqTEtWMkNyZVAyeThub28?oc=5</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo milionário após encerrar operações em Araxá e Patrocínio - JM Online</t>
+          <t>Novo revestimento de ureia controla liberação e reduz perdas - Agrolink</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6198,19 +6198,19 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNQkZGXzhCdVRrM3pfOEFZWF9YemljbG94ZWM0TEt5MmVRZ1plcEpwVjNhZGl4S3BnMEhjMXp6T3RPVFlxNzZZQS1ZNTlGUXVEdktVdkZaT3N6dUFyNEJtM0FRQ2p5SVBoY1lxY05FODRTUlhpOWdUZTdqRURFODhVa1hoOXZRWkVva2R6X1E5LTRVT0trcl9DMnZuWGJSdG53RjNBVzg4UC1NVEZHTFVqamt1UUI1QdIBvgFBVV95cUxPM3BIRjRldGZwM3RMSXRuTmk4S0NodGdXRmFZcEJHaTgtYkNRTEl2VDFoYnNnZkxndHB2YVdNX3ZmRVEyWlNhM1hheWFuNDh1Qlg2b2IxMkJMNDlDQnVkaUdRWURfQ0ZtZENVRUt0cHhPZkY2UFlDcDdTTEFGeG5CQlZ2OUU1bnhyMjg3cFBNQVlMZTNLU0tOUVM0TzRrUlhmS3V6MjlLR0JLT0ZQZGhydkwxQ3RPS25LWkQ5UTBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQZ01QdFBLLUUtYkI4VmRsYkpIMF9KZ0x4QV9fWGR1ak1YWTQ4enZhMkFCbkQ2dmJFbHgtVlRObml5X1Z3VWZVcnlrd2xSVFlJdzl3ZGdzTjNKUnM1b1pacXlZRjhxZ2RrNEZXWmVaZHBxdzZuMGFyNFJaVEhnVmtOYjJiMVV6enZUODk3bEgzdzRBME5rMkQ2a1NIbklNeGVmWlJ6YWZUamYwQTB4SThBLWxXMzhFcG1jLXFYR3Y5WFd2d3pFT2psV2ItaXRDelhYeURN?oc=5</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES TEM PREJUÍZO DE US$ 422 MILHÕES COM PARALISAÇÕES EM ARAXÁ E PATROCÍNIO - Jornal de Patrocínio</t>
+          <t>Ureia cai após meses de valorização - Agrolink</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNSmlUbVFybFZNbFluRHpHc1hhczRiN09pREhsMm5DMjRlSkV2blV2dUdReVI5bmo1RW1NZ1oxLWJBWHl4SnJEN29EV3lMU3A4enhVNjBmNUxfbmhVZVpmaTVsTzFJOXhMZWFJWUlCX0V5djVNQmktSHNJMzFiMkh2TVp3aHo4THF4VlJ0LU1tNmxmVkVDTHdfTEctNnpUdUtOc184ZjRfLTI4WVVkSlVVb3g5bXlqTEtWMkNyZVAyeThub28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOamEzNkdxNEZfcGNucldUQll1RjZYQzBwZE1sYlh4Ty1MaFdpSUZuckVHTk9uVXU1WTRPLTRLZ2Z1eEVVVU1Wa0haSXZURmhycm0tTEJubGJnZEE3ODRaQmt6bUVkUVlJTkVJWDlTUUVxSWZid3RzOHBhelAwZ082WGs3dkxnMXVwaU9PbQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6232,17 +6232,17 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Prefeitura de Paranaguá e Mosaic inauguram unidade do programa Horta Educa na Escola Eva Cavani - Secultur</t>
+          <t>Mosaic Fertilizantes tem prejuízo de US$ 422 mi com paralisações em Minas - Diário do Comércio</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>11/05/2026 13:42</t>
+          <t>12/05/2026 04:00</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE54NVh6Qmh3SVFMbFV1Qng5SGdpT3JPSXVHNmt4WDhxdVpGV1l6T3VyVHR6WXVsNEtSX2FUWURvSnNmZzFVTmt0WE9ReEd2dTZvQmpuMEpBSnFncjA4VEQ0aHFCdU55cmM3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1OTzdvNnBuejJSeVRQaXZRQXBnTHVzNFoxNUp6dl9JcEVDUlVoUmpEcTNpUXRlSG1nNHVKSTd4d1E0eWFTemR2UzJyWnhYZXB2SFc5RWlILXJnaGpoQjh3N0hxV0R2MVQzbU9BU2EySHpIY0VjVUJ6YWZJM1gyUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6254,29 +6254,29 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>“Não há fosfato suficiente para atender à demanda global”, alerta CEO da Mosaic - The AgriBiz</t>
+          <t>Prefeitura de Paranaguá e Mosaic inauguram unidade do programa Horta Educa na Escola Eva Cavani - Secultur</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>11/05/2026 04:00</t>
+          <t>11/05/2026 13:42</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVDBiNGg1Yk1uby1oMlVYeW1ZU2VVQUdUUlNNRXYzWUV5OF9tV2wxdXJZWnNQZ2Jpc0ZRNW14UmwyMF9mSVM5U29iVnZqdkhGMk9ZaUN4VzZNTzA0NTlNX3JJTnVMSDNlc3p4M1F3Ml9EX1AzaERiMzFNQjFJVDd0UUtjanZzNXhSVTZoN09mMl8yOGh2M0dYTXpwV1lScGx1dlVxc3dERnkxeHdIRnM4ZTVpU29abkNzLXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE54NVh6Qmh3SVFMbFV1Qng5SGdpT3JPSXVHNmt4WDhxdVpGV1l6T3VyVHR6WXVsNEtSX2FUWURvSnNmZzFVTmt0WE9ReEd2dTZvQmpuMEpBSnFncjA4VEQ0aHFCdU55cmM3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Demanda fraca derruba preços da ureia mas não destrava mercado - CNN Brasil</t>
+          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -6286,19 +6286,19 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONnJwX0hzX1RaX3dlVGxVVjVBczRMV3Jtd1dBaXBNeU4tVUFJLU9iNGNPY0JKSGFxUjBUVDlONWNvNDRrd1NLOTFWYTJPNjFhVGVIUW4xVDNyWlE3OVlmWjhQWUgyZk0wOU56bTJfcTJ3dkJCYU9Ub0JSUVlMWDFCT0txUzU0ZlJJNXpTMGlnRUw1cjhwd25rYjAyNjBvdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Margens derretem no Brasil e Mosaic começa 2026 no vermelho (mesmo com alta na receita) - AgFeed</t>
+          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -6308,19 +6308,19 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORklOTkFqdEJTSkRkVUgwalFVWjdVOVNRTjZzOFBhS1h4Xzl1YnM4dU56QWY3UnFHeVdpaGNFdnVwTzctWURPQUVwZExqN1MzZWYwemxndGxVVE93eUxybzEzQVFxbkVWWVJhMU5hOHU5TGpUTGNRZ1dWVXRuV2xBNHZBMUprWEpYYnYyX3Y3ekhRbVNvWWpfSVpYZ1NTeURnOXJfc1Z2eUFERkh5TlZGUjBmMzlKS1ox?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVkZIWHBTbDkyUzZ6RktMXzZBenVZRWFfN1NTeUxRaDJGSkxTVmlmamFpM2ZxdjlTQWV6WHJtMG9EU1Jzd094RnpXQVZDQ0lQWVhTWXM2bDYtNWRNYkdpcFlhWUtGN0tvWXR4SXJXUTNlcWhKQzBxWXJGalV2Zk1rX1B4LXpyNEN0b3lEWkZwQ3lLUnB4VGM0ZnA3clFnQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
+          <t>Demanda fraca derruba preços da ureia mas não destrava mercado - CNN Brasil</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -6330,19 +6330,19 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONnJwX0hzX1RaX3dlVGxVVjVBczRMV3Jtd1dBaXBNeU4tVUFJLU9iNGNPY0JKSGFxUjBUVDlONWNvNDRrd1NLOTFWYTJPNjFhVGVIUW4xVDNyWlE3OVlmWjhQWUgyZk0wOU56bTJfcTJ3dkJCYU9Ub0JSUVlMWDFCT0txUzU0ZlJJNXpTMGlnRUw1cjhwd25rYjAyNjBvdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Jornal Correio Centro Oeste Arcos</t>
+          <t>Margens derretem no Brasil e Mosaic começa 2026 no vermelho (mesmo com alta na receita) - AgFeed</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -6352,19 +6352,19 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORklOTkFqdEJTSkRkVUgwalFVWjdVOVNRTjZzOFBhS1h4Xzl1YnM4dU56QWY3UnFHeVdpaGNFdnVwTzctWURPQUVwZExqN1MzZWYwemxndGxVVE93eUxybzEzQVFxbkVWWVJhMU5hOHU5TGpUTGNRZ1dWVXRuV2xBNHZBMUprWEpYYnYyX3Y3ekhRbVNvWWpfSVpYZ1NTeURnOXJfc1Z2eUFERkh5TlZGUjBmMzlKS1ox?oc=5</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
+          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Jornal Correio Centro Oeste Arcos</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVkZIWHBTbDkyUzZ6RktMXzZBenVZRWFfN1NTeUxRaDJGSkxTVmlmamFpM2ZxdjlTQWV6WHJtMG9EU1Jzd094RnpXQVZDQ0lQWVhTWXM2bDYtNWRNYkdpcFlhWUtGN0tvWXR4SXJXUTNlcWhKQzBxWXJGalV2Zk1rX1B4LXpyNEN0b3lEWkZwQ3lLUnB4VGM0ZnA3clFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 258 milhões no trimestre - CNN Brasil</t>
+          <t>“Não há fosfato suficiente para atender à demanda global”, alerta CEO da Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -6396,51 +6396,51 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZC1GeGtLMy0wY2l4ay1zQ3RUblZncTFoTzdEM2s3b3dQeEdWQjZ5X2ZDLTI3VDNJZkdwQTl0S3N2UGN1OUw5Q2Vla19aS0p1RV91R3JMN0RzOVd3UGJnNGh0N1BCckRvSndoMmxYMERNU2RIQ0wwRlR6U19nb2h6bHJoWEEyeWxIN0xrYnFfdTlFT3VMMDlrMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVDBiNGg1Yk1uby1oMlVYeW1ZU2VVQUdUUlNNRXYzWUV5OF9tV2wxdXJZWnNQZ2Jpc0ZRNW14UmwyMF9mSVM5U29iVnZqdkhGMk9ZaUN4VzZNTzA0NTlNX3JJTnVMSDNlc3p4M1F3Ml9EX1AzaERiMzFNQjFJVDd0UUtjanZzNXhSVTZoN09mMl8yOGh2M0dYTXpwV1lScGx1dlVxc3dERnkxeHdIRnM4ZTVpU29abkNzLXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Macuco e Monerá lideram a Copa do Calcário - FERJ</t>
+          <t>Mosaic tem prejuízo líquido de US$ 258 milhões no trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>10/05/2026 04:00</t>
+          <t>11/05/2026 04:00</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOWG5SM0pRYV8yeVhlRzFwVlBLUG5XRmNYTWpMMEdaRFd2OFlBT2d3WHIwcmNJMVlWRkNONTI4b0hpeVZrdlVxc01uTEoyUm92WnQ4R2JSTGx4M1ZnaWZtRlB2UkFRZjRybjhwaWdzRDB0Ym1sdy1vRGdDN2k0V1NtZXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZC1GeGtLMy0wY2l4ay1zQ3RUblZncTFoTzdEM2s3b3dQeEdWQjZ5X2ZDLTI3VDNJZkdwQTl0S3N2UGN1OUw5Q2Vla19aS0p1RV91R3JMN0RzOVd3UGJnNGh0N1BCckRvSndoMmxYMERNU2RIQ0wwRlR6U19nb2h6bHJoWEEyeWxIN0xrYnFfdTlFT3VMMDlrMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Carga de enxofre cai na pista da Rodovia Ayrton Senna após acidente - G1</t>
+          <t>Macuco e Monerá lideram a Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>08/05/2026 04:00</t>
+          <t>10/05/2026 04:00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPVURlU1pkY2xFUkxKczI2WGNkZnJBMk1MOHhSRTI2ZEJWMUhfdjBFU1F1TGpMbUl6eVkxc1FWOWlheHNpN1hIQ3NRejI1Y2dsbHZwTS1fSmlJZnFtWWZuM2gtUUZhblBKdGFMelF1cTdLN0xJUWd2dkh2UUQwWGlBUGgyTDdtLWtVRXJrc3FXX3pmZENBb0RKc21MVndkUHR6VGxYM0RjN3FMelhpOF9zQmgtTkNnNy01QVl1ZFg2eXV1b3MzdUxFYTFPeUZWQdIB3AFBVV95cUxNNVFUeU9TN3Z2S3N5M240dmZOTmg3VnNjX1p4NzZkdXl5NU4zc0dFbGEySjJ3enNQb3VPSkdGdGJBVHVBZ2dLa3hxUnNsX1JPQmNiX2RKVEE2SE1KemhlbnhPLTJRc3U5VnRFeVpXdThGNFlXZDk0YjlyazlxTWNfT3o3R2RfVVBrSi1TNWlJQjQ1VnY2b0tienVBSlpvbHhJbWtCLU0xamNJWTRMLTA0bmFLZ2dhRm1SSm9VVjI2ZmtobWxpd3J5aDNFajFOODJ2U3NyVnNJNjFLRzQy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOWG5SM0pRYV8yeVhlRzFwVlBLUG5XRmNYTWpMMEdaRFd2OFlBT2d3WHIwcmNJMVlWRkNONTI4b0hpeVZrdlVxc01uTEoyUm92WnQ4R2JSTGx4M1ZnaWZtRlB2UkFRZjRybjhwaWdzRDB0Ym1sdy1vRGdDN2k0V1NtZXh3?oc=5</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Carga de enxofre é derramada na Rodovia Ayrton Senna após acidente entre dois caminhões em Itaquaquecetuba - G1</t>
+          <t>Carga de enxofre cai na pista da Rodovia Ayrton Senna após acidente - G1</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -6462,51 +6462,51 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMjJXYVBLSHRScWpkR1pXa1F4R1Q2R1N5UzczQ3JGSkxaaGJrOUc5aGVzbU4xZTJ6WVVBMTVJeWJLS0l3VmlUMExTT09oUmFEbUR0ZldLTXUwSmJ2UkR1MFVCUkN2dzMzLWxtTkNfOGh5aFdyNjJzVUM2Wkgyc1dfcEJDUnZCQk4xUUR5cjZpT2VfNHlxVUFZYVphTTNWd2Y1U1NUTy1fcnFIM2p6S3dpR1BfMHRKeG1yS2ppVm5sTmMwZk3SAdIBQVVfeXFMTmVyUjFibUtlTnhSRkRwbFl2LVQ2RE9BdTdQRUM0Z2dSUmF6RnFRUlNrS3pIZzNBTy10NDdEWXBNYTVJZlB6X05CeTQycjdjelI4c1VHZ2QxRDdia0s5NFR0b3p1aGZPUi1RQlBiTDlRY3RLekdXXzBBdzQ2RUVLRDRhNGxlSUZBbjJXVlRKRkV1ZjhxXzlkanRqZmdERzZYemJnOFRzRWNLTHd1SnIxSmk0T3dtT2NhWHJiTjRUM0ZUbkVIdmZUS3R4OVJueS1LbzRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPVURlU1pkY2xFUkxKczI2WGNkZnJBMk1MOHhSRTI2ZEJWMUhfdjBFU1F1TGpMbUl6eVkxc1FWOWlheHNpN1hIQ3NRejI1Y2dsbHZwTS1fSmlJZnFtWWZuM2gtUUZhblBKdGFMelF1cTdLN0xJUWd2dkh2UUQwWGlBUGgyTDdtLWtVRXJrc3FXX3pmZENBb0RKc21MVndkUHR6VGxYM0RjN3FMelhpOF9zQmgtTkNnNy01QVl1ZFg2eXV1b3MzdUxFYTFPeUZWQdIB3AFBVV95cUxNNVFUeU9TN3Z2S3N5M240dmZOTmg3VnNjX1p4NzZkdXl5NU4zc0dFbGEySjJ3enNQb3VPSkdGdGJBVHVBZ2dLa3hxUnNsX1JPQmNiX2RKVEE2SE1KemhlbnhPLTJRc3U5VnRFeVpXdThGNFlXZDk0YjlyazlxTWNfT3o3R2RfVVBrSi1TNWlJQjQ1VnY2b0tienVBSlpvbHhJbWtCLU0xamNJWTRMLTA0bmFLZ2dhRm1SSm9VVjI2ZmtobWxpd3J5aDNFajFOODJ2U3NyVnNJNjFLRzQy?oc=5</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Memórias do calcário: Château Pavie Macquin renasce em Saint-Émilion - Revista ADEGA ·</t>
+          <t>Carga de enxofre é derramada na Rodovia Ayrton Senna após acidente entre dois caminhões em Itaquaquecetuba - G1</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>06/05/2026 11:23</t>
+          <t>08/05/2026 04:00</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQaC1QaG1CQnVDUFU4N2JNTUp5Vld2TzBOZXFsdDU4UXZ4c0tDZXZRX2hGVDl2UlRoTjFEN0VCNlRrUU5qejV3cUpkcW1XdFBmcXlNeWVCSU9qdVV1TWpRdUlNZEstaG4yd1hrTHJSbmxLZkJGSF9zUXlyM3FVZjhHaEdROHVMeWdqLVNuMVRnMmdkOWpRMl9xQTlwa1RKNWlvLWRybHZrUDJ0bVBkYXA5atIBtgFBVV95cUxOQV9OR2ZkY0wtR0pvX05MVVNxZm9KaG1Cb3BCT21WMHFoak1kVF8zYlBSMl9NeTVrT0dubk5uWFVTMENMemQtSDJwa3p0TC1oejhEdmRidnBHNzB2OV9LUHVNTnJueTNFUi1GRm9wSnZwdGVJTUIteENFOHZ2czhFSllaMFk4aF95LVVtMXV3NGhqeHZBbmxBZkRObzMwMjMtUmRaN2dBVldfZGt0ZlRXQmZDejF0Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMjJXYVBLSHRScWpkR1pXa1F4R1Q2R1N5UzczQ3JGSkxaaGJrOUc5aGVzbU4xZTJ6WVVBMTVJeWJLS0l3VmlUMExTT09oUmFEbUR0ZldLTXUwSmJ2UkR1MFVCUkN2dzMzLWxtTkNfOGh5aFdyNjJzVUM2Wkgyc1dfcEJDUnZCQk4xUUR5cjZpT2VfNHlxVUFZYVphTTNWd2Y1U1NUTy1fcnFIM2p6S3dpR1BfMHRKeG1yS2ppVm5sTmMwZk3SAdIBQVVfeXFMTmVyUjFibUtlTnhSRkRwbFl2LVQ2RE9BdTdQRUM0Z2dSUmF6RnFRUlNrS3pIZzNBTy10NDdEWXBNYTVJZlB6X05CeTQycjdjelI4c1VHZ2QxRDdia0s5NFR0b3p1aGZPUi1RQlBiTDlRY3RLekdXXzBBdzQ2RUVLRDRhNGxlSUZBbjJXVlRKRkV1ZjhxXzlkanRqZmdERzZYemJnOFRzRWNLTHd1SnIxSmk0T3dtT2NhWHJiTjRUM0ZUbkVIdmZUS3R4OVJueS1LbzRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Alta do enxofre pressiona uso de fosfatado no país - agrolink.com.br</t>
+          <t>Memórias do calcário: Château Pavie Macquin renasce em Saint-Émilion - Revista ADEGA ·</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>06/05/2026 04:00</t>
+          <t>06/05/2026 11:23</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQaC1QaG1CQnVDUFU4N2JNTUp5Vld2TzBOZXFsdDU4UXZ4c0tDZXZRX2hGVDl2UlRoTjFEN0VCNlRrUU5qejV3cUpkcW1XdFBmcXlNeWVCSU9qdVV1TWpRdUlNZEstaG4yd1hrTHJSbmxLZkJGSF9zUXlyM3FVZjhHaEdROHVMeWdqLVNuMVRnMmdkOWpRMl9xQTlwa1RKNWlvLWRybHZrUDJ0bVBkYXA5atIBtgFBVV95cUxOQV9OR2ZkY0wtR0pvX05MVVNxZm9KaG1Cb3BCT21WMHFoak1kVF8zYlBSMl9NeTVrT0dubk5uWFVTMENMemQtSDJwa3p0TC1oejhEdmRidnBHNzB2OV9LUHVNTnJueTNFUi1GRm9wSnZwdGVJTUIteENFOHZ2czhFSllaMFk4aF95LVVtMXV3NGhqeHZBbmxBZkRObzMwMjMtUmRaN2dBVldfZGt0ZlRXQmZDejF0Zw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>EUA ainda precisam importar ureia - agrolink.com.br</t>
+          <t>EUA ainda precisam importar ureia - Agrolink</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -6535,12 +6535,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
+          <t>Alta do enxofre pressiona uso de fosfatado no país - Agrolink</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZENuS3MwY1NDNlVENVlLT3FhbGpTMUZacGNmc3lKR2NINjRRdkNGUndsRW1QaEhPVG1yMkx5eG5mYTRpMENzbXRVVVlZSXFPQnJKMF9UbjBNeW1xTTl0cXdjOEpMQk5CaktWT0c0anZvVEFwQkQ3LXdhRWkzNXN5eE9yTldTUzg5Ul9QLWo2WWZDbk5BbUMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
         </is>
       </c>
     </row>
@@ -6562,17 +6562,17 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Ureia inicia movimento de queda global após dois meses de alta - Canal Rural</t>
+          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>05/05/2026 04:00</t>
+          <t>06/05/2026 04:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxONUk3RS1YMGFVeTl3VFlxaTNTcXQxMmtGNHYwdWh4MzlWZmlHaFZUNDlhX3hFY2lEcXdnR0ZaQVFRaE5VN2JOUE82LXI0blB4V3cwRmZ6aUN3ZVhacnFmZVhybEVtWWlrMHV2TG1KUGZhQVRqdDNCeXRKeUd6bWxlMGNsWjdnV0JOQWQtSnFvaDdlU01zSVRkcE5RbWx2bjU2OXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZENuS3MwY1NDNlVENVlLT3FhbGpTMUZacGNmc3lKR2NINjRRdkNGUndsRW1QaEhPVG1yMkx5eG5mYTRpMENzbXRVVVlZSXFPQnJKMF9UbjBNeW1xTTl0cXdjOEpMQk5CaktWT0c0anZvVEFwQkQ3LXdhRWkzNXN5eE9yTldTUzg5Ul9QLWo2WWZDbk5BbUMw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6584,29 +6584,29 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
+          <t>Ureia inicia movimento de queda global após dois meses de alta - canalrural.com.br</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>04/05/2026 04:00</t>
+          <t>05/05/2026 04:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxONUk3RS1YMGFVeTl3VFlxaTNTcXQxMmtGNHYwdWh4MzlWZmlHaFZUNDlhX3hFY2lEcXdnR0ZaQVFRaE5VN2JOUE82LXI0blB4V3cwRmZ6aUN3ZVhacnFmZVhybEVtWWlrMHV2TG1KUGZhQVRqdDNCeXRKeUd6bWxlMGNsWjdnV0JOQWQtSnFvaDdlU01zSVRkcE5RbWx2bjU2OXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Mineração vira aposta bilionária no Equador: China fecha acordo de US$ 1,7 bilhão para explorar uma das maiores jazidas de ouro do país, promete US$ 4,39 bilhões ao Estado e amplia sua força na América do Sul - CPG Click Petróleo e Gás</t>
+          <t>Após forte alta, preço da ureia começa a cair, mostra levantamento - canalrural.com.br</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -6616,19 +6616,19 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNYWlRUWx5RGM2b3h1UEJTdzNRcmRXVzRRQjBWcFY5cDRiVjhwMUIyeE9tdGh5LXUxLU5QcUxxNDBfQkVYa3BWVUV0enZxYlh5cDVISlNNY1ZRVXd6LXY0bFgwQ2diUUp6YmtWb3gtSTZQR0hfUmE5Y2dpWXk4RW03MVVfODFZNmt0Y2hORTQ3TEZrWmR5TXdfWlNuLU9HSTItUGQwb1R5R25zWi04ZzdsU3VWcjJUVnJzaFdzT2pQQkp4RDBSR0NOX3hmXzBmSGdxQk5hcU1aM2ZLMkJkRmpZRjI1enBHN25HVWw1TFVpMUxfTTY3bF9hdUxQZHZzTFpPaDloMzh0cmJfZUUxeWJHSUNxdXFkcnFVQW1Bb2xQYnhYZ1J6U2xJNWtRbkZHbS1D?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcUZLcjlzMlFBNFM4Nlo2U2ZYdk1hc2YyOGg3Rng2VThuZVY3cXk2V1BXNWFjaWQyb3lvbnM1d2E0b1BwVFYwZzhEX2drSWxyQllLQlM5S25Uamd6U0pYTVo0cjFjcjRHMGJVXzQ0SUM3V2tIR3hpTER6NjF0OUZ2T1VNNWxyeWloRjlTRDlqSkhtcTFBQk50akZscERXME9DRjF4dWtnaGRvbFU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Sine Araxá inicia recebimento de currículos para recolocação de trabalhadores da Mosaic - Prefeitura de Araxá</t>
+          <t>Preços da ureia cedem após dois meses em alta - Globo Rural</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -6638,19 +6638,19 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPWXRhQzl0UFljZ25weHRsTWo5VmlfOGlPWDBvcHZFTGVqb0pJWW9rTE1TZlVtQXo3UjI2TWhscWhCSWFfWWpJZ3JIRmwycjNWTld6UllKMFBBVjhWRU5BM1laZC01Wjd5S1pRLWxwdjhXYjVPZDRMWjBCcmtmcG1rZFlUWG5oQnFlMFdjenJwbDFWZzc1X1FKWjd6RTZhQVNOTG9Rb3JoRGhib1U2RXJyYWZiNmJPRjlTV0tEbkJmN3U3QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQTFfM1dYaG9xa0s1eXk4bXRQb0d6V2Q0NzFvOEJ4dlB2b2NRMlkxRE5ZZUZQdlV1ZFdyWGljN3Z5RVRFUTVuTjZ4cDIyUDdrZWpWMUJtNHJrZmxsWV9zZkRobXoyd0VBRXFvYXB0WDFsSC1vMDZBN2haLXYyUFp6UWtzQTlYb0xSMERMWElPN3FZSDFQN0l4ckd1U3RIaDM4cnRNNUoyUdIBtgFBVV95cUxOVlRkd0NYWjUzZEhHblM0eGlJdjlNblRaWDAwWWlNclRFbXVYY3VBQmczNVpEdWdzOXJqNHY5dUVZVWVYMzNsNHNsRTYxenZkMXRqQkNYUlU3YWxWajc5NmZld2dwRmRzaER1T1lTdG1KZ0hUdVJqeW9kNDBjWTRfaHo5eG1oZThZTzVsQ0M2aXljcURYWk1YWGdxeno1M1JkTTlZZjVKR2x5U2xrTUNSeUJfMmRJdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Rodada quente e com muitos gols na Copa do Calcário - FERJ</t>
+          <t>Ureia inicia queda global após disparada dos preços - StoneX</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQcjJSS2JUOW9EbGNBMlhnOW05Q1NodTh6Sks5a21QYzFJTGRGYnlmamIzMmxfNVNaOXRqQVA1OTg4NENjVHZ6U19FVjZSYjQwOG11Z0o5YW82VGs3ZXRaQWp5UHJqSk0wVHRZcU11R0pZaVpMZ1J4ZC1veVFpd1puc0V5RWdqQWE0VXhicEd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPNUMtNEYyR21sTTRYZ2Z5UE9XNGJfMmJvYkJaMjc5em5ZVmx5U3hINmg1MVpHZUdHS2hqbzVnOWN2T0tKV0dmeGFvamdFazhzQ0I3RU9Oa2xEbXBGRDNlUHFfemNTLXpOWUpLeVNCMkZjeWxuS3lDdWE0bEpNLTdBNTRzRDQ0QThrWE9sNDdDdW10ZkZfVFVBUE5zb2E5M29EbkdvLUdSOXRlTTEyZkJ2T0l1aw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Ureia inicia queda global após disparada dos preços - StoneX</t>
+          <t>Preços da ureia começam a desacelerar após forte alta com conflito - CNN Brasil</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6682,19 +6682,19 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPNUMtNEYyR21sTTRYZ2Z5UE9XNGJfMmJvYkJaMjc5em5ZVmx5U3hINmg1MVpHZUdHS2hqbzVnOWN2T0tKV0dmeGFvamdFazhzQ0I3RU9Oa2xEbXBGRDNlUHFfemNTLXpOWUpLeVNCMkZjeWxuS3lDdWE0bEpNLTdBNTRzRDQ0QThrWE9sNDdDdW10ZkZfVFVBUE5zb2E5M29EbkdvLUdSOXRlTTEyZkJ2T0l1aw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPd0VHZGk0YmpqT3Jzd0hnMVRySDYzYU9wZC1ieXJPc1dPX081SkpEdDZNUUNBYUJMWlNNVk5mQVp0eEdPNVA3d1B2d1VTREo3QmJvYkQ1YjZfdG9zMHgzTnludnA4U1VFcUNCd1d0SjVzWDdYd0JNM2xSLWs1czZmcTVPZllkTkdDbFlPblQ4MEttaUdySWo1enhoakxocEk5SVpF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Preços da ureia cedem após dois meses em alta - Globo Rural</t>
+          <t>Rodada quente e com muitos gols na Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQTFfM1dYaG9xa0s1eXk4bXRQb0d6V2Q0NzFvOEJ4dlB2b2NRMlkxRE5ZZUZQdlV1ZFdyWGljN3Z5RVRFUTVuTjZ4cDIyUDdrZWpWMUJtNHJrZmxsWV9zZkRobXoyd0VBRXFvYXB0WDFsSC1vMDZBN2haLXYyUFp6UWtzQTlYb0xSMERMWElPN3FZSDFQN0l4ckd1U3RIaDM4cnRNNUoyUdIBtgFBVV95cUxOVlRkd0NYWjUzZEhHblM0eGlJdjlNblRaWDAwWWlNclRFbXVYY3VBQmczNVpEdWdzOXJqNHY5dUVZVWVYMzNsNHNsRTYxenZkMXRqQkNYUlU3YWxWajc5NmZld2dwRmRzaER1T1lTdG1KZ0hUdVJqeW9kNDBjWTRfaHo5eG1oZThZTzVsQ0M2aXljcURYWk1YWGdxeno1M1JkTTlZZjVKR2x5U2xrTUNSeUJfMmRJdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQcjJSS2JUOW9EbGNBMlhnOW05Q1NodTh6Sks5a21QYzFJTGRGYnlmamIzMmxfNVNaOXRqQVA1OTg4NENjVHZ6U19FVjZSYjQwOG11Z0o5YW82VGs3ZXRaQWp5UHJqSk0wVHRZcU11R0pZaVpMZ1J4ZC1veVFpd1puc0V5RWdqQWE0VXhicEd3?oc=5</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Após forte alta, preço da ureia começa a cair, mostra levantamento - Canal Rural</t>
+          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcUZLcjlzMlFBNFM4Nlo2U2ZYdk1hc2YyOGg3Rng2VThuZVY3cXk2V1BXNWFjaWQyb3lvbnM1d2E0b1BwVFYwZzhEX2drSWxyQllLQlM5S25Uamd6U0pYTVo0cjFjcjRHMGJVXzQ0SUM3V2tIR3hpTER6NjF0OUZ2T1VNNWxyeWloRjlTRDlqSkhtcTFBQk50akZscERXME9DRjF4dWtnaGRvbFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - agrolink.com.br</t>
+          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -6755,12 +6755,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Preços da ureia começam a desacelerar após forte alta com conflito - CNN Brasil</t>
+          <t>Mineração vira aposta bilionária no Equador: China fecha acordo de US$ 1,7 bilhão para explorar uma das maiores jazidas de ouro do país, promete US$ 4,39 bilhões ao Estado e amplia sua força na América do Sul - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPd0VHZGk0YmpqT3Jzd0hnMVRySDYzYU9wZC1ieXJPc1dPX081SkpEdDZNUUNBYUJMWlNNVk5mQVp0eEdPNVA3d1B2d1VTREo3QmJvYkQ1YjZfdG9zMHgzTnludnA4U1VFcUNCd1d0SjVzWDdYd0JNM2xSLWs1czZmcTVPZllkTkdDbFlPblQ4MEttaUdySWo1enhoakxocEk5SVpF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNYWlRUWx5RGM2b3h1UEJTdzNRcmRXVzRRQjBWcFY5cDRiVjhwMUIyeE9tdGh5LXUxLU5QcUxxNDBfQkVYa3BWVUV0enZxYlh5cDVISlNNY1ZRVXd6LXY0bFgwQ2diUUp6YmtWb3gtSTZQR0hfUmE5Y2dpWXk4RW03MVVfODFZNmt0Y2hORTQ3TEZrWmR5TXdfWlNuLU9HSTItUGQwb1R5R25zWi04ZzdsU3VWcjJUVnJzaFdzT2pQQkp4RDBSR0NOX3hmXzBmSGdxQk5hcU1aM2ZLMkJkRmpZRjI1enBHN25HVWw1TFVpMUxfTTY3bF9hdUxQZHZzTFpPaDloMzh0cmJfZUUxeWJHSUNxdXFkcnFVQW1Bb2xQYnhYZ1J6U2xJNWtRbkZHbS1D?oc=5</t>
         </is>
       </c>
     </row>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Petrobras volta a produzir ureia em fábrica de fertilizante no Paraná - agrolink.com.br</t>
+          <t>Petrobras volta a produzir ureia em fábrica de fertilizante no Paraná - Agrolink</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -6799,12 +6799,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Em meio à crise dos fertilizantes, Petrobras volta a produzir ureia no Paraná após seis anos - VEJA</t>
+          <t>Cotações Agrícolas para esta Quinta-feira 30 de Abril de 2026 - RRMAIS</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -6814,19 +6814,19 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU2E5eUdWYzFxMHoxdzFrdktxNndmLXhpOC1mY0kwcUVPdWpoVnVkZVgxRXZQY1N2UFJNRmozQ0p5UVlWREZKaGFLMWR6WUU0UmxSTG5xaE1lSWJ1QjdaOWhMQVNUY29Lams4WnE3bS1Tb3JhaUR6MDJSbWtkUU9ZOGlvSS1IOHFWSGJjY01PYTBkN1d0UE5xWHZTTDFmUEpiUTEwN1BQWWNpZnRXRjBxLXR4MktvUWJOMzRfVVl5TWNwRENEUnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOUXhYaUtDQ3pyNUxlZFV3ZjlIYVFHOTNhV21VN3RPdFNGTUYtSWpURXVnZjlhWHl1cDdfN3phMmNDcmQxejFrVkdqdG96Ymc2YTFwLXlzaUFsZXFKaG5GZ2Z2c3pCMnBuZk14RjVXclZlRmhjbVdfMUFXUEFOVVBNVl81NzdCdlNJQXhPbE01eTJBX1hPRm12dC0ybURMV3YtbG1aUldwSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
+          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZXpsRmRrRjkycUpIaUJaY1V2cWxzelVBZnAtTm5ETEdJY1lQTUUtTHFVMkNBTkZyem9xVHUtS1cyaVpmSHdnc3doMTdFWkdGTThsbEJNU3dFSDVIRjZIaUlxODlHd2F1cUdJU3NuTGpQT01OMUN3MnhkR3o4S2gwd1dMMWR2QV81X2tOZ21PS2JIbU5STlAzT1hNV0wyczdVbHlLMGtFVFVpYXlHMnFyNk1UVmo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
+          <t>Petrobras inicia produção de ureia em usina desativada há 6 anos - Poder360</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -6858,19 +6858,19 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRGJmX0JoNWk0dFFBRGRrcXBleVZaUjVud1dPakQwcUt0X25QUTFEUVh4N0MzWDVTRUlJZ3NOaXF4cWNfZkktckFlRGRTRlRYRkNKOXJFSFI2VlRKUDRMOVpUWWM4b2NSa1NYM2VtX3FSdUVwZ1U1LVJDcVJTc0FoMjN3Ui1RWkg5MF92Q0FXLTRocDZMUWpfR1VIbVVmS01qWGYxblhFTm0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 - Valor Econômico</t>
+          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -6880,19 +6880,19 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZXpsRmRrRjkycUpIaUJaY1V2cWxzelVBZnAtTm5ETEdJY1lQTUUtTHFVMkNBTkZyem9xVHUtS1cyaVpmSHdnc3doMTdFWkdGTThsbEJNU3dFSDVIRjZIaUlxODlHd2F1cUdJU3NuTGpQT01OMUN3MnhkR3o4S2gwd1dMMWR2QV81X2tOZ21PS2JIbU5STlAzT1hNV0wyczdVbHlLMGtFVFVpYXlHMnFyNk1UVmo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Cotações Agrícolas para esta Quinta-feira 30 de Abril de 2026 - RRMAIS</t>
+          <t>Fafen PR volta a produzir ureia: fertilizante na fábrica é comida na mesa! - fup.org.br</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOUXhYaUtDQ3pyNUxlZFV3ZjlIYVFHOTNhV21VN3RPdFNGTUYtSWpURXVnZjlhWHl1cDdfN3phMmNDcmQxejFrVkdqdG96Ymc2YTFwLXlzaUFsZXFKaG5GZ2Z2c3pCMnBuZk14RjVXclZlRmhjbVdfMUFXUEFOVVBNVl81NzdCdlNJQXhPbE01eTJBX1hPRm12dC0ybURMV3YtbG1aUldwSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcmtibVp2QVZDY19yQXhVZC1ybWpjb0dqUXhGMlo5OFhodXpBczFOWThhLTc3RHBvdHNxVU9iSXZyQnVMdm8xUmtWbkNNcHRTWUYweXNpcTc3bUI5Ym56Z1pzckdTazllVFRzTzVrLUVJYm5ydDlkXy1mclNEdTlncWVFN0g5U1JfbnBoTmVzTTE1eHJCVDdF?oc=5</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Fafen PR volta a produzir ureia: fertilizante na fábrica é comida na mesa! - FUP - Federação Única dos Petroleiros</t>
+          <t>Em meio à crise dos fertilizantes, Petrobras volta a produzir ureia no Paraná após seis anos - VEJA</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcmtibVp2QVZDY19yQXhVZC1ybWpjb0dqUXhGMlo5OFhodXpBczFOWThhLTc3RHBvdHNxVU9iSXZyQnVMdm8xUmtWbkNNcHRTWUYweXNpcTc3bUI5Ym56Z1pzckdTazllVFRzTzVrLUVJYm5ydDlkXy1mclNEdTlncWVFN0g5U1JfbnBoTmVzTTE1eHJCVDdF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU2E5eUdWYzFxMHoxdzFrdktxNndmLXhpOC1mY0kwcUVPdWpoVnVkZVgxRXZQY1N2UFJNRmozQ0p5UVlWREZKaGFLMWR6WUU0UmxSTG5xaE1lSWJ1QjdaOWhMQVNUY29Lams4WnE3bS1Tb3JhaUR6MDJSbWtkUU9ZOGlvSS1IOHFWSGJjY01PYTBkN1d0UE5xWHZTTDFmUEpiUTEwN1BQWWNpZnRXRjBxLXR4MktvUWJOMzRfVVl5TWNwRENEUnc?oc=5</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
+          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 - Valor Econômico</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkOA?oc=5</t>
         </is>
       </c>
     </row>
@@ -6975,56 +6975,56 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Mosaic vê produtor mais cauteloso e reforça aposta em fertilizantes biológicos - Estadão</t>
+          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>29/04/2026 04:00</t>
+          <t>30/04/2026 04:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOaUtJV3gtWHNiUFBmZkJObWRoUWs2eUFKakh3dzhRRVhWcERRVDR5Mlc3Y3JCMUpsLWtWNW9KLXEzdkdiWEtQTUJxVTRrNXVqbzhCeGotdEM1cV9udEVwTGItQjRCZzV4Z242cFhULXVVV08wb1ZHcHhPLU01QWR4SVh4bTlqRUpsRWlrYjFWS3lVRTB3blNKeG14Q2VHU1FPTFRlcjRRZXdEUDDSAbABQVVfeXFMTTNmd01RNXBKS1ZYUllOYmYybzhnY1gyZFYwUnFVNlpyZFJNYlNwMWNOcG5Zd04zOHhnNlVZLUh6eUw5ekJ5XzZNbi12aGktMFFNY2ZEUVlBb01XY2VIMGhRTUQ1dU5sTzhfNURuOHhIclppUWdXOG8tV2UtT2w3ekZMUUlOMG1SVkpOS2VGS2plX2dMc09KNVdJZzBrdmNWcGREYU1LNldDYXl3WklhUTE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Unidade da CMOC assina acordo de US$ 1,7 bilhão para desenvolver mina de ouro e cobre no Equador - Valor Econômico</t>
+          <t>Mosaic vê produtor mais cauteloso e reforça aposta em fertilizantes biológicos - Estadão</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>28/04/2026 04:00</t>
+          <t>29/04/2026 04:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQWXI3c2c1Nkg5UTVTWkJ2QTVPNEd1Tmt0aUowbms1aFFrbEt3VTdtYTlQYWpNS0RiNVR1NU45ZWR6enpSdDhSbHZVNDNsSUdjSHJxbmxSUWt3U1NieGMtYTU0RDRtWXV2eUowSzdyem9UNUFfcHQwbXRqc2FldjZacDl0MVhFYmdJek9IWVZKWlRLbEoxUS1aTmVFdERsNHhhY180MzhhcERmWlhZZzc5VkhoSENab3JFUXM5V1pJUnZ6MVVWeVprbkpCUzQtTXIzRGtfd01rRWtQXzZFQUVKZXdSONIB8gFBVV95cUxOcEN2M0tCSFEtSVA4Y0ZtQV9EOWlFUERlR3JFb2RzZHFZVjVQWTZyUk9DZC1tTFpFcU8zeGNMR2pBRzl3ZDVKRElVa0RTTmxxZnNSWFJTNHVxX3c1b3FBX3JSLVhKcVdQY05BT1hRQ0ZibWJBWWttX2hDUjFFRk1TRTNBRV9DbGRSZHZkNlFIMkwtSlJNMkpoNTNGcVQ1ZVBSSDJpeW81eGRIT3B1aHM4alhLVkJPREk5cnFBdjdSSzZkMk9tVU1Oa3Fyd3ZrZWJKTXY5bDhFaWxfT3djU2FSdVpjclBXWHdLUml1MG5Ic2xHQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOaUtJV3gtWHNiUFBmZkJObWRoUWs2eUFKakh3dzhRRVhWcERRVDR5Mlc3Y3JCMUpsLWtWNW9KLXEzdkdiWEtQTUJxVTRrNXVqbzhCeGotdEM1cV9udEVwTGItQjRCZzV4Z242cFhULXVVV08wb1ZHcHhPLU01QWR4SVh4bTlqRUpsRWlrYjFWS3lVRTB3blNKeG14Q2VHU1FPTFRlcjRRZXdEUDDSAbABQVVfeXFMTTNmd01RNXBKS1ZYUllOYmYybzhnY1gyZFYwUnFVNlpyZFJNYlNwMWNOcG5Zd04zOHhnNlVZLUh6eUw5ekJ5XzZNbi12aGktMFFNY2ZEUVlBb01XY2VIMGhRTUQ1dU5sTzhfNURuOHhIclppUWdXOG8tV2UtT2w3ekZMUUlOMG1SVkpOS2VGS2plX2dMc09KNVdJZzBrdmNWcGREYU1LNldDYXl3WklhUTE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Mercado de enxofre corto de compressão varre através da cadeia de suprimentos - Sunsirs</t>
+          <t>Unidade da CMOC assina acordo de US$ 1,7 bilhão para desenvolver mina de ouro e cobre no Equador - Valor Econômico</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7034,19 +7034,19 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBQbnRCaEVzdkRzQ0tXZHFVZWd1cmFPVlJxcDc5VDY4bnRxaUx2YmRBdXdLOW9TaEhfWTk1Vmp2SldCZktYcmRfNzRaLVozOE9pZ3p4NEZEdTZXNmk1a2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQWXI3c2c1Nkg5UTVTWkJ2QTVPNEd1Tmt0aUowbms1aFFrbEt3VTdtYTlQYWpNS0RiNVR1NU45ZWR6enpSdDhSbHZVNDNsSUdjSHJxbmxSUWt3U1NieGMtYTU0RDRtWXV2eUowSzdyem9UNUFfcHQwbXRqc2FldjZacDl0MVhFYmdJek9IWVZKWlRLbEoxUS1aTmVFdERsNHhhY180MzhhcERmWlhZZzc5VkhoSENab3JFUXM5V1pJUnZ6MVVWeVprbkpCUzQtTXIzRGtfd01rRWtQXzZFQUVKZXdSONIB8gFBVV95cUxOcEN2M0tCSFEtSVA4Y0ZtQV9EOWlFUERlR3JFb2RzZHFZVjVQWTZyUk9DZC1tTFpFcU8zeGNMR2pBRzl3ZDVKRElVa0RTTmxxZnNSWFJTNHVxX3c1b3FBX3JSLVhKcVdQY05BT1hRQ0ZibWJBWWttX2hDUjFFRk1TRTNBRV9DbGRSZHZkNlFIMkwtSlJNMkpoNTNGcVQ1ZVBSSDJpeW81eGRIT3B1aHM4alhLVkJPREk5cnFBdjdSSzZkMk9tVU1Oa3Fyd3ZrZWJKTXY5bDhFaWxfT3djU2FSdVpjclBXWHdLUml1MG5Ic2xHQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>CMOC assegura projeto Cangrejos por US$1,7bi no Equador - bnamericas.com</t>
+          <t>Mercado de enxofre corto de compressão varre através da cadeia de suprimentos - Sunsirs</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -7056,41 +7056,41 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPUDFMYWdTWDQ3ZGljdUF2VDY3UkRwLS1xNXBxLWZQVEpEMG5nU1dvTjdqZ0lyZ2JFRC0xelhXR2FINldleXlJWUJDOTBwU0NEQm14LWlqNVFOcWVPc1Q4a0tXWTNQYTFkZThzUkE4MElVeXBXOVdqaXZUNTJyQlpIMFhzX0xXclg4QWtqR1kxOVZES1NyVWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBQbnRCaEVzdkRzQ0tXZHFVZWd1cmFPVlJxcDc5VDY4bnRxaUx2YmRBdXdLOW9TaEhfWTk1Vmp2SldCZktYcmRfNzRaLVozOE9pZ3p4NEZEdTZXNmk1a2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Uma nova Mosaic, com menos ativos, mais bioinsumos e “sem plano de deixar o Brasil” - AgFeed</t>
+          <t>CMOC assegura projeto Cangrejos por US$1,7bi no Equador - BNamericas</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>27/04/2026 04:00</t>
+          <t>28/04/2026 04:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQOGk5c2lwZUhVRXBjb2VSNW5xU283VzdIRl9JTDU0RFk5bEZGM0ZxVEJaaWJERkp3TUtNY0FxX1NpTUlGSWxYTzl5RVRxcEdid0NNaEhDS3RXTjQzQkp0ZjFlNGhsUHd4V1ZjaVBXZWFTMS1qMjctLXZGcU9xeVdMTGJMMzZDQkVOUlA3TU0yNl9hSDFyejloZHRXT0lfRUtlN0g2S1JGQjdSRlFaOXkycA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPUDFMYWdTWDQ3ZGljdUF2VDY3UkRwLS1xNXBxLWZQVEpEMG5nU1dvTjdqZ0lyZ2JFRC0xelhXR2FINldleXlJWUJDOTBwU0NEQm14LWlqNVFOcWVPc1Q4a0tXWTNQYTFkZThzUkE4MElVeXBXOVdqaXZUNTJyQlpIMFhzX0xXclg4QWtqR1kxOVZES1NyVWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Ureia acumula alta de 63% com Guerra no Oriente Médio - Canal Rural</t>
+          <t>Uma nova Mosaic, com menos ativos, mais bioinsumos e “sem plano de deixar o Brasil” - AgFeed</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeXdPY2EtX2lWTng0WWcycU1zNjlEeEYtd1RiVmFpd3Y4ZzJOeGhpOUdZRnBSREVDVFBVM3g0QkNNRFBfRDl5V3pmRG1DTzFESWgwQzI2amx6NGpCR0FVM3JTMC05cDhtNUtEdXotU3JLMzNiQkJpN0dQVmRkQWZHSTR3OVdMNUVFQllvdm16b3E2MUctQjN1MTRFQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQOGk5c2lwZUhVRXBjb2VSNW5xU283VzdIRl9JTDU0RFk5bEZGM0ZxVEJaaWJERkp3TUtNY0FxX1NpTUlGSWxYTzl5RVRxcEdid0NNaEhDS3RXTjQzQkp0ZjFlNGhsUHd4V1ZjaVBXZWFTMS1qMjctLXZGcU9xeVdMTGJMMzZDQkVOUlA3TU0yNl9hSDFyejloZHRXT0lfRUtlN0g2S1JGQjdSRlFaOXkycA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Copa do Calcário: Macuco lidera e disputa segue acirrada após nova rodada - Serra News</t>
+          <t>Macuco vence novamente e segue na liderança da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -7122,19 +7122,19 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVzdyNUh6M1JxbnZwVjlaS0Z0Ui05cjJWMkg0bDlOWmNSeUFJYlNMMDFJT1VXSDMxbVlfWk1UYWJqSGNpOXVXQkRfMnBXN2FycUxjbF9HbGczY0x3MmdQekEyWEZNV3RkWFFkTlMxb3h4TmRvb2VDQU1STVd3aEtxbE9uZ0ZNT25lNzVVa1FDSWdWQXpGZjA3aTNaS2YyTjBI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPeVpoTFlKbDN4ZXlpQk9ETTNhUmROaVJFWEJqcklXb2ZyWUZhSzFRTENuZjg1aUxkaEgxSVNTNTc3a0ZtbUFkUUdCM1VCaTM3a0hmbTZLemZfN0hFT2t4TmM0SWVlQkk2S1BJWnVmdjlYUTFXWnFzU2hXS3FHZVNMMGxoUzdMWG1OMkY1UDRzYlBpVXJDM1IxT0RVUTBnQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Mosaic participará de audiência pública para apresentação de Estudos e Relatórios de Impacto de Vizinhança em Paranaguá - folhadolitoral.com.br</t>
+          <t>Copa do Calcário: Macuco lidera e disputa segue acirrada após nova rodada - Serra News</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -7144,19 +7144,19 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQaWZoSTZ5YmdmWE41TjhTVkdiVXpuX2J1aElCUkZhWlA2Z0xRbEtMSVl3N1NOYk9xYjlBUGhtRFdocldac0QzaFdEejdNR1FqRlZuUnc3STJWWlcxQVJrVTctZUFMTGVIeUY2MGh1SHA4NllFMDF5VVdzU0phTHNPaDRLVHRjRVBvMEJPRzk5a2hiV3ZKWmhKSlhSWW52QWpJdjY0THBKb01maGc0bTNMN0ppUFZXSzFoWXZHTy1GUGswZFhfVU5wNHBrOWhkUTdkZlBReWxMRHdyRE9RMzZwenhqakhXSVhIaVBKekhRT2pIcG9XQXhHQXJiMFo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVzdyNUh6M1JxbnZwVjlaS0Z0Ui05cjJWMkg0bDlOWmNSeUFJYlNMMDFJT1VXSDMxbVlfWk1UYWJqSGNpOXVXQkRfMnBXN2FycUxjbF9HbGczY0x3MmdQekEyWEZNV3RkWFFkTlMxb3h4TmRvb2VDQU1STVd3aEtxbE9uZ0ZNT25lNzVVa1FDSWdWQXpGZjA3aTNaS2YyTjBI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Macuco vence novamente e segue na liderança da Copa do Calcário - FERJ</t>
+          <t>Mosaic participará de audiência pública para apresentação de Estudos e Relatórios de Impacto de Vizinhança em Paranaguá - Folha do Litoral News</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -7166,51 +7166,51 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPeVpoTFlKbDN4ZXlpQk9ETTNhUmROaVJFWEJqcklXb2ZyWUZhSzFRTENuZjg1aUxkaEgxSVNTNTc3a0ZtbUFkUUdCM1VCaTM3a0hmbTZLemZfN0hFT2t4TmM0SWVlQkk2S1BJWnVmdjlYUTFXWnFzU2hXS3FHZVNMMGxoUzdMWG1OMkY1UDRzYlBpVXJDM1IxT0RVUTBnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQaWZoSTZ5YmdmWE41TjhTVkdiVXpuX2J1aElCUkZhWlA2Z0xRbEtMSVl3N1NOYk9xYjlBUGhtRFdocldac0QzaFdEejdNR1FqRlZuUnc3STJWWlcxQVJrVTctZUFMTGVIeUY2MGh1SHA4NllFMDF5VVdzU0phTHNPaDRLVHRjRVBvMEJPRzk5a2hiV3ZKWmhKSlhSWW52QWpJdjY0THBKb01maGc0bTNMN0ppUFZXSzFoWXZHTy1GUGswZFhfVU5wNHBrOWhkUTdkZlBReWxMRHdyRE9RMzZwenhqakhXSVhIaVBKekhRT2pIcG9XQXhHQXJiMFo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Margem do córrego do Enxofre, no Jardim Conceição, começa a receber muro de gabião para conter erosão - Portal do Município de Piracicaba</t>
+          <t>Ureia acumula alta de 63% com Guerra no Oriente Médio - canalrural.com.br</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>24/04/2026 04:00</t>
+          <t>27/04/2026 04:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRVJObFdmcnE3SmlfbERhbXhJa2hkd2taSzQxcGVjSFp1bGpSWjh2a25nanBtNGRsT0JYS0xvQkZlZ0JxSF85UktCU3hyN3RBbVpPZ0V2dGd4Q0RUMEp4LTVqT0pkcTNUZHlHTnFVeFZiWmozYUtqNnhkY0VWTjZxRmh4RzhYTkd6SS1pYUxoVzJZLURDOEZwbG9EeXdwWXpCNHpkYTFCQUVYRlNYV3RscldENEI5QzhqQ1BFLXZoazZSU09TUEtvbzkwdmhsbElJUnkwRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeXdPY2EtX2lWTng0WWcycU1zNjlEeEYtd1RiVmFpd3Y4ZzJOeGhpOUdZRnBSREVDVFBVM3g0QkNNRFBfRDl5V3pmRG1DTzFESWgwQzI2amx6NGpCR0FVM3JTMC05cDhtNUtEdXotU3JLMzNiQkJpN0dQVmRkQWZHSTR3OVdMNUVFQllvdm16b3E2MUctQjN1MTRFQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Justiça anula licença para extração de calcário em área quilombola no MA e determina indenização de R$ 100 mil - G1</t>
+          <t>Margem do córrego do Enxofre, no Jardim Conceição, começa a receber muro de gabião para conter erosão - Portal do Município de Piracicaba</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>22/04/2026 04:00</t>
+          <t>24/04/2026 04:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQSi1hWVV3Y3VUZmNsUEFqcTVlc0lpUzZEMnBYWkdGNnJRVXU0WFF6LXkwRlVHMEFCMnRPbTVzbHJSS3BXTGI3WnpMOUVKSlJ5ZjBHSGZ1WXF0NkptY05fb0VvVzdDa3BlLXFYamQ3YTBFWWpGUi03cXZzbWJkZlFjQVRGS0lEUl9haDF1U0lfbDEyQ0ZkZ19EcGhCMzZ5d2ItYURqX1NMMUduZ2RzeGt2UUwzZ0NteVdPaUwzM0ZadnV0TnhJS2lrbk1JMnVaRkkzQlBUR2FjNWFpRnJwX3JpVWhrSUk2bjF2d3NBcVVSdVJzWGtpZ19OSW5jUTZ1Z9IBjAJBVV95cUxQdU9IMnNVTTlweXVDZ1lrR2VZeVlNdC1vQk00YVBGV1U1ajdjM0lDZDdTcmVxNF9SX2N5dWdfSVZwVFktSVVrTnZUNE9pWFQyNkxGM1VPMHg3d1l6R0Q4alZwMENMUkdTcUlydjRjYzFSZHJqTDJnSll0MHZlUVhxbnY3YmJjcXVmc1VYaE95TFRmZlBVMl9ZaTZ6YzN6UnRvUVdLekZNNC10QjV1Skwxd0tKaWxfeUphVE1QOHBMZUVzMk5MWjhfVGJLNG43TzZobmtRUFhERlpXVjlsZzZiY1l6dWU1ZGhhQjJhZVhta1FkTndJMkpwYUpVb21OVEN1S0RlLURxWUVjd0ps?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRVJObFdmcnE3SmlfbERhbXhJa2hkd2taSzQxcGVjSFp1bGpSWjh2a25nanBtNGRsT0JYS0xvQkZlZ0JxSF85UktCU3hyN3RBbVpPZ0V2dGd4Q0RUMEp4LTVqT0pkcTNUZHlHTnFVeFZiWmozYUtqNnhkY0VWTjZxRmh4RzhYTkd6SS1pYUxoVzJZLURDOEZwbG9EeXdwWXpCNHpkYTFCQUVYRlNYV3RscldENEI5QzhqQ1BFLXZoazZSU09TUEtvbzkwdmhsbElJUnkwRg?oc=5</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Guerra no Oriente Médio faz ureia disparar e segue pressionando preços dos fertilizantes - Canal Rural</t>
+          <t>Guerra no Oriente Médio faz ureia disparar e segue pressionando preços dos fertilizantes - canalrural.com.br</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7283,78 +7283,78 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Melhor potencial para produtos químicos aplicados no solo - Tessenderlo Kerley</t>
+          <t>Justiça anula licença para extração de calcário em área quilombola no MA e determina indenização de R$ 100 mil - G1</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>21/04/2026 19:19</t>
+          <t>22/04/2026 04:00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOZXh4a3hTUHJ5SUp3aGU5YlVLQTE1RzdWT2htc0lWWjgxVUNVQnVZVXc2eVFPbGo1OW1saXJyZmluSWRqQjhHUUY0czBVZUdvLVdiMnlRWE54RWh5QmJfTlVoWTg0aUVKdlJrS0lLbUM3THBFNDRVTjc1UFRUZEdGSms4SDJKODZkcXBwbnFaRkNvSU5BbG13di0zZ3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQSi1hWVV3Y3VUZmNsUEFqcTVlc0lpUzZEMnBYWkdGNnJRVXU0WFF6LXkwRlVHMEFCMnRPbTVzbHJSS3BXTGI3WnpMOUVKSlJ5ZjBHSGZ1WXF0NkptY05fb0VvVzdDa3BlLXFYamQ3YTBFWWpGUi03cXZzbWJkZlFjQVRGS0lEUl9haDF1U0lfbDEyQ0ZkZ19EcGhCMzZ5d2ItYURqX1NMMUduZ2RzeGt2UUwzZ0NteVdPaUwzM0ZadnV0TnhJS2lrbk1JMnVaRkkzQlBUR2FjNWFpRnJwX3JpVWhrSUk2bjF2d3NBcVVSdVJzWGtpZ19OSW5jUTZ1Z9IBjAJBVV95cUxQdU9IMnNVTTlweXVDZ1lrR2VZeVlNdC1vQk00YVBGV1U1ajdjM0lDZDdTcmVxNF9SX2N5dWdfSVZwVFktSVVrTnZUNE9pWFQyNkxGM1VPMHg3d1l6R0Q4alZwMENMUkdTcUlydjRjYzFSZHJqTDJnSll0MHZlUVhxbnY3YmJjcXVmc1VYaE95TFRmZlBVMl9ZaTZ6YzN6UnRvUVdLekZNNC10QjV1Skwxd0tKaWxfeUphVE1QOHBMZUVzMk5MWjhfVGJLNG43TzZobmtRUFhERlpXVjlsZzZiY1l6dWU1ZGhhQjJhZVhta1FkTndJMkpwYUpVb21OVEN1S0RlLURxWUVjd0ps?oc=5</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Potássio e enxofre: os pilares da alfafa de alto rendimento e alta qualidade - Tessenderlo Kerley</t>
+          <t>Melhor potencial para produtos químicos aplicados no solo - Tessenderlo Kerley</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>21/04/2026 18:42</t>
+          <t>21/04/2026 19:19</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdWRPaG5oTlo5V0E4aG5RRG1CeTY0YVNrbWVFZndXMURZNTU3N1IxLVYzWEZMaEEzYmk4TXk0d3lYcVQtcExUYzZORlZRaENDNkZuVExMOEhnQ0MtRXozQ1d1U21NbUlWczV3dG53VlZhRU1WUmh2d3J5am9Fd1JoMGRJYjhRcVJjVWpUUU05QkJjQ2ZNYnRBS3FvMVVXMUQ3ZGEtOHVPOGVFcU1jRThuZVFaQTY5a3prQURWendYNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOZXh4a3hTUHJ5SUp3aGU5YlVLQTE1RzdWT2htc0lWWjgxVUNVQnVZVXc2eVFPbGo1OW1saXJyZmluSWRqQjhHUUY0czBVZUdvLVdiMnlRWE54RWh5QmJfTlVoWTg0aUVKdlJrS0lLbUM3THBFNDRVTjc1UFRUZEdGSms4SDJKODZkcXBwbnFaRkNvSU5BbG13di0zZ3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Macuco vence novamente e lidera a Copa do Calcário - FERJ</t>
+          <t>Potássio e enxofre: os pilares da alfafa de alto rendimento e alta qualidade - Tessenderlo Kerley</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>20/04/2026 04:00</t>
+          <t>21/04/2026 18:42</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPQnFTQVFGck1DaWNqWmRkcW1KY3dLTDJRNFRtNlRtREVUdHoyLXZyNWlHS2k1bDlBMzdyQnVOZVhfd2FqUXppTk9BU0Q2azBNcWxGYzlweG5NWVdGR1NpenFnMGdZSDk1QWVtMVdXNllwZElMQWFfZ1Y3R01RWkxSeWJPelZGSkg3dTlNUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdWRPaG5oTlo5V0E4aG5RRG1CeTY0YVNrbWVFZndXMURZNTU3N1IxLVYzWEZMaEEzYmk4TXk0d3lYcVQtcExUYzZORlZRaENDNkZuVExMOEhnQ0MtRXozQ1d1U21NbUlWczV3dG53VlZhRU1WUmh2d3J5am9Fd1JoMGRJYjhRcVJjVWpUUU05QkJjQ2ZNYnRBS3FvMVVXMUQ3ZGEtOHVPOGVFcU1jRThuZVFaQTY5a3prQURWendYNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Mosaic reestrutura ativos no País para manter eficiência - Estadão</t>
+          <t>Macuco vence novamente e lidera a Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQYmstUHhzM3FUS2ZwQk5iRHEtWmpqYnBMVW1RZ1dpaVhQZVltbUZtU2V0eURVTGpLaGhYQXBLTTNacUprNDU2UGZkS1VQU09mN1RoZWpBMm9Da2dyOFZhU2hhUXdvTGJab2RJZDV1akZnN3pvajZhMng4NjBIZktUaVFhTmNNSlNucUhZMTdIb2YtdmY1X1VqaUNoaGFIaEtwOXFyWGxyLTBpT0w1dmtqeDdXTVAxX3dIZGfSAb8BQVVfeXFMT3lPSFRFUERhUmtkSHU4NV92MkVEY3RwcXlOY09mWkZnVG9RQmN6eU51Q2FyRkJXV0JGbGxxV3MxcWE4U3otX0pkUEhZWWp5TDBfZnhITmM1OUowVk1JeDdfbFd5cGQ4dW5PSWFfcGlQS1E0Y1hZRmpnUlNKY2RSU1d6RV9ZTElRendwTGluT0tFQ243b1NoZkFSSFo2RS1SM3FzekZvbDhsRGkwTGttR1dRUGNKRlBJM3I4TGxhOTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPQnFTQVFGck1DaWNqWmRkcW1KY3dLTDJRNFRtNlRtREVUdHoyLXZyNWlHS2k1bDlBMzdyQnVOZVhfd2FqUXppTk9BU0Q2azBNcWxGYzlweG5NWVdGR1NpenFnMGdZSDk1QWVtMVdXNllwZElMQWFfZ1Y3R01RWkxSeWJPelZGSkg3dTlNUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7376,105 +7376,105 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Prefeitura de Araxá e CBMM firmam parceria para aproveitamento de mão de obra da Mosaic - Prefeitura de Araxá</t>
+          <t>Mosaic reestrutura ativos no País para manter eficiência - Estadão</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>17/04/2026 04:00</t>
+          <t>20/04/2026 04:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOcW9Ja2xnSUxXTmNMNnhTTjBsS1dHSFZwa0FFbFI5TEQ2UlBaTkYzQ0ZyMjNHQXh6NVBFLUpweHAyc205TDV6M2tHZjgwS1E0LUFiZ1c0bVlMUm5VRG9QeTJHUmFHLU9JVFFvdTM5RFhuOE1SNTVIUjhwb1lFWUNLTnVPWmViRFgtVlFoWlFmTkN6UVNPakNmUGN0RXNYSzE3RTlCdnNjbFhvbUMtcXhwV0ZUa0E5QTdUZFNieXZTbHI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQYmstUHhzM3FUS2ZwQk5iRHEtWmpqYnBMVW1RZ1dpaVhQZVltbUZtU2V0eURVTGpLaGhYQXBLTTNacUprNDU2UGZkS1VQU09mN1RoZWpBMm9Da2dyOFZhU2hhUXdvTGJab2RJZDV1akZnN3pvajZhMng4NjBIZktUaVFhTmNNSlNucUhZMTdIb2YtdmY1X1VqaUNoaGFIaEtwOXFyWGxyLTBpT0w1dmtqeDdXTVAxX3dIZGfSAb8BQVVfeXFMT3lPSFRFUERhUmtkSHU4NV92MkVEY3RwcXlOY09mWkZnVG9RQmN6eU51Q2FyRkJXV0JGbGxxV3MxcWE4U3otX0pkUEhZWWp5TDBfZnhITmM1OUowVk1JeDdfbFd5cGQ4dW5PSWFfcGlQS1E0Y1hZRmpnUlNKY2RSU1d6RV9ZTElRendwTGluT0tFQ243b1NoZkFSSFo2RS1SM3FzekZvbDhsRGkwTGttR1dRUGNKRlBJM3I4TGxhOTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Santo Antônio do Caiuá distribui mais de 300 toneladas de calcário a produtores rurais - Diário do Noroeste</t>
+          <t>Prefeitura de Araxá e CBMM firmam parceria para aproveitamento de mão de obra da Mosaic - Prefeitura de Araxá</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>16/04/2026 04:00</t>
+          <t>17/04/2026 04:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPZzk0S1M0WnlzVGd1MGpETEIwX05pUEphT0Z4MVpaU2p1cnB5NE41R1ZqRmx6cWxVc3M2T1RYTVBOTzhHaTlkMlU4QWdUTktNc0ZhOUdVcUNXWmVueTI1UGxVWm1GcWtSRmVOTDMtN3BHM2wxNjZ0SUZseWh5Yml1MUVhdlFpN0lnejJhbF9DMnlRaUdlUEwtdTNLdjlneURmWE9pMDRnaGZQUkZyZ2lJVmZWU0ZBaTVUa044?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOcW9Ja2xnSUxXTmNMNnhTTjBsS1dHSFZwa0FFbFI5TEQ2UlBaTkYzQ0ZyMjNHQXh6NVBFLUpweHAyc205TDV6M2tHZjgwS1E0LUFiZ1c0bVlMUm5VRG9QeTJHUmFHLU9JVFFvdTM5RFhuOE1SNTVIUjhwb1lFWUNLTnVPWmViRFgtVlFoWlFmTkN6UVNPakNmUGN0RXNYSzE3RTlCdnNjbFhvbUMtcXhwV0ZUa0E5QTdUZFNieXZTbHI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Importância do enxofre na agricultura - Tessenderlo Kerley</t>
+          <t>Santo Antônio do Caiuá distribui mais de 300 toneladas de calcário a produtores rurais - Diário do Noroeste</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>15/04/2026 19:32</t>
+          <t>16/04/2026 04:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNbVFvNXFNcE9MU25FN1hKS25KaUs0TWdEMnZJZHhsMVZicEUxU3FhR2RlN0UwQjV0T00tX05kSjZuWEdxVWd4NDNkTWR3VF9HLU14M2xEUC0ybEVpekEtbWthUDN5ZFZiN3ZxeUlNT2Q5TFJwaGxMYTlOMjhWUWEteXpIQU1DeXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPZzk0S1M0WnlzVGd1MGpETEIwX05pUEphT0Z4MVpaU2p1cnB5NE41R1ZqRmx6cWxVc3M2T1RYTVBOTzhHaTlkMlU4QWdUTktNc0ZhOUdVcUNXWmVueTI1UGxVWm1GcWtSRmVOTDMtN3BHM2wxNjZ0SUZseWh5Yml1MUVhdlFpN0lnejJhbF9DMnlRaUdlUEwtdTNLdjlneURmWE9pMDRnaGZQUkZyZ2lJVmZWU0ZBaTVUa044?oc=5</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil volta a subir em março de 2026. Preço dispara! - Farmnews</t>
+          <t>Importância do enxofre na agricultura - Tessenderlo Kerley</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>14/04/2026 04:00</t>
+          <t>15/04/2026 19:32</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPczdiWDNkX2ppUzNiRklsRHVVemRScDFoWDRoNXcySHFwdnlPenhmN1JKOEdtUnJhNnozLV95bmtFaE9sZkg3WVlUcWRodjdVT0NYelBZbC1YMl9obV93ZmdLSmh3Y2lMN3Fzd3AtTjI4bmFWZVhZNVdDNGpjazI2d2tnYUpBZFhRMW9uX3R0TUdZME05UXJWc29JcjAyYWJ3c0pBUUlXc3BNZ0U2aVc5Y09SQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNbVFvNXFNcE9MU25FN1hKS25KaUs0TWdEMnZJZHhsMVZicEUxU3FhR2RlN0UwQjV0T00tX05kSjZuWEdxVWd4NDNkTWR3VF9HLU14M2xEUC0ybEVpekEtbWthUDN5ZFZiN3ZxeUlNT2Q5TFJwaGxMYTlOMjhWUWEteXpIQU1DeXM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
+          <t>Importação de ureia pelo Brasil volta a subir em março de 2026. Preço dispara! - Farmnews</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>13/04/2026 04:00</t>
+          <t>14/04/2026 04:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPczdiWDNkX2ppUzNiRklsRHVVemRScDFoWDRoNXcySHFwdnlPenhmN1JKOEdtUnJhNnozLV95bmtFaE9sZkg3WVlUcWRodjdVT0NYelBZbC1YMl9obV93ZmdLSmh3Y2lMN3Fzd3AtTjI4bmFWZVhZNVdDNGpjazI2d2tnYUpBZFhRMW9uX3R0TUdZME05UXJWc29JcjAyYWJ3c0pBUUlXc3BNZ0U2aVc5Y09SQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7508,29 +7508,29 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Disparada histórica do enxofre pressiona toda a cadeia - agrolink.com.br</t>
+          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>10/04/2026 04:00</t>
+          <t>13/04/2026 04:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPVHdRX1FTQlk4azZQcGd3bERfUThfTENPWmZ4bnNuVkFCaEZDUlk0MmphdFBsdnZvam5jWGdZTDItbllDZzBNRHNGRmdTcGRxa0loRTVEYWhFR2RKc1FiUzktM3NXN1VJQUdDWFVPY0hPTzJDY0M3MzVYX05TLXhrUGJqMXNWaWYyZjZneFBpSk1UODRWbUJDaVZURFJkT09TNENHUmZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>St George tem interesse em comprar ativos da Mosaic em Araxá, dizem fontes - CNN Brasil</t>
+          <t>Queda da ureia acompanha alívio geopolítico - Agrolink</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -7540,19 +7540,19 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxONlhxcHQzelN2ZlNmOEhFbzI1SFN0TXdwbFNLbHk3Zl9WSEg3c3RTZFhvVWpBUWt1TnBoYjR5TG1SUDlRakNZRy1CcktIaFpyTWJicEdpdlN1dDVCUHJrR2JpLTJhbjFzTWE1RzYzUDc1VGo2ZDI0MHMtMDlaUXhVNUdLZmZxTWFsYW1ERm94bEVkNlZiRm15UjhLZUJlcjFaV1lqcW1JeGRmZmVjelE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQNEppb0R2TFlCUmIzRW0xckJYSWVvQUJ5cTc3MldveFBqTVZtbU95MFVfNVJLYVR1SUhVM1BFTXd1OHZhVzVoVkQtczA4NXVwLTc0VUdpY0RjN002TXk1aDlnM0w5U1ZvWUUySHREcG9LZUZfdFl2QmxubUpnbEJWdUE3UGZZNXRrNmFOWUFwVDUtRkJsVTBn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Queda da ureia acompanha alívio geopolítico - agrolink.com.br</t>
+          <t>St George tem interesse em comprar ativos da Mosaic em Araxá, dizem fontes - CNN Brasil</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -7562,29 +7562,29 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQNEppb0R2TFlCUmIzRW0xckJYSWVvQUJ5cTc3MldveFBqTVZtbU95MFVfNVJLYVR1SUhVM1BFTXd1OHZhVzVoVkQtczA4NXVwLTc0VUdpY0RjN002TXk1aDlnM0w5U1ZvWUUySHREcG9LZUZfdFl2QmxubUpnbEJWdUE3UGZZNXRrNmFOWUFwVDUtRkJsVTBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxONlhxcHQzelN2ZlNmOEhFbzI1SFN0TXdwbFNLbHk3Zl9WSEg3c3RTZFhvVWpBUWt1TnBoYjR5TG1SUDlRakNZRy1CcktIaFpyTWJicEdpdlN1dDVCUHJrR2JpLTJhbjFzTWE1RzYzUDc1VGo2ZDI0MHMtMDlaUXhVNUdLZmZxTWFsYW1ERm94bEVkNlZiRm15UjhLZUJlcjFaV1lqcW1JeGRmZmVjelE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>INSCRIÇÃO NO PROGRAMA DE CALCÁRIO ATÉ O FINAL DO MÊS - Prefeitura de Mato Leitão</t>
+          <t>Disparada histórica do enxofre pressiona toda a cadeia - Agrolink</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>09/04/2026 04:00</t>
+          <t>10/04/2026 04:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPQ2xHNUVCT202aDlGai1PVTBaS0tmbFAyaDVCYThDdVpQdTFhcWlzTGtDWThuWkhVRU5zTDdwOF9ENUlSd2k2TUNuUktNU3Y1WXpMck1qMkVCeHprRVpUZE9KSUNMQ3lfaWRSMkVwS2hEbXVFTDNmZndjZkh1ek9VQU43VV9SR09aUHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPVHdRX1FTQlk4azZQcGd3bERfUThfTENPWmZ4bnNuVkFCaEZDUlk0MmphdFBsdnZvam5jWGdZTDItbllDZzBNRHNGRmdTcGRxa0loRTVEYWhFR2RKc1FiUzktM3NXN1VJQUdDWFVPY0hPTzJDY0M3MzVYX05TLXhrUGJqMXNWaWYyZjZneFBpSk1UODRWbUJDaVZURFJkT09TNENHUmZn?oc=5</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Mosaic coloca ativos de fertilizantes à venda no Brasil - bnamericas.com</t>
+          <t>Mosaic paralisa operações em Minas Gerais e reduz produção de fertilizantes - canalrural.com.br</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -7606,19 +7606,19 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNNkRQQ0V3N0JuU05aaVV3LU1zcGlRLTA3dFRCZndyZnEwUjhvcDFVa1k5eVdsa3ZMbWxFRWtHSGFvSlQyUXpaR2l2Y1NKNmczUlBUN25TWkpHOXlOTWpWanlobVBSY0dZbXV1MUJsNGhvZ1BLRzMwTmZtWkJ0bU5pUFg2MjZLODFVeWdhRkdUZF8zSkVlUDUyZGZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNnVZeUNJdHBJOThrQTk2UW9EeXBQcFowX2p1TnlzS0I1Zmc4RGhkMkZIVXJTbUdsYUJKUGx0Y0ctTlAxUU1zcGNGU2ZxNWppSFRsaHU3aU9nNS0xZ093bkV3UlB3NzlVaXVDYTBCeXRJSmVoNUlSaktHRHhDbWF3dFdqSlpKOW9BU1pncGVBM3htRUVDbTZJVWo2S2VuQW1jWk1RZGlOdlpZM0RKZVFFMGVrSnBzQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Mosaic paralisa operações em Minas Gerais e reduz produção de fertilizantes - Canal Rural</t>
+          <t>INSCRIÇÃO NO PROGRAMA DE CALCÁRIO ATÉ O FINAL DO MÊS - Prefeitura de Mato Leitão</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNnVZeUNJdHBJOThrQTk2UW9EeXBQcFowX2p1TnlzS0I1Zmc4RGhkMkZIVXJTbUdsYUJKUGx0Y0ctTlAxUU1zcGNGU2ZxNWppSFRsaHU3aU9nNS0xZ093bkV3UlB3NzlVaXVDYTBCeXRJSmVoNUlSaktHRHhDbWF3dFdqSlpKOW9BU1pncGVBM3htRUVDbTZJVWo2S2VuQW1jWk1RZGlOdlpZM0RKZVFFMGVrSnBzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPQ2xHNUVCT202aDlGai1PVTBaS0tmbFAyaDVCYThDdVpQdTFhcWlzTGtDWThuWkhVRU5zTDdwOF9ENUlSd2k2TUNuUktNU3Y1WXpMck1qMkVCeHprRVpUZE9KSUNMQ3lfaWRSMkVwS2hEbXVFTDNmZndjZkh1ek9VQU43VV9SR09aUHc?oc=5</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Mosaic anuncia paralisação em Araxá e Patrocínio com corte de funcionários e queda de 1 milhão de toneladas na produção de fosfato - G1</t>
+          <t>Mosaic coloca ativos de fertilizantes à venda no Brasil - BNamericas</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPYVNQbkdxNThhSW1ydHJLMUlzcjQ1eE1vbFMyZVZiSVkzVE1KbC1lcEVYZnZnV3lLNW1wWG03VzJ4OWdQTTBBRDlDUzI4NXlmYlhmM0l6MjhJY2Z6Z2tLbjFHVHc1dW9aTlA5OEd3aEFaN2Y0MXlIdDNEM1BCQ3NqS1ZidzMtc2VSUWhBWVk0cUJIY2V4VWRsQnQyM1lPTmMyTEhFZmZ6ekNpQnFhM3FMRi1adFJpMmhjQWNVVWNZUFMyNnplbEgwOTZUZXg4d2hFYW9TUUJacldTbzR3QlVjRHpIYkFZZmJJRUJVdmRzdmtwbjE1VXdtRVd5OWlCOTZVZ1JidjgtQmdoOVYzdlZ0QWZqUVVYZDU5dU1rU3FaSjNvcWPSAbICQVVfeXFMT0NZVFdGbHgwUkYwU2xxM3RTWVd1YS1UdkVlc1VfS3pURUU5OTQ0NzVmekVFb01UUjVkbkVrVWJXaWZ5SUtNQTlfQWx2NWJ3emd3bXR4WkFEUmg0Z3hqa0RnLWk1YUVmZmNTLWpyQmhKSXVGM2pEbURiaDNHa1BDa3RvNGtoX3ItM2p3UEVoVXdHSjg2T0MxZExiVTk1RFlJaENuQU5hMnpabFZ3YTZ1SHZ2OVRjV2h4amRpVVBhYXBPZWVld1BkWVVLVThVVDBRSy11YWNWT01RV01MSXJYNS1aV29YUHZVZl9oazhEajBad1FkSmdKS01FcVlvYmxRcUtSVVR6am1qYU9UZHl4Y3o5ZlE3THNDb0lOMFIxVXJBOUF2TGVrSUJzeUlyMUFpczR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNNkRQQ0V3N0JuU05aaVV3LU1zcGlRLTA3dFRCZndyZnEwUjhvcDFVa1k5eVdsa3ZMbWxFRWtHSGFvSlQyUXpaR2l2Y1NKNmczUlBUN25TWkpHOXlOTWpWanlobVBSY0dZbXV1MUJsNGhvZ1BLRzMwTmZtWkJ0bU5pUFg2MjZLODFVeWdhRkdUZF8zSkVlUDUyZGZn?oc=5</t>
         </is>
       </c>
     </row>
@@ -7662,17 +7662,17 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
+          <t>Mosaic anuncia paralisação em Araxá e Patrocínio com corte de funcionários e queda de 1 milhão de toneladas na produção de fosfato - G1</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>08/04/2026 09:32</t>
+          <t>09/04/2026 04:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPYVNQbkdxNThhSW1ydHJLMUlzcjQ1eE1vbFMyZVZiSVkzVE1KbC1lcEVYZnZnV3lLNW1wWG03VzJ4OWdQTTBBRDlDUzI4NXlmYlhmM0l6MjhJY2Z6Z2tLbjFHVHc1dW9aTlA5OEd3aEFaN2Y0MXlIdDNEM1BCQ3NqS1ZidzMtc2VSUWhBWVk0cUJIY2V4VWRsQnQyM1lPTmMyTEhFZmZ6ekNpQnFhM3FMRi1adFJpMmhjQWNVVWNZUFMyNnplbEgwOTZUZXg4d2hFYW9TUUJacldTbzR3QlVjRHpIYkFZZmJJRUJVdmRzdmtwbjE1VXdtRVd5OWlCOTZVZ1JidjgtQmdoOVYzdlZ0QWZqUVVYZDU5dU1rU3FaSjNvcWPSAbICQVVfeXFMT0NZVFdGbHgwUkYwU2xxM3RTWVd1YS1UdkVlc1VfS3pURUU5OTQ0NzVmekVFb01UUjVkbkVrVWJXaWZ5SUtNQTlfQWx2NWJ3emd3bXR4WkFEUmg0Z3hqa0RnLWk1YUVmZmNTLWpyQmhKSXVGM2pEbURiaDNHa1BDa3RvNGtoX3ItM2p3UEVoVXdHSjg2T0MxZExiVTk1RFlJaENuQU5hMnpabFZ3YTZ1SHZ2OVRjV2h4amRpVVBhYXBPZWVld1BkWVVLVThVVDBRSy11YWNWT01RV01MSXJYNS1aV29YUHZVZl9oazhEajBad1FkSmdKS01FcVlvYmxRcUtSVVR6am1qYU9UZHl4Y3o5ZlE3THNDb0lOMFIxVXJBOUF2TGVrSUJzeUlyMUFpczR3?oc=5</t>
         </is>
       </c>
     </row>
@@ -7684,17 +7684,17 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
+          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>08/04/2026 04:00</t>
+          <t>08/04/2026 09:32</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
+          <t>Mosaic, fabricante de fertilizantes, vai paralisar produção de 1 milhão de toneladas de fosfato em meio à alta dos preços - InvestNews</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOMlE2aTNkQ1drWHNGNjhJckFIY3hkM1A2S3lfdkhJbXBtaDN5VmV4NHVPNFdra1FTXzV2ZUprdGNsaDZxa21sWmk2dlpabDJ3aUpROUE3YVdFd0VEZDdscnd0RjAzS3huS1N1Ujh0b01DVld0OUpWUDV4c091SW1kcjBDNFRHZDl0ZTdIMFBlTHRuRnZYenNneG4yUHFLa1BnZEhmY1ZhenhwSTJpb0NFdXE3dDBGVlI3aERwQ0NHWWk0d0JBdS04dFZzbHNySXZNcFp2YlJGNjVCNnZ3YUZtdW55MHhQa29QVnhn0gHwAUFVX3lxTE9IakdwRXpVeExMWDhnSkZFci1UWFRqLTZscWVWcS11Q3lSMmdnX2V4Mm1IUmw5WEF6MURadm1KdEdlLWxMWjlIa3lBNXVJYjVrSzdBTHA4QUFTblNrSV9uRDdLR2g0R3lrUTBSV2hEMi1IVHdHeUxFdVZCNU9xbTktc0xHWUVnLWliZThlUnplY3pGbDBnaXdPTFpicFZ1NEo4RGdjbVlEUW5HSDlIb2U3RUZQLTRlOVBWZVZQZDU3WDR3YkJZbmJ5WHBXa0RZZXIzc3hpbU5OSFo2cWF6M05iZHJUVzl1VWhaRnZUblhWVw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>FERTILIZANTES | Mosaic anuncia paralisação das instalações de Araxá e Patrocínio e busca vender ativos de Araxá - Brasil Mineral</t>
+          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPNVM2Q3ktX2tVc29Wb3RHZGdacTN1TXFhS0xET1k1YmVVWXY2MUI4NVNIUUJENUl6M1ZDM1lIQzNBUi1zYmVYcWJvM3JxSHJLSU13R3NCNG0yS0NfRUpWaGVSRV8wUUt4M2taUGdzX01qUHA3dFpPQ1QzSFpnLTU1TC1oZXBzQVAtcXl3cHhKZ25aNG9FbGt5TVdsNlRqOG1EVmxqNS1vSHZUNVFPWjJZcVZJT01KeGIza3FYYzUtWllscFVtSnlmMkVBMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações no Brasil e reduz produção em 1 milhão de toneladas - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Mosaic paralisa operação de fosfatados em MG e põe à venda ativos - Globo Rural</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOb1pWNXlKY05IeUlLM2M5NUFqWmYtWEgzYWR3UFh4Y2tISnlBZ0JWVnVfMF9POEFOM1k2dXZ2X0k0Z3FpVzYyNUsyRlJCTEs1Mmw0cGhibGdaTXNrMXMxWTA4VmwwSC00TkREbEJQTk5kekdxc3FFQkN1YmxrT1UxOHhyc2YxZFgtUWNLRXdmdi14SlZZY29CUzBxOE4xY3J5Nm41aDBrYVRQS2JyQUZfaDl2T2d3eXZRd1RUSE8xdUtzT3pQOXdDTmFtc2ZyQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZmtnalFlYUVpZzc1V1FCQWVZR3d1dUR2SkJCeG43bi0teDJkVUZiclItMWp4YWxUd2tyaElmLUlEMzVnNnZsUmFhYzRLcVExdndfMml0SWJqV0plN19ZeGVwbC1JRWJuNjBmZUtXUm1ZTHhxRm5TNUJDN08tOHVGYWtBZjRZRHFJblBVeDhiT2J1UFJtS1ItcVZ2SWQzWmxHWmFYNjlqX0hfa3F4eC1SS2lfR1hNRFBMdWZV0gHKAUFVX3lxTE9xRW5TWVBCc3J3OE9JbGx1NTNnUHJlMVZXek42RDlWeTFHa2R2SXFiY3dwTkNldGZFUlhXS0xzMWdfVjRIVTdhMWdwMGQweHdCdi1Jckx5b2pQVEtZTkc4XzNpellPMEx6N2hOWXdMTjVhVjdzZGJPZEI5MjJQeS1jeFFxNWdMRVpTX3JmNldpRVpXY1ZaQXVaZVh4ZUtxeEQxWklhS1Z6YnhYellTMVBJYjkzcVVtZ2NvMkF3Slh0WmRFZW1ibWRnQWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Mosaic, fabricante de fertilizantes, vai paralisar produção de 1 milhão de toneladas de fosfato em meio à alta dos preços - InvestNews</t>
+          <t>FERTILIZANTES | Mosaic anuncia paralisação das instalações de Araxá e Patrocínio e busca vender ativos de Araxá - Brasil Mineral</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -7804,19 +7804,19 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOMlE2aTNkQ1drWHNGNjhJckFIY3hkM1A2S3lfdkhJbXBtaDN5VmV4NHVPNFdra1FTXzV2ZUprdGNsaDZxa21sWmk2dlpabDJ3aUpROUE3YVdFd0VEZDdscnd0RjAzS3huS1N1Ujh0b01DVld0OUpWUDV4c091SW1kcjBDNFRHZDl0ZTdIMFBlTHRuRnZYenNneG4yUHFLa1BnZEhmY1ZhenhwSTJpb0NFdXE3dDBGVlI3aERwQ0NHWWk0d0JBdS04dFZzbHNySXZNcFp2YlJGNjVCNnZ3YUZtdW55MHhQa29QVnhn0gHwAUFVX3lxTE9IakdwRXpVeExMWDhnSkZFci1UWFRqLTZscWVWcS11Q3lSMmdnX2V4Mm1IUmw5WEF6MURadm1KdEdlLWxMWjlIa3lBNXVJYjVrSzdBTHA4QUFTblNrSV9uRDdLR2g0R3lrUTBSV2hEMi1IVHdHeUxFdVZCNU9xbTktc0xHWUVnLWliZThlUnplY3pGbDBnaXdPTFpicFZ1NEo4RGdjbVlEUW5HSDlIb2U3RUZQLTRlOVBWZVZQZDU3WDR3YkJZbmJ5WHBXa0RZZXIzc3hpbU5OSFo2cWF6M05iZHJUVzl1VWhaRnZUblhWVw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPNVM2Q3ktX2tVc29Wb3RHZGdacTN1TXFhS0xET1k1YmVVWXY2MUI4NVNIUUJENUl6M1ZDM1lIQzNBUi1zYmVYcWJvM3JxSHJLSU13R3NCNG0yS0NfRUpWaGVSRV8wUUt4M2taUGdzX01qUHA3dFpPQ1QzSFpnLTU1TC1oZXBzQVAtcXl3cHhKZ25aNG9FbGt5TVdsNlRqOG1EVmxqNS1vSHZUNVFPWjJZcVZJT01KeGIza3FYYzUtWllscFVtSnlmMkVBMA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Mosaic paralisa operação de fosfatados em MG e põe à venda ativos - Globo Rural</t>
+          <t>Copa do Calcário 2026 inicia em abril com sete clubes da Região Centro-Norte - Jornal O Fluminense</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -7826,19 +7826,19 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZmtnalFlYUVpZzc1V1FCQWVZR3d1dUR2SkJCeG43bi0teDJkVUZiclItMWp4YWxUd2tyaElmLUlEMzVnNnZsUmFhYzRLcVExdndfMml0SWJqV0plN19ZeGVwbC1JRWJuNjBmZUtXUm1ZTHhxRm5TNUJDN08tOHVGYWtBZjRZRHFJblBVeDhiT2J1UFJtS1ItcVZ2SWQzWmxHWmFYNjlqX0hfa3F4eC1SS2lfR1hNRFBMdWZV0gHKAUFVX3lxTE9xRW5TWVBCc3J3OE9JbGx1NTNnUHJlMVZXek42RDlWeTFHa2R2SXFiY3dwTkNldGZFUlhXS0xzMWdfVjRIVTdhMWdwMGQweHdCdi1Jckx5b2pQVEtZTkc4XzNpellPMEx6N2hOWXdMTjVhVjdzZGJPZEI5MjJQeS1jeFFxNWdMRVpTX3JmNldpRVpXY1ZaQXVaZVh4ZUtxeEQxWklhS1Z6YnhYellTMVBJYjkzcVVtZ2NvMkF3Slh0WmRFZW1ibWRnQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNTFV2aE9QamdoTlhzd051c1VfLWpKQTdQcnNoM250c0dZd0VUd2NTMG5MWW1laWY3N2hEVkp4cUNNelJDam1WWFZOMHVrNUdONzVFVlZrNS1CaHBSVmNwV1Q2QmxyM0tqVnF3MmhDLTA0ajJXeGUyRUN0WlQ1dU9CeVZPTHl5WkdHN2xSVDBfdXo5Z2dFaUN5UnY4RFN4clpkU2taZ2hDOA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Mosaic vai paralisar fábricas de fertilizantes no Brasil após disparada do enxofre - Bloomberg Línea Brasil</t>
+          <t>Mosaic suspende operações no Brasil e reduz produção em 1 milhão de toneladas - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -7848,19 +7848,19 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNSnRVSDBoS3ZweUtqVkF5TXZldHhZZ1VRVXRkcW81aDNRNW9sNTVvTG9lZ0Z0U3dWZC1hdFkxblFmNjZ1ZDZsS2tvY25oazRUcVRkb3lSbUxwZHFJUGgtSFVOZWU0WU5JeUs4SG1hYWpUQnlvZ2F1TzgzU3ZqYV9iNEVld1dKaU1pdlRrX0FpbTBMNWFTclFsOTA3RkMwUjhCN1RxODRZSmFJMzlwQm1oNjl5S05Ja1FsNTIwVS1TVdIB0wFBVV95cUxQSzJqM05BZ0ZiSVp6MUtIV0h4U2ZGcjM1ZWJaMXNvMHB1UklIM2hxZE1oLTVIYlpXdVJWLWNUZzZidVZERWZOUHNFa0txdXItQzJ1UWpUWmJpcVdnVEMxazlpRWIxT0xoQzdxakhRQTFmMTA4MnZrckljT0ZYUnZDb3RlN09YQUZ5TWhucGQyX2gzcVdJVzdVTXE3X2IySGl3U19ZalBPcUdwREJmNjZab0pnTzllNnM3S2wxVTJGdE5YSkxVUWd4NGVRUF9xNmhuQW1j?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOb1pWNXlKY05IeUlLM2M5NUFqWmYtWEgzYWR3UFh4Y2tISnlBZ0JWVnVfMF9POEFOM1k2dXZ2X0k0Z3FpVzYyNUsyRlJCTEs1Mmw0cGhibGdaTXNrMXMxWTA4VmwwSC00TkREbEJQTk5kekdxc3FFQkN1YmxrT1UxOHhyc2YxZFgtUWNLRXdmdi14SlZZY29CUzBxOE4xY3J5Nm41aDBrYVRQS2JyQUZfaDl2T2d3eXZRd1RUSE8xdUtzT3pQOXdDTmFtc2ZyQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Copa do Calcário 2026 inicia em abril com sete clubes da Região Centro-Norte - Jornal O Fluminense</t>
+          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -7870,29 +7870,29 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNTFV2aE9QamdoTlhzd051c1VfLWpKQTdQcnNoM250c0dZd0VUd2NTMG5MWW1laWY3N2hEVkp4cUNNelJDam1WWFZOMHVrNUdONzVFVlZrNS1CaHBSVmNwV1Q2QmxyM0tqVnF3MmhDLTA0ajJXeGUyRUN0WlQ1dU9CeVZPTHl5WkdHN2xSVDBfdXo5Z2dFaUN5UnY4RFN4clpkU2taZ2hDOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>China garante fertilizante barato, em meio à crise global - CNN Brasil</t>
+          <t>Mosaic vai paralisar fábricas de fertilizantes no Brasil após disparada do enxofre - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>07/04/2026 04:00</t>
+          <t>08/04/2026 04:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQUmZJMDZzZzQ4aEhsdDhjbmpCazN6RVpGVXpFM0ZLb2QzZk9RRnUwVUEteXBVbEZpNkJXN3cyT1Y4c2JuM1RJTHJURWZzTV9mSU1fWHkydGRwSnVTcnMtN0xWSV9wNFpvOVhHMnNaVWZjenJLUjBPLTJEenBrX0tCQVY1ZGxTV2hmWjBhV0dyQkF0T1RnMGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNSnRVSDBoS3ZweUtqVkF5TXZldHhZZ1VRVXRkcW81aDNRNW9sNTVvTG9lZ0Z0U3dWZC1hdFkxblFmNjZ1ZDZsS2tvY25oazRUcVRkb3lSbUxwZHFJUGgtSFVOZWU0WU5JeUs4SG1hYWpUQnlvZ2F1TzgzU3ZqYV9iNEVld1dKaU1pdlRrX0FpbTBMNWFTclFsOTA3RkMwUjhCN1RxODRZSmFJMzlwQm1oNjl5S05Ja1FsNTIwVS1TVdIB0wFBVV95cUxQSzJqM05BZ0ZiSVp6MUtIV0h4U2ZGcjM1ZWJaMXNvMHB1UklIM2hxZE1oLTVIYlpXdVJWLWNUZzZidVZERWZOUHNFa0txdXItQzJ1UWpUWmJpcVdnVEMxazlpRWIxT0xoQzdxakhRQTFmMTA4MnZrckljT0ZYUnZDb3RlN09YQUZ5TWhucGQyX2gzcVdJVzdVTXE3X2IySGl3U19ZalBPcUdwREJmNjZab0pnTzllNnM3S2wxVTJGdE5YSkxVUWd4NGVRUF9xNmhuQW1j?oc=5</t>
         </is>
       </c>
     </row>
@@ -7921,22 +7921,22 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Alta do enxofre preocupa indústria de fertilizantes, que vê risco de desabastecimento - AgFeed</t>
+          <t>China garante fertilizante barato, em meio à crise global - CNN Brasil</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>06/04/2026 04:00</t>
+          <t>07/04/2026 04:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd3piekJKRGJmWE80SVlOQ2NWLVBibnRnc29HR253UlVrNndYQ0F2eUJ3V3BWaGQ0NE5RT0V5c25FeWMwekJxYV9SQUNxZ1NhNTdFQUZDbHF4VFF0LWVMc2lWR3lxd1ZqRGtqM3ZkWHozOElSQlVRYko0WWVaeHJxa2JQREdtSEJOS05iWkxhRkxOZ25RQ3VEMVZIR2xMeVVzc0luand4ZEpVTVNwelNzeTBDa0ItWTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQUmZJMDZzZzQ4aEhsdDhjbmpCazN6RVpGVXpFM0ZLb2QzZk9RRnUwVUEteXBVbEZpNkJXN3cyT1Y4c2JuM1RJTHJURWZzTV9mSU1fWHkydGRwSnVTcnMtN0xWSV9wNFpvOVhHMnNaVWZjenJLUjBPLTJEenBrX0tCQVY1ZGxTV2hmWjBhV0dyQkF0T1RnMGc?oc=5</t>
         </is>
       </c>
     </row>
@@ -7965,56 +7965,56 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Transporte de calcário fortalece produção rural na comunidade do Formigueiro - Prefeitura Municipal de Várzea Grande</t>
+          <t>Alta do enxofre preocupa indústria de fertilizantes, que vê risco de desabastecimento - AgFeed</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>02/04/2026 17:10</t>
+          <t>06/04/2026 04:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRlBlekZQVnQ4X0Q4N2l6VGNpbVJjS0VtSmlHYmZqZTl1WnVTS1RPVEtwSTdCbjQxdk8yNzBVS3E2LS1ZLVFZX19lQkVGV2R2SE5FSms5UEhwOEd4cVMxQ2cwa2NYWTRCRWxjaWVLbkpjRXdfZExuZnh2UFNjUGZKX291dy1nZllOanBtSGlMUU1GTVIzUmJ1U3RLbWplenRWRmltampybC0xNHkzTjBnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd3piekJKRGJmWE80SVlOQ2NWLVBibnRnc29HR253UlVrNndYQ0F2eUJ3V3BWaGQ0NE5RT0V5c25FeWMwekJxYV9SQUNxZ1NhNTdFQUZDbHF4VFF0LWVMc2lWR3lxd1ZqRGtqM3ZkWHozOElSQlVRYko0WWVaeHJxa2JQREdtSEJOS05iWkxhRkxOZ25RQ3VEMVZIR2xMeVVzc0luand4ZEpVTVNwelNzeTBDa0ItWTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Biofragane</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Empresas compram terrenos no Distrito Industrial de Ponta Grossa e prefeitura arrecada R$ 11,8 milhões - Bem Paraná</t>
+          <t>Transporte de calcário fortalece produção rural na comunidade do Formigueiro - Prefeitura Municipal de Várzea Grande</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>01/04/2026 04:00</t>
+          <t>02/04/2026 17:10</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdjVTa3FTVDU1VGZQay1sMlVFTkw3eHRVdXFlVWxrbGtMRnU3aFIyTnpWZ3NEeURSYjJJTDhlWTVOeUtoZWFrNm1zNnRtNEZNVXJMMlhWSFJJYXNzckdOTUxZUjcxYXczMzhqVGFhZHhPemVZbFhhYktFVXZDTzZjZlp6OGJ5czlxdjJnZnB5SzgtMVlpQTI1TmFKSFloZ0lyMHpsSHpQRm90cTdid0lKcmR3QTQ1RUpwS05LRzNJZmdWbm1UZXdGek1reDlKNU1LdzZzbUQ3NGJTQ0ZFQ2NBTWpnNTltU0VNMFdQSy1kM0dib3Np0gH6AUFVX3lxTE40RlkzbktwRTA5SmFTOGw2Ykt0TUd1ZlotUGtnRmpiSGFnWVR4Um95cUlILUwxYkVjcE01OVZreXdGdW9ERmVya0M0MHNCTUpjOS04cVhoSktGcnliRTBhUmdndlJ2NVVDb3dkQ2IwOVlRNHRCdEcyZ3laemtUdS0zQmVpdVBEX2FoVi1MbXlhenZ4R05sSlpNZUpTUkhhV0l1SUJYU1lhUDRnc1MzU2h3ZWQ2a1h2S05DZnlyRGRKbUlVcWFjT1NoNGhmR196T2F0OWR6YWZXaWxjTFdYU1lLMEpnR2ZPZ3ltRERhaGNYdUlJSjRraTdUYUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRlBlekZQVnQ4X0Q4N2l6VGNpbVJjS0VtSmlHYmZqZTl1WnVTS1RPVEtwSTdCbjQxdk8yNzBVS3E2LS1ZLVFZX19lQkVGV2R2SE5FSms5UEhwOEd4cVMxQ2cwa2NYWTRCRWxjaWVLbkpjRXdfZExuZnh2UFNjUGZKX291dy1nZllOanBtSGlMUU1GTVIzUmJ1U3RLbWplenRWRmltampybC0xNHkzTjBnQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Biofragane</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Ormuz: 20% da energia, 30% do GLP e 50% do enxofre - Agência de Notícias Brasil-Árabe - ANBA</t>
+          <t>Empresas compram terrenos no Distrito Industrial de Ponta Grossa e prefeitura arrecada R$ 11,8 milhões - Bem Paraná</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -8024,41 +8024,41 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE91akhDZG5kTFBRM2x2UVhuWGZfa1hOZENjNFotbEI4QnRDU2VYaGtjWm5jUHo3MnJWalZQLVdVbnU0SGl5WkNkd0ZBdXFXa2RYSF9DLTBEYnpLa2hoM1dYcmQ4SERVdlFVdjEtMXk1SnVRYkdY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdjVTa3FTVDU1VGZQay1sMlVFTkw3eHRVdXFlVWxrbGtMRnU3aFIyTnpWZ3NEeURSYjJJTDhlWTVOeUtoZWFrNm1zNnRtNEZNVXJMMlhWSFJJYXNzckdOTUxZUjcxYXczMzhqVGFhZHhPemVZbFhhYktFVXZDTzZjZlp6OGJ5czlxdjJnZnB5SzgtMVlpQTI1TmFKSFloZ0lyMHpsSHpQRm90cTdid0lKcmR3QTQ1RUpwS05LRzNJZmdWbm1UZXdGek1reDlKNU1LdzZzbUQ3NGJTQ0ZFQ2NBTWpnNTltU0VNMFdQSy1kM0dib3Np0gH6AUFVX3lxTE40RlkzbktwRTA5SmFTOGw2Ykt0TUd1ZlotUGtnRmpiSGFnWVR4Um95cUlILUwxYkVjcE01OVZreXdGdW9ERmVya0M0MHNCTUpjOS04cVhoSktGcnliRTBhUmdndlJ2NVVDb3dkQ2IwOVlRNHRCdEcyZ3laemtUdS0zQmVpdVBEX2FoVi1MbXlhenZ4R05sSlpNZUpTUkhhV0l1SUJYU1lhUDRnc1MzU2h3ZWQ2a1h2S05DZnlyRGRKbUlVcWFjT1NoNGhmR196T2F0OWR6YWZXaWxjTFdYU1lLMEpnR2ZPZ3ltRERhaGNYdUlJSjRraTdUYUE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Cotações Agrícolas para esta Terça-feira 31 de Março de 2026 - RRMAIS</t>
+          <t>Ormuz: 20% da energia, 30% do GLP e 50% do enxofre - Agência de Notícias Brasil-Árabe - ANBA</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>31/03/2026 04:00</t>
+          <t>01/04/2026 04:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQczNPajlCZ1pKNG5sTDZfcEpwMW1ESHJZTF9TSmpkbnM3TVNqTW9BMjNnRUpYUzdkZldzMVI2aG5LZk5yVXBlNGI1MExmd3RJT2lBN09KWW5SSE9YUjRFbFhibkhwc1RERGRtdmZrWS1iYjE5X2E0MnB0TFFJdERxT2YxUVp4eXdJZW01SXU4U3lMaWwwb3F6SnJ4VE1GazFLdGxkcW0yNTBfaDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE91akhDZG5kTFBRM2x2UVhuWGZfa1hOZENjNFotbEI4QnRDU2VYaGtjWm5jUHo3MnJWalZQLVdVbnU0SGl5WkNkd0ZBdXFXa2RYSF9DLTBEYnpLa2hoM1dYcmQ4SERVdlFVdjEtMXk1SnVRYkdY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Preço da ureia dispara e atinge maior patamar desde 2022 - Poder360</t>
+          <t>Cotações Agrícolas para esta Terça-feira 31 de Março de 2026 - RRMAIS</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZUIxSkk2bGJHRnlhMlNaYW5xVVdiZmctUGhDQ0NFQXlmakJzOFhwN0JrTVFOUzZmeGFaV0dwSUJsaDdZdy1DVEJRR0JDMjJGbVdEelpFNjQ1ZVQ2cFQ3Q1MzbmtrMklTT1p6UDd6MzBQcVVDT215MkluWWJnb0NQbjBTQnFHQXZwNXhGRXF1akk4bDJGMWY5SGF0SkM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQczNPajlCZ1pKNG5sTDZfcEpwMW1ESHJZTF9TSmpkbnM3TVNqTW9BMjNnRUpYUzdkZldzMVI2aG5LZk5yVXBlNGI1MExmd3RJT2lBN09KWW5SSE9YUjRFbFhibkhwc1RERGRtdmZrWS1iYjE5X2E0MnB0TFFJdERxT2YxUVp4eXdJZW01SXU4U3lMaWwwb3F6SnJ4VE1GazFLdGxkcW0yNTBfaDA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8080,7 +8080,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Ureia avança ao maior nível desde 2022, mas demanda brasileira perde força - CNN Brasil</t>
+          <t>Preço da ureia dispara e atinge maior patamar desde 2022 - Poder360</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -8090,51 +8090,51 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQai1ZMXRrWW8zbGNQRWwyOXVteEg3SnVUZWtIUGpJVTFKUmM5VmlkbDdnYWhIN3VDSmR1Sk5mOXVyU1ZSM1hBS1YzUnRkdXh4RkM2aGNTVzQtWDdsb29ab0J2RHFPR1lvWjV6eXZBaU5WbmhYSzBRb2N0ejFaSldHdTFveEtMb2pWZXZMbnlNSmxyU2lJaTB4T2w2QThOSHFqbEEtVXVXUFRaaVZCeHVrdElxbWp0RHA5Ny1kZGphcWJVR0RUWjhfZXJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZUIxSkk2bGJHRnlhMlNaYW5xVVdiZmctUGhDQ0NFQXlmakJzOFhwN0JrTVFOUzZmeGFaV0dwSUJsaDdZdy1DVEJRR0JDMjJGbVdEelpFNjQ1ZVQ2cFQ3Q1MzbmtrMklTT1p6UDd6MzBQcVVDT215MkluWWJnb0NQbjBTQnFHQXZwNXhGRXF1akk4bDJGMWY5SGF0SkM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Corte de 80% na CFEM deve baratear calcário agrícola - CompreRural</t>
+          <t>Ureia avança ao maior nível desde 2022, mas demanda brasileira perde força - CNN Brasil</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>27/03/2026 04:00</t>
+          <t>31/03/2026 04:00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQa2dGQlVRajItTmU5MnBNVHE0R3F2TTlWbHNvZlNSMFJZLXVXWW5pNlp3X0xFSU9OcHltNXVKM3FpTGc2Y3pKZkZxZkFoUGlmdnVrQ3NoSDd3MnR1QXlnakVJR2lQajJ1YjNIR1VHNm9SNV9CSDB5TjMwaXhoNU5VSzVLckpKU2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQai1ZMXRrWW8zbGNQRWwyOXVteEg3SnVUZWtIUGpJVTFKUmM5VmlkbDdnYWhIN3VDSmR1Sk5mOXVyU1ZSM1hBS1YzUnRkdXh4RkM2aGNTVzQtWDdsb29ab0J2RHFPR1lvWjV6eXZBaU5WbmhYSzBRb2N0ejFaSldHdTFveEtMb2pWZXZMbnlNSmxyU2lJaTB4T2w2QThOSHFqbEEtVXVXUFRaaVZCeHVrdElxbWp0RHA5Ny1kZGphcWJVR0RUWjhfZXJR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Corretivo de solo sustentável entra no RenovaBio e gera Créditos de Descarbonização - JornalCana</t>
+          <t>Corte de 80% na CFEM deve baratear calcário agrícola - comprerural.com</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>26/03/2026 04:00</t>
+          <t>27/03/2026 04:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQZHNpQzdqYTdMVEl3Tm9xS0R5ZlpYbEpTeFF3ckdFVElTRkZFcGVIVUkwZzQwZC1fenEyVzJLekY2cmNJQmNpMTcwTnRDdjNhQVdHQ0lxZGM2VTdQTmNiOUZGWC1UeGI2S29JeFF2cGR5QWF5Q1dqZFd4S2pucU9fUWMyUVAyMkFRLVhkQkJBZnRRNnpGLUpyVzBOX1FJeHhqTTh1U1pER0YycjZ6VzJId0VqQW93ellCUnJjQnlJWTlPMnZTVzBILUJiME9iaWVScUVDYg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQa2dGQlVRajItTmU5MnBNVHE0R3F2TTlWbHNvZlNSMFJZLXVXWW5pNlp3X0xFSU9OcHltNXVKM3FpTGc2Y3pKZkZxZkFoUGlmdnVrQ3NoSDd3MnR1QXlnakVJR2lQajJ1YjNIR1VHNm9SNV9CSDB5TjMwaXhoNU5VSzVLckpKU2s?oc=5</t>
         </is>
       </c>
     </row>
@@ -8146,39 +8146,39 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização</t>
+          <t>Corretivo de solo sustentável entra no RenovaBio e gera Créditos de Descarbonização - JornalCana</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>25/03/2026 08:19</t>
+          <t>26/03/2026 04:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a708df749304381a4ad0ae0406775c0&amp;url=https%3a%2f%2fwww.segs.com.br%2fmais%2fagro%2f443607-corretivo-de-solo-sustentavel-entra-para-o-programa-renovabio-e-gera-creditos-de-descarbonizacao&amp;c=17562555972134783382&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQZHNpQzdqYTdMVEl3Tm9xS0R5ZlpYbEpTeFF3ckdFVElTRkZFcGVIVUkwZzQwZC1fenEyVzJLekY2cmNJQmNpMTcwTnRDdjNhQVdHQ0lxZGM2VTdQTmNiOUZGWC1UeGI2S29JeFF2cGR5QWF5Q1dqZFd4S2pucU9fUWMyUVAyMkFRLVhkQkJBZnRRNnpGLUpyVzBOX1FJeHhqTTh1U1pER0YycjZ6VzJId0VqQW93ellCUnJjQnlJWTlPMnZTVzBILUJiME9iaWVScUVDYg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Ureia dispara 50% em 30 dias - agrolink.com.br</t>
+          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>25/03/2026 04:00</t>
+          <t>25/03/2026 08:19</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a70b55360ee4ce0b0aa0ac3f6869496&amp;url=https%3a%2f%2fwww.segs.com.br%2fmais%2fagro%2f443607-corretivo-de-solo-sustentavel-entra-para-o-programa-renovabio-e-gera-creditos-de-descarbonizacao&amp;c=17562555972134783382&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -8212,39 +8212,39 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia segue subindo: valor próximo de US$700 por tonelada para abril - Farmnews</t>
+          <t>Ureia dispara 50% em 30 dias - Agrolink</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>23/03/2026 04:00</t>
+          <t>25/03/2026 04:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNcHkzSlA3V284QW9KcWRCR0hnbmpYZVFlNWVTVl93TmRPbG5QbUdLcWliZEcxZ0N2T1JlMWQ0NTJwRXFPVjZ5b1I1V1pzZVdySlJkdmNtTW9jVWlWUVY4dk5GLXlpdjhoSk1MRTZPc0hwX0tXYm9qZUo2Vk5ubjc1bWhUdE8xTnNQRlFtdGtsVEs1T3lzZnZjeVVQMWV5dERkMVZHemxkQ09CdnBWRURXcEdMNXlGZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - CircuitoMT</t>
+          <t>Preço futuro da ureia segue subindo: valor próximo de US$700 por tonelada para abril - Farmnews</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>21/03/2026 04:00</t>
+          <t>23/03/2026 04:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNVkFwWkxpMVFhdFh2WDZORExyazZ6WWZucVBZS3pzVlhNbHh6ajF0RXpYRG84cFZWWDBwMmY4LWdaNUdfM29sQW1wVE43QXNSbjlpdmlET1g4M0RCRkI2R2loc2xpaFgyUTl6U2FFSUhNUlJTVkRvV3U3TlZtM0RQX05MaHRRcE42ay1kOG9aUHdISHIzMWJ6SXpjdldUZEk1ck8yQmhhTWN3djlXUDkyYWZZTGo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNcHkzSlA3V284QW9KcWRCR0hnbmpYZVFlNWVTVl93TmRPbG5QbUdLcWliZEcxZ0N2T1JlMWQ0NTJwRXFPVjZ5b1I1V1pzZVdySlJkdmNtTW9jVWlWUVY4dk5GLXlpdjhoSk1MRTZPc0hwX0tXYm9qZUo2Vk5ubjc1bWhUdE8xTnNQRlFtdGtsVEs1T3lzZnZjeVVQMWV5dERkMVZHemxkQ09CdnBWRURXcEdMNXlGZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -8256,17 +8256,17 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - Tribuna de Petrópolis</t>
+          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - CircuitoMT</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>20/03/2026 18:35</t>
+          <t>21/03/2026 04:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQbkthazMxNGdTNWUxZ1FCNTZobG1VQjJVMm5nTXg1djFDUHdLVHpNU0VYRWhFOC1NbVkycXBoSkg4azA5Q2NmcE1GWWhBOXprUFVFcDV4Sl85cGppakY3MzljaXd6UWVuYlp2MWQ5cHdpRFhzc00zSjM1blBIOHd0d0E3UkoxX1JqaTY2Q0Z2WGp4bGpDMHFHWm5ZWER1YzN4MTF0S3lWY1poQzF6X3B4NzlsUmstZUJZRk12MDNUNUhocmUzWEJpRkZTY3E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNVkFwWkxpMVFhdFh2WDZORExyazZ6WWZucVBZS3pzVlhNbHh6ajF0RXpYRG84cFZWWDBwMmY4LWdaNUdfM29sQW1wVE43QXNSbjlpdmlET1g4M0RCRkI2R2loc2xpaFgyUTl6U2FFSUhNUlJTVkRvV3U3TlZtM0RQX05MaHRRcE42ay1kOG9aUHdISHIzMWJ6SXpjdldUZEk1ck8yQmhhTWN3djlXUDkyYWZZTGo?oc=5</t>
         </is>
       </c>
     </row>
@@ -8295,12 +8295,12 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Mosaic, gigante do agronegócio, aposta em IA para enfrentar volatilidade e reduzir custos logísticos - Globo Rural</t>
+          <t>Sindical-BA alerta para impacto da nova tributação sobre calcário agrícola, que deve elevar custos do setor - Sistema FIEB</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -8310,19 +8310,19 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxOME5qTE54MnlMcWFJeS02bUs2dGRlR0VSRWJHT001NEtPcS1XaURNbC1UaGd1Q2hkWld2ay1ITHptMTdBcHRPLUJPVzZWTkR5d21GNHJHZGEwZ3U3ckltNnNQN2x3WnQtT2FwdkJ1eTNDYVFSX2ZreUJ2dFQ3M1pOSENSRGhTeTg5djRfaWxWbC1FTEp5TWVBR24wVlNZNEhLc2N0VVB5XzAxWXZqbHNJU2hTUUQ2dlJRaTRkTGdId3NIREtxdWR1dXpqSVY4V1lQRlJzbTVodXFSOXBpT05RVkdpZmJSNXVpYzJGaUdLcjUwLWQyNGdoMWNlOVBVSU5PQmVjX1o5cmZPN1pY0gGbAkFVX3lxTE5YUjI3TVduTnRpaUdEeW0tYnZvSGpRdHd4MXE1VUtsc3ZsQ004emFwdGU4cFZqQ25XSnVTQjYxUG5DNE4xcHZKZk1JLXNjVk5hMkNuNmJZdllRVW5uQmtGQ0o3UVBJLWp5M0g4YXJPY3FqajNsVWttc2pJNjBFdHpkMVFEYWJvaGZUU1hQMXFzTDNleFhVakdxTmRPTElXTXA4U0xacTJfNFYwS0I4UE42S0wydUtudEU5d0RNOGYtQk83SVBtc3VFeTk3X3BhOHVFanBOd3VEaHYySllENWMxdnhDRUJXd2VfNXdhRDl0cHRkVU1BM3ViMWt2azdDbW03THJ0WGRBQllJaW1aRVM1WEJuSTdRNm9Bak0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOQUNveWVYZUNwX3BMRXdqRzdqUThDTkNOZk9vVWNMbHNsVlg2N1oxcDZjRV9nVHVrajNfaGVieG5RYVhiMDhjeGxobmdCRmhkQnFDSy1rR2hvbUhjb056WTNZeWpkSGpmVWhlMWxQTjJCN0dqRFRibmZRLVhOb1R5X3c5UmZBcmlYVTNYd2trZUNCak4xWHY1OTBtUHROZVZwUm5UVWJINWc2dzgwOVg2RnJMNFlaZ0p4aFIxdjBfWUZfUi1WaGd0MVJEeDhFa1ByeXhmVThUVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Sindical-BA alerta para impacto da nova tributação sobre calcário agrícola, que deve elevar custos do setor - Sistema FIEB</t>
+          <t>Alta da ureia pressiona mercado e pode impulsionar uso de alternativas em 2026 - Feed&amp;Food</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -8332,19 +8332,19 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOQUNveWVYZUNwX3BMRXdqRzdqUThDTkNOZk9vVWNMbHNsVlg2N1oxcDZjRV9nVHVrajNfaGVieG5RYVhiMDhjeGxobmdCRmhkQnFDSy1rR2hvbUhjb056WTNZeWpkSGpmVWhlMWxQTjJCN0dqRFRibmZRLVhOb1R5X3c5UmZBcmlYVTNYd2trZUNCak4xWHY1OTBtUHROZVZwUm5UVWJINWc2dzgwOVg2RnJMNFlaZ0p4aFIxdjBfWUZfUi1WaGd0MVJEeDhFa1ByeXhmVThUVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOZWl0bUdaQVRHdjR0MVZmM1kwREFfQjl4bl9pM3RETHFoc2QwUThjcWdFUmxzQnNSZ1Q1VjM3dXE0NXV6dEE0eURjNlZVTXVLZXpZVDdERkZWMVBjcjJjd0lrQWowSFptbVBpVGx2c1V2WDdweUJYQ0l6RVlHdHZUbXZKQkdKMDVxVkVYekV3dnhzUk5QeVd6WHZiM2pLU244eGk4SjNB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Alta da ureia pressiona mercado e pode impulsionar uso de alternativas em 2026 - feedfood.com.br</t>
+          <t>Mosaic, gigante do agronegócio, aposta em IA para enfrentar volatilidade e reduzir custos logísticos - Globo Rural</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -8354,7 +8354,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOZWl0bUdaQVRHdjR0MVZmM1kwREFfQjl4bl9pM3RETHFoc2QwUThjcWdFUmxzQnNSZ1Q1VjM3dXE0NXV6dEE0eURjNlZVTXVLZXpZVDdERkZWMVBjcjJjd0lrQWowSFptbVBpVGx2c1V2WDdweUJYQ0l6RVlHdHZUbXZKQkdKMDVxVkVYekV3dnhzUk5QeVd6WHZiM2pLU244eGk4SjNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxOME5qTE54MnlMcWFJeS02bUs2dGRlR0VSRWJHT001NEtPcS1XaURNbC1UaGd1Q2hkWld2ay1ITHptMTdBcHRPLUJPVzZWTkR5d21GNHJHZGEwZ3U3ckltNnNQN2x3WnQtT2FwdkJ1eTNDYVFSX2ZreUJ2dFQ3M1pOSENSRGhTeTg5djRfaWxWbC1FTEp5TWVBR24wVlNZNEhLc2N0VVB5XzAxWXZqbHNJU2hTUUQ2dlJRaTRkTGdId3NIREtxdWR1dXpqSVY4V1lQRlJzbTVodXFSOXBpT05RVkdpZmJSNXVpYzJGaUdLcjUwLWQyNGdoMWNlOVBVSU5PQmVjX1o5cmZPN1pY0gGbAkFVX3lxTE5YUjI3TVduTnRpaUdEeW0tYnZvSGpRdHd4MXE1VUtsc3ZsQ004emFwdGU4cFZqQ25XSnVTQjYxUG5DNE4xcHZKZk1JLXNjVk5hMkNuNmJZdllRVW5uQmtGQ0o3UVBJLWp5M0g4YXJPY3FqajNsVWttc2pJNjBFdHpkMVFEYWJvaGZUU1hQMXFzTDNleFhVakdxTmRPTElXTXA4U0xacTJfNFYwS0I4UE42S0wydUtudEU5d0RNOGYtQk83SVBtc3VFeTk3X3BhOHVFanBOd3VEaHYySllENWMxdnhDRUJXd2VfNXdhRDl0cHRkVU1BM3ViMWt2azdDbW03THJ0WGRBQllJaW1aRVM1WEJuSTdRNm9Bak0?oc=5</t>
         </is>
       </c>
     </row>
@@ -8383,12 +8383,12 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>CRA aprova selo para café e alíquota menor sobre calcário - Senado</t>
+          <t>Cobertura linear ganha novo andar e vira duplex de 400 m² no Rio - Casa Cor</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -8398,19 +8398,19 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNY2pRTWs2S3NtQlQwenhTVkJoWWpXV1ZYWEJmS1ZBcVRJOUNnYUR1YUJEXzRneGxSdlZFenh3d1c4TXVLaktTSi1Xek5TUEU3d0ppS2s4ZTdBaG9QSzcxV1pmOVpZOU16Tjl1T05kT3lIaHNkRXBtck9UY2xOYnpVVFV1MWMxTjdFbXYzektEQ1I4Uy00MU41dTQ2ODhzV1p2MUpENTZ6bUV4dzlOaXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNM3ZSSWI2SU5GM19FMFIza3l0dEFFUXZjUUZzaDBBaVRWYWg2MWtvenB1S3dOUG1qRjVod0lTR1JReENZelpid0tYY1dyQk9kWl9HVUlFQTA0dVBpUlluS3J2b0NkVjFmZGs0OXJ5azJEWHRSaFNwckxWeDJLLVpXMjdCVFhOQ3dMX1Fia256eVNYcVB5Y2pXRmo0aEZ0c0dkdy16YmhkVmcxb2FyQkVR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Disparada histórica do enxofre pressiona fertilizantes - agrolink.com.br</t>
+          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -8420,19 +8420,19 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOREtjdjl3OVV3M3BodzJUN2tTS09qQjdCaHVYcHJVak9fWlBKcl96ZWlkaWhYSmJSazVXQ3c4LUl4YTU4MXh6VjNwd09JaGRsblVrajRXNTlHUXp6X0V1Y0E1YmYwTXZxa2ZXX1AwNEVJcnpibWRMMTRXcG9ibGRSb21BOGNHMDFxZWJhVnRmeTJ4SjY1ejUzTlVqelJ6dE4xUkFpWkhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado</t>
+          <t>Disparada histórica do enxofre pressiona fertilizantes - Agrolink</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -8442,19 +8442,19 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOREtjdjl3OVV3M3BodzJUN2tTS09qQjdCaHVYcHJVak9fWlBKcl96ZWlkaWhYSmJSazVXQ3c4LUl4YTU4MXh6VjNwd09JaGRsblVrajRXNTlHUXp6X0V1Y0E1YmYwTXZxa2ZXX1AwNEVJcnpibWRMMTRXcG9ibGRSb21BOGNHMDFxZWJhVnRmeTJ4SjY1ejUzTlVqelJ6dE4xUkFpWkhn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Cobertura linear ganha novo andar e vira duplex de 400 m² no Rio - casacor.abril.com.br</t>
+          <t>CRA aprova selo para café e alíquota menor sobre calcário - Senado</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNM3ZSSWI2SU5GM19FMFIza3l0dEFFUXZjUUZzaDBBaVRWYWg2MWtvenB1S3dOUG1qRjVod0lTR1JReENZelpid0tYY1dyQk9kWl9HVUlFQTA0dVBpUlluS3J2b0NkVjFmZGs0OXJ5azJEWHRSaFNwckxWeDJLLVpXMjdCVFhOQ3dMX1Fia256eVNYcVB5Y2pXRmo0aEZ0c0dkdy16YmhkVmcxb2FyQkVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNY2pRTWs2S3NtQlQwenhTVkJoWWpXV1ZYWEJmS1ZBcVRJOUNnYUR1YUJEXzRneGxSdlZFenh3d1c4TXVLaktTSi1Xek5TUEU3d0ppS2s4ZTdBaG9QSzcxV1pmOVpZOU16Tjl1T05kT3lIaHNkRXBtck9UY2xOYnpVVFV1MWMxTjdFbXYzektEQ1I4Uy00MU41dTQ2ODhzV1p2MUpENTZ6bUV4dzlOaXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -8559,12 +8559,12 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Limestone: a pedra calcária em evidência na arquitetura - Portobello Archtrends</t>
+          <t>Importação de ureia pelo Brasil cai forte em 2026 e preço segue em alta - Farmnews</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -8574,19 +8574,19 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5Xa21Zc0YzY0pUazFLbDJVMmlTYzcwYTd3RG1OcjNNalZVblN0N2gwMV9NczFWZURPa2MwaXNMcmxfdE5seHo0QWozSFdBbmfSAVRBVV95cUxNUEhPRGZuQlpIS1NNTm1lMW8zblJQUVVYWkhNXzlfcVk4N3dfZHRRb0xCcE9IWTZIMHdhNnYtOE4wNjh4YlBrSTY4ZUtVenF6NDdKemg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPMlQ0WWR5RTFCWmljNEI2OU4wQXFKdHVteERIZk9JbjlEZXJHcFFGdC1XNEFZcmozWVdjV0FmdVMwS2RrM0lMWDZ5bTNMTmY5eVN1UnlHS0NRQlZOOE1CckxWSkROZUhCTDBxWUNZTWNvRnZzWFNXaTNPeDJMeWlkWE92QW1HeGRod0d5TDdYeUlaLTNxNGVIbVpkUGs3MVV1VzU3WVpBNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil cai forte em 2026 e preço segue em alta - Farmnews</t>
+          <t>Limestone: a pedra calcária em evidência na arquitetura - blog.archtrends.com</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPMlQ0WWR5RTFCWmljNEI2OU4wQXFKdHVteERIZk9JbjlEZXJHcFFGdC1XNEFZcmozWVdjV0FmdVMwS2RrM0lMWDZ5bTNMTmY5eVN1UnlHS0NRQlZOOE1CckxWSkROZUhCTDBxWUNZTWNvRnZzWFNXaTNPeDJMeWlkWE92QW1HeGRod0d5TDdYeUlaLTNxNGVIbVpkUGs3MVV1VzU3WVpBNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5Xa21Zc0YzY0pUazFLbDJVMmlTYzcwYTd3RG1OcjNNalZVblN0N2gwMV9NczFWZURPa2MwaXNMcmxfdE5seHo0QWozSFdBbmfSAVRBVV95cUxNUEhPRGZuQlpIS1NNTm1lMW8zblJQUVVYWkhNXzlfcVk4N3dfZHRRb0xCcE9IWTZIMHdhNnYtOE4wNjh4YlBrSTY4ZUtVenF6NDdKemg?oc=5</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Guerra no Oriente Médio faz preço da ureia subir e eleva custos de produção, aponta Imea - Canal Rural</t>
+          <t>Guerra no Oriente Médio faz preço da ureia subir e eleva custos de produção, aponta Imea - canalrural.com.br</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -8647,12 +8647,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>CMOC | Investimentos socioambientais somaram quase R$ 14 milhões em 2025 - Brasil Mineral</t>
+          <t>Mosaic avalia entrada no mercado de terras raras com projeto em Uberaba - CNN Brasil</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -8662,19 +8662,19 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNNllOeHNGcldnbTlPcnJhb09pVWRYc3dmcWNhWWlZUkx4Rm9PRkQ4SmQ4M04wUFJGZE13V1BJR01xQ0hVcHVxdlpOSzJKSHR2LUNLSjZETHBhTy1yTkhkZ0hPUmJDSHF3SjNMV0VMV1R5QnhkZm90SjlBNFRJZWVUSWhEb3FJc2Y3Vi1JbDZHZFFXRGVqWEhtaU9JZEVncHlCR0dGajZONXpUdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaDhHU1U4Z1ZUcDhvSzBheGZqQUxjOXFvZFpKQWI5Q0pTdG4yMkMxbGtoS0JtdDg2Tm5GQ0VRMC1NZ2tBRS12RFowanRSZ0V5b2F1R0Z5RGw2NlYwbzdoRzZzS2NGbi1PNFV3aHBxRHhsUTkyeFdXdDZKS1QxV2RKdThyU2JGS1E4amZXN05CYjZFS1BpRXAwX0hmcXVVLTgwc2RqUkJFeFlKQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>TERRAS RARAS | Mosaic e Rainbow planejam projeto conjunto em Minas Gerais - Brasil Mineral</t>
+          <t>CMOC | Investimentos socioambientais somaram quase R$ 14 milhões em 2025 - Brasil Mineral</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQbWZYenFKcUV3ejJVdWJLTDYwY0duaXVYY1VhRzZ2UlNuXzh5OTZ6T19QRktEemp4WWI5S2ZqSWlWMVNRQ1FIeGhmVEtWTENVTFRYNWZobDB3blBuc3RTUUFQWnFMaVpLT01YOUhFQXg2UksyUEZMUmpVeUpGdFUtYzc2YnkwRjZDOHJGVlAwclk0cS1fOFJvRS1LN2gzZVR1NGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNNllOeHNGcldnbTlPcnJhb09pVWRYc3dmcWNhWWlZUkx4Rm9PRkQ4SmQ4M04wUFJGZE13V1BJR01xQ0hVcHVxdlpOSzJKSHR2LUNLSjZETHBhTy1yTkhkZ0hPUmJDSHF3SjNMV0VMV1R5QnhkZm90SjlBNFRJZWVUSWhEb3FJc2Y3Vi1JbDZHZFFXRGVqWEhtaU9JZEVncHlCR0dGajZONXpUdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Mosaic avalia entrada no mercado de terras raras com projeto em Uberaba - CNN Brasil</t>
+          <t>TERRAS RARAS | Mosaic e Rainbow planejam projeto conjunto em Minas Gerais - Brasil Mineral</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaDhHU1U4Z1ZUcDhvSzBheGZqQUxjOXFvZFpKQWI5Q0pTdG4yMkMxbGtoS0JtdDg2Tm5GQ0VRMC1NZ2tBRS12RFowanRSZ0V5b2F1R0Z5RGw2NlYwbzdoRzZzS2NGbi1PNFV3aHBxRHhsUTkyeFdXdDZKS1QxV2RKdThyU2JGS1E4amZXN05CYjZFS1BpRXAwX0hmcXVVLTgwc2RqUkJFeFlKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQbWZYenFKcUV3ejJVdWJLTDYwY0duaXVYY1VhRzZ2UlNuXzh5OTZ6T19QRktEemp4WWI5S2ZqSWlWMVNRQ1FIeGhmVEtWTENVTFRYNWZobDB3blBuc3RTUUFQWnFMaVpLT01YOUhFQXg2UksyUEZMUmpVeUpGdFUtYzc2YnkwRjZDOHJGVlAwclk0cS1fOFJvRS1LN2gzZVR1NGc?oc=5</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Mosaic aprova pagamento de dividendos para acionistas e detentores de BDRs - Globo Rural</t>
+          <t>Conflito no Irã acelera alta de preços de fertilizantes - Globo Rural</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -8838,19 +8838,19 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQMHQ4cjVsQVFTNmdFcHFWTWNSeUxaQWhUY3FvRkF0LUxKcF9oUHprQ0ZPdUhYaFNwYlJDN3pUaTF3YnhPZjVHMkhVNEwwV2NaM0hLTllQa2dwQTUwZTZIWjBiRHFGTWlUallPLXRwU0NndC1YQ0ttbllZVzJkVUl5Tk1aN3lMdTNBeFc1WXd3RlFCcFpMa0ZMNFFFZXR1b05jdXV6TEJvZFZFTTZXVHE2Z0ozaW5adTRZOFkyb1p1ak91MVluaEkyZTFZTDRWZ3PSAd4BQVVfeXFMUG9xZERneW5ycklwM3BUcGVnRV9KaTZsenFUYjRObWthYnRQREpMWUgyamgyWDZQd2FFTUJ3UnlwQnhGSzA1czYxUVgwTHBqTlNuM1hCT2ZkUGwwaTF6SE1hTTZZMnF3V28wWng3WVZRT0xqYlVBYkFfX2gzMVl2ZXk5ajdQUF9NMFgzbTdBa1ZtbTVFUUJxYW5rakFkOW1Qb0hzSjZvZm9CTGhMX08xMDRPQmJEdkxvdnFpZVRoRlJQTW5xV1RpeVVGTUVpcjRqVk44RFNxblNQOTQ5cnlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYVZhOFowUnN1VW5xSFlObjg1U19vdE16RTRKc09UaU1vclgtanJLLWVSZ3hINjh3QzZkTU5UcFJRbkJTMm1MTU1UZEJEVDA4cVV0eE54ZzZEelFyZTBzTmNaZjhHazNpc0ZHTElIVTJHZ1VySWd3RnlwY3FEMU5wQlI2MEJaTkZhd1E3ZXNYSVZlSEU4cUhqemJsSUlwVTNrZV9nSTlLbHBla2V4eUQ2UGdJZ2HSAcMBQVVfeXFMTWR5MEtub0FYbkRpa0lUUlI0VTlmRE8xcW53OGNKdFhtX2pxZkZoVGNGUUVwZzJyN1NtYklFaEFBTDJmM3RldXhvRFBSSnpVSFhLMUJnWndyNFVKM2p6Zmt3U0JYX19NZDJ2X3hQcVJtVTlLU3BRaldad3BvbzRnWXc0cEhYX2h5Q1hkbmFvcTg1VnU1aFF1bGcxdEZ4RTB3LXYtcS1hRkgyRGJmZThrZzl5dHFzMWFyYWpkTlR4T2ZfT19V?oc=5</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Conflito no Irã acelera alta de preços de fertilizantes - Globo Rural</t>
+          <t>Mosaic aprova pagamento de dividendos para acionistas e detentores de BDRs - Globo Rural</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYVZhOFowUnN1VW5xSFlObjg1U19vdE16RTRKc09UaU1vclgtanJLLWVSZ3hINjh3QzZkTU5UcFJRbkJTMm1MTU1UZEJEVDA4cVV0eE54ZzZEelFyZTBzTmNaZjhHazNpc0ZHTElIVTJHZ1VySWd3RnlwY3FEMU5wQlI2MEJaTkZhd1E3ZXNYSVZlSEU4cUhqemJsSUlwVTNrZV9nSTlLbHBla2V4eUQ2UGdJZ2HSAcMBQVVfeXFMTWR5MEtub0FYbkRpa0lUUlI0VTlmRE8xcW53OGNKdFhtX2pxZkZoVGNGUUVwZzJyN1NtYklFaEFBTDJmM3RldXhvRFBSSnpVSFhLMUJnWndyNFVKM2p6Zmt3U0JYX19NZDJ2X3hQcVJtVTlLU3BRaldad3BvbzRnWXc0cEhYX2h5Q1hkbmFvcTg1VnU1aFF1bGcxdEZ4RTB3LXYtcS1hRkgyRGJmZThrZzl5dHFzMWFyYWpkTlR4T2ZfT19V?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQMHQ4cjVsQVFTNmdFcHFWTWNSeUxaQWhUY3FvRkF0LUxKcF9oUHprQ0ZPdUhYaFNwYlJDN3pUaTF3YnhPZjVHMkhVNEwwV2NaM0hLTllQa2dwQTUwZTZIWjBiRHFGTWlUallPLXRwU0NndC1YQ0ttbllZVzJkVUl5Tk1aN3lMdTNBeFc1WXd3RlFCcFpMa0ZMNFFFZXR1b05jdXV6TEJvZFZFTTZXVHE2Z0ozaW5adTRZOFkyb1p1ak91MVluaEkyZTFZTDRWZ3PSAd4BQVVfeXFMUG9xZERneW5ycklwM3BUcGVnRV9KaTZsenFUYjRObWthYnRQREpMWUgyamgyWDZQd2FFTUJ3UnlwQnhGSzA1czYxUVgwTHBqTlNuM1hCT2ZkUGwwaTF6SE1hTTZZMnF3V28wWng3WVZRT0xqYlVBYkFfX2gzMVl2ZXk5ajdQUF9NMFgzbTdBa1ZtbTVFUUJxYW5rakFkOW1Qb0hzSjZvZm9CTGhMX08xMDRPQmJEdkxvdnFpZVRoRlJQTW5xV1RpeVVGTUVpcjRqVk44RFNxblNQOTQ5cnlB?oc=5</t>
         </is>
       </c>
     </row>
@@ -8889,12 +8889,12 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Fertilizantes puxam alta de preços de outros produtos químicos para indústria, diz IBGE - Valor Econômico</t>
+          <t>Com a guerra no Oriente Médio, cotação da ureia sobe 10% no Brasil - CNN Brasil</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWjd4MFdUanZwVU1jUGhrbTVtempwWEFlRWt3RWZNWlNyQVp2RnRNY2lNTGtYTWFNbGRibVVObUlEVGZXNnZqN1pwYnN5Ul9DSlBjSTgyYmlzV3VseFVFbjlwdjRCM0UzekVyNVF2LUY0ZEpxanE2aFdWdnBuRWJDYTJYUnJjYVFyaUo3dUFtZ0tTS3Awd3BLTjBEcVZfNFpXVlpMSTdCSnc5YW9GNjNTT1poT1RteF9NMVNZUzRzUXdsSXlGX0JYZ0o0R2RDYWZZcXVRVnk3RXV1d9IB6AFBVV95cUxOc1gzenZmMHEwTzFZWkprT2FDd0hTT29qUmZrNFdpd2pxWC1hTXlCZ0YxZkNZdm1sR3E1LTdkWm44Vy1XZHZYT3lRaG5ZY01OdkVyUzZSUEczSFNpSk00YmlCM0N3ZUVvOHNZcy1rMExWNlZlM2VPUTZSRFc5QXhvY1dIdDhBSC1FOVdQUlVTa282Um94ZWtHRGF6SHNVcm1vSGl5NENxSy1TTTdTNkRqcUNKS1QzZTZtOVJtZ24xSDBEUFlibnY4WWtQN0d2aDNpZUJ5TDFpMVBrRHFOZTdPOXE0U1pITlpo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYW9TZEpwLW1mVXFiU2xTQ202YWlDdXRJTzZGdTBNbExhTVk3dFFWRU1MeDFOZHRuZkd1N0dmQ2o2MkU4MmwydjNMektWZHBUSGxhZlVZcnZFRlpERXF0M3U5VHBnZHZONWlzb1MxQlVZc1FGUEhjV292Mkw4dXZtR1JDRHVZU1ZTY09pQTdiY2REeF9OYV9qQldLNjl1SXVN?oc=5</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Justiça da Bahia suspende venda bilionária de mina de ouro entre canadenses e chineses - BPMoney</t>
+          <t>JUSTIÇA DA BAHIA SUSPENDE VENDA BILIONÁRIA DE MINA DE OURO - bahiaeconomica.com.br</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -8926,19 +8926,19 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOV0F3R0dXNDk1eVUxZDJ3SF9QQUE0anFSeEkxOEp1a0dfMXRGZ2lRNTgwbDJsSlhJcjljMVJXS3ZxRDFEaUFUWFpYdmFXTE51YllrZDZSY2JMaGRWTTM2eFRxamhkd0hRbUFCVXY1LWpKbnJzXzNtN3JOMHB3dGdZU1Jicl9mTFdVN242eFl1OS1MLVVvdGtyN0tqU19iSHpmdzdKeDROMVltV0tzS0RfcjhFNVVqT1df?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNVGFROXRCUlk3alljZnJUbDU2VnJqS1Y2ZHhheEM0UUV6bERYLWtHYmV2OUpMdF9MUGtDUlljUHg3eVBnamFZUk1GUEk2NTRfOV9YOFM5QndQcm5FTDh0NVlXNGVOVjR2S0kyaEMxTjI2RnBQZWtUMzlvdGlKRUs2QU1HR1pjQmFhYi1xV2hVZUg0bVpqNE54aDE5NGdNcWtDcWYySnRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>JUSTIÇA DA BAHIA SUSPENDE VENDA BILIONÁRIA DE MINA DE OURO - - Bahia Economica</t>
+          <t>Fertilizantes puxam alta de preços de outros produtos químicos para indústria, diz IBGE - Valor Econômico</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -8948,19 +8948,19 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNVGFROXRCUlk3alljZnJUbDU2VnJqS1Y2ZHhheEM0UUV6bERYLWtHYmV2OUpMdF9MUGtDUlljUHg3eVBnamFZUk1GUEk2NTRfOV9YOFM5QndQcm5FTDh0NVlXNGVOVjR2S0kyaEMxTjI2RnBQZWtUMzlvdGlKRUs2QU1HR1pjQmFhYi1xV2hVZUg0bVpqNE54aDE5NGdNcWtDcWYySnRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWjd4MFdUanZwVU1jUGhrbTVtempwWEFlRWt3RWZNWlNyQVp2RnRNY2lNTGtYTWFNbGRibVVObUlEVGZXNnZqN1pwYnN5Ul9DSlBjSTgyYmlzV3VseFVFbjlwdjRCM0UzekVyNVF2LUY0ZEpxanE2aFdWdnBuRWJDYTJYUnJjYVFyaUo3dUFtZ0tTS3Awd3BLTjBEcVZfNFpXVlpMSTdCSnc5YW9GNjNTT1poT1RteF9NMVNZUzRzUXdsSXlGX0JYZ0o0R2RDYWZZcXVRVnk3RXV1d9IB6AFBVV95cUxOc1gzenZmMHEwTzFZWkprT2FDd0hTT29qUmZrNFdpd2pxWC1hTXlCZ0YxZkNZdm1sR3E1LTdkWm44Vy1XZHZYT3lRaG5ZY01OdkVyUzZSUEczSFNpSk00YmlCM0N3ZUVvOHNZcy1rMExWNlZlM2VPUTZSRFc5QXhvY1dIdDhBSC1FOVdQUlVTa282Um94ZWtHRGF6SHNVcm1vSGl5NENxSy1TTTdTNkRqcUNKS1QzZTZtOVJtZ24xSDBEUFlibnY4WWtQN0d2aDNpZUJ5TDFpMVBrRHFOZTdPOXE0U1pITlpo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Com a guerra no Oriente Médio, cotação da ureia sobe 10% no Brasil - CNN Brasil</t>
+          <t>Justiça da Bahia suspende venda bilionária de mina de ouro entre canadenses e chineses - BPMoney</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -8970,19 +8970,19 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYW9TZEpwLW1mVXFiU2xTQ202YWlDdXRJTzZGdTBNbExhTVk3dFFWRU1MeDFOZHRuZkd1N0dmQ2o2MkU4MmwydjNMektWZHBUSGxhZlVZcnZFRlpERXF0M3U5VHBnZHZONWlzb1MxQlVZc1FGUEhjV292Mkw4dXZtR1JDRHVZU1ZTY09pQTdiY2REeF9OYV9qQldLNjl1SXVN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOV0F3R0dXNDk1eVUxZDJ3SF9QQUE0anFSeEkxOEp1a0dfMXRGZ2lRNTgwbDJsSlhJcjljMVJXS3ZxRDFEaUFUWFpYdmFXTE51YllrZDZSY2JMaGRWTTM2eFRxamhkd0hRbUFCVXY1LWpKbnJzXzNtN3JOMHB3dGdZU1Jicl9mTFdVN242eFl1OS1MLVVvdGtyN0tqU19iSHpmdzdKeDROMVltV0tzS0RfcjhFNVVqT1df?oc=5</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Produtores de ureia do Oriente Médio seguram oferta em meio à guerra no Irã - Globo Rural</t>
+          <t>Justiça da Bahia suspende negócio bilionário de minas de ouro entre canadenses e chineses - folha.uol.com.br</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -8992,19 +8992,19 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOT0xmQU1XdUV0MFAxYW5SVnY1N2lOMDZlOFY1LWZKN09NSE9nS0EyUUVvYmZ4dERnZVI3OWlxeEt3aldwaHNaZ0VMNUtrb3dqWjZ0SEl0M2k3WnRYS055RFBmRm5HN1EtQmFoNE1uQThKcWFiM2V5end2aGtWUGJYeXdPX0VCU0prZE9KYWE3TVpFM3BnOG9MaENaOUNQc2ozVnVkWlRvV0JJTGEzdXhlUkFXMVlwMEwxampxdTlOdkNsclpGMnBJQzRnVVc2V3PSAd4BQVVfeXFMTzlHTHRVNzBueXBMWEl0a0lTM1NfN3YwTkRoM3Y0ZXR2OENJbm90ak5zQ2ZmT05rYWVOOE5mYjZJZ2hwRXJkaTVqcXNMckVwVG1rX21NTS05OFNlY0hDSE1VNUlZY1YtYl9oTFZTZm1mdDhqZkgtVXl3c2JFYjlHbm50cHNXLWhjT05XN1FpMnRidTJzQlRCOHpTbm1kYVlnSVBXU3J1dlB0TFFudzlFcjc5TGM2UF9TTlM4azUwMEFmYlNkTERadUY2b2Q1ckFWNDhacGlvWjJSZWdMM0xn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQYWNULVM2dHlzUUd3UDNyYUp6SDZrdGs4VjJSdUllMlJYQWFMdkJJblVjaUxfSGpTNXJ6S3gxOENtQTl3clNIeG56VVpVZkdWNWs5a05DWE04N3ZyZWJySzFRZEZESVhiVEcyMHZSWUVETVRaOUtnWlMwLWNjUXY0Ti11ZjF0UXJ0ODNXcG5lYldORXJuU2JQX0xaTHJBRGxKVWk5QmFwbVd2cUc5Z2wtSk5oNC1vV3F1U0U1WkJGMEhDRHNWVVpBNmltMVBzUTdnV0Rqbm8tcFTSAd4BQVVfeXFMTlE5cnFkMU1MWjZsaHVCdkxKM3JmOURJV25ZSUh3LU1xc2RsYmZhTzNOaEZjRGlBeTg5RFRndzE5X2h2cGxLb3BQYXY0aEc4b0dkbjh4VzdLbmRudXlYUEhwU1pnZVRGODRvY0ltTEsxWkE3OW15ZmZNOTZYdHRuWXN0ZzJMMnppM3h1WnBHSW5XM09QVVdBWlRBZFdzc0o3eDhvc3BUdW05VmhIRWl2RVVaUFRtRGVCWG1iSlFTTkpBTGwyS2RRc1Q4aDdjSFEwbzBsOTJTbU5lN3g3SGd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Justiça da Bahia suspende negócio bilionário de minas de ouro entre canadenses e chineses - folha.uol.com.br</t>
+          <t>Ureia dispara e mercado reduz negociações em meio à guerra do Irã - CNN Brasil</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQYWNULVM2dHlzUUd3UDNyYUp6SDZrdGs4VjJSdUllMlJYQWFMdkJJblVjaUxfSGpTNXJ6S3gxOENtQTl3clNIeG56VVpVZkdWNWs5a05DWE04N3ZyZWJySzFRZEZESVhiVEcyMHZSWUVETVRaOUtnWlMwLWNjUXY0Ti11ZjF0UXJ0ODNXcG5lYldORXJuU2JQX0xaTHJBRGxKVWk5QmFwbVd2cUc5Z2wtSk5oNC1vV3F1U0U1WkJGMEhDRHNWVVpBNmltMVBzUTdnV0Rqbm8tcFTSAd4BQVVfeXFMTlE5cnFkMU1MWjZsaHVCdkxKM3JmOURJV25ZSUh3LU1xc2RsYmZhTzNOaEZjRGlBeTg5RFRndzE5X2h2cGxLb3BQYXY0aEc4b0dkbjh4VzdLbmRudXlYUEhwU1pnZVRGODRvY0ltTEsxWkE3OW15ZmZNOTZYdHRuWXN0ZzJMMnppM3h1WnBHSW5XM09QVVdBWlRBZFdzc0o3eDhvc3BUdW05VmhIRWl2RVVaUFRtRGVCWG1iSlFTTkpBTGwyS2RRc1Q4aDdjSFEwbzBsOTJTbU5lN3g3SGd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNYi1XSk5GWVlFUFlZVzR2UXlURVpUajhfTjd5c0tBUUVqVUkxQy1OVFNfc3M3eDJWdndqSzJSZEJYRTdlTXI2ejdGbmlYQ1pGUmlkMVlJRGtIbmVZeDdNLXM2YS0xajQxc0p1b2pKYjJmT2Z4TGxBU0VoUTAxRlFuYkZNUWVGZWsybUdXLUxrQzNvcFRnZnNLQkxjQTBLTW5mMmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -9026,61 +9026,61 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Ureia dispara e mercado reduz negociações em meio à guerra do Irã - CNN Brasil</t>
+          <t>Venezuela: ataque dos EUA dificulta embarque de ureia - CNN Brasil</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>03/03/2026 05:00</t>
+          <t>27/02/2026 05:00</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNYi1XSk5GWVlFUFlZVzR2UXlURVpUajhfTjd5c0tBUUVqVUkxQy1OVFNfc3M3eDJWdndqSzJSZEJYRTdlTXI2ejdGbmlYQ1pGUmlkMVlJRGtIbmVZeDdNLXM2YS0xajQxc0p1b2pKYjJmT2Z4TGxBU0VoUTAxRlFuYkZNUWVGZWsybUdXLUxrQzNvcFRnZnNLQkxjQTBLTW5mMmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOc1QwVjNFUlRKTWc5LXFXYzh0NDl2RGtrWTEzQWpWc2E5cmZZMXJ3M3N3R0RzMnJQakRDbHVFcUVnV1hYSlJ3R1FNaEJjZFM2a2RTWWx5azVOeW5KZGo2dlNoaS1mUzJnSnJIajRBckl6TmdLX0VOSjlSMUowdjN6bndwaldrSVQtSXhnMVZPSEM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Venezuela: ataque dos EUA dificulta embarque de ureia - CNN Brasil</t>
+          <t>Água da Europa deixa o cabelo 'pior' do que no Brasil? Entenda os efeitos do calcário - G1</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>27/02/2026 05:00</t>
+          <t>26/02/2026 05:00</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOc1QwVjNFUlRKTWc5LXFXYzh0NDl2RGtrWTEzQWpWc2E5cmZZMXJ3M3N3R0RzMnJQakRDbHVFcUVnV1hYSlJ3R1FNaEJjZFM2a2RTWWx5azVOeW5KZGo2dlNoaS1mUzJnSnJIajRBckl6TmdLX0VOSjlSMUowdjN6bndwaldrSVQtSXhnMVZPSEM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNSmYwcUxQbk0yTW9FdFhMbDlPRnF0OXNTcVRQbXhIM0g5dGNzbkVGS0lMR2htNXI0dm1uQVJNaElaY2FDOVduemRVb2N5VWRPdTM3WnpISUpaSXItZ0x5N01HZ3d2WU9XVE14c0ZoaWdJVVpUX3FMX2ZXOWNEM0NpdUFFMW0tUW5rY2JpTGRVcXJuaGM3d3dEdmhNSFZmdXFrZDQ2T0ZCTTlBM2Vpd05HbUFDaFNiVzdpSXFXVDE5QndlOXNEVy1NRVk5OGg2azTSAd4BQVVfeXFMUEVCUXMxOWxPekRlX05jVFVRRG50X0lMY0E5eTR3TC1CaWVqc1JJbFZxb0JKVFRiOW1fT0Y5ZU5UWmlfX1ptRnRnTWZ0MjY2TnozVWtLYnM1WmFjdmJZRVhWV0ZSTWRGS2VENDdKUlhMTnRvQ1VqNU9SdUZMUFlOTEJKZGV0SnMtR0dZZTZzNXoxRzhveW50OGZDcy13eW9Za1Z1N1Y4YkU4cF9naGZwSWVpUkpPdERWVS1JRU9CWXVDV0JXblp5VEJIajZjMGU5NnZnVzUzYkdWNGZLcFdn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Água da Europa deixa o cabelo 'pior' do que no Brasil? Entenda os efeitos do calcário - G1</t>
+          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>26/02/2026 05:00</t>
+          <t>25/02/2026 05:00</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNSmYwcUxQbk0yTW9FdFhMbDlPRnF0OXNTcVRQbXhIM0g5dGNzbkVGS0lMR2htNXI0dm1uQVJNaElaY2FDOVduemRVb2N5VWRPdTM3WnpISUpaSXItZ0x5N01HZ3d2WU9XVE14c0ZoaWdJVVpUX3FMX2ZXOWNEM0NpdUFFMW0tUW5rY2JpTGRVcXJuaGM3d3dEdmhNSFZmdXFrZDQ2T0ZCTTlBM2Vpd05HbUFDaFNiVzdpSXFXVDE5QndlOXNEVy1NRVk5OGg2azTSAd4BQVVfeXFMUEVCUXMxOWxPekRlX05jVFVRRG50X0lMY0E5eTR3TC1CaWVqc1JJbFZxb0JKVFRiOW1fT0Y5ZU5UWmlfX1ptRnRnTWZ0MjY2TnozVWtLYnM1WmFjdmJZRVhWV0ZSTWRGS2VENDdKUlhMTnRvQ1VqNU9SdUZMUFlOTEJKZGV0SnMtR0dZZTZzNXoxRzhveW50OGZDcy13eW9Za1Z1N1Y4YkU4cF9naGZwSWVpUkpPdERWVS1JRU9CWXVDV0JXblp5VEJIajZjMGU5NnZnVzUzYkdWNGZLcFdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
         </is>
       </c>
     </row>
@@ -9092,7 +9092,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
+          <t>Mosaic confirma quarto trimestre ruim, mas vê lucro triplicar no ano com ajuda do Brasil - AgFeed</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -9102,41 +9102,41 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOUlZZR1AyRF9aRm14eldYQ3FwYXVoaTdRMHBsR0FpMmJGU1liUVRmamEtYUVIbmN1a1Vkb192b3BxclpiZkw0VzhTUWdJb01Vbm11c1NXZmtRXzdpaUVNamFkR0J3YnVpVnZ5R0pKUWltUGJhajlpMGdPak0tZGdQUUEtZ0VxTVhMTXBxcDhiWEF2Z1BIWnc1MlRpM3hyajV0VDhKZ0xUR1FFVTFxNzl3WUtoWkxfQlRyQnFZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Mosaic confirma quarto trimestre ruim, mas vê lucro triplicar no ano com ajuda do Brasil - AgFeed</t>
+          <t>Novo presidente de esquerda do Peru será julgado por corrupção - gazetadopovo.com.br</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>25/02/2026 05:00</t>
+          <t>20/02/2026 05:00</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOUlZZR1AyRF9aRm14eldYQ3FwYXVoaTdRMHBsR0FpMmJGU1liUVRmamEtYUVIbmN1a1Vkb192b3BxclpiZkw0VzhTUWdJb01Vbm11c1NXZmtRXzdpaUVNamFkR0J3YnVpVnZ5R0pKUWltUGJhajlpMGdPak0tZGdQUUEtZ0VxTVhMTXBxcDhiWEF2Z1BIWnc1MlRpM3hyajV0VDhKZ0xUR1FFVTFxNzl3WUtoWkxfQlRyQnFZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWGxsYkZLamdUbENJS0dQVjF2T18xODhVYWNfcHFNZGpJOVE1Q3BWSER5V1R0NXRvalpObHdzcmF0TEMteFJpRjNrV2gxeUVPU2NkSUpjS3Rta2xfNkxkZURnSnhOeDJvY0Q1Q0c1Z1JEZVRwc1RhS1RDX1pLUWVVZEhpSXVRQzR3X2xETHVTVEZvQnZmV3JNblBJYmVHNDgzV1J3VndMUjlPSFdnc1Y2T1RaRGU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Custos da safra 2026/27 variam em MT; algodão e soja recuam, milho sobe 7,19% - Nativa News</t>
+          <t>CRA vai analisar redução de alíquota sobre o calcário de uso agrícola - Senado</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOWnBBY2Uwc2FseU4zdDQ2aVhkdWdVNXJGRDZJR0tTZ0Y1UWZSREc2ZDVySi1rMndqSkMyWEgyVzVQTGlOSmhKTEgzWXRfNm5zd280WW5BUFhwdFNYemdvc1dqX095TG9kQ3dNSmU3VmdnNFJkMjNBeHZSZEprSzBOVHhLSWEzbDcyZUNnbnY1U0xpLVZTNVBHdEVFMDRVMVlySU1XNHJZQWdwbVJ3QkVuZ2lMWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeWVQYnFWb2NCX2FFS3ltNHh0enBBZFVrS0tCSVJJb3ZBQ1FldnRaUVNQNF91WXN1V0ZNd1JENkVjVzBmVUNwS2RDTTZ1eW53WndKTDdHVWtUUmE1UDktTUsxSjdYMzBiMzJkV3B1aWY0d2VmczFJeUl6ZlpjRXd0VlFZUTlIN2tHQnlrRXlYNzZ4Rk5ZNThGWGtaZV9BSVV5SUVFNS1yREwweS1aQVMwOS1yZm5yQThBaDNVSnZKb1VWV1dO?oc=5</t>
         </is>
       </c>
     </row>
@@ -9175,12 +9175,12 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>CRA vai analisar redução de alíquota sobre o calcário de uso agrícola - Senado</t>
+          <t>Custos da safra 2026/27 variam em MT; algodão e soja recuam, milho sobe 7,19% - nativanews.com.br</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeWVQYnFWb2NCX2FFS3ltNHh0enBBZFVrS0tCSVJJb3ZBQ1FldnRaUVNQNF91WXN1V0ZNd1JENkVjVzBmVUNwS2RDTTZ1eW53WndKTDdHVWtUUmE1UDktTUsxSjdYMzBiMzJkV3B1aWY0d2VmczFJeUl6ZlpjRXd0VlFZUTlIN2tHQnlrRXlYNzZ4Rk5ZNThGWGtaZV9BSVV5SUVFNS1yREwweS1aQVMwOS1yZm5yQThBaDNVSnZKb1VWV1dO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOWnBBY2Uwc2FseU4zdDQ2aVhkdWdVNXJGRDZJR0tTZ0Y1UWZSREc2ZDVySi1rMndqSkMyWEgyVzVQTGlOSmhKTEgzWXRfNm5zd280WW5BUFhwdFNYemdvc1dqX095TG9kQ3dNSmU3VmdnNFJkMjNBeHZSZEprSzBOVHhLSWEzbDcyZUNnbnY1U0xpLVZTNVBHdEVFMDRVMVlySU1XNHJZQWdwbVJ3QkVuZ2lMWQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9202,95 +9202,95 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Novo presidente de esquerda do Peru será julgado por corrupção - Gazeta do Povo</t>
+          <t>Quem é José Balcázar, eleito novo presidente do Peru após ‘impeachment express’ de antecessor - Estadão</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>20/02/2026 05:00</t>
+          <t>19/02/2026 05:00</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWGxsYkZLamdUbENJS0dQVjF2T18xODhVYWNfcHFNZGpJOVE1Q3BWSER5V1R0NXRvalpObHdzcmF0TEMteFJpRjNrV2gxeUVPU2NkSUpjS3Rta2xfNkxkZURnSnhOeDJvY0Q1Q0c1Z1JEZVRwc1RhS1RDX1pLUWVVZEhpSXVRQzR3X2xETHVTVEZvQnZmV3JNblBJYmVHNDgzV1J3VndMUjlPSFdnc1Y2T1RaRGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNYVhsZm1rdjFZbzloczVNbENDbEFwTWxCNjZFWjlmQ3hHQk1TaWRNN0pEcmpXZ1RxY2NUMjBCU1JqQTJhWGdfUDJrLUZ4Nm9KZ1drbklMdWFJNXgyWkZFaE1faFFtbng0MDRZbWFsV1I4d3JSMUs3b1hKWHlLOTUxRUtnOHA2b3o0Yk13UlZjYzZYbDZmM2pmdTJpcXlBbnhnV29tdWFTVjdnZE9femFvSm9CbDl3Yjg2dVFrWXZlTkRROW1xWW9JSU9Cay1wVTJXckHSAdcBQVVfeXFMT2lHdENCUHVjQVlBUDlMQkVkNWNGVGhBUXUtQVJmQUJnNnhoWndMQlZTUGxjVHdYTG1pUHl3V1FkbUlLZmlYTUxKckxmWFVVX2NIRXJfVTMyMk1OZkRwalM2TkJDdzFpRXpIeXRfcDZ6ZDJhUHJRblZuMFA1VFFzcmNsMXpud1lZVGJMZGNQS2l1TmZSNThjTTVWVkVCRUdCSnc1bTh1Ujlua19uUTF1ZTUyZ3o4QXFJM2pJV29UcEdQZVNXY09QZmRQRDg1aXk1RGFqRURDWU0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>cal agricola</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Quem é José Balcázar, eleito novo presidente do Peru após ‘impeachment express’ de antecessor - Estadão</t>
+          <t>Agricultura orgânica: aprenda preparo de calda para controle de pragas - ParaibaOnline</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>19/02/2026 05:00</t>
+          <t>18/02/2026 05:00</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNYVhsZm1rdjFZbzloczVNbENDbEFwTWxCNjZFWjlmQ3hHQk1TaWRNN0pEcmpXZ1RxY2NUMjBCU1JqQTJhWGdfUDJrLUZ4Nm9KZ1drbklMdWFJNXgyWkZFaE1faFFtbng0MDRZbWFsV1I4d3JSMUs3b1hKWHlLOTUxRUtnOHA2b3o0Yk13UlZjYzZYbDZmM2pmdTJpcXlBbnhnV29tdWFTVjdnZE9femFvSm9CbDl3Yjg2dVFrWXZlTkRROW1xWW9JSU9Cay1wVTJXckHSAdcBQVVfeXFMT2lHdENCUHVjQVlBUDlMQkVkNWNGVGhBUXUtQVJmQUJnNnhoWndMQlZTUGxjVHdYTG1pUHl3V1FkbUlLZmlYTUxKckxmWFVVX2NIRXJfVTMyMk1OZkRwalM2TkJDdzFpRXpIeXRfcDZ6ZDJhUHJRblZuMFA1VFFzcmNsMXpud1lZVGJMZGNQS2l1TmZSNThjTTVWVkVCRUdCSnc1bTh1Ujlua19uUTF1ZTUyZ3o4QXFJM2pJV29UcEdQZVNXY09QZmRQRDg1aXk1RGFqRURDWU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNS3pzSjFUQ0VKY2VDNjJZVkVHaWZKT2xjclQ0Q0QzaE1ZclpEX1liX1E1Y19iMFNtWTR0ZlBtQnBPSlZjX2lxQ3dPM0FRM3BPOGg2dmdMWUZ4Vmw5ZEtZeG9rMXNoV2JKWDB3TTBPd3poaGJMXzBBUm91N2I4dWcxRmtDTWgwLTBINXQ3MTQ4UHdXbGFWUU9PTHh4Zk01OWVyNU9KMzV1SGRrMGw4ZzZhMkFRcnNEdDJ5N0tZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>cal agricola</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Agricultura orgânica: aprenda preparo de calda para controle de pragas - ParaibaOnline</t>
+          <t>Grolime brings high-performance benefits for Scottish soils</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>18/02/2026 05:00</t>
+          <t>14/02/2026 06:00</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNS3pzSjFUQ0VKY2VDNjJZVkVHaWZKT2xjclQ0Q0QzaE1ZclpEX1liX1E1Y19iMFNtWTR0ZlBtQnBPSlZjX2lxQ3dPM0FRM3BPOGg2dmdMWUZ4Vmw5ZEtZeG9rMXNoV2JKWDB3TTBPd3poaGJMXzBBUm91N2I4dWcxRmtDTWgwLTBINXQ3MTQ4UHdXbGFWUU9PTHh4Zk01OWVyNU9KMzV1SGRrMGw4ZzZhMkFRcnNEdDJ5N0tZ?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a70b554b1fb44d3bd04c691a5851b8e&amp;url=https%3a%2f%2fwww.thescottishfarmer.co.uk%2fnews%2f25845962.grolime-brings-high-performance-benefits-scottish-soils%2f&amp;c=18200927900201231641&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Grolime brings high-performance benefits for Scottish soils</t>
+          <t>Programa Terra Boa subsidia aquisição de calcário, essencial à melhoria da produção e produtividade das lavouras - Prefeitura de Lages</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>14/02/2026 06:00</t>
+          <t>13/02/2026 05:00</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a708df9e25249dbab0f0f4f5ec02cba&amp;url=https%3a%2f%2fwww.thescottishfarmer.co.uk%2fnews%2f25845962.grolime-brings-high-performance-benefits-scottish-soils%2f&amp;c=18200927900201231641&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPZ3RHQm91RjZUTHh5WEhFQUI0d2RpaEJYR0lYM1liUVJPMElqeUg4U3dQY1FjdkJMUU5wS1FOS3RaMGlxUms2MUpMSFZFTVMyOGRrQU9JcERnU2VVNnNJbHljUUhJdjFpVDZlTWl5Vno5clVUR3YxcmZ5VDZiLXJYa0xqc2dJVWttd2xOZFdCN21EdlhiT25EY0ZOclVndGxXQU45UzFFR1VvdjhUZ3ZLV1c4ZkpITndFMk1GSmZiMGpBVVVQOWk4MTBTOUplLWVtUU5qaDFuUVZibURHNjEyQmE3a0FIZ0ttRFU4X1FrME9qdHli?oc=5</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Programa Terra Boa subsidia aquisição de calcário, essencial à melhoria da produção e produtividade das lavouras - Prefeitura de Lages</t>
+          <t>Como monitorar o enxofre em lavoura de soja no Cerrado - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -9300,29 +9300,29 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPZ3RHQm91RjZUTHh5WEhFQUI0d2RpaEJYR0lYM1liUVJPMElqeUg4U3dQY1FjdkJMUU5wS1FOS3RaMGlxUms2MUpMSFZFTVMyOGRrQU9JcERnU2VVNnNJbHljUUhJdjFpVDZlTWl5Vno5clVUR3YxcmZ5VDZiLXJYa0xqc2dJVWttd2xOZFdCN21EdlhiT25EY0ZOclVndGxXQU45UzFFR1VvdjhUZ3ZLV1c4ZkpITndFMk1GSmZiMGpBVVVQOWk4MTBTOUplLWVtUU5qaDFuUVZibURHNjEyQmE3a0FIZ0ttRFU4X1FrME9qdHli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNODFZUlpibktCelpQVkdtOWpPRS1sWGtCZERVZlhpcVZ1MFF2UF83RTQ4bWkyV1ZKOS1FRWhfU1FZTHVEb0NHVWNaUUNzZVh0Z2wtTm9WZzVrcTBRX1gtUHFLNFpsM0g1Q3dfWHYwSlltQkM5V3lSWHF6Yk9Mb2Z4V21Rcl94aGpFMlVtNkhINmpEVE5JTklZMm9MRDAyaG5GN2dDRFU4NTdWaVdzbzRVN19fTUs1aU5tWThFdW1yVdIBxAFBVV95cUxNQUREVU1ScmxfQ1EzbGoxNUNiMzJ6RENlNndmYV9QQ2NFUlRDVG1YVi1TTkVYMkhYd1ZMQmFwLW1ia282WmQwTUdjMTlXQ2E4QTFJT3Myb1gwdVdQY3R4Z3VzaS1HUWgwWmcwRTFxTm5PN2szMUFWOFhkWkVuR2dWWG1haG1QMDM5R2hrUndjbXNKWllkQWZuN3hmcWk4VGthU05TT2NBRTRxVXh4bUdKUW9mT0E4UXpLTjVBY1dkQ1dQTW5h?oc=5</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Como monitorar o enxofre em lavoura de soja no Cerrado - Notícias Agrícolas</t>
+          <t>Empresas do Araripe começam a escoar gipsita e calcário pela Transnordestina - Movimento Econômico</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>13/02/2026 05:00</t>
+          <t>12/02/2026 05:00</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNODFZUlpibktCelpQVkdtOWpPRS1sWGtCZERVZlhpcVZ1MFF2UF83RTQ4bWkyV1ZKOS1FRWhfU1FZTHVEb0NHVWNaUUNzZVh0Z2wtTm9WZzVrcTBRX1gtUHFLNFpsM0g1Q3dfWHYwSlltQkM5V3lSWHF6Yk9Mb2Z4V21Rcl94aGpFMlVtNkhINmpEVE5JTklZMm9MRDAyaG5GN2dDRFU4NTdWaVdzbzRVN19fTUs1aU5tWThFdW1yVdIBxAFBVV95cUxNQUREVU1ScmxfQ1EzbGoxNUNiMzJ6RENlNndmYV9QQ2NFUlRDVG1YVi1TTkVYMkhYd1ZMQmFwLW1ia282WmQwTUdjMTlXQ2E4QTFJT3Myb1gwdVdQY3R4Z3VzaS1HUWgwWmcwRTFxTm5PN2szMUFWOFhkWkVuR2dWWG1haG1QMDM5R2hrUndjbXNKWllkQWZuN3hmcWk4VGthU05TT2NBRTRxVXh4bUdKUW9mT0E4UXpLTjVBY1dkQ1dQTW5h?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQX2Zpa2cxcGRrbUREWl9iX0oxUTdIYUZWWXVmNEdHaV9oLS1pcWdLWDhLYW4yMWw3NnNEQlVsU2NQUEdVRlBMWEFuVUtDS0tteEpSTmNmRWMxemZfb1RKVUtEVXptSHV1VkVuMWdEQkdPellZb2tNMEVkQnE5Uy1fdWV2RGhlZ2RKRmxWODhhSWJ6ZFIzNjZqcFkweE1SM0pJOXF0UmxPUTNSZ2ppTndZNHdweGFjMm9wRm1xZXQ2OEZxQXFJdzB2VFVzTTVUak1KU2pIY3NDd0RlR3NEWDczcmhQTVdOZ2c?oc=5</t>
         </is>
       </c>
     </row>
@@ -9334,17 +9334,17 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Empresas do Araripe começam a escoar gipsita e calcário pela Transnordestina - Movimento Econômico</t>
+          <t>Marco Histórico: Victor Coelho celebra primeira operação de transporte de calcário pela Transnordestina em Ouricuri - FalaPE</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>12/02/2026 05:00</t>
+          <t>11/02/2026 05:00</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQX2Zpa2cxcGRrbUREWl9iX0oxUTdIYUZWWXVmNEdHaV9oLS1pcWdLWDhLYW4yMWw3NnNEQlVsU2NQUEdVRlBMWEFuVUtDS0tteEpSTmNmRWMxemZfb1RKVUtEVXptSHV1VkVuMWdEQkdPellZb2tNMEVkQnE5Uy1fdWV2RGhlZ2RKRmxWODhhSWJ6ZFIzNjZqcFkweE1SM0pJOXF0UmxPUTNSZ2ppTndZNHdweGFjMm9wRm1xZXQ2OEZxQXFJdzB2VFVzTTVUak1KU2pIY3NDd0RlR3NEWDczcmhQTVdOZ2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPaU5meFFvcXlxY2VjZ0xRbkt0ajI1cE44dERBYk9LWWRxMW8tLUhSUGxZenU5VWZjYVBQSWprTHhLX1VON2o1RWhVTm0tM3cwd0RJN19GbUs3UlNaOWI0VWhTYjg1Wnc2aFNyd29hSnBxQUJTdHNuUWhLRWN0RjdtOV92SDdBckNoN3BCeFNPRVA4WWtoRjNnd1NVdnRMWUV5MHVTU2lTdVRZVW5lZUlhUm9teExyX1dWSmpnUlJTQ2RHaW42d2VQemNYaGVEZ1k?oc=5</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Marco Histórico: Victor Coelho celebra primeira operação de transporte de calcário pela Transnordestina em Ouricuri - FalaPE</t>
+          <t>Tecnologia transforma gases de navios em calcário e corta até 95% do CO₂ - Fast Company Brasil</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -9366,107 +9366,107 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPaU5meFFvcXlxY2VjZ0xRbkt0ajI1cE44dERBYk9LWWRxMW8tLUhSUGxZenU5VWZjYVBQSWprTHhLX1VON2o1RWhVTm0tM3cwd0RJN19GbUs3UlNaOWI0VWhTYjg1Wnc2aFNyd29hSnBxQUJTdHNuUWhLRWN0RjdtOV92SDdBckNoN3BCeFNPRVA4WWtoRjNnd1NVdnRMWUV5MHVTU2lTdVRZVW5lZUlhUm9teExyX1dWSmpnUlJTQ2RHaW42d2VQemNYaGVEZ1k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPM0xiM1JFaEhZME4xSTFHTlhycmNXem9RdjI1Zm8wYmY1cS04VHVWUURZWlBRRzdvV2VEYmFsaWxPT3g0VmVYX1k5eXFWUW5KM0ltU0J1amh3UHhqU3I4RHdZbzNsZXJmQk1hV1pFUnZOZnVlazFoN1cwdFhtOS1vWU9BdXVBT0tZSkFVc2kxMnhWd0tEMGFYcExsbnI1dzBqMVBxNFFYeklQV0kxUmJDcVpWNzRWMUdPWEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Tecnologia transforma gases de navios em calcário e corta até 95% do CO₂ - Fast Company Brasil</t>
+          <t>Geopolítica: em Foz, pesquisas abrem diálogo sobre multilateralismo e integração latino-americana - h2foz.com.br</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>11/02/2026 05:00</t>
+          <t>08/02/2026 05:00</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPM0xiM1JFaEhZME4xSTFHTlhycmNXem9RdjI1Zm8wYmY1cS04VHVWUURZWlBRRzdvV2VEYmFsaWxPT3g0VmVYX1k5eXFWUW5KM0ltU0J1amh3UHhqU3I4RHdZbzNsZXJmQk1hV1pFUnZOZnVlazFoN1cwdFhtOS1vWU9BdXVBT0tZSkFVc2kxMnhWd0tEMGFYcExsbnI1dzBqMVBxNFFYeklQV0kxUmJDcVpWNzRWMUdPWEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPcUYxX0FCUkdYUGJ6Z2N1Rm5oWWRBNkxyQXhDZTZEaXZ4cDdQSDZxNGp3Tzdnc29JXzg0Unl4Qk1fTEpLS1RyLUdFNHF5WElMWDRtMFJDaWZpRUpJS1laSEd6UTVmbVNBSldwYUstZDdfSFAyT2thT0QxZC1RRW1YMnZoMkFyMzBxTTNpUlo3NXFPTlRzNVVHNzFVVmhpZDFCU2FabFFKbGt5WlA5STVJa2Q3QUZ5WWE2SV9odnBuMFdhOWFCUWlDVmN3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Geopolítica: em Foz, pesquisas abrem diálogo sobre multilateralismo e integração latino-americana - h2foz.com.br</t>
+          <t>Correção do solo 2: Formas de aplicação do calcário e os resultados da pesquisa - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>08/02/2026 05:00</t>
+          <t>06/02/2026 05:00</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPcUYxX0FCUkdYUGJ6Z2N1Rm5oWWRBNkxyQXhDZTZEaXZ4cDdQSDZxNGp3Tzdnc29JXzg0Unl4Qk1fTEpLS1RyLUdFNHF5WElMWDRtMFJDaWZpRUpJS1laSEd6UTVmbVNBSldwYUstZDdfSFAyT2thT0QxZC1RRW1YMnZoMkFyMzBxTTNpUlo3NXFPTlRzNVVHNzFVVmhpZDFCU2FabFFKbGt5WlA5STVJa2Q3QUZ5WWE2SV9odnBuMFdhOWFCUWlDVmN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZ0hBMUJwVjlRWVlXcXo3MHI1M0h3bklvSkk3enp1eTBiM1Y1cjNWMjF3TjBPTFRKQkhPMjUxYWxjREJNRU1vaHVlN0xfcTBpSTdoWlBDZk9UdWV2RDU3OGNHMnppV0U4R0w0VUl4M0ZwT0ZCSzZRVkttZHNFV2t5YWU5N0o1OXJxdXBSQU5vVXlHVW5jaEdxYlJUUnMzZ0FNTzVXbWRyNHJScEg4blBPLW1wcWxVNXpHaTBxQkZkTDhqRnptNVHSAcsBQVVfeXFMUEk4c0ZPT3pFdGZETWNxWG5RWEdJSWI2WnllSnd6SHM1WS1nVkM2NEVIR29kYlhobi1Vc2ZxenpYR29VYkdyV0FzTEJUMHpuYUVNTGpWNjVpNkl5M19VZ2hMc2s3aU9OZkNqTElpV2xfV3YzaGZEMFpMVEFSSXhaQkR6SXMzTVRON0FTS05vMXdLSzZLSTJCZVR2ZzlTcEtDYjhVM1JYNjBIV2syNHU1d2ZBbDg4TkdQWHJVSVVuNWpXMDBMb3hqekZudVk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Correção do solo 2: Formas de aplicação do calcário e os resultados da pesquisa - Notícias Agrícolas</t>
+          <t>Parceria entre Governo de Minas e Harsco completa dois anos e beneficia mais de 2 mil agricultores familiares</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>06/02/2026 05:00</t>
+          <t>04/02/2026 08:38</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZ0hBMUJwVjlRWVlXcXo3MHI1M0h3bklvSkk3enp1eTBiM1Y1cjNWMjF3TjBPTFRKQkhPMjUxYWxjREJNRU1vaHVlN0xfcTBpSTdoWlBDZk9UdWV2RDU3OGNHMnppV0U4R0w0VUl4M0ZwT0ZCSzZRVkttZHNFV2t5YWU5N0o1OXJxdXBSQU5vVXlHVW5jaEdxYlJUUnMzZ0FNTzVXbWRyNHJScEg4blBPLW1wcWxVNXpHaTBxQkZkTDhqRnptNVHSAcsBQVVfeXFMUEk4c0ZPT3pFdGZETWNxWG5RWEdJSWI2WnllSnd6SHM1WS1nVkM2NEVIR29kYlhobi1Vc2ZxenpYR29VYkdyV0FzTEJUMHpuYUVNTGpWNjVpNkl5M19VZ2hMc2s3aU9OZkNqTElpV2xfV3YzaGZEMFpMVEFSSXhaQkR6SXMzTVRON0FTS05vMXdLSzZLSTJCZVR2ZzlTcEtDYjhVM1JYNjBIV2syNHU1d2ZBbDg4TkdQWHJVSVVuNWpXMDBMb3hqekZudVk?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a70b55360ee4ce0b0aa0ac3f6869496&amp;url=https%3a%2f%2fdiariodocomercio.com.br%2fagronegocio%2fparceria-entre-governo-minas-harsco-completa-dois-anos%2f&amp;c=8635377947739043430&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Parceria entre Governo de Minas e Harsco completa dois anos e beneficia mais de 2 mil agricultores familiares</t>
+          <t>Correção do solo: O uso correto do calcário em solos de cerrado - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>04/02/2026 08:38</t>
+          <t>04/02/2026 05:00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a708df749304381a4ad0ae0406775c0&amp;url=https%3a%2f%2fdiariodocomercio.com.br%2fagronegocio%2fparceria-entre-governo-minas-harsco-completa-dois-anos%2f&amp;c=8635377947739043430&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPdl9xRy1tdHdrNnRjTlctbmpsWDctNEFrZ2FyYUtSVjBSWGlZaUc2cktLWlNJWXJpS2VrYVBtUzhMc3pOUHBERFRvU3RVWXhQbEN0SU1DR2MweTNjbFp5X0tUQXNHdFliLWhPM1UyX0UyaGFnb2F0UGV5VGVSbTA0WVdzNjJ6cHM3SFNPN3NDWWhTY3FlMFhFTFBNZi1Pd3hlUDVXa3U5bm5kbllkc2xTNkQ2X3NhYzFpcFA3X2pBYlBWZzVvTldwblZEV1rSAdIBQVVfeXFMTldVV296U1h2TjROejRMUkVpaWs2eWlKVDJzVjg4eDF4anBCamt3T1FXdW9rOGRsbUg2bEJNZUlBcEVycHdFZHB0OGNGdW10TW1FWEZ2WlJlVHNvbFp5S29QbVZfSGl6SDhQWFk4UF9IM3pXaEVja2NaTi1XdjdVN1VVX3FsYjZMNld4RE5tOFVlTmMyNGdxeFl6RElYQ3ZhcEZxVERKM0FtQkZ5a1NLLUduS18zYkNTQWlvQ3NpdEVFMlhON19iYUJwejA5M0lRZzZ3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Correção do solo: O uso correto do calcário em solos de cerrado - Notícias Agrícolas</t>
+          <t>Estatal da Bahia tenta anular negócio bilionário de ouro entre canadenses e chineses - folha.uol.com.br</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPdl9xRy1tdHdrNnRjTlctbmpsWDctNEFrZ2FyYUtSVjBSWGlZaUc2cktLWlNJWXJpS2VrYVBtUzhMc3pOUHBERFRvU3RVWXhQbEN0SU1DR2MweTNjbFp5X0tUQXNHdFliLWhPM1UyX0UyaGFnb2F0UGV5VGVSbTA0WVdzNjJ6cHM3SFNPN3NDWWhTY3FlMFhFTFBNZi1Pd3hlUDVXa3U5bm5kbllkc2xTNkQ2X3NhYzFpcFA3X2pBYlBWZzVvTldwblZEV1rSAdIBQVVfeXFMTldVV296U1h2TjROejRMUkVpaWs2eWlKVDJzVjg4eDF4anBCamt3T1FXdW9rOGRsbUg2bEJNZUlBcEVycHdFZHB0OGNGdW10TW1FWEZ2WlJlVHNvbFp5S29QbVZfSGl6SDhQWFk4UF9IM3pXaEVja2NaTi1XdjdVN1VVX3FsYjZMNld4RE5tOFVlTmMyNGdxeFl6RElYQ3ZhcEZxVERKM0FtQkZ5a1NLLUduS18zYkNTQWlvQ3NpdEVFMlhON19iYUJwejA5M0lRZzZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPVUlXUktSbEdjOC1NTzE1d0ZIVmNad0RVMDE5VlpBWGh0X0VkZkZqSTFuR2EwNVBpNHVnOEtuUWdaTF9DeGRIV0FYNW01M3E5c1ViZVgtT1h1VnVhVFRoZnVRNDNNbm9fVG5FMmVGQTZiU2w4UmlOTXVwRnZIaWhzNjNXTXpEcHRRMGZ3ZmYxazByT01MZXJiRjhLajh6X1VEdjhILUtaZllZa3BRZUZVcGJXTmFCRjF4bDRWWE5FeUQxYlNabF9mMnlvMER1akRaclHSAdcBQVVfeXFMTmFLYWxidHM1czVENlhQTzdaSlZmSUZmT3M4LXZtV2k3ZXBranlIb2F3clBQQ3lIaWpIVC1mNXoxZUYzaVc1cDFLbUR2R0VydTNsZUktcWVKRkZqeGp1TEhKUTN1Z3JpeG9wZjItdzJyanlUTW14WE1yVnE5VmNUa3FVWXNudnNzeEdyUEIxbklVSldyRzVoR2tMcTVIQXEyTm41ZVRMOUpsVmJfdVBLc1RscS1zY1JPYW8tTUlmODdRbm8xMmF5NWV3clZqdURDTTMzVURncGM?oc=5</t>
         </is>
       </c>
     </row>
@@ -9505,22 +9505,22 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Estatal da Bahia tenta anular negócio bilionário de ouro entre canadenses e chineses - folha.uol.com.br</t>
+          <t>CRA deve votar redução de alíquota sobre calcário nesta quarta - Senado</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>04/02/2026 05:00</t>
+          <t>03/02/2026 05:00</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPVUlXUktSbEdjOC1NTzE1d0ZIVmNad0RVMDE5VlpBWGh0X0VkZkZqSTFuR2EwNVBpNHVnOEtuUWdaTF9DeGRIV0FYNW01M3E5c1ViZVgtT1h1VnVhVFRoZnVRNDNNbm9fVG5FMmVGQTZiU2w4UmlOTXVwRnZIaWhzNjNXTXpEcHRRMGZ3ZmYxazByT01MZXJiRjhLajh6X1VEdjhILUtaZllZa3BRZUZVcGJXTmFCRjF4bDRWWE5FeUQxYlNabF9mMnlvMER1akRaclHSAdcBQVVfeXFMTmFLYWxidHM1czVENlhQTzdaSlZmSUZmT3M4LXZtV2k3ZXBranlIb2F3clBQQ3lIaWpIVC1mNXoxZUYzaVc1cDFLbUR2R0VydTNsZUktcWVKRkZqeGp1TEhKUTN1Z3JpeG9wZjItdzJyanlUTW14WE1yVnE5VmNUa3FVWXNudnNzeEdyUEIxbklVSldyRzVoR2tMcTVIQXEyTm41ZVRMOUpsVmJfdVBLc1RscS1zY1JPYW8tTUlmODdRbm8xMmF5NWV3clZqdURDTTMzVURncGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeTNjVGxONFNqaV92QmFjbHM5a2VHMHgwNE9sNkV1MzNBNnowdjFiNjhjdm9oeFFsNWdxX3p0Y0xRMDRJMmNRdDV6eEtZOFNwU3V2RURWc2VsMTlVMEZLcXN1aGJ6ZlNMa0hxTDF3ZDhlMTdMSXNCTmw2bGNtZVBEakhuY0NBZjVrUEdUNXFfUk1TZjM1U2hERkl1Y1BaSlZ0QmJVdnY1V1pVSXd2NGFSbnR1ZkdaUDBWREtN?oc=5</t>
         </is>
       </c>
     </row>
@@ -9549,22 +9549,22 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>CRA deve votar redução de alíquota sobre calcário nesta quarta - Senado</t>
+          <t>China vai investir quase US$ 1 bilhão para assumir minas de ouro no Brasil, controlar milhões de onças do metal e reforçar sua posição global no setor de mineração estratégica - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>03/02/2026 05:00</t>
+          <t>02/02/2026 05:00</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeTNjVGxONFNqaV92QmFjbHM5a2VHMHgwNE9sNkV1MzNBNnowdjFiNjhjdm9oeFFsNWdxX3p0Y0xRMDRJMmNRdDV6eEtZOFNwU3V2RURWc2VsMTlVMEZLcXN1aGJ6ZlNMa0hxTDF3ZDhlMTdMSXNCTmw2bGNtZVBEakhuY0NBZjVrUEdUNXFfUk1TZjM1U2hERkl1Y1BaSlZ0QmJVdnY1V1pVSXd2NGFSbnR1ZkdaUDBWREtN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQMkQtMmxTWjZWVEdwcmZYell3OU1VRTl6Z1BTS012WVV3UndnYnZMZ0dLR3pIeElIUndoTlhXLTlQUTVIQnVzcTc4UTgtcm1HSmtjWnhOVkxJdktFSS15dm9jSXpJR19zd1RhcTVzV2ljV21mMnYyMzNoWngyTkt2RmRKN1doQmFEZDAya3BYQ0VOYkN3d01UZkZET3dKWFFSNTdZMEI0bG80Z0pLMXpyWWtQR0ktUG5ab2pISlZVWFhGWVA0cV84RUR6R051Uno1WVd2RVdmQmdiSEhpZ25HQmJjMA?oc=5</t>
         </is>
       </c>
     </row>
@@ -9576,39 +9576,39 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>China vai investir quase US$ 1 bilhão para assumir minas de ouro no Brasil, controlar milhões de onças do metal e reforçar sua posição global no setor de mineração estratégica - CPG Click Petróleo e Gás</t>
+          <t>China vai gastar 900 milhões de dólares para levar o ouro do Brasil - Diário do Comércio</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>02/02/2026 05:00</t>
+          <t>01/02/2026 05:00</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQMkQtMmxTWjZWVEdwcmZYell3OU1VRTl6Z1BTS012WVV3UndnYnZMZ0dLR3pIeElIUndoTlhXLTlQUTVIQnVzcTc4UTgtcm1HSmtjWnhOVkxJdktFSS15dm9jSXpJR19zd1RhcTVzV2ljV21mMnYyMzNoWngyTkt2RmRKN1doQmFEZDAya3BYQ0VOYkN3d01UZkZET3dKWFFSNTdZMEI0bG80Z0pLMXpyWWtQR0ktUG5ab2pISlZVWFhGWVA0cV84RUR6R051Uno1WVd2RVdmQmdiSEhpZ25HQmJjMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQWDRpY3Jud3ZwV1RMTVBJQVFMWGt6RDVuNWZ1WTEwX1l2MTA2cnM3VGNzT3dId3FTNm9VdXdiQjNLWnZGbjhONDRBRFMwU2VtVDBsRmlLdGE0c3Rrek5YU3BYR3ViTGt0OWdVV1Z2S1kwLVJXVEJHUDh2dUdjd1dJeGthc1NabXJkcVlabWZaWU1NVm1jeGxLWnQ2WUFnaHBFTUtEc0F5Yw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>China vai gastar 900 milhões de dólares para levar o ouro do Brasil - diariodocomercio.com.br</t>
+          <t>Programa Solo Fértil garante transporte gratuito de calcário a agricultores familiares em Sidrolândia - Prefeitura de Sidrolândia</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>01/02/2026 05:00</t>
+          <t>30/01/2026 05:00</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQWDRpY3Jud3ZwV1RMTVBJQVFMWGt6RDVuNWZ1WTEwX1l2MTA2cnM3VGNzT3dId3FTNm9VdXdiQjNLWnZGbjhONDRBRFMwU2VtVDBsRmlLdGE0c3Rrek5YU3BYR3ViTGt0OWdVV1Z2S1kwLVJXVEJHUDh2dUdjd1dJeGthc1NabXJkcVlabWZaWU1NVm1jeGxLWnQ2WUFnaHBFTUtEc0F5Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxPNDhDY3Y4R201VG42YXpqT2loUGJSYzZURWFwTVhlTXB6TUtIZ3ZtSEYxV25LdEU5OXVIM1B2RGp6MUIyM01VUmdKQThSVjQzTFpPR29wU0xGemZheGw3Yk92U185ckkxT2Fob2tPT01UWGU4MFRlRTRnRVViTUZTSzBNYWZQNHZtc0toZE1qRGdtcEVFQmJVVWVSXzE0U3M3ZDFxNWVHc1I2V3hKOFJxRlBxWDFtdEt6N2ZkdEJTekJKOHMwS0N0QmhQMmFROTY2ajgtSEhRM25GWERWdE1BbDZIaW9hSXp3NURDeFdBNXVvaEVCb2ZFMHRPVlJmTHQyaHZwa0VmNDZ0SGdwUW1Z?oc=5</t>
         </is>
       </c>
     </row>
@@ -9659,22 +9659,22 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Programa Solo Fértil garante transporte gratuito de calcário a agricultores familiares em Sidrolândia - Prefeitura de Sidrolândia</t>
+          <t>Ricaços do ouro vendem minas no Brasil por R$ 5,36 bilhões - A Crítica</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>30/01/2026 05:00</t>
+          <t>28/01/2026 05:00</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxPNDhDY3Y4R201VG42YXpqT2loUGJSYzZURWFwTVhlTXB6TUtIZ3ZtSEYxV25LdEU5OXVIM1B2RGp6MUIyM01VUmdKQThSVjQzTFpPR29wU0xGemZheGw3Yk92U185ckkxT2Fob2tPT01UWGU4MFRlRTRnRVViTUZTSzBNYWZQNHZtc0toZE1qRGdtcEVFQmJVVWVSXzE0U3M3ZDFxNWVHc1I2V3hKOFJxRlBxWDFtdEt6N2ZkdEJTekJKOHMwS0N0QmhQMmFROTY2ajgtSEhRM25GWERWdE1BbDZIaW9hSXp3NURDeFdBNXVvaEVCb2ZFMHRPVlJmTHQyaHZwa0VmNDZ0SGdwUW1Z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPMmFvSnQ5bmpvS0ctdmh4VVZSaEFBb1ZfdGZ0TmxvX3htb0dMZTItdmVNVl9VX0tZRTJVb1RLVV9oQjNWZUg1cXBWTmxEWE1zamNwbF9OeWJFeHVLaTdWdnByNUc0QVpray1TUTFXWjdFamFYZzg0MGZnMXA1Qk1ublVQUUtWT2dzZHBHamsxYm9TQ2M?oc=5</t>
         </is>
       </c>
     </row>
@@ -9686,17 +9686,17 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Ricaços do ouro vendem minas no Brasil por R$ 5,36 bilhões - A Crítica</t>
+          <t>Negócio bilionário faz a China entrar de vez no ouro brasileiro - CartaCapital</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>28/01/2026 05:00</t>
+          <t>27/01/2026 05:00</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPMmFvSnQ5bmpvS0ctdmh4VVZSaEFBb1ZfdGZ0TmxvX3htb0dMZTItdmVNVl9VX0tZRTJVb1RLVV9oQjNWZUg1cXBWTmxEWE1zamNwbF9OeWJFeHVLaTdWdnByNUc0QVpray1TUTFXWjdFamFYZzg0MGZnMXA1Qk1ublVQUUtWT2dzZHBHamsxYm9TQ2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNFdxT2RJVUZPMmhHNmdJMU12a2VxWDlSYXNjOWxJLVNCRUFpeS1zd3VGd2ZtVmxqdDdudzBLYjZkVmRGSXM1QWM3cVplTzhNWDFFeDJMTm9rRlNCT1N5dFB2XzRMQ1BjNzN0bVdCbU92UWlpdGtFQmlybFFZc0JkakxaY1BkM2xJSU16NC1EVVJQbXBTRU9ZbXNvaUJ1SHhYTWNOR1p6ZWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -9708,51 +9708,51 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Negócio bilionário faz a China entrar de vez no ouro brasileiro - CartaCapital</t>
+          <t>NEGÓCIOS | Equinox Gold conclui venda de minas para a CMOC por US$ 1,05 bilhão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>27/01/2026 05:00</t>
+          <t>23/01/2026 05:00</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNFdxT2RJVUZPMmhHNmdJMU12a2VxWDlSYXNjOWxJLVNCRUFpeS1zd3VGd2ZtVmxqdDdudzBLYjZkVmRGSXM1QWM3cVplTzhNWDFFeDJMTm9rRlNCT1N5dFB2XzRMQ1BjNzN0bVdCbU92UWlpdGtFQmlybFFZc0JkakxaY1BkM2xJSU16NC1EVVJQbXBTRU9ZbXNvaUJ1SHhYTWNOR1p6ZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcFVPMXJSRE9mcmNsY0U2NnZVb2RWMkxhWm02dmpteHRLYnhKb19nbkFWdURBakVzZmdLVlVuNDVBbi1lcDhPLXdmUGpHTElRaGZFSHBFSldackR4RmxDa00zTXNIdFVranNXQUZZOXZ2S1kyU0xuMGROcXY0ckE0VWpjS2dleXJjQndISnhWYXZvZHd3QVpqUm1Ud1VWUlZ6RV93SnNsVmZITnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | Equinox Gold conclui venda de minas para a CMOC por US$ 1,05 bilhão - Brasil Mineral</t>
+          <t>Passa Sete abre inscrições para pedidos de calcário - radiosobradinho.com.br</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>23/01/2026 05:00</t>
+          <t>15/01/2026 05:00</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcFVPMXJSRE9mcmNsY0U2NnZVb2RWMkxhWm02dmpteHRLYnhKb19nbkFWdURBakVzZmdLVlVuNDVBbi1lcDhPLXdmUGpHTElRaGZFSHBFSldackR4RmxDa00zTXNIdFVranNXQUZZOXZ2S1kyU0xuMGROcXY0ckE0VWpjS2dleXJjQndISnhWYXZvZHd3QVpqUm1Ud1VWUlZ6RV93SnNsVmZITnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNQkVmeU43d3FMWjBLMTZ1SWJnVFZSVXFmT3JmM2dFOTdkeFkxLVNodG1ub3hvWEs2eHR4Z3NMd2c5VkFVU2t0S25XYVVEWXRtTHVkUmdVOFdQVGZ3OGJ3YkNmY2xMeGRyLWgxbktJXzhOUF9uN0FWUUcxSnk2cUtFRk5JQ1NHSXJJRHlwcE9oQUU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Passa Sete abre inscrições para pedidos de calcário - radiosobradinho.com.br</t>
+          <t>Tensão no Irã gera incerteza no mercado de ureia - Agrolink</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNQkVmeU43d3FMWjBLMTZ1SWJnVFZSVXFmT3JmM2dFOTdkeFkxLVNodG1ub3hvWEs2eHR4Z3NMd2c5VkFVU2t0S25XYVVEWXRtTHVkUmdVOFdQVGZ3OGJ3YkNmY2xMeGRyLWgxbktJXzhOUF9uN0FWUUcxSnk2cUtFRk5JQ1NHSXJJRHlwcE9oQUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONkdHa0VwT2VKZExwWll5QlRHbEJoWW4zOW1HRE12cF9ZUTRvTUhodXA1dWlRRGd1Vy1uVC00TS15YkVXU0MyWGs0aGMxdERmdW1KamFNWGZuZTZXUnJqRUFYRVFqN3hXVS1xNllzQ0l1WEdsbnlWV09QOXF0NFpSU3VibVlBV1BpS0gwWld3QXNBX3ZPb3gtTmduZ2VOZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -9791,12 +9791,12 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Combinação Potássio e Enxofre maximiza potencial da soja - agrolink.com.br</t>
+          <t>FAFENs Bahia e Sergipe entram em operação e reforçam produção nacional de fertilizantes - Agência Petrobras de Notícias</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -9806,19 +9806,19 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNnRoQks2V3lYaVduWHRXZTd0OU5NdUIzc0Z3a2toUW1wMm9XdVFueVlKaURfYzJ4LU54eFVxdmUyTWt2ck80NjJGRXVNM3UxSGUyV2FGRld1WjNZSlo4Sm5HNzdtV21seDVHcllQMGQwRjB6dWE4RUZ1RWNjMmZWU0lFNmcxR2NJUHY5cTBmUEQ2RS1yYm9YLW40aFRWa3hUdGd5UDgtWUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQVGg5TXhFc3VydTJjQ0lfakF5VjFPMTFDNU5LSmllZ0xfVUFWR05INHBQdmE0b1RJX2h4QlN5SzdjTzExYzBiWHVZaV9tTWpjZE9SamQ1TXZVM3BPUTBpd3RQTEFOQ0dQcUJiNHFyMDVJZ0tmR2ZlYnd5U2pINnpwS2Z3TEw0S3R3ZkwwbzNFUzNvVkpzeFVQYkNGRWVJYm5pSnNxekpPSzRBMC0zS0RLdUQzYVpoLVlYcFptYWdqZHBKdVU0YkhReWdJb3hSRklSbzhEUEIxZTJwbUthX1JaQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>FAFENs Bahia e Sergipe entram em operação e reforçam produção nacional de fertilizantes - Agência Petrobras de Notícias</t>
+          <t>Combinação Potássio e Enxofre maximiza potencial da soja - Agrolink</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQVGg5TXhFc3VydTJjQ0lfakF5VjFPMTFDNU5LSmllZ0xfVUFWR05INHBQdmE0b1RJX2h4QlN5SzdjTzExYzBiWHVZaV9tTWpjZE9SamQ1TXZVM3BPUTBpd3RQTEFOQ0dQcUJiNHFyMDVJZ0tmR2ZlYnd5U2pINnpwS2Z3TEw0S3R3ZkwwbzNFUzNvVkpzeFVQYkNGRWVJYm5pSnNxekpPSzRBMC0zS0RLdUQzYVpoLVlYcFptYWdqZHBKdVU0YkhReWdJb3hSRklSbzhEUEIxZTJwbUthX1JaQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNnRoQks2V3lYaVduWHRXZTd0OU5NdUIzc0Z3a2toUW1wMm9XdVFueVlKaURfYzJ4LU54eFVxdmUyTWt2ck80NjJGRXVNM3UxSGUyV2FGRld1WjNZSlo4Sm5HNzdtV21seDVHcllQMGQwRjB6dWE4RUZ1RWNjMmZWU0lFNmcxR2NJUHY5cTBmUEQ2RS1yYm9YLW40aFRWa3hUdGd5UDgtWUk?oc=5</t>
         </is>
       </c>
     </row>
@@ -9928,17 +9928,17 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Baterias de lítio-enxofre para carros elétricos enfrentam um problema e fezes humanas podem ser a solução - Terra</t>
+          <t>Trem com enxofre tóxico descarrila nos EUA; autoridades ordenam confinamento temporário - O GLOBO</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>04/01/2026 05:00</t>
+          <t>30/12/2025 05:00</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxOSHF3RVJQUG5SdTB4bkFzNU5qZjRUMzVHcG1lMzUwR1lvVVd6M25rb1NnajhiU3BqWnZsdlA1NGhQQm9sQTBaWU9lQnRMUkNnVURYYU9YdFJ2RDNUeGY5aTlWUDVmUHdnRFVoblJmd0lGTGptU2V2VmRoVlhESGNibjFiUGVVYlU3VHNza0hBVWxLQWQ3Zy0wSmdwbDlrQVh0bmJqVU81ZFlQRHNlMS0yaDU5aS1PbWRKbWNtN21WUDg1VmVPSWpERUo5OVRSVGZCOU1tSHVHT1lpbEVBYlY5LU85QU9XZXFLYlA3SU5wZ0JCTGc0ZnJ6RzJFajhKU3lMbV9jazAweUhPTHE5UlFtZXBySTVkUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNMFE1VEdfT3A5OG1pS25pYzl0SktuRmtLRlJVSzczWlVEQXV3TWN5NmpCb2JrZGVnUVRRMWx6ZTBJNmhteVhLMWVHZENCUUkycldMWExiVXY0UldsVWdaNXJaRDMtb09SamFXbEhqT0FJWXJyWXNPVVNkZDA3clh6RXFpclR0Zy1raS1pb1pzTXFFN242LVJFMjVrb1lSbGV1WUhTU0VtYUFmMzJmb2ExZFQ1eXBLNnVvMTBoNFBBcXVhdUFLTmt2bk1sTHZ4Y2txX0NSbGQxX3pJaW5Dcm5ybHN30gHwAUFVX3lxTE8xMV80NEVMcm9zLS1XZ0lVUERHNWczaDQwMVBZOVR2cW5YS3BmUXphdjJPZzJ6amp0dVpjcmo4bG90a1dTb09ncHFiX2ZlS2FCNXN4NktGM0lrQTZyZXhacTFlTjVrQU9kUFNoU2Z0bWhZdVBnaWVuMnRORm16YXNqQzdqX1lLTERqZGdUSk9TUVFrVVZDVnRLY3Z1OXJBaHlRRkt3MTE2R1NMc0VEYkl1S0FKY0xzT0VXWjJEN05XXzFSb3hILWcyamNDUzBuNzJGamQ1WF9PdmdKTi1BQm5KTl9ZNmdaZ3R4cXFzbXZKaw?oc=5</t>
         </is>
       </c>
     </row>
@@ -9967,22 +9967,22 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Trem com enxofre tóxico descarrila nos EUA; autoridades ordenam confinamento temporário - O GLOBO</t>
+          <t>Venda de minas de ouro no Brasil por US$ 1 bilhão reacende debate sobre recursos naturais e soberania - MEON</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>30/12/2025 05:00</t>
+          <t>22/12/2025 05:00</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNMFE1VEdfT3A5OG1pS25pYzl0SktuRmtLRlJVSzczWlVEQXV3TWN5NmpCb2JrZGVnUVRRMWx6ZTBJNmhteVhLMWVHZENCUUkycldMWExiVXY0UldsVWdaNXJaRDMtb09SamFXbEhqT0FJWXJyWXNPVVNkZDA3clh6RXFpclR0Zy1raS1pb1pzTXFFN242LVJFMjVrb1lSbGV1WUhTU0VtYUFmMzJmb2ExZFQ1eXBLNnVvMTBoNFBBcXVhdUFLTmt2bk1sTHZ4Y2txX0NSbGQxX3pJaW5Dcm5ybHN30gHwAUFVX3lxTE8xMV80NEVMcm9zLS1XZ0lVUERHNWczaDQwMVBZOVR2cW5YS3BmUXphdjJPZzJ6amp0dVpjcmo4bG90a1dTb09ncHFiX2ZlS2FCNXN4NktGM0lrQTZyZXhacTFlTjVrQU9kUFNoU2Z0bWhZdVBnaWVuMnRORm16YXNqQzdqX1lLTERqZGdUSk9TUVFrVVZDVnRLY3Z1OXJBaHlRRkt3MTE2R1NMc0VEYkl1S0FKY0xzT0VXWjJEN05XXzFSb3hILWcyamNDUzBuNzJGamQ1WF9PdmdKTi1BQm5KTl9ZNmdaZ3R4cXFzbXZKaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQRnFCa2dQWTktSUZxQW1BRnVBdzhNSkxZUWtlUFVjUWFUTWhMU045UTZWcTJTQ2hneE9wQ1NaU0t4ZFE5MHNVN3dMNWh3NlF1UW1RN0lDVDFfSzZmQlpuMWhfdG1sQ19wWmdweGFaWDNOSHFhTnB3aEo1dXBpRmhTWGF1NE9RaVdSY3ozaTdYbjAyUndhVzZEX3ZJNXJyTlVjazJWRkpVcXVDQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9994,17 +9994,17 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Venda de minas de ouro no Brasil por US$ 1 bilhão reacende debate sobre recursos naturais e soberania - MEON</t>
+          <t>Mineradora chinesa CMOC adquire operações da Equinox Gold no Brasil por US$ 1 bilhão - Brasília in Foco</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>22/12/2025 05:00</t>
+          <t>20/12/2025 05:00</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQRnFCa2dQWTktSUZxQW1BRnVBdzhNSkxZUWtlUFVjUWFUTWhMU045UTZWcTJTQ2hneE9wQ1NaU0t4ZFE5MHNVN3dMNWh3NlF1UW1RN0lDVDFfSzZmQlpuMWhfdG1sQ19wWmdweGFaWDNOSHFhTnB3aEo1dXBpRmhTWGF1NE9RaVdSY3ozaTdYbjAyUndhVzZEX3ZJNXJyTlVjazJWRkpVcXVDQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWFdEYV81d254OFd5Y09QdjZqWFpOcHgwSnZ5c0s1Wnh6bGpiUlJIR3EyQXMwQTd0N25iQ1BLeVh5Q0NOQnJ0bUpxVE5wNDAyX0pKZDF0SmFxb0R6WEp0dU9oeklvd3lxdWhjeTFTMHg3SGRnTkJObF9HWmtIQzF1Tl9IS0sxbHVJbGxLYnpQZDhWcmxFWm1Ec2JmbDM3SEtxZmgteXM3NFpvMGhORXYxSQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10016,29 +10016,29 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Mineradora chinesa CMOC adquire operações da Equinox Gold no Brasil por US$ 1 bilhão - Brasília in Foco</t>
+          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>20/12/2025 05:00</t>
+          <t>17/12/2025 05:00</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWFdEYV81d254OFd5Y09QdjZqWFpOcHgwSnZ5c0s1Wnh6bGpiUlJIR3EyQXMwQTd0N25iQ1BLeVh5Q0NOQnJ0bUpxVE5wNDAyX0pKZDF0SmFxb0R6WEp0dU9oeklvd3lxdWhjeTFTMHg3SGRnTkJObF9HWmtIQzF1Tl9IS0sxbHVJbGxLYnpQZDhWcmxFWm1Ec2JmbDM3SEtxZmgteXM3NFpvMGhORXYxSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeEczVHluQ0N4cDRucDc3SWpBNzV1SGdHdUJ0RUg1ZFdCQlYzZGlIM0RZaXd6bHJ3b2tUZjgzWll1dGRiOFN3S09kM3Z3aFItTmkyR0YyRkMtRUZyMGFENUxXOGpCbEdURHlPNVM2d0NJendkdXd1aWtpVUZPSVhtMFFxWEJWMlRzQkx5LW4zUEF3ajRUVU1QVEYtSUFxOHdXa0dLeE1yb18yNnlRYzRwNlBNOXBmdk5vd3B3Rmx5VQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Alta do enxofre pausa produção de fosfato - agrolink.com.br</t>
+          <t>CMOC entra no ouro no Brasil e compra minas da Equinox por até US$ 1,015 bi - Estado de Minas</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOMlZBcS1qQl9tcHNMLUh2NVk0SjJ5UmF5YUZxS0cwZGRfUXQ5ZExzdzFOWjRjdV90RkEwYjFVcEk1UnFNTGliTUZuT3JuVWN2U2Y3dFlPYS1YbmpXU0ZsMWFSTEJkSjR1M091RkNyX21Ca016ckUwZTBFd2NXTWUxaW93VWZDY0dHekRLdy02VmdianNt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNYmxtd1NMbXd3d3lRSnhVZF9GLXd3a0JfMHJhel81U1BQTFV0bl9JUTBPMFdCVVNFZFF4TjN4NWEwa254cV9pdFl0M1Y1UGt3VHhrLXBxTy1od29NaTZUc2ZvdkZva3YwVklDdmFxcVdyXzU1Yy0wT2Jkb3B6cTFIdFplZTBNLXpvLVJSSll2cFBoelpUUlFjNDc5WWc1WnI4ZUdjVWlKcWhLOWctM1JtMlA5QXIyWDllY0RScDJOYV8zYzBvdW5rVVNRalg5YldIOGdz0gHYAUFVX3lxTFBCd3RLUWlLUm4wZnlCUFVMdE05RXUzcVNXTXlEYnZIem9wbG5TaWJPVmJjem5kNUtQSFpjWFRfdm1jRHdVMUlhb1p0Z0NHeE9yVnA2SjdaOWtGRjNWVENxbEZQcWtQVFZHUmpadUg4VVZiUlUyOEQ0NDhqaXZZSi1LWGM5TG5OaEhGcExFQkdtQTA5b1AwdDZTbW9SM1ZyZzN3UU1YWUJTUDhTaW5HMlJ6clloeUthcnJ5dDRjUXJITXNSUXR1VzVBdm5XS1VQX0lPQk11eGU4QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
+          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeEczVHluQ0N4cDRucDc3SWpBNzV1SGdHdUJ0RUg1ZFdCQlYzZGlIM0RZaXd6bHJ3b2tUZjgzWll1dGRiOFN3S09kM3Z3aFItTmkyR0YyRkMtRUZyMGFENUxXOGpCbEdURHlPNVM2d0NJendkdXd1aWtpVUZPSVhtMFFxWEJWMlRzQkx5LW4zUEF3ajRUVU1QVEYtSUFxOHdXa0dLeE1yb18yNnlRYzRwNlBNOXBmdk5vd3B3Rmx5VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
         </is>
       </c>
     </row>
@@ -10082,7 +10082,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>EMPRESA CHINESA COMPRA MINAS DE OURO NO BRASIL E VAI ASSUMIR A MINERAÇÃO DE OURO NA BAHIA - - Bahia Economica</t>
+          <t>EMPRESA CHINESA COMPRA MINAS DE OURO NO BRASIL E VAI ASSUMIR A MINERAÇÃO DE OURO NA BAHIA - bahiaeconomica.com.br</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -10099,12 +10099,12 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
+          <t>Alta do enxofre pausa produção de fosfato - Agrolink</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -10114,41 +10114,41 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOMlZBcS1qQl9tcHNMLUh2NVk0SjJ5UmF5YUZxS0cwZGRfUXQ5ZExzdzFOWjRjdV90RkEwYjFVcEk1UnFNTGliTUZuT3JuVWN2U2Y3dFlPYS1YbmpXU0ZsMWFSTEJkSjR1M091RkNyX21Ca016ckUwZTBFd2NXTWUxaW93VWZDY0dHekRLdy02VmdianNt?oc=5</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>CMOC entra no ouro no Brasil e compra minas da Equinox por até US$ 1,015 bi - em.com.br</t>
+          <t>Mosaic interrompe produção de superfosfato simples no Brasil com alta do enxofre - Globo Rural</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>17/12/2025 05:00</t>
+          <t>16/12/2025 05:00</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNYmxtd1NMbXd3d3lRSnhVZF9GLXd3a0JfMHJhel81U1BQTFV0bl9JUTBPMFdCVVNFZFF4TjN4NWEwa254cV9pdFl0M1Y1UGt3VHhrLXBxTy1od29NaTZUc2ZvdkZva3YwVklDdmFxcVdyXzU1Yy0wT2Jkb3B6cTFIdFplZTBNLXpvLVJSSll2cFBoelpUUlFjNDc5WWc1WnI4ZUdjVWlKcWhLOWctM1JtMlA5QXIyWDllY0RScDJOYV8zYzBvdW5rVVNRalg5YldIOGdz0gHYAUFVX3lxTFBCd3RLUWlLUm4wZnlCUFVMdE05RXUzcVNXTXlEYnZIem9wbG5TaWJPVmJjem5kNUtQSFpjWFRfdm1jRHdVMUlhb1p0Z0NHeE9yVnA2SjdaOWtGRjNWVENxbEZQcWtQVFZHUmpadUg4VVZiUlUyOEQ0NDhqaXZZSi1LWGM5TG5OaEhGcExFQkdtQTA5b1AwdDZTbW9SM1ZyZzN3UU1YWUJTUDhTaW5HMlJ6clloeUthcnJ5dDRjUXJITXNSUXR1VzVBdm5XS1VQX0lPQk11eGU4QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOVENsYjV0WjhZbTEzUy1kOFo0Q1BNOHRXZ1Jwd1lYMWdFVG5jeUpjVDJKNi1FLVJrX1psN3k2enVQQVBzcmxKeW13X3lUS2NNNHpRd2lGdzhHbkpBcmNscC1uSFJzclpqMmRSSW5qdHNRdDF1eEg3M3ppYTFENE1Wb2F0N1hoZ1IzSTdPOW5xM0h3SVFZbVNPVHJrQ09vZFhDaVVUV0tqNXpCZzlFNHhDcXdfZUVjTzlKYkxWa2h0VVNoZVBzWFpibUVyUDBCRjVvektiTHRB0gHkAUFVX3lxTFBQRVRzdEZPSzcwcXJuZTBLZW8zR18zNDMxVi1HeFJEZVFCcElEa1FHNXg3SERqc09CTWRqcW8yeFJvN0ZTQXctRGxYaWE2SHp3S2NaTzJaMllZYTB3TEtXbFJSNUM3Q2NjUFZIMDBVR2g2NEpfR05ZaEFFZDdXOG1VaHpIdklCY0pGczJkS2NqVTdQVlF4N1dmLXgyeGtmSHNCMEx1cVNTN0JkN19zN2hVWWxvdzgtMmppWnUyVFhlYUtBZ1ZIZ21EYjlYcVRib0xJdmJEV1lGZXkyYXBvc3dqRTNNdg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
+          <t>Em meio à disparada do enxofre, Mosaic paralisa produção de superfosfato simples - The AgriBiz</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -10158,19 +10158,19 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQc2RkWEZTUy1Ea283N19QQlhkUWJ1VE9wYUdJMXdVUGlyWXZwLVhkeTQ3SWVOdFdWMl80MElvczhkeHJFYkZ4LWIxSzhIcEItS00zdmpHT04wanN0Ym9PUnI4eXBwb1RiWFF6WVNGSnNNZXlEX3Y5NFJFTVVuRUJkLS1RdkI3VVVSSUNrbWtlQ3EzQlZkMWxxaVQzSVdiUmZwUERrV0F6VUNXeVFXQWxUcXUzTUU2dw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Suspensão de produção em fábricas da Mosaic faz soar mais um alerta no mercado de fertilizantes - AgFeed</t>
+          <t>Chinesa CMOC compra operações da Equinox e produzirá ouro no Brasil - Valor Econômico</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -10180,19 +10180,19 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRnpldHB2SFFfMDU2ZWxsNGxxZklNRlFNT0JYd3k2ZGxYSUo2MlNHcnBrY1BVY1lhd0Q1X1BPLU0xeXprVkw0ZFJYb0VkNkRXWEI4aklPX21NcW82Z3NacVp0ZlJfTmRLbTIxeXBXeElhNnRwdjlaX19GdVlqTTgwMERZMEpUNDBWcTBpUTZKN0lxRUYyRE1BbEtObWpBcjZYLTJ2bVA2dXpUdGJ5d2lBTm9FVFlqRWhiaFNjdTJuWmRTemstTVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNdjJLdXR0TWF1WVRBWGpwZW5vUlAtZk9scmFlMUxKbWxpcUVKZ2ZkNGJqZXhCVENIRVpaRlBPWE9ycnJteDJnbW1WcmZUVjVJOG9DTjF0andnXzMweFV0anRSLXdjVUllZ3JvYUNLU1U3SnFoRWx4Z21OVnFNQ05nWDZaVVRBQnoxMFVSYm5PQ3AyZlVqdmpabzNCY25qZVE0VkI4NGlKVGEzd3RncWNtX0swakhzYjh5WUktLUx2bjdrQkHSAdIBQVVfeXFMTndraVAxVThDT0d6d0xTbVdRa25WdENfanhibkVOamNHaVFMR3VJQWp4b1RiVmFaRXFGQmIwLUZHVTlTdHcxWnZhZERhRWRyRmhBUFlmakVxRHYtZVJNNW5OS1JuZ0xyVXdWVFVSdDU3NmN5MWt4Zmw2R01fR2ZMNG5fVDB0LVNtRENfdlNZS2hmSGg0a2xES1p4aDdzMk1RODRWaHBjVVE0MXNLcWRfMGJuSHZ2SVhZcHcyZnQ5eVN6UXhkd2ZhZGdzeDc0UzRFUkln?oc=5</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Mosaic interrompe produção de superfosfato simples no Brasil com alta do enxofre - Globo Rural</t>
+          <t>China CMOC compra quatro minas de ouro no Brasil por 863 milhões de euros - RTP</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -10202,7 +10202,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOVENsYjV0WjhZbTEzUy1kOFo0Q1BNOHRXZ1Jwd1lYMWdFVG5jeUpjVDJKNi1FLVJrX1psN3k2enVQQVBzcmxKeW13X3lUS2NNNHpRd2lGdzhHbkpBcmNscC1uSFJzclpqMmRSSW5qdHNRdDF1eEg3M3ppYTFENE1Wb2F0N1hoZ1IzSTdPOW5xM0h3SVFZbVNPVHJrQ09vZFhDaVVUV0tqNXpCZzlFNHhDcXdfZUVjTzlKYkxWa2h0VVNoZVBzWFpibUVyUDBCRjVvektiTHRB0gHkAUFVX3lxTFBQRVRzdEZPSzcwcXJuZTBLZW8zR18zNDMxVi1HeFJEZVFCcElEa1FHNXg3SERqc09CTWRqcW8yeFJvN0ZTQXctRGxYaWE2SHp3S2NaTzJaMllZYTB3TEtXbFJSNUM3Q2NjUFZIMDBVR2g2NEpfR05ZaEFFZDdXOG1VaHpIdklCY0pGczJkS2NqVTdQVlF4N1dmLXgyeGtmSHNCMEx1cVNTN0JkN19zN2hVWWxvdzgtMmppWnUyVFhlYUtBZ1ZIZ21EYjlYcVRib0xJdmJEV1lGZXkyYXBvc3dqRTNNdg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQV0FjeGVtTGVqd2VhNU5fanJxQVlOSWI5ckFnZTFhLVgtdjZQNXlzUUFIYVJhS285THFzZjRiNUw4QnJJcENRVmtQT3l0NUVzR3c0UzlnT3I0anItNXprX0Qzd1R2b000V3Bya3NsSVVtMi16U2JQaERkcFZQRVFxalA1cTByWEVjTzZKQjc5RHZrdWdncy1zWEh6ZURSTFJXWG1HdlE1cV9iLXpMRG1sVWl4R0ltNDF5VHVJ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>China CMOC compra quatro minas de ouro no Brasil por 863 milhões de euros - RTP</t>
+          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -10224,19 +10224,19 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQV0FjeGVtTGVqd2VhNU5fanJxQVlOSWI5ckFnZTFhLVgtdjZQNXlzUUFIYVJhS285THFzZjRiNUw4QnJJcENRVmtQT3l0NUVzR3c0UzlnT3I0anItNXprX0Qzd1R2b000V3Bya3NsSVVtMi16U2JQaERkcFZQRVFxalA1cTByWEVjTzZKQjc5RHZrdWdncy1zWEh6ZURSTFJXWG1HdlE1cV9iLXpMRG1sVWl4R0ltNDF5VHVJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Chinesa CMOC compra operações da Equinox e produzirá ouro no Brasil - Valor Econômico</t>
+          <t>Suspensão de produção em fábricas da Mosaic faz soar mais um alerta no mercado de fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -10246,29 +10246,29 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNdjJLdXR0TWF1WVRBWGpwZW5vUlAtZk9scmFlMUxKbWxpcUVKZ2ZkNGJqZXhCVENIRVpaRlBPWE9ycnJteDJnbW1WcmZUVjVJOG9DTjF0andnXzMweFV0anRSLXdjVUllZ3JvYUNLU1U3SnFoRWx4Z21OVnFNQ05nWDZaVVRBQnoxMFVSYm5PQ3AyZlVqdmpabzNCY25qZVE0VkI4NGlKVGEzd3RncWNtX0swakhzYjh5WUktLUx2bjdrQkHSAdIBQVVfeXFMTndraVAxVThDT0d6d0xTbVdRa25WdENfanhibkVOamNHaVFMR3VJQWp4b1RiVmFaRXFGQmIwLUZHVTlTdHcxWnZhZERhRWRyRmhBUFlmakVxRHYtZVJNNW5OS1JuZ0xyVXdWVFVSdDU3NmN5MWt4Zmw2R01fR2ZMNG5fVDB0LVNtRENfdlNZS2hmSGg0a2xES1p4aDdzMk1RODRWaHBjVVE0MXNLcWRfMGJuSHZ2SVhZcHcyZnQ5eVN6UXhkd2ZhZGdzeDc0UzRFUkln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRnpldHB2SFFfMDU2ZWxsNGxxZklNRlFNT0JYd3k2ZGxYSUo2MlNHcnBrY1BVY1lhd0Q1X1BPLU0xeXprVkw0ZFJYb0VkNkRXWEI4aklPX21NcW82Z3NacVp0ZlJfTmRLbTIxeXBXeElhNnRwdjlaX19GdVlqTTgwMERZMEpUNDBWcTBpUTZKN0lxRUYyRE1BbEtObWpBcjZYLTJ2bVA2dXpUdGJ5d2lBTm9FVFlqRWhiaFNjdTJuWmRTemstTVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Em meio à disparada do enxofre, Mosaic paralisa produção de superfosfato simples - The AgriBiz</t>
+          <t>Mineradora chinesa compra minas de ouro no Brasil por US$ 1 bi - Poder360</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>16/12/2025 05:00</t>
+          <t>15/12/2025 05:00</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQc2RkWEZTUy1Ea283N19QQlhkUWJ1VE9wYUdJMXdVUGlyWXZwLVhkeTQ3SWVOdFdWMl80MElvczhkeHJFYkZ4LWIxSzhIcEItS00zdmpHT04wanN0Ym9PUnI4eXBwb1RiWFF6WVNGSnNNZXlEX3Y5NFJFTVVuRUJkLS1RdkI3VVVSSUNrbWtlQ3EzQlZkMWxxaVQzSVdiUmZwUERrV0F6VUNXeVFXQWxUcXUzTUU2dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOUE5hQ3pzUmR2cE5qdjZTUEFxQWVUOXpPTDlLLVNLSVZVR3hmVXVFUG0yLVpRZUN1MHRCMHAxUDRsUm5peUhTSmRsYTdUZnlzNkdEWXdhMHU1ZUFRNTIzNGtXakFfWGo0VFl6OEU3dTdrMXBXQUMxbWM0Ry1CWmJhYV85YlZLSmZmazVjVV8yT2F6NkpIUlEzaHpqSDZycExZd2VhVQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Equinox Gold vende operações no Brasil para chinesa CMOC por US$ 1,015 bilhão - broadcast.com.br</t>
+          <t>Mineração chinesa avança no Brasil com compra bilionária de ativos de ouro da Equinox Gold - Agência Brasil China</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPY21WSmFRbjB2aU1QUUlkbGgtdW5SUUIyeFhabGpTclNfSHdKbmFGQlJueFY5dU43bzY1R0NtVU5ObkhiTU9jRm1kakNPa0dIOWhsekRnV0VlSnpYLUJCaVNHOXduUDI0enpQczROeVViZGQ1X2kzLWpxMnZiXzh5Q1NSNHJnQ2dSOTlacTZXcjVaOVZSS3hXRTFPbzRzeDBsRFFSM2FERVpLVktSWnVZeTBKbU5DQkNoXy1mRw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2pwVXU4OGJVUHdzb2xLaHhoS21XQVVoN0kyeEF0Qm1LSzE2UnBCYzVUMXBRcGVYWTg2TkMyVXZiRW1zamNtdmF3WFFSMXFNYW1mcmJIUngtS2JIMTNWU3Q0ME9uV2k5aHlHT05DYUpqLWJvM0FIYlhhVm5mUFhtMHNzekNaYkZNLUFpaWVGb3lTdkViVDRWWGxJQWljSE1EM1BKUnpua3Vuc0NMTGtvdGVB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Equinox vende minas de ouro no Brasil por US$ 1 bilhão para focar na América do Norte - timesbrasil.com.br</t>
+          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR28ySFpHMzJDeW0xM3dXcXktU19yeVBESW1qVXF3dDA0dThMVkZ2WXFiT2J5ak5ZUjdzQW16Q0Z3dE5PZm9MVEkyb3F0MndOSDZTM2RhUFlBX2VTdVozR0ZaTHc2Y3d5M3JWdF9vNjJ6aGJXNko5RThyZjByeWtlSFRNdE1JZFdhVUUzVVBoUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
+          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Empresa chinesa compra minas de ouro no Brasil e amplia presença global - Revista Oeste</t>
+          <t>Equinox Gold vende minas no Brasil à chinesa CMOC por US$ 1 bilhão - Brasil 247</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQNzRxZEFqRTNNS3dablR5U2liLVhrbUZOVThwYUhwUGFrdWR1eWcwWHJGckxoWG5JNHY3V3hDZjhaRTRvX2wtaFRkdnJjdFUyZ1BlRjdCV2oxMTA1ZUxlYnlXOHY4ZjFxMGl2ODZDaUM2VWJhcWVjbE4wUWxPLVRxejFzaWduNnlGUFUzOGEzSE9CckhDUFBhTG5xNjJZSGR5OU1UUmtHblAtUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPU1ZKalFzaTc5NjZlSmE4UVY0dzNMMTZUWk9Cd0o5VDFxYVdVZDY1SEVUbVZKLXphOWcydlFQcXk2ZzZMUnhSVUNqSnNzY2s4bkdQcnNmU3FuT0ppTnZ1VmpfS3RZVlNRdzNlVWpMSDdJWENUby1ld2Y1X2lUeThtTFlRcEdNYXcyWi1qZWJUQkhmRHlXYUpMVElFeWlHMUladlA0?oc=5</t>
         </is>
       </c>
     </row>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Mineração chinesa avança no Brasil com compra bilionária de ativos de ouro da Equinox Gold - Agência Brasil China</t>
+          <t>Por US$ 1 bi, chineses compram minas no Brasil para tirar 7,5 t/ano de ouro - bncamazonas.com.br</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2pwVXU4OGJVUHdzb2xLaHhoS21XQVVoN0kyeEF0Qm1LSzE2UnBCYzVUMXBRcGVYWTg2TkMyVXZiRW1zamNtdmF3WFFSMXFNYW1mcmJIUngtS2JIMTNWU3Q0ME9uV2k5aHlHT05DYUpqLWJvM0FIYlhhVm5mUFhtMHNzekNaYkZNLUFpaWVGb3lTdkViVDRWWGxJQWljSE1EM1BKUnpua3Vuc0NMTGtvdGVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNWU5GdXJHYUhsWkRHZjc4MDdKbGRObU1uRVRfWUdGUlNrQlJXbHlNRXNNalFBbE1FT1VNdnZYeXlCR1N0TEJyQm91c2VPc25ZRkJlZUZONmZxSDhrSzN5SHNkejBsUXFKS0lwLUlXekNzbWFhT19aRjRPZFR0WXZKVl9mUHlXWWtCcTNzcFZ1UGtXVzE4Y0VRUFZnWmdOWnpDa3pOTDdkd25QUXdQM0hyNg?oc=5</t>
         </is>
       </c>
     </row>
@@ -10412,7 +10412,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
+          <t>Equinox vende minas de ouro no Brasil por US$ 1 bilhão para focar na América do Norte - Times Brasil | CNBC</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR28ySFpHMzJDeW0xM3dXcXktU19yeVBESW1qVXF3dDA0dThMVkZ2WXFiT2J5ak5ZUjdzQW16Q0Z3dE5PZm9MVEkyb3F0MndOSDZTM2RhUFlBX2VTdVozR0ZaTHc2Y3d5M3JWdF9vNjJ6aGJXNko5RThyZjByeWtlSFRNdE1JZFdhVUUzVVBoUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
+          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas no Brasil à chinesa CMOC por US$ 1 bilhão - Brasil 247</t>
+          <t>Equinox Gold vende operações no Brasil para chinesa CMOC por US$ 1,015 bilhão - broadcast.com.br</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPU1ZKalFzaTc5NjZlSmE4UVY0dzNMMTZUWk9Cd0o5VDFxYVdVZDY1SEVUbVZKLXphOWcydlFQcXk2ZzZMUnhSVUNqSnNzY2s4bkdQcnNmU3FuT0ppTnZ1VmpfS3RZVlNRdzNlVWpMSDdJWENUby1ld2Y1X2lUeThtTFlRcEdNYXcyWi1qZWJUQkhmRHlXYUpMVElFeWlHMUladlA0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPY21WSmFRbjB2aU1QUUlkbGgtdW5SUUIyeFhabGpTclNfSHdKbmFGQlJueFY5dU43bzY1R0NtVU5ObkhiTU9jRm1kakNPa0dIOWhsekRnV0VlSnpYLUJCaVNHOXduUDI0enpQczROeVViZGQ1X2kzLWpxMnZiXzh5Q1NSNHJnQ2dSOTlacTZXcjVaOVZSS3hXRTFPbzRzeDBsRFFSM2FERVpLVktSWnVZeTBKbU5DQkNoXy1mRw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Mineradora chinesa compra minas de ouro no Brasil por US$ 1 bi - Poder360</t>
+          <t>Empresa chinesa compra minas de ouro no Brasil e amplia presença global - revistaoeste.com</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOUE5hQ3pzUmR2cE5qdjZTUEFxQWVUOXpPTDlLLVNLSVZVR3hmVXVFUG0yLVpRZUN1MHRCMHAxUDRsUm5peUhTSmRsYTdUZnlzNkdEWXdhMHU1ZUFRNTIzNGtXakFfWGo0VFl6OEU3dTdrMXBXQUMxbWM0Ry1CWmJhYV85YlZLSmZmazVjVV8yT2F6NkpIUlEzaHpqSDZycExZd2VhVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQNzRxZEFqRTNNS3dablR5U2liLVhrbUZOVThwYUhwUGFrdWR1eWcwWHJGckxoWG5JNHY3V3hDZjhaRTRvX2wtaFRkdnJjdFUyZ1BlRjdCV2oxMTA1ZUxlYnlXOHY4ZjFxMGl2ODZDaUM2VWJhcWVjbE4wUWxPLVRxejFzaWduNnlGUFUzOGEzSE9CckhDUFBhTG5xNjJZSGR5OU1UUmtHblAtUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10500,17 +10500,17 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Por US$ 1 bi, chineses compram minas no Brasil para tirar 7,5 t/ano de ouro - bncamazonas.com.br</t>
+          <t>OURO | Equinox Gold vende operações brasileiras para CMOC por US$ 1,015 bilhão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>15/12/2025 05:00</t>
+          <t>14/12/2025 05:00</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNWU5GdXJHYUhsWkRHZjc4MDdKbGRObU1uRVRfWUdGUlNrQlJXbHlNRXNNalFBbE1FT1VNdnZYeXlCR1N0TEJyQm91c2VPc25ZRkJlZUZONmZxSDhrSzN5SHNkejBsUXFKS0lwLUlXekNzbWFhT19aRjRPZFR0WXZKVl9mUHlXWWtCcTNzcFZ1UGtXVzE4Y0VRUFZnWmdOWnpDa3pOTDdkd25QUXdQM0hyNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRVJxVWY5aVdLMG85emtjZ04xVG10c3JUSkdSVjdhQko5UUU4S2gtRXdzang5ckZmOHFoYUlqR2huemllR0lOMUQxYVFDWjAwbkIxSUx2ZjhFa1dQbTkyVGh0MlZlb3BWbWMwN2p3TEplUzM4UEpTQWxFckJsMVU0ckJmZXAwbEh6Vm9WbjRyNWhRZGdMRHJBT3ROZ1ZvcWFJYUVGMEVpekZQck9idWlmRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10544,193 +10544,193 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>OURO | Equinox Gold vende operações brasileiras para CMOC por US$ 1,015 bilhão - Brasil Mineral</t>
+          <t>CMOC Brasil é reconhecida nacionalmente com o Selo ODS Brasil 2025 - ibram.org.br</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>14/12/2025 05:00</t>
+          <t>12/12/2025 05:00</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRVJxVWY5aVdLMG85emtjZ04xVG10c3JUSkdSVjdhQko5UUU4S2gtRXdzang5ckZmOHFoYUlqR2huemllR0lOMUQxYVFDWjAwbkIxSUx2ZjhFa1dQbTkyVGh0MlZlb3BWbWMwN2p3TEplUzM4UEpTQWxFckJsMVU0ckJmZXAwbEh6Vm9WbjRyNWhRZGdMRHJBT3ROZ1ZvcWFJYUVGMEVpekZQck9idWlmRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQMFRzbEdjWV9haVd4T0hEeGU3b3pvRkJTMjRCbFRnZkRjRzczZ2pWVm1ZcjdOSFBPN2dXR1BBOXF5Z1ZmRk9pUkJCNlZ0ZW1wZ3RDdVVsbGZxRkgwUHJON0c4NkNBUWhjbE91Q1pMLXBDTVJZVGlWWmdlaER6YldSa3FYRGc2LUtXTFdkVEpsZG55U0JHVHhmTGl4bzU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>CMOC Brasil é reconhecida nacionalmente com o Selo ODS Brasil 2025 - ibram.org.br</t>
+          <t>Estudo revela papel do dióxido de enxofre na composição das uvas - Revista ADEGA ·</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>12/12/2025 05:00</t>
+          <t>09/12/2025 09:26</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQMFRzbEdjWV9haVd4T0hEeGU3b3pvRkJTMjRCbFRnZkRjRzczZ2pWVm1ZcjdOSFBPN2dXR1BBOXF5Z1ZmRk9pUkJCNlZ0ZW1wZ3RDdVVsbGZxRkgwUHJON0c4NkNBUWhjbE91Q1pMLXBDTVJZVGlWWmdlaER6YldSa3FYRGc2LUtXTFdkVEpsZG55U0JHVHhmTGl4bzU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOd0xRZElFOFotSVVrSVhMdE43b1hhUWl4cTFUS3EtOFRUekxsM0lhYkJidFBpX255Y0Zpblp1cUlwa2UzZUVlYTIzWlNBVF9VcjdOZjUtWTI2TjVkYldTc21SaHFOS2EzMGJQX3psLXRpbVRjZ2FZX0pFUnFrWEtZQUlvckY3WmwwdTFIRnQ5UU9jV1dNRWJKajRBanRzZmlxOURZQUtHbFpETWpVWGl30gG0AUFVX3lxTE1vWkc5SEtsb19TRzFGMUlOYjdvZVVXd0pGZWpoRlczRF9OaGRQTTZsWWVsOGFTMEFmTFBwU1l3Z3VwclZaNnRmVzRzM0daeWtReW5ZMmlTcEJkYUt6dFIyU0pUazVBVkJaaVZhaWJzZVBnTXlVcXRuY01ZbDFsTVRDS0hQTk1jck9FeHRJWmZUd1FYQnBLV2x0WHRoRG5DU1FET2kxTEs0bXNHRC1NMU9oN1N5TA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Estudo revela papel do dióxido de enxofre na composição das uvas - Revista ADEGA ·</t>
+          <t>Maximize Soybean Yield by Applying Lime for Soil</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>09/12/2025 09:26</t>
+          <t>07/12/2025 19:00</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOd0xRZElFOFotSVVrSVhMdE43b1hhUWl4cTFUS3EtOFRUekxsM0lhYkJidFBpX255Y0Zpblp1cUlwa2UzZUVlYTIzWlNBVF9VcjdOZjUtWTI2TjVkYldTc21SaHFOS2EzMGJQX3psLXRpbVRjZ2FZX0pFUnFrWEtZQUlvckY3WmwwdTFIRnQ5UU9jV1dNRWJKajRBanRzZmlxOURZQUtHbFpETWpVWGl30gG0AUFVX3lxTE1vWkc5SEtsb19TRzFGMUlOYjdvZVVXd0pGZWpoRlczRF9OaGRQTTZsWWVsOGFTMEFmTFBwU1l3Z3VwclZaNnRmVzRzM0daeWtReW5ZMmlTcEJkYUt6dFIyU0pUazVBVkJaaVZhaWJzZVBnTXlVcXRuY01ZbDFsTVRDS0hQTk1jck9FeHRJWmZUd1FYQnBLV2x0WHRoRG5DU1FET2kxTEs0bXNHRC1NMU9oN1N5TA?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a70b554b1fb44d3bd04c691a5851b8e&amp;url=https%3a%2f%2fwww.agweb.com%2fnews%2fcrops%2flime-soybean-yield&amp;c=11130810557354802507&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Maximize Soybean Yield by Applying Lime for Soil</t>
+          <t>Parabenos e dióxido de enxofre fazem mal à saúde? Conheça esses conservantes - Olhar Digital</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>07/12/2025 19:00</t>
+          <t>05/12/2025 05:00</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a708df9e25249dbab0f0f4f5ec02cba&amp;url=https%3a%2f%2fwww.agweb.com%2fnews%2fcrops%2flime-soybean-yield&amp;c=11130810557354802507&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNdWF2bGw2UWZLUTRmVzV4TE1UYlVkQjl6Q1NQMFZ6VVBsZzBMYUk0aWhfYmp2czBONHFCejlJeFVfNGVQQ3RDd2JuTUhJdFFPbHgzSV8tRU9BZTk2aS1ncFZDOUhBZkV4TGh0ZmthdnVjRnFwQng5VGhUQW9MZENYVG9ReDBGTC1IS0VtZkhCaS02VG5wV21UQ2xvc2xva1NHQWh6M1M5cG5CZHk3UkFXMjNpdllxeVQ4TW84bHFWcWhUMzlOR0tOckRua0w?oc=5</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Parabenos e dióxido de enxofre fazem mal à saúde? Conheça esses conservantes - Olhar Digital</t>
+          <t>Viter, da Votorantim, dá novo passo em seu plano para o agro de MT - Globo Rural</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>05/12/2025 05:00</t>
+          <t>02/12/2025 05:00</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNdWF2bGw2UWZLUTRmVzV4TE1UYlVkQjl6Q1NQMFZ6VVBsZzBMYUk0aWhfYmp2czBONHFCejlJeFVfNGVQQ3RDd2JuTUhJdFFPbHgzSV8tRU9BZTk2aS1ncFZDOUhBZkV4TGh0ZmthdnVjRnFwQng5VGhUQW9MZENYVG9ReDBGTC1IS0VtZkhCaS02VG5wV21UQ2xvc2xva1NHQWh6M1M5cG5CZHk3UkFXMjNpdllxeVQ4TW84bHFWcWhUMzlOR0tOckRua0w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMDlja0FtOTBHX1ZRTUdWS3owOWVranBrZU53WGZIZVp6QnAzdWxpZC1qRGtSTEhRdldUbFNxd1QwX3F4cEhqZy1Kb21jcGRoT2YyaUY2alprTGFHOFlLRlc4WHo3cmtLWWhtUzhkYmFCaHE1dmpIMnlaVDAwa0IzZzk4QzFxQkJqdlpScnd4V1VZbl9RWmhmdWt1RV8xZkdWNlF5UG96R2lNTV9ocmVBN3VsSWUzNlBSdzhOYTBPc0fSAc8BQVVfeXFMTzF5NVFKcUZmWGZiY2FzdGl6U19DR082dHFlcHAzc3A5bktBT0ZpU2lnZVdjQ3VLcklVd3Qwc1A5WldEUmRNQ29zT1JySklwNWlNdG5tWTdJeXJSVFd3U2t1MHNmV1dITkdOamNtSkZ2bW5fZnFMNmFMWGwwU3BvLWNKX2dadVAyclNIQXVBX0VNakdmdzhlM1dwQmFMMnVtVURjbE9NVUYyMWdabnpUc0JHX3N4S19zb1labHF5Sm50UlpTV2RTSEtNdnJ2Q053?oc=5</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Viter, da Votorantim, dá novo passo em seu plano para o agro de MT - Globo Rural</t>
+          <t>Escalada global do enxofre pressiona mercado - Agrolink</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>02/12/2025 05:00</t>
+          <t>01/12/2025 05:00</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMDlja0FtOTBHX1ZRTUdWS3owOWVranBrZU53WGZIZVp6QnAzdWxpZC1qRGtSTEhRdldUbFNxd1QwX3F4cEhqZy1Kb21jcGRoT2YyaUY2alprTGFHOFlLRlc4WHo3cmtLWWhtUzhkYmFCaHE1dmpIMnlaVDAwa0IzZzk4QzFxQkJqdlpScnd4V1VZbl9RWmhmdWt1RV8xZkdWNlF5UG96R2lNTV9ocmVBN3VsSWUzNlBSdzhOYTBPc0fSAc8BQVVfeXFMTzF5NVFKcUZmWGZiY2FzdGl6U19DR082dHFlcHAzc3A5bktBT0ZpU2lnZVdjQ3VLcklVd3Qwc1A5WldEUmRNQ29zT1JySklwNWlNdG5tWTdJeXJSVFd3U2t1MHNmV1dITkdOamNtSkZ2bW5fZnFMNmFMWGwwU3BvLWNKX2dadVAyclNIQXVBX0VNakdmdzhlM1dwQmFMMnVtVURjbE9NVUYyMWdabnpUc0JHX3N4S19zb1labHF5Sm50UlpTV2RTSEtNdnJ2Q053?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxObXVxLVFyVkN1SnNXVXZMa3hWU2VjVkNuZXRuWTZ4QTJ3bjl5ZTdEb1FFaXV1RC1aWjdBcVZWR09LNm9pWS1LdUdHbTZ2bThXc2l1WVV5eDYyQ081cXZEOW14UVh3T2RFTWFtTi1yUWstM0RMS2JiLTVLLWx2dFl5R2xFbEdUMnRxNVZVVm5sUGpCNU1WTnA3OQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Escalada global do enxofre pressiona mercado - agrolink.com.br</t>
+          <t>ANM autoriza MBF Fertilizantes a extrair calcário no litoral do Piauí - Agência iNFRA</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>01/12/2025 05:00</t>
+          <t>27/11/2025 05:00</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxObXVxLVFyVkN1SnNXVXZMa3hWU2VjVkNuZXRuWTZ4QTJ3bjl5ZTdEb1FFaXV1RC1aWjdBcVZWR09LNm9pWS1LdUdHbTZ2bThXc2l1WVV5eDYyQ081cXZEOW14UVh3T2RFTWFtTi1yUWstM0RMS2JiLTVLLWx2dFl5R2xFbEdUMnRxNVZVVm5sUGpCNU1WTnA3OQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPLV9uSnA0c3dNdUtMaTNUbGU2YThONXZtdFk5cTVMZHFuSDlrYml2dHV4ZmZLcllzQnd6d0hpRzYzdVFVMEJWX2ttQ2EtME9ic0lPZnREcDJJRExzMEpicUluUEIzdzR5NHZYZHlCVU1meFdweFh2RjBRb3J1dkttenFNNHl0Y01hR1dEZUJTTDVUX1NfajMtN2VwN3B1d00?oc=5</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>ANM autoriza MBF Fertilizantes a extrair calcário no litoral do Piauí - Agência iNFRA</t>
+          <t>Lhoist e TotalEnergies inauguram central solar na Lusical em Alcanede - Mais Ribatejo</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>27/11/2025 05:00</t>
+          <t>26/11/2025 03:44</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPLV9uSnA0c3dNdUtMaTNUbGU2YThONXZtdFk5cTVMZHFuSDlrYml2dHV4ZmZLcllzQnd6d0hpRzYzdVFVMEJWX2ttQ2EtME9ic0lPZnREcDJJRExzMEpicUluUEIzdzR5NHZYZHlCVU1meFdweFh2RjBRb3J1dkttenFNNHl0Y01hR1dEZUJTTDVUX1NfajMtN2VwN3B1d00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQZ2hKV0x5cnRyTG9HYU5mS2ZKT0ZoZFV3bFczcDdvcHgyNkh2RGFFOEhLUm00V21uU1ExRG83MEtycU5vZ0Q1dzBpem5GRllxQzdodEIxam9FSFVOWEVIS3hjdXc2ejc3V3AzSkFTam1BMTJPQ25YU0ZPWjljM1RmcjVvYlhvTGZXRlVUdnFOYTh1MDVyNFFUNk9R?oc=5</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Lhoist e TotalEnergies inauguram central solar na Lusical em Alcanede - Mais Ribatejo</t>
+          <t>Fertilizante e corretivo de solo sustentável, AgroSilício entra na conta dos CBios da produção de cana - AgFeed</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>26/11/2025 03:44</t>
+          <t>24/11/2025 05:00</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQZ2hKV0x5cnRyTG9HYU5mS2ZKT0ZoZFV3bFczcDdvcHgyNkh2RGFFOEhLUm00V21uU1ExRG83MEtycU5vZ0Q1dzBpem5GRllxQzdodEIxam9FSFVOWEVIS3hjdXc2ejc3V3AzSkFTam1BMTJPQ25YU0ZPWjljM1RmcjVvYlhvTGZXRlVUdnFOYTh1MDVyNFFUNk9R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPU3V5TmVZdTBGR2VEQVNkQmhZbXVuMC14VGN4NHdTWDBfYzZoT3RqU25YbGFMeEpocm9xZzVZQmE4T0p1dm13Wl8zYnZjcHhYdkJSOTlsOFNEMXluck41X09vdEQ4U0VmMEJibU1ObWJUalBLcGxUOWE1VHBkNjk3cXBfSUk0dE1YNFduUFUxQ2VfYUFyeFJUMGZYR01kNHg5N19sbjI5M0dJcXhVWTc1U3Jfd3ZfNGFvMGtkLVNZRmw4ZjZ5SFRzWXJyRmZhdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10742,17 +10742,17 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Fertilizante e corretivo de solo sustentável, AgroSilício entra na conta dos CBios da produção de cana - AgFeed</t>
+          <t>MAPA libera agregado siderúrgico da CSN para uso agrícola em todo o país - A Voz da Cidade</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>24/11/2025 05:00</t>
+          <t>19/11/2025 05:00</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPU3V5TmVZdTBGR2VEQVNkQmhZbXVuMC14VGN4NHdTWDBfYzZoT3RqU25YbGFMeEpocm9xZzVZQmE4T0p1dm13Wl8zYnZjcHhYdkJSOTlsOFNEMXluck41X09vdEQ4U0VmMEJibU1ObWJUalBLcGxUOWE1VHBkNjk3cXBfSUk0dE1YNFduUFUxQ2VfYUFyeFJUMGZYR01kNHg5N19sbjI5M0dJcXhVWTc1U3Jfd3ZfNGFvMGtkLVNZRmw4ZjZ5SFRzWXJyRmZhdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQdkNtbm82QkJhN0V3TjhhSUktbHlkU3NCTS1LdzVHWEtXVTF5UXdDWEZXanh3M0o3S2F3RXhwdmZWbE1EaUx4bENjU2cwTnFSdE5NUUZ4ZWlEVmV2SWtkOU8wQi1UUE00aWoxWC0zamtLbzU1TTUxZDdKTWdNenhaRjMyZTduNUpLR0tTRGZqOFFzYmRDYlZXdS11bGZSTnRyTUw0?oc=5</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>MAPA libera agregado siderúrgico da CSN para uso agrícola em todo o país - A Voz da Cidade</t>
+          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -10796,129 +10796,129 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQdkNtbm82QkJhN0V3TjhhSUktbHlkU3NCTS1LdzVHWEtXVTF5UXdDWEZXanh3M0o3S2F3RXhwdmZWbE1EaUx4bENjU2cwTnFSdE5NUUZ4ZWlEVmV2SWtkOU8wQi1UUE00aWoxWC0zamtLbzU1TTUxZDdKTWdNenhaRjMyZTduNUpLR0tTRGZqOFFzYmRDYlZXdS11bGZSTnRyTUw0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
+          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>19/11/2025 05:00</t>
+          <t>17/11/2025 13:00</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a70b55360ee4ce0b0aa0ac3f6869496&amp;url=https%3a%2f%2fdiariodovale.com.br%2feconomia%2fcsn-e-prefeituras-testarao-residuos-como-corretivo-de-solo-no-vale-do-cafe%2f&amp;c=17301919194020704168&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café</t>
+          <t>Prefeitura de Itabuna intensifica o fortalecimento da agricultura familiar com nova remessa de calcário para associações rurais - Prefeitura de Itabuna</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>17/11/2025 13:00</t>
+          <t>17/11/2025 05:00</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a708df749304381a4ad0ae0406775c0&amp;url=https%3a%2f%2fdiariodovale.com.br%2feconomia%2fcsn-e-prefeituras-testarao-residuos-como-corretivo-de-solo-no-vale-do-cafe%2f&amp;c=17301919194020704168&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQS3hSaWdZcnZzaWJaelBFbnN0aUExa2xWQUhUa2xFMFJPYWI1QXFBR3VTOFVqRm1BS1VjQkxmYmo4OVd4R0JXWno0dDBrYjYtWXhFVzI3LXhYeXh0Z0xsbUxvWmp6MG9xSGVaMktwUFpUbkZyMkpRcEY0anI5eUdaTUlhblJlMUpsbnl0dmx0OXJrZTk1MDVMNGJscDc5T2hINk9ZQUd6c0dXNVpSNGZMc2hGTU40X3VlaUdtMmJvaGlXM1oxdnpLSld2d1hMZGlHaUdOTFljOW1mdmJmVDlYWk9BUFFDaFYyR2hPSUNkRThWZl96SHdaNg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Prefeitura de Itabuna intensifica o fortalecimento da agricultura familiar com nova remessa de calcário para associações rurais - Prefeitura de Itabuna</t>
+          <t>Alta do enxofre supera 130% em 2025 - Agrolink</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>17/11/2025 05:00</t>
+          <t>11/11/2025 05:00</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQS3hSaWdZcnZzaWJaelBFbnN0aUExa2xWQUhUa2xFMFJPYWI1QXFBR3VTOFVqRm1BS1VjQkxmYmo4OVd4R0JXWno0dDBrYjYtWXhFVzI3LXhYeXh0Z0xsbUxvWmp6MG9xSGVaMktwUFpUbkZyMkpRcEY0anI5eUdaTUlhblJlMUpsbnl0dmx0OXJrZTk1MDVMNGJscDc5T2hINk9ZQUd6c0dXNVpSNGZMc2hGTU40X3VlaUdtMmJvaGlXM1oxdnpLSld2d1hMZGlHaUdOTFljOW1mdmJmVDlYWk9BUFFDaFYyR2hPSUNkRThWZl96SHdaNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOalZhb0h6TTl5Nkx4dlY5d3NZc0tXS0c1anVfX3B5WXMxa1NTS1lXNmlwRmhvdlFiMDhtYmszbS13cl9UeUlOeW9xQVAzd05BM3ZudnRYZUt5LUkwSmdJbVVpaEg2NFZMdmJtVHQ1Z1pCenBjSmhFaV8yN3FWR1VIeHExS21UZzQyT21YcA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Alta do enxofre supera 130% em 2025 - agrolink.com.br</t>
+          <t>Autoridades acompanham recebimento de nova remessa de calcário para fortalecer agricultura familiar - Prefeitura de Itabuna</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>11/11/2025 05:00</t>
+          <t>08/11/2025 05:00</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOalZhb0h6TTl5Nkx4dlY5d3NZc0tXS0c1anVfX3B5WXMxa1NTS1lXNmlwRmhvdlFiMDhtYmszbS13cl9UeUlOeW9xQVAzd05BM3ZudnRYZUt5LUkwSmdJbVVpaEg2NFZMdmJtVHQ1Z1pCenBjSmhFaV8yN3FWR1VIeHExS21UZzQyT21YcA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNdlJVcUg5WXdKaDVrNmtoTWtpNlhxWi1oMFEwTjduTHU2d2E0cHVkaEV3M05Cd0pocDVDY2Z4aEZNWEhMY2I0WjhZNGxYQTNQaVUxaDFZaWpCckdSdkM5T0xjdWxnaVpabGY3OEV0c0xxN1R5anROVmFUS0ZaYW1meHp5cXNocTBCUl9aUDU5Vi1qTDR0dGotYVlkZG5FcXNOdTZIMnQxRzQ4TkJvY0RuVVRfOW9qbUIzaFZ3U0I5cVdTSFdxOVBpeDlIWWphd2hVQjdR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Autoridades acompanham recebimento de nova remessa de calcário para fortalecer agricultura familiar - Prefeitura de Itabuna</t>
+          <t>Empresa mineira cria primeiro e-commerce para o setor de mineração - Diário do Comércio</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>08/11/2025 05:00</t>
+          <t>30/10/2025 04:00</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNdlJVcUg5WXdKaDVrNmtoTWtpNlhxWi1oMFEwTjduTHU2d2E0cHVkaEV3M05Cd0pocDVDY2Z4aEZNWEhMY2I0WjhZNGxYQTNQaVUxaDFZaWpCckdSdkM5T0xjdWxnaVpabGY3OEV0c0xxN1R5anROVmFUS0ZaYW1meHp5cXNocTBCUl9aUDU5Vi1qTDR0dGotYVlkZG5FcXNOdTZIMnQxRzQ4TkJvY0RuVVRfOW9qbUIzaFZ3U0I5cVdTSFdxOVBpeDlIWWphd2hVQjdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOYjhzVnJadjNlOHRJMXVuLVlrd25FQWUzWGduc1FPRXFsbE91a2NoOHFCdWg2cjg5eDlCaUZOWTZqOXY4VnpwdTFrb05ReXBlTzlXUE9qSzB6M2FpNTZER3FMLTFZcUJabzQ0VnY2QXRzSHlfMXdRei14MEdJTFpvTXU1NUhpdm9aT3BlS3BqV3Y4U2pnQnQwVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Empresa mineira cria primeiro e-commerce para o setor de mineração - diariodocomercio.com.br</t>
+          <t>Trabalhadores da mineração podem parar: Metabase contesta proposta da CMOC em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -10928,151 +10928,151 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOYjhzVnJadjNlOHRJMXVuLVlrd25FQWUzWGduc1FPRXFsbE91a2NoOHFCdWg2cjg5eDlCaUZOWTZqOXY4VnpwdTFrb05ReXBlTzlXUE9qSzB6M2FpNTZER3FMLTFZcUJabzQ0VnY2QXRzSHlfMXdRei14MEdJTFpvTXU1NUhpdm9aT3BlS3BqV3Y4U2pnQnQwVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNOTg0UGo4RnZPRGE0RUY3TTcyamY2cEZROVhGT3dTNjZpdjRKX0poYXhWR01YOURsT1FoU0lQRU5WNW0zdGtndG5sUUM5YlhqOFNmTER6eF9OLWtOT0ZrMmdLR0ZzeHpVRGE0T0FfMjdPeVJydk5yNEEwem9xMlVNbjRwUWltd9IBiwFBVV95cUxNN2lrTE5FN3BabGE3UzhMOG1qRWRsUWFsVE5CUXZCeWQ0VkVpa0pONUVqdzJBNTdTdW1tY1VreHI1TnM1bDE5UDZIbWtKWjlHemdHOVR6UU13VFJvS0xtXzVHdEplaHgxQ0txcnNncW1TMTM0ZzVDakpPQ3FTMEVhM3ZJWFhrZXR1UWFn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Trabalhadores da mineração podem parar: Metabase contesta proposta da CMOC em Catalão - Badiinho</t>
+          <t>Enxofre dispara 115% em 2025 e preocupa setor de fertilizantes - revistacultivar.com.br</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>30/10/2025 04:00</t>
+          <t>27/10/2025 04:00</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNOTg0UGo4RnZPRGE0RUY3TTcyamY2cEZROVhGT3dTNjZpdjRKX0poYXhWR01YOURsT1FoU0lQRU5WNW0zdGtndG5sUUM5YlhqOFNmTER6eF9OLWtOT0ZrMmdLR0ZzeHpVRGE0T0FfMjdPeVJydk5yNEEwem9xMlVNbjRwUWltd9IBiwFBVV95cUxNN2lrTE5FN3BabGE3UzhMOG1qRWRsUWFsVE5CUXZCeWQ0VkVpa0pONUVqdzJBNTdTdW1tY1VreHI1TnM1bDE5UDZIbWtKWjlHemdHOVR6UU13VFJvS0xtXzVHdEplaHgxQ0txcnNncW1TMTM0ZzVDakpPQ3FTMEVhM3ZJWFhrZXR1UWFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQSFlkU21VODVuMXFLakZsaktmNlRORjVPd0pET2F1bE5FWEJaNWkxUEhNcDVNUVRXaEJlODI3ZG05RTBLZ21rWTE4dk9zOW82NVBFZjltNzlWNTZEb2IteDRNa2dCZkpDNlQxeUJPWW42UjR5SkJDckhXbnFRRHYxTUk2SGlfQl8xY3BJUW1qREM3WFMtSzN3THRqMl9KYThhX2lv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Enxofre dispara 115% em 2025 e preocupa setor de fertilizantes - Revista Cultivar</t>
+          <t>Agricultural lime spills on Mattis; drivers encouraged to wash it off ASAP</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>27/10/2025 04:00</t>
+          <t>22/10/2025 10:56</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQSFlkU21VODVuMXFLakZsaktmNlRORjVPd0pET2F1bE5FWEJaNWkxUEhNcDVNUVRXaEJlODI3ZG05RTBLZ21rWTE4dk9zOW82NVBFZjltNzlWNTZEb2IteDRNa2dCZkpDNlQxeUJPWW42UjR5SkJDckhXbnFRRHYxTUk2SGlfQl8xY3BJUW1qREM3WFMtSzN3THRqMl9KYThhX2lv?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a70b554b1fb44d3bd04c691a5851b8e&amp;url=https%3a%2f%2fwww.yahoo.com%2fnews%2farticles%2fagricultural-lime-spills-mattis-drivers-205639042.html&amp;c=8051146937692834356&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Agricultural lime spills on Mattis; drivers encouraged to wash it off ASAP</t>
+          <t>Especialistas registram a maior coruja do continente que come até gambás e coalas - Revista Fórum</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>22/10/2025 10:56</t>
+          <t>20/10/2025 04:00</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a708df9e25249dbab0f0f4f5ec02cba&amp;url=https%3a%2f%2fwww.yahoo.com%2fnews%2farticles%2fagricultural-lime-spills-mattis-drivers-205639042.html&amp;c=8051146937692834356&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOZWZIam82STB1M05WMm45bHNjdVJBTl9rRU9zanpRMV9XM0ZXbERYTmFJVVF4M25ZSlVsTWNTVEtTZmR1cXI0REt4SnU2Y3ZyaGNiUTVNenlyNXJHMnhMNTVnbHNnS2FqQjVLZTNvYTN3ZzZaYkplc21fUzB2MGZSM2tvQ0FXSnZpbEJWOG9nRmM0ME1sYnU3R3Zod1hyVzRpRGd4NVZmTjZNZ051dDFkY0FOeVZEeWVRYWtVUFlLSGFLOWowQ2ticnFn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Especialistas registram a maior coruja do continente que come até gambás e coalas - revistaforum.com.br</t>
+          <t>Após casos de metanol, cresce busca por regularização da cachaça em MG - Rádio Itatiaia</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>20/10/2025 04:00</t>
+          <t>15/10/2025 04:00</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOZWZIam82STB1M05WMm45bHNjdVJBTl9rRU9zanpRMV9XM0ZXbERYTmFJVVF4M25ZSlVsTWNTVEtTZmR1cXI0REt4SnU2Y3ZyaGNiUTVNenlyNXJHMnhMNTVnbHNnS2FqQjVLZTNvYTN3ZzZaYkplc21fUzB2MGZSM2tvQ0FXSnZpbEJWOG9nRmM0ME1sYnU3R3Zod1hyVzRpRGd4NVZmTjZNZ051dDFkY0FOeVZEeWVRYWtVUFlLSGFLOWowQ2ticnFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPdXJKTTRWVzZzUm0zSkpRRVJvRXpBQnNQRlg2YUk5MjFSWjhFenlIeHlmYklmS3YyS3A1TFhYSlNab080RHpmcndRckQ5bHl0Yk9aYzRtVkQzTFRiTGo3S05tU3QzcVluYnhZSEk4LXZDdDlfX2JTZFZnekVxVTdnWmtzanhxSkRHcjJDT2YwUERObklaSWgxU0lzYUNoSmF2NlBGbjF3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Após casos de metanol, cresce busca por regularização da cachaça em MG - Rádio Itatiaia</t>
+          <t>Corredor hidroviário opera em Roraima com potencial para movimentar soja, calcário e fertilizantes - GlobalFert</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>15/10/2025 04:00</t>
+          <t>14/10/2025 04:00</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPdXJKTTRWVzZzUm0zSkpRRVJvRXpBQnNQRlg2YUk5MjFSWjhFenlIeHlmYklmS3YyS3A1TFhYSlNab080RHpmcndRckQ5bHl0Yk9aYzRtVkQzTFRiTGo3S05tU3QzcVluYnhZSEk4LXZDdDlfX2JTZFZnekVxVTdnWmtzanhxSkRHcjJDT2YwUERObklaSWgxU0lzYUNoSmF2NlBGbjF3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPWS13UUhhekp2enROZ3Z3SEpNWFd1REZvME9tS0EwT1Z0Y2ZxSHZOTE1oRWNKQ3lGZUV4TW5Gd2ZtT0lpZ1o2YWZXbWh3cjZNSlpaMHZfaF9vZUREMTJObk56TUlSRERYWk5Vd1BWZTJtOXBEMzJlVDZqRnc5M0xMTndCOU56SDZrOFF1dDJUeEFmRzlBdG1fc0pXVEJWTmJaODliQjJnWkdHVGVWak9hY3BtWllxa3lCTFl5SXZNYTRfakNBU1RneXhjR2RxWkxVU0RHZm9oLWp1RXdLZkl3WnVjdExGcjZ3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Corredor hidroviário opera em Roraima com potencial para movimentar soja, calcário e fertilizantes - GlobalFert</t>
+          <t>De 100 mil a 1,2 milhão: UGC faz sabonete de enxofre da Granado multiplicar as vendas - Mundo do Marketing</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>14/10/2025 04:00</t>
+          <t>13/10/2025 04:00</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPWS13UUhhekp2enROZ3Z3SEpNWFd1REZvME9tS0EwT1Z0Y2ZxSHZOTE1oRWNKQ3lGZUV4TW5Gd2ZtT0lpZ1o2YWZXbWh3cjZNSlpaMHZfaF9vZUREMTJObk56TUlSRERYWk5Vd1BWZTJtOXBEMzJlVDZqRnc5M0xMTndCOU56SDZrOFF1dDJUeEFmRzlBdG1fc0pXVEJWTmJaODliQjJnWkdHVGVWak9hY3BtWllxa3lCTFl5SXZNYTRfakNBU1RneXhjR2RxWkxVU0RHZm9oLWp1RXdLZkl3WnVjdExGcjZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQTWprTW9RT3lxQkVOTjZ3QzVvX2R0RHhCZUxFeE1BNGtMY3VKc1Z4NWViSEYyLXdFQnRkWlYwTEZSOHg4UHpQLTJ3RDEySk9Ld2xkaGp4WnVLQWUtcFdrVzcyQ01pUGxfS2lwbzNERGp3WVdYYmdTd2h6SUxVdEhnUHdDRG5Hb2lRZjlBNUQ5QU1MYnlDV3kyRHpFR3lRcXNMa2xDMTR6Y2ZSaE1JczI2RkpENGU1VE0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>De 100 mil a 1,2 milhão: UGC faz sabonete de enxofre da Granado multiplicar as vendas - Mundo do Marketing</t>
+          <t>Prefeitura de Itabuna recebe 25 toneladas de calcário para fortalecer a produção rural - Prefeitura de Itabuna</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -11082,107 +11082,107 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQTWprTW9RT3lxQkVOTjZ3QzVvX2R0RHhCZUxFeE1BNGtMY3VKc1Z4NWViSEYyLXdFQnRkWlYwTEZSOHg4UHpQLTJ3RDEySk9Ld2xkaGp4WnVLQWUtcFdrVzcyQ01pUGxfS2lwbzNERGp3WVdYYmdTd2h6SUxVdEhnUHdDRG5Hb2lRZjlBNUQ5QU1MYnlDV3kyRHpFR3lRcXNMa2xDMTR6Y2ZSaE1JczI2RkpENGU1VE0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPM0Ztc21zYlQ0UThHanYxVnMtV3F4VElqcUtOLWt5S1FhYy1IUU9FdURWenZ0RkIzNGVFMVhRRGdHc25IZDFSNDU1NFc4N0c3NmtQMDVHVjcyREpWWWtFNlY5U0k2OE9waFRZWFkxTEIxYkoyd3lkd2ZyRTBRcVg1cEs3WEtTSHgzRkQ5N01ocTVNWjhhQmxBcUpXbEFJRTBiZHIxSzczZGRwNm5NWldZTmdIY0hsUTA4RE1qOXNMdkZLdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Prefeitura de Itabuna recebe 25 toneladas de calcário para fortalecer a produção rural - Prefeitura de Itabuna</t>
+          <t>Notícias - Caçapava do Sul - Enacal 2025: O Futuro do Calcário e da Produtividade Agrícola Nacional em debate - PORTAL FARRAPO</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>13/10/2025 04:00</t>
+          <t>10/10/2025 04:00</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPM0Ztc21zYlQ0UThHanYxVnMtV3F4VElqcUtOLWt5S1FhYy1IUU9FdURWenZ0RkIzNGVFMVhRRGdHc25IZDFSNDU1NFc4N0c3NmtQMDVHVjcyREpWWWtFNlY5U0k2OE9waFRZWFkxTEIxYkoyd3lkd2ZyRTBRcVg1cEs3WEtTSHgzRkQ5N01ocTVNWjhhQmxBcUpXbEFJRTBiZHIxSzczZGRwNm5NWldZTmdIY0hsUTA4RE1qOXNMdkZLdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPX0g1MjlaM01tc2JuWk5KX2dHeG41elVsX3laa0FBemVkVC01eGJzZlhaY0xndEFXNHcxVjNNdmR5YmZiRGotcERXWXVHaFBnWmZYdFk0cmhqNXV3TnMzV0had0NKbE5DTlJ4cDh5dWdSTFZhM1kyU2M3SVVJdXRoeDdsTGxHZTF1RHI5RnFiVmNuMXhpcm42T2xkTUgyVG5IbW5RTGRxRHdUb3RGemtkemhlOTZoaWplTnhoTU12ZGZ5aExmZ0EyVTMwOHJMN25veGgxbFYzaEtjU0FfOU9Wam5B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Carmeuse</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Notícias - Caçapava do Sul - Enacal 2025: O Futuro do Calcário e da Produtividade Agrícola Nacional em debate - PORTAL FARRAPO</t>
+          <t>Carmeuse Brasil inaugura nova planta em Taquaritinga e fortalece presença no setor - JornalCana</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>10/10/2025 04:00</t>
+          <t>09/10/2025 04:00</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPX0g1MjlaM01tc2JuWk5KX2dHeG41elVsX3laa0FBemVkVC01eGJzZlhaY0xndEFXNHcxVjNNdmR5YmZiRGotcERXWXVHaFBnWmZYdFk0cmhqNXV3TnMzV0had0NKbE5DTlJ4cDh5dWdSTFZhM1kyU2M3SVVJdXRoeDdsTGxHZTF1RHI5RnFiVmNuMXhpcm42T2xkTUgyVG5IbW5RTGRxRHdUb3RGemtkemhlOTZoaWplTnhoTU12ZGZ5aExmZ0EyVTMwOHJMN25veGgxbFYzaEtjU0FfOU9Wam5B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOOTlxVkNXc2dQdlFScWo4WTJRb2wwd0tGVDUzcGVKakwycEJTWWlGRGo2S1JfNEJUZkF5TjB0LVRqNFc3a3lweTZvZ1dkVkxvanQxU0FOdEtjSC1NRVMzUTN6TFBVMmloa1JRdXdMc1ZmSU83YXNHeXNMQUhQUDd5RFAyWDltYlJKa1ZBSHhnVUNpSDBlZFpRamRaN2RXU0tITjBQa0hORk1zU0RNTl9pQ21pRDA0YVEwbWI0V3k1ZlRFYUZWZWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Carmeuse Brasil inaugura nova planta em Taquaritinga e fortalece presença no setor - JornalCana</t>
+          <t>Aplicar calcário na cobertura da pastagem funciona mesmo? - Portal DBO</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>09/10/2025 04:00</t>
+          <t>02/10/2025 04:00</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOOTlxVkNXc2dQdlFScWo4WTJRb2wwd0tGVDUzcGVKakwycEJTWWlGRGo2S1JfNEJUZkF5TjB0LVRqNFc3a3lweTZvZ1dkVkxvanQxU0FOdEtjSC1NRVMzUTN6TFBVMmloa1JRdXdMc1ZmSU83YXNHeXNMQUhQUDd5RFAyWDltYlJKa1ZBSHhnVUNpSDBlZFpRamRaN2RXU0tITjBQa0hORk1zU0RNTl9pQ21pRDA0YVEwbWI0V3k1ZlRFYUZWZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOOUUtMGV2R2N5MEo2X3BWR3J2REloQS1Vb0oxVUNWazU1c2FUWHBTWnJoS2E5ODZoaW5JT1lNSlFDT0NIQkVqSFI0RTNQai1vQWhlR0JFcWdXTGJFSkNVa2RjOXBRaEVwYjBzNmc4R0R6YlNEbURKbGt2SEZRU0V6ZktaWEhzTWpla1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Aplicar calcário na cobertura da pastagem funciona mesmo? - Portal DBO</t>
+          <t>Preço do enxofre sobe 90% e pressiona mercado de fertilizantes - Agrishow</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>02/10/2025 04:00</t>
+          <t>01/10/2025 04:00</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOOUUtMGV2R2N5MEo2X3BWR3J2REloQS1Vb0oxVUNWazU1c2FUWHBTWnJoS2E5ODZoaW5JT1lNSlFDT0NIQkVqSFI0RTNQai1vQWhlR0JFcWdXTGJFSkNVa2RjOXBRaEVwYjBzNmc4R0R6YlNEbURKbGt2SEZRU0V6ZktaWEhzTWpla1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTkJ5d2xkbzI1SmJpQUVVbEptOWZ3ZFp2Q2FlajdjQW9HUEdPa2tCVzlYRHdXU0lmeHJnd0VnZHVOMXlzd3hBOWpSU0w2WXVlY0djNFNWT2hSS0x0blItY2J1a0IweTVZVlRKV1U4Yzlkb19WU1BiZjdZemQtcmhvVUpsSDEydW1mLTQydnBjTWJ3alRBWjJyM1V0WTZQb2x6QXNwTg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Preço do enxofre sobe 90% e pressiona mercado de fertilizantes - Agrishow</t>
+          <t>Lhoist abre inscrições para nova edição do Programa Jovem Aprendiz com 40 vagas para mulheres - portalarcos.com.br</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -11192,183 +11192,183 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTkJ5d2xkbzI1SmJpQUVVbEptOWZ3ZFp2Q2FlajdjQW9HUEdPa2tCVzlYRHdXU0lmeHJnd0VnZHVOMXlzd3hBOWpSU0w2WXVlY0djNFNWT2hSS0x0blItY2J1a0IweTVZVlRKV1U4Yzlkb19WU1BiZjdZemQtcmhvVUpsSDEydW1mLTQydnBjTWJ3alRBWjJyM1V0WTZQb2x6QXNwTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNSGxOMXVsOFpvTE9mS0Y5ZW1JdFcwRWRvdHE4NmNBZzFBWWdLSmxzOE4wY0RGdXNTMk8wNDJ5RHRXSVhobXhYaVJaMU9LU0tFZ29KRXZPYWhEenc1ckRKVlUtamphUnoyVnlIZTF4VVBJTkFvVkNDcGFYWmhUUnR1RWhlYy1rN3BBcXZNdTMzU2pfRzhReFR5d3VoWV9CZHh6aUtPTjdnaTRjMmQxZ3ZWWER0bC12UHRfRnR4bk5rRl8wNjc5UDBaLTNZb3RTX19ZMTdPbg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Lhoist abre inscrições para nova edição do Programa Jovem Aprendiz com 40 vagas para mulheres - Portal Arcos</t>
+          <t>Congo vai retomar a exportação de cobalto, depois de ter forçado uma alta de 60% - InvestNews - InvestNews</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>01/10/2025 04:00</t>
+          <t>21/09/2025 04:00</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNSGxOMXVsOFpvTE9mS0Y5ZW1JdFcwRWRvdHE4NmNBZzFBWWdLSmxzOE4wY0RGdXNTMk8wNDJ5RHRXSVhobXhYaVJaMU9LU0tFZ29KRXZPYWhEenc1ckRKVlUtamphUnoyVnlIZTF4VVBJTkFvVkNDcGFYWmhUUnR1RWhlYy1rN3BBcXZNdTMzU2pfRzhReFR5d3VoWV9CZHh6aUtPTjdnaTRjMmQxZ3ZWWER0bC12UHRfRnR4bk5rRl8wNjc5UDBaLTNZb3RTX19ZMTdPbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNckRwbnFjSEdfS3dIN0t4S21CdkE1U1lZUWpLVE9Ubjh4MTltOFRtbS1hTi03YXVqczV3QWVnOEptUzRoXzYwb1drZy1RMzlEa2tOY19mN1JsUG8wWFlWeGpCbS1iMnFFUFByR095ZUpEbWVqOXcyTTVJV050R0g4QXlxQ0hzdXNoMUNLdHNwM3FHVjFORUxiakREZ2R6cXgzajdScGMzcTdVZUQtRDVQcnpaX2zSAboBQVVfeXFMT3NhcHA1NWlldE1CSTZCYlFFMXdYaExRSjU0UEhfRlRZWDFUam1OQzZLbXdxcnlqUnZBSW92bFN6WnczVlNwZ1VQRDNlMWIzaGFIWjF3V2FCZFVUY0ljTWRQWE5BTVFNY0EzUjlWd0xQa0RWdmZBSE9OdUhVd2F3a3JHaWNvei02NV83R3hfNkUyQU84UnpiMlRhU3laWDB5TXViclZ5SzJTcjd1bllCcFhXc0hGb3dMdVZB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Congo vai retomar a exportação de cobalto, depois de ter forçado uma alta de 60% - InvestNews - InvestNews</t>
+          <t>Aplicação conjunta de calcário e fosfato natural gera 12 sacas de soja a mais por hectare - canalrural.com.br</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>21/09/2025 04:00</t>
+          <t>20/09/2025 04:00</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNckRwbnFjSEdfS3dIN0t4S21CdkE1U1lZUWpLVE9Ubjh4MTltOFRtbS1hTi03YXVqczV3QWVnOEptUzRoXzYwb1drZy1RMzlEa2tOY19mN1JsUG8wWFlWeGpCbS1iMnFFUFByR095ZUpEbWVqOXcyTTVJV050R0g4QXlxQ0hzdXNoMUNLdHNwM3FHVjFORUxiakREZ2R6cXgzajdScGMzcTdVZUQtRDVQcnpaX2zSAboBQVVfeXFMT3NhcHA1NWlldE1CSTZCYlFFMXdYaExRSjU0UEhfRlRZWDFUam1OQzZLbXdxcnlqUnZBSW92bFN6WnczVlNwZ1VQRDNlMWIzaGFIWjF3V2FCZFVUY0ljTWRQWE5BTVFNY0EzUjlWd0xQa0RWdmZBSE9OdUhVd2F3a3JHaWNvei02NV83R3hfNkUyQU84UnpiMlRhU3laWDB5TXViclZ5SzJTcjd1bllCcFhXc0hGb3dMdVZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPWmZCdkpqRF9uYUhERS1tS050aHNvaGpjNE1XUWJ4QTZmZ1dtQk1JcElPNEZLaXA1NENVX3hDQ0YwQWZTMVgyY3FsTi12cVBUSG5CaTR2aldlSXRRNWJGeklvNTh0YlZsSmV6SUY5amN5aUJGbFZBZWVuTmhjN1Fsa1VuZVVfSk9IWGtjbFRTUG1GQURHTHV3VDkzRHlKMEowaFdmMjlCc2JyQkZzeno3WktXd212WUhHenBCRy1uUVZQV3VPbHUwUXF6bGI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Aplicação conjunta de calcário e fosfato natural gera 12 sacas de soja a mais por hectare - Canal Rural</t>
+          <t>Áurea investe em novo distribuidor de calcário para o setor agrícola - jornalbomdia.com.br</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>20/09/2025 04:00</t>
+          <t>15/09/2025 04:00</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPWmZCdkpqRF9uYUhERS1tS050aHNvaGpjNE1XUWJ4QTZmZ1dtQk1JcElPNEZLaXA1NENVX3hDQ0YwQWZTMVgyY3FsTi12cVBUSG5CaTR2aldlSXRRNWJGeklvNTh0YlZsSmV6SUY5amN5aUJGbFZBZWVuTmhjN1Fsa1VuZVVfSk9IWGtjbFRTUG1GQURHTHV3VDkzRHlKMEowaFdmMjlCc2JyQkZzeno3WktXd212WUhHenBCRy1uUVZQV3VPbHUwUXF6bGI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPOGs0MF9ObWVia181OG5TRmxlNmswYjA4LVZUNjdNSko5akptRGRFX2w4R3Yzam9aM24xazdsUU1PbjRqOXFNbDF6LWhscllMYWJYVUlPVExVSWptRUNrY3J6YWZYdEtqUjNyR0tIb1B2bkVLRGdrMzg5NzJ2SVpzYzVhdlhFUm1uNHRWY2xYX1VOSUp5dkVqc1hUX01GWjFaQWxYTzRRMUdOOTIxb0I4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Áurea investe em novo distribuidor de calcário para o setor agrícola - Jornal Bom Dia</t>
+          <t>CSN apresenta projeto de aproveitamento de resíduos ao secretário de Agricultura</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>15/09/2025 04:00</t>
+          <t>07/09/2025 14:00</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPOGs0MF9ObWVia181OG5TRmxlNmswYjA4LVZUNjdNSko5akptRGRFX2w4R3Yzam9aM24xazdsUU1PbjRqOXFNbDF6LWhscllMYWJYVUlPVExVSWptRUNrY3J6YWZYdEtqUjNyR0tIb1B2bkVLRGdrMzg5NzJ2SVpzYzVhdlhFUm1uNHRWY2xYX1VOSUp5dkVqc1hUX01GWjFaQWxYTzRRMUdOOTIxb0I4?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a70b55360ee4ce0b0aa0ac3f6869496&amp;url=https%3a%2f%2fdiariodovale.com.br%2fdestaque%2fcsn-apresenta-projeto-de-aproveitamento-de-residuos-ao-secretario-de-agricultura%2f&amp;c=15059526041694740664&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>CSN apresenta projeto de aproveitamento de resíduos ao secretário de Agricultura</t>
+          <t>Pesquisa da UFMT aponta ganhos na soja com calcário e gesso - revistacultivar.com.br</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>07/09/2025 14:00</t>
+          <t>05/09/2025 04:00</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a708df749304381a4ad0ae0406775c0&amp;url=https%3a%2f%2fdiariodovale.com.br%2fdestaque%2fcsn-apresenta-projeto-de-aproveitamento-de-residuos-ao-secretario-de-agricultura%2f&amp;c=15059526041694740664&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNTlZiNHZqcS1SX0dWTEZ0OEh6UnNzb2EzNEl6bjVNODBrZHFoODcybHlyRjlOd1JJalliX3F1UDczcGdoU2F0bnFDck9tbDJpYjREX2pQVExqdVJxSzNDTHIwVm5DckEwOElfdmYtbmhBYkd5TVJjbWtxenhtWWJITXhETVVYUER2dVFVNXpwalVXV2hLLUhvbzNGdXlvOXJB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Pesquisa da UFMT aponta ganhos na soja com calcário e gesso - Revista Cultivar</t>
+          <t>Mais de 5 mil toneladas de calcário foram entregues pelo governo de RO a produtores em 2025</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>05/09/2025 04:00</t>
+          <t>02/09/2025 14:00</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNTlZiNHZqcS1SX0dWTEZ0OEh6UnNzb2EzNEl6bjVNODBrZHFoODcybHlyRjlOd1JJalliX3F1UDczcGdoU2F0bnFDck9tbDJpYjREX2pQVExqdVJxSzNDTHIwVm5DckEwOElfdmYtbmhBYkd5TVJjbWtxenhtWWJITXhETVVYUER2dVFVNXpwalVXV2hLLUhvbzNGdXlvOXJB?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a70b55360ee4ce0b0aa0ac3f6869496&amp;url=https%3a%2f%2fwww.tudorondonia.com%2fnoticias%2fmais-de-5-mil-toneladas-de-calcario-foram-entregues-pelo-governo-de-ro-a-produtores-em-2025%2c146623.shtml&amp;c=898900062870723656&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Mais de 5 mil toneladas de calcário foram entregues pelo governo de RO a produtores em 2025</t>
+          <t>Novo método propõe cálculo mais preciso da calagem para aumentar produtividade agrícola - UFLA - Universidade Federal de Lavras</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>02/09/2025 14:00</t>
+          <t>02/09/2025 04:00</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a708df749304381a4ad0ae0406775c0&amp;url=https%3a%2f%2fwww.tudorondonia.com%2fnoticias%2fmais-de-5-mil-toneladas-de-calcario-foram-entregues-pelo-governo-de-ro-a-produtores-em-2025%2c146623.shtml&amp;c=898900062870723656&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUTRJN01vT2x1dVliRnVleUlieDVXbkc5eWYtZVZBSXc2OEt5VmttWWhyX1liTzQ1SGx4YWN3alZMNWdMNmVYVjJoM2ZYNzN5OXZyUGZOQXVZSUxLYjNLcXktdVVMY0hqNWdNMVU1NXR5cVBRM0NpMFMtdzNDajJTTUNRbTYtOVVXRTdocWgtV3ptN2ZDbXZMeS1YbjFSVjBTY2RtT1N5VkxOX1VhVEYyOGcxWWF2UVh2RGlzY2ZPUEpyWVJQZ0E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Novo método propõe cálculo mais preciso da calagem para aumentar produtividade agrícola - UFLA - Universidade Federal de Lavras</t>
+          <t>RESULTADOS | CMOC Brasil produz 3% a mais de nióbio no primeiro semestre - Brasil Mineral</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>02/09/2025 04:00</t>
+          <t>01/09/2025 04:00</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUTRJN01vT2x1dVliRnVleUlieDVXbkc5eWYtZVZBSXc2OEt5VmttWWhyX1liTzQ1SGx4YWN3alZMNWdMNmVYVjJoM2ZYNzN5OXZyUGZOQXVZSUxLYjNLcXktdVVMY0hqNWdNMVU1NXR5cVBRM0NpMFMtdzNDajJTTUNRbTYtOVVXRTdocWgtV3ptN2ZDbXZMeS1YbjFSVjBTY2RtT1N5VkxOX1VhVEYyOGcxWWF2UVh2RGlzY2ZPUEpyWVJQZ0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWXVjQkdsWUV3ZktWcld5RzIyZFlBSFhybW9wNEV4NGV4OGdnaDBha0NrZzI0X3VzN2N4d0M0bGNUdkRtYmR6bFE2Q0JDbkJyN25iVzFDemJDbTlOSDJ4NENpTjNZWWpTbFkzTzF0SXhIQUhCdkw2Y1J4aW9nVEFhdVRBR25aTVJldElQQ2pabFZZNWVyMWNoSndGd1hTUzBXS3c?oc=5</t>
         </is>
       </c>
     </row>
@@ -11397,130 +11397,108 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>RESULTADOS | CMOC Brasil produz 3% a mais de nióbio no primeiro semestre - Brasil Mineral</t>
+          <t>Mais de 1.600 toneladas de calcário são entregues a agricultores familiares para preparo de solo - Prefeitura Municipal de Boa Vista</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>01/09/2025 04:00</t>
+          <t>22/08/2025 04:00</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWXVjQkdsWUV3ZktWcld5RzIyZFlBSFhybW9wNEV4NGV4OGdnaDBha0NrZzI0X3VzN2N4d0M0bGNUdkRtYmR6bFE2Q0JDbkJyN25iVzFDemJDbTlOSDJ4NENpTjNZWWpTbFkzTzF0SXhIQUhCdkw2Y1J4aW9nVEFhdVRBR25aTVJldElQQ2pabFZZNWVyMWNoSndGd1hTUzBXS3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQLXdRbkZkNHpnb1NhakYtOWNSTkFBa2VTdFNJTUhPUXZZeXhrekp3dlg4UEZuUWZDWk5SZm44LUQtWDdUNkVkZUdRSWRkcXZ1QUhCUzVqRzM3YTU3TkFGYlJrcE93YXQ5LS15X29oWkE2OV82ZmVKQ2JaWXhJcjZycDl5ZURxMGhDVERtcEttT0NVb1M4V2hOdEpCd2JpZWdlWWV0STZXdk9HZUtrTm04WmNSb2JJalVsbTk5Wk43OTAyTF9ESXNobjQ0VU5XS2xMQ0dHaQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Mais de 1.600 toneladas de calcário são entregues a agricultores familiares para preparo de solo - Prefeitura Municipal de Boa Vista</t>
+          <t>Spreading Ag Lime for Food Plots | Improving Deer Habitat on Our Southern Illinois Farm</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>22/08/2025 04:00</t>
+          <t>18/08/2025 14:00</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQLXdRbkZkNHpnb1NhakYtOWNSTkFBa2VTdFNJTUhPUXZZeXhrekp3dlg4UEZuUWZDWk5SZm44LUQtWDdUNkVkZUdRSWRkcXZ1QUhCUzVqRzM3YTU3TkFGYlJrcE93YXQ5LS15X29oWkE2OV82ZmVKQ2JaWXhJcjZycDl5ZURxMGhDVERtcEttT0NVb1M4V2hOdEpCd2JpZWdlWWV0STZXdk9HZUtrTm04WmNSb2JJalVsbTk5Wk43OTAyTF9ESXNobjQ0VU5XS2xMQ0dHaQ?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a70b554b1fb44d3bd04c691a5851b8e&amp;url=https%3a%2f%2fwww.msn.com%2fen-us%2ffoodanddrink%2ffoodnews%2fspreading-ag-lime-for-food-plots-improving-deer-habitat-on-our-southern-illinois-farm%2fvi-AA1KMIuT&amp;c=14837966501036489110&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>Carmeuse</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Spreading Ag Lime for Food Plots | Improving Deer Habitat on Our Southern Illinois Farm</t>
+          <t>Multinacional Carmeuse Brasil anuncia investimento em Araçatuba - O LIBERAL REGIONAL</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>18/08/2025 14:00</t>
+          <t>15/08/2025 04:00</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a708df9e25249dbab0f0f4f5ec02cba&amp;url=https%3a%2f%2fwww.msn.com%2fen-us%2ffoodanddrink%2ffoodnews%2fspreading-ag-lime-for-food-plots-improving-deer-habitat-on-our-southern-illinois-farm%2fvi-AA1KMIuT&amp;c=14837966501036489110&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUC16YUloeERuMjNLeHMtOVBReUltWEN5dGhOMFctRmd0T25uYzdUbVM4SnFZcVA4X0owRzMtQUg5eUN1WXpRdk5abjZrYkVNcXcyYzNYQ2hsZGdFWFo4SU9JTTNOcnJqVVhMc0ttTDd2T2d3X21WZzlNUUhFck1MSzVUdFVRZENCZ21LN2h4NURZR0NjRTBKaFRhUjRoemFOY2ZJ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Multinacional Carmeuse Brasil anuncia investimento em Araçatuba - O LIBERAL REGIONAL</t>
+          <t>Calcário líquido: é por isso que ele não funciona na correção do solo - canalrural.com.br</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>15/08/2025 04:00</t>
+          <t>13/08/2025 04:00</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUC16YUloeERuMjNLeHMtOVBReUltWEN5dGhOMFctRmd0T25uYzdUbVM4SnFZcVA4X0owRzMtQUg5eUN1WXpRdk5abjZrYkVNcXcyYzNYQ2hsZGdFWFo4SU9JTTNOcnJqVVhMc0ttTDd2T2d3X21WZzlNUUhFck1MSzVUdFVRZENCZ21LN2h4NURZR0NjRTBKaFRhUjRoemFOY2ZJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNSHlxZDdybW5fY0FOMmRRMEN0bURlZDAxSjQ1LWJrOExhWUxTa1RqT2l6Z2FqVWZZWFlLOG9LekduQTA3Vmp0QW5VME1oNEktdmZ4cDdsbU9YX0pJMUNwbVdzaDdkbzB5Mi1DalF0Z0JoN1ZoVE1ENVB2UjJpdHp3LWFVZGZsV2pETlZRTlhQNkxlR2o1RkstSUhiQ1FqX3ZXSDROcFpWdFh4Yzd2?oc=5</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Calcário líquido: é por isso que ele não funciona na correção do solo - Canal Rural</t>
+          <t>Limestone Capital Investe na Nokken para Abastecer a Expansão de Hospitalidade Modular - PR Newswire</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>13/08/2025 04:00</t>
+          <t>11/08/2025 04:00</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNSHlxZDdybW5fY0FOMmRRMEN0bURlZDAxSjQ1LWJrOExhWUxTa1RqT2l6Z2FqVWZZWFlLOG9LekduQTA3Vmp0QW5VME1oNEktdmZ4cDdsbU9YX0pJMUNwbVdzaDdkbzB5Mi1DalF0Z0JoN1ZoVE1ENVB2UjJpdHp3LWFVZGZsV2pETlZRTlhQNkxlR2o1RkstSUhiQ1FqX3ZXSDROcFpWdFh4Yzd2?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" t="inlineStr">
-        <is>
-          <t>limestone</t>
-        </is>
-      </c>
-      <c r="B505" t="inlineStr">
-        <is>
-          <t>Limestone Capital Investe na Nokken para Abastecer a Expansão de Hospitalidade Modular - PR Newswire</t>
-        </is>
-      </c>
-      <c r="C505" t="inlineStr">
-        <is>
-          <t>11/08/2025 04:00</t>
-        </is>
-      </c>
-      <c r="D505" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPWU80YXJ5NDJUWmw1VjJscFpVbDRWVlJsM09lZ3Vjdkg4czlKekxPUWJUWXpaQjg4WDZONGk1MjdxV29mRm1aTHZWRG5FeUFsWHpPTk50VFVhak9QU1dYak9tM3Buc21nRGxmLTljbzNSd1I2ZVlZa2luY3BrRGIwb1lTcml2RU1NMUlrdmt6WVExREs4S1psdHdXM3czY2pUcjBzeU92UDhpZ0lELTFZQjZaaHN6WVY1WjRDWmdJZklfV2dpbWk0ZDBjUk8xcDlnQjU0X05nU01idTJCZmNmUmNZUXpaRWZveHBv?oc=5</t>
         </is>
